--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E643"/>
+  <dimension ref="A1:E650"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5997,17 +5997,17 @@
       <c r="A287" s="1" t="n"/>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CondenseMax</t>
+          <t>UI.Character.Size</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>누적 {0} · 최고</t>
+          <t>크기</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>Total {0} · Max</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="E287" s="1" t="n"/>
@@ -6016,17 +6016,17 @@
       <c r="A288" s="1" t="n"/>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CondenseProgress</t>
+          <t>UI.Character.SizeSmall</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>누적 {0}/{1}</t>
+          <t>소형</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>Total {0}/{1}</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="E288" s="1" t="n"/>
@@ -6035,17 +6035,17 @@
       <c r="A289" s="1" t="n"/>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.Star</t>
+          <t>UI.Character.SizeMedium</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>{0}성</t>
+          <t>중형</t>
         </is>
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>{0}★</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E289" s="1" t="n"/>
@@ -6054,17 +6054,17 @@
       <c r="A290" s="1" t="n"/>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CondenseBonus</t>
+          <t>UI.Character.SizeLarge</t>
         </is>
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
-          <t>응축 가산</t>
+          <t>대형</t>
         </is>
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>Condense Bonus</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="E290" s="1" t="n"/>
@@ -6073,17 +6073,17 @@
       <c r="A291" s="1" t="n"/>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WorkSpeedAdd</t>
+          <t>UI.Character.SizeSmallShort</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>작업속도 +{0}%</t>
+          <t>소</t>
         </is>
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>Work Speed +{0}%</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E291" s="1" t="n"/>
@@ -6092,17 +6092,17 @@
       <c r="A292" s="1" t="n"/>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.Slot</t>
+          <t>UI.Character.SizeMediumShort</t>
         </is>
       </c>
       <c r="C292" s="6" t="inlineStr">
         <is>
-          <t>슬롯 {0}</t>
+          <t>중</t>
         </is>
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>Slot {0}</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E292" s="1" t="n"/>
@@ -6111,17 +6111,17 @@
       <c r="A293" s="1" t="n"/>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WornBy</t>
+          <t>UI.Character.SizeLargeShort</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>{0} 착용</t>
+          <t>대</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>Worn by {0}</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E293" s="1" t="n"/>
@@ -6130,17 +6130,17 @@
       <c r="A294" s="1" t="n"/>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.Storage</t>
+          <t>UI.Inventory.CondenseMax</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>보관</t>
+          <t>누적 {0} · 최고</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Total {0} · Max</t>
         </is>
       </c>
       <c r="E294" s="1" t="n"/>
@@ -6149,17 +6149,17 @@
       <c r="A295" s="1" t="n"/>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.Warehouse</t>
+          <t>UI.Inventory.CondenseProgress</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>창고</t>
+          <t>누적 {0}/{1}</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Total {0}/{1}</t>
         </is>
       </c>
       <c r="E295" s="1" t="n"/>
@@ -6168,17 +6168,17 @@
       <c r="A296" s="1" t="n"/>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.Controls</t>
+          <t>UI.Inventory.Star</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
-          <t>조작</t>
+          <t>{0}성</t>
         </is>
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>{0}★</t>
         </is>
       </c>
       <c r="E296" s="1" t="n"/>
@@ -6187,17 +6187,17 @@
       <c r="A297" s="1" t="n"/>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.Drag</t>
+          <t>UI.Inventory.CondenseBonus</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>끌기</t>
+          <t>응축 가산</t>
         </is>
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>Drag</t>
+          <t>Condense Bonus</t>
         </is>
       </c>
       <c r="E297" s="1" t="n"/>
@@ -6206,17 +6206,17 @@
       <c r="A298" s="1" t="n"/>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.DragFromWarehouse</t>
+          <t>UI.Inventory.WorkSpeedAdd</t>
         </is>
       </c>
       <c r="C298" s="6" t="inlineStr">
         <is>
-          <t>칸 이동 · 인벤토리로 꺼내기</t>
+          <t>작업속도 +{0}%</t>
         </is>
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
-          <t>Move slot · Take out to inventory</t>
+          <t>Work Speed +{0}%</t>
         </is>
       </c>
       <c r="E298" s="1" t="n"/>
@@ -6225,17 +6225,17 @@
       <c r="A299" s="1" t="n"/>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.DragToWarehouse</t>
+          <t>UI.Inventory.Slot</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
-          <t>칸 이동 · 창고에 맡기기</t>
+          <t>슬롯 {0}</t>
         </is>
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>Move slot · Store in warehouse</t>
+          <t>Slot {0}</t>
         </is>
       </c>
       <c r="E299" s="1" t="n"/>
@@ -6244,17 +6244,17 @@
       <c r="A300" s="1" t="n"/>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitSort</t>
+          <t>UI.Inventory.WornBy</t>
         </is>
       </c>
       <c r="C300" s="6" t="inlineStr">
         <is>
-          <t>{0} 정렬</t>
+          <t>{0} 착용</t>
         </is>
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
-          <t>Sort {0}</t>
+          <t>Worn by {0}</t>
         </is>
       </c>
       <c r="E300" s="1" t="n"/>
@@ -6263,17 +6263,17 @@
       <c r="A301" s="1" t="n"/>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitMove</t>
+          <t>UI.Inventory.Storage</t>
         </is>
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
-          <t>{0} 칸 이동</t>
+          <t>보관</t>
         </is>
       </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>Move {0} Slot</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="E301" s="1" t="n"/>
@@ -6282,17 +6282,17 @@
       <c r="A302" s="1" t="n"/>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CantList</t>
+          <t>UI.Inventory.Warehouse</t>
         </is>
       </c>
       <c r="C302" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없습니다 — {0}</t>
+          <t>창고</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>Can't list — {0}</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="E302" s="1" t="n"/>
@@ -6301,17 +6301,17 @@
       <c r="A303" s="1" t="n"/>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CantSell</t>
+          <t>UI.Inventory.Controls</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
-          <t>팔 수 없습니다 — {0}</t>
+          <t>조작</t>
         </is>
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>Can't sell — {0}</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E303" s="1" t="n"/>
@@ -6320,17 +6320,17 @@
       <c r="A304" s="1" t="n"/>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskSell</t>
+          <t>UI.Inventory.Drag</t>
         </is>
       </c>
       <c r="C304" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 팔까?</t>
+          <t>끌기</t>
         </is>
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>How many to sell?</t>
+          <t>Drag</t>
         </is>
       </c>
       <c r="E304" s="1" t="n"/>
@@ -6339,17 +6339,17 @@
       <c r="A305" s="1" t="n"/>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskOpen</t>
+          <t>UI.Inventory.DragFromWarehouse</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 열까?</t>
+          <t>칸 이동 · 인벤토리로 꺼내기</t>
         </is>
       </c>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>How many to open?</t>
+          <t>Move slot · Take out to inventory</t>
         </is>
       </c>
       <c r="E305" s="1" t="n"/>
@@ -6358,17 +6358,17 @@
       <c r="A306" s="1" t="n"/>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskStore</t>
+          <t>UI.Inventory.DragToWarehouse</t>
         </is>
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 창고에 넣을까?</t>
+          <t>칸 이동 · 창고에 맡기기</t>
         </is>
       </c>
       <c r="D306" s="6" t="inlineStr">
         <is>
-          <t>How many to store?</t>
+          <t>Move slot · Store in warehouse</t>
         </is>
       </c>
       <c r="E306" s="1" t="n"/>
@@ -6377,17 +6377,17 @@
       <c r="A307" s="1" t="n"/>
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskTakeOut</t>
+          <t>UI.Inventory.WaitSort</t>
         </is>
       </c>
       <c r="C307" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 꺼낼까?</t>
+          <t>{0} 정렬</t>
         </is>
       </c>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>How many to take out?</t>
+          <t>Sort {0}</t>
         </is>
       </c>
       <c r="E307" s="1" t="n"/>
@@ -6396,17 +6396,17 @@
       <c r="A308" s="1" t="n"/>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitStore</t>
+          <t>UI.Inventory.WaitMove</t>
         </is>
       </c>
       <c r="C308" s="6" t="inlineStr">
         <is>
-          <t>창고에 넣기</t>
+          <t>{0} 칸 이동</t>
         </is>
       </c>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>Store in Warehouse</t>
+          <t>Move {0} Slot</t>
         </is>
       </c>
       <c r="E308" s="1" t="n"/>
@@ -6415,17 +6415,17 @@
       <c r="A309" s="1" t="n"/>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitTakeOut</t>
+          <t>UI.Inventory.CantList</t>
         </is>
       </c>
       <c r="C309" s="6" t="inlineStr">
         <is>
-          <t>창고에서 꺼내기</t>
+          <t>올릴 수 없습니다 — {0}</t>
         </is>
       </c>
       <c r="D309" s="6" t="inlineStr">
         <is>
-          <t>Take Out of Warehouse</t>
+          <t>Can't list — {0}</t>
         </is>
       </c>
       <c r="E309" s="1" t="n"/>
@@ -6434,17 +6434,17 @@
       <c r="A310" s="1" t="n"/>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitOpenBox</t>
+          <t>UI.Inventory.CantSell</t>
         </is>
       </c>
       <c r="C310" s="6" t="inlineStr">
         <is>
-          <t>상자 개봉 {0}개</t>
+          <t>팔 수 없습니다 — {0}</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Open {0} Box(es)</t>
+          <t>Can't sell — {0}</t>
         </is>
       </c>
       <c r="E310" s="1" t="n"/>
@@ -6453,17 +6453,17 @@
       <c r="A311" s="1" t="n"/>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoMoveWhileFiltering</t>
+          <t>UI.Inventory.AskSell</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
-          <t>찾기 중에는 칸을 옮길 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
+          <t>몇 개를 팔까?</t>
         </is>
       </c>
       <c r="D311" s="6" t="inlineStr">
         <is>
-          <t>You can't move slots while searching. Clear the search first.</t>
+          <t>How many to sell?</t>
         </is>
       </c>
       <c r="E311" s="1" t="n"/>
@@ -6472,17 +6472,17 @@
       <c r="A312" s="1" t="n"/>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoDropWhileFiltering</t>
+          <t>UI.Inventory.AskOpen</t>
         </is>
       </c>
       <c r="C312" s="6" t="inlineStr">
         <is>
-          <t>찾기 중에는 넣을 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
+          <t>몇 개를 열까?</t>
         </is>
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>You can't drop items while searching. Clear the search first.</t>
+          <t>How many to open?</t>
         </is>
       </c>
       <c r="E312" s="1" t="n"/>
@@ -6491,17 +6491,17 @@
       <c r="A313" s="1" t="n"/>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoEmptySlot</t>
+          <t>UI.Inventory.AskStore</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
-          <t>{0}에 빈 칸이 없습니다.</t>
+          <t>몇 개를 창고에 넣을까?</t>
         </is>
       </c>
       <c r="D313" s="6" t="inlineStr">
         <is>
-          <t>No empty slot in {0}.</t>
+          <t>How many to store?</t>
         </is>
       </c>
       <c r="E313" s="1" t="n"/>
@@ -6510,19 +6510,17 @@
       <c r="A314" s="1" t="n"/>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.RewardToMail</t>
+          <t>UI.Inventory.AskTakeOut</t>
         </is>
       </c>
       <c r="C314" s="6" t="inlineStr">
         <is>
-          <t>인벤토리가 가득 차 보상을 우편함에 보관했습니다.
-우편함에서 받아 주세요.</t>
+          <t>몇 개를 꺼낼까?</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>Inventory is full, so rewards were sent to your mailbox.
-Claim them from the mailbox.</t>
+          <t>How many to take out?</t>
         </is>
       </c>
       <c r="E314" s="1" t="n"/>
@@ -6531,17 +6529,17 @@
       <c r="A315" s="1" t="n"/>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.CartCount</t>
+          <t>UI.Inventory.WaitStore</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
         <is>
-          <t>담은 수량</t>
+          <t>창고에 넣기</t>
         </is>
       </c>
       <c r="D315" s="6" t="inlineStr">
         <is>
-          <t>In Cart</t>
+          <t>Store in Warehouse</t>
         </is>
       </c>
       <c r="E315" s="1" t="n"/>
@@ -6550,17 +6548,17 @@
       <c r="A316" s="1" t="n"/>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Each</t>
+          <t>UI.Inventory.WaitTakeOut</t>
         </is>
       </c>
       <c r="C316" s="6" t="inlineStr">
         <is>
-          <t>개당</t>
+          <t>창고에서 꺼내기</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>Take Out of Warehouse</t>
         </is>
       </c>
       <c r="E316" s="1" t="n"/>
@@ -6569,17 +6567,17 @@
       <c r="A317" s="1" t="n"/>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.GoldToGet</t>
+          <t>UI.Inventory.WaitOpenBox</t>
         </is>
       </c>
       <c r="C317" s="6" t="inlineStr">
         <is>
-          <t>받을 골드</t>
+          <t>상자 개봉 {0}개</t>
         </is>
       </c>
       <c r="D317" s="6" t="inlineStr">
         <is>
-          <t>Gold to Receive</t>
+          <t>Open {0} Box(es)</t>
         </is>
       </c>
       <c r="E317" s="1" t="n"/>
@@ -6588,17 +6586,17 @@
       <c r="A318" s="1" t="n"/>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.IfAuctioned</t>
+          <t>UI.Inventory.NoMoveWhileFiltering</t>
         </is>
       </c>
       <c r="C318" s="6" t="inlineStr">
         <is>
-          <t>경매로 올리면</t>
+          <t>찾기 중에는 칸을 옮길 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>If Listed on Auction</t>
+          <t>You can't move slots while searching. Clear the search first.</t>
         </is>
       </c>
       <c r="E318" s="1" t="n"/>
@@ -6607,17 +6605,17 @@
       <c r="A319" s="1" t="n"/>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.UnitPrice</t>
+          <t>UI.Inventory.NoDropWhileFiltering</t>
         </is>
       </c>
       <c r="C319" s="6" t="inlineStr">
         <is>
-          <t>개당 단가</t>
+          <t>찾기 중에는 넣을 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
         </is>
       </c>
       <c r="D319" s="6" t="inlineStr">
         <is>
-          <t>unit price</t>
+          <t>You can't drop items while searching. Clear the search first.</t>
         </is>
       </c>
       <c r="E319" s="1" t="n"/>
@@ -6626,17 +6624,17 @@
       <c r="A320" s="1" t="n"/>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.SetInAuction</t>
+          <t>UI.Inventory.NoEmptySlot</t>
         </is>
       </c>
       <c r="C320" s="6" t="inlineStr">
         <is>
-          <t>경매장 [등록] 탭에서 직접 정합니다</t>
+          <t>{0}에 빈 칸이 없습니다.</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>Set it yourself in the Auction [List] tab</t>
+          <t>No empty slot in {0}.</t>
         </is>
       </c>
       <c r="E320" s="1" t="n"/>
@@ -6645,17 +6643,19 @@
       <c r="A321" s="1" t="n"/>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Total</t>
+          <t>UI.Inventory.RewardToMail</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매 {0} G</t>
+          <t>인벤토리가 가득 차 보상을 우편함에 보관했습니다.
+우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D321" s="6" t="inlineStr">
         <is>
-          <t>Instant Sell {0} G</t>
+          <t>Inventory is full, so rewards were sent to your mailbox.
+Claim them from the mailbox.</t>
         </is>
       </c>
       <c r="E321" s="1" t="n"/>
@@ -6664,17 +6664,17 @@
       <c r="A322" s="1" t="n"/>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Wait</t>
+          <t>UI.Sell.CartCount</t>
         </is>
       </c>
       <c r="C322" s="6" t="inlineStr">
         <is>
-          <t>판매</t>
+          <t>담은 수량</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>In Cart</t>
         </is>
       </c>
       <c r="E322" s="1" t="n"/>
@@ -6683,17 +6683,17 @@
       <c r="A323" s="1" t="n"/>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SortRarity</t>
+          <t>UI.Sell.Each</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
         <is>
-          <t>등급순</t>
+          <t>개당</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
         <is>
-          <t>By Rarity</t>
+          <t>each</t>
         </is>
       </c>
       <c r="E323" s="1" t="n"/>
@@ -6702,17 +6702,17 @@
       <c r="A324" s="1" t="n"/>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SortName</t>
+          <t>UI.Sell.GoldToGet</t>
         </is>
       </c>
       <c r="C324" s="6" t="inlineStr">
         <is>
-          <t>이름순</t>
+          <t>받을 골드</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>By Name</t>
+          <t>Gold to Receive</t>
         </is>
       </c>
       <c r="E324" s="1" t="n"/>
@@ -6721,17 +6721,17 @@
       <c r="A325" s="1" t="n"/>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SortCount</t>
+          <t>UI.Sell.IfAuctioned</t>
         </is>
       </c>
       <c r="C325" s="6" t="inlineStr">
         <is>
-          <t>수량순</t>
+          <t>경매로 올리면</t>
         </is>
       </c>
       <c r="D325" s="6" t="inlineStr">
         <is>
-          <t>By Count</t>
+          <t>If Listed on Auction</t>
         </is>
       </c>
       <c r="E325" s="1" t="n"/>
@@ -6740,17 +6740,17 @@
       <c r="A326" s="1" t="n"/>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.RarityOrBelow</t>
+          <t>UI.Sell.UnitPrice</t>
         </is>
       </c>
       <c r="C326" s="6" t="inlineStr">
         <is>
-          <t>{0} 이하</t>
+          <t>개당 단가</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>{0} or lower</t>
+          <t>unit price</t>
         </is>
       </c>
       <c r="E326" s="1" t="n"/>
@@ -6759,17 +6759,17 @@
       <c r="A327" s="1" t="n"/>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.AllRarities</t>
+          <t>UI.Sell.SetInAuction</t>
         </is>
       </c>
       <c r="C327" s="6" t="inlineStr">
         <is>
-          <t>등급 전체</t>
+          <t>경매장 [등록] 탭에서 직접 정합니다</t>
         </is>
       </c>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>All Rarities</t>
+          <t>Set it yourself in the Auction [List] tab</t>
         </is>
       </c>
       <c r="E327" s="1" t="n"/>
@@ -6778,17 +6778,17 @@
       <c r="A328" s="1" t="n"/>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.AllGroups</t>
+          <t>UI.Sell.Total</t>
         </is>
       </c>
       <c r="C328" s="6" t="inlineStr">
         <is>
-          <t>분류 전체</t>
+          <t>즉시 판매 {0} G</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>All Categories</t>
+          <t>Instant Sell {0} G</t>
         </is>
       </c>
       <c r="E328" s="1" t="n"/>
@@ -6797,17 +6797,17 @@
       <c r="A329" s="1" t="n"/>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.AllIndustries</t>
+          <t>UI.Sell.Wait</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
         <is>
-          <t>산업 전체</t>
+          <t>판매</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>All Industries</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="E329" s="1" t="n"/>
@@ -6816,17 +6816,17 @@
       <c r="A330" s="1" t="n"/>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NoneToAdd</t>
+          <t>UI.Tool.SortRarity</t>
         </is>
       </c>
       <c r="C330" s="6" t="inlineStr">
         <is>
-          <t>{0} 이하로 담을 {1}이(가) 없습니다.</t>
+          <t>등급순</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>No {1} at {0} or lower to add.</t>
+          <t>By Rarity</t>
         </is>
       </c>
       <c r="E330" s="1" t="n"/>
@@ -6835,17 +6835,17 @@
       <c r="A331" s="1" t="n"/>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.Added</t>
+          <t>UI.Tool.SortName</t>
         </is>
       </c>
       <c r="C331" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}을(를) 담았습니다.</t>
+          <t>이름순</t>
         </is>
       </c>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>Added {1} {0}.</t>
+          <t>By Name</t>
         </is>
       </c>
       <c r="E331" s="1" t="n"/>
@@ -6854,17 +6854,17 @@
       <c r="A332" s="1" t="n"/>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.KindResource</t>
+          <t>UI.Tool.SortCount</t>
         </is>
       </c>
       <c r="C332" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>수량순</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>By Count</t>
         </is>
       </c>
       <c r="E332" s="1" t="n"/>
@@ -6873,17 +6873,17 @@
       <c r="A333" s="1" t="n"/>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.KindCharacter</t>
+          <t>UI.Tool.RarityOrBelow</t>
         </is>
       </c>
       <c r="C333" s="6" t="inlineStr">
         <is>
-          <t>캐릭터</t>
+          <t>{0} 이하</t>
         </is>
       </c>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>characters</t>
+          <t>{0} or lower</t>
         </is>
       </c>
       <c r="E333" s="1" t="n"/>
@@ -6892,17 +6892,17 @@
       <c r="A334" s="1" t="n"/>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.KindEquip</t>
+          <t>UI.Tool.AllRarities</t>
         </is>
       </c>
       <c r="C334" s="6" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>등급 전체</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>gear</t>
+          <t>All Rarities</t>
         </is>
       </c>
       <c r="E334" s="1" t="n"/>
@@ -6911,17 +6911,17 @@
       <c r="A335" s="1" t="n"/>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NItem</t>
+          <t>UI.Tool.AllGroups</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
         <is>
-          <t>{0}종</t>
+          <t>분류 전체</t>
         </is>
       </c>
       <c r="D335" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>All Categories</t>
         </is>
       </c>
       <c r="E335" s="1" t="n"/>
@@ -6930,17 +6930,17 @@
       <c r="A336" s="1" t="n"/>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NCharacter</t>
+          <t>UI.Tool.AllIndustries</t>
         </is>
       </c>
       <c r="C336" s="6" t="inlineStr">
         <is>
-          <t>{0}명</t>
+          <t>산업 전체</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>All Industries</t>
         </is>
       </c>
       <c r="E336" s="1" t="n"/>
@@ -6949,17 +6949,17 @@
       <c r="A337" s="1" t="n"/>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NEquip</t>
+          <t>UI.Tool.NoneToAdd</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
         <is>
-          <t>{0}개</t>
+          <t>{0} 이하로 담을 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>No {1} at {0} or lower to add.</t>
         </is>
       </c>
       <c r="E337" s="1" t="n"/>
@@ -6968,17 +6968,17 @@
       <c r="A338" s="1" t="n"/>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.LockedN</t>
+          <t>UI.Tool.Added</t>
         </is>
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
-          <t>잠금 {0}</t>
+          <t>{0} {1}을(를) 담았습니다.</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
         <is>
-          <t>{0} locked</t>
+          <t>Added {1} {0}.</t>
         </is>
       </c>
       <c r="E338" s="1" t="n"/>
@@ -6987,17 +6987,17 @@
       <c r="A339" s="1" t="n"/>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.ExcludedWrap</t>
+          <t>UI.Tool.KindResource</t>
         </is>
       </c>
       <c r="C339" s="6" t="inlineStr">
         <is>
-          <t>({0} 제외)</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D339" s="6" t="inlineStr">
         <is>
-          <t>(excluded: {0})</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="E339" s="1" t="n"/>
@@ -7006,17 +7006,17 @@
       <c r="A340" s="1" t="n"/>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SkippedWrap</t>
+          <t>UI.Tool.KindCharacter</t>
         </is>
       </c>
       <c r="C340" s="6" t="inlineStr">
         <is>
-          <t>({0} 제외 — [제외]에서 체크를 풀면 함께 담깁니다)</t>
+          <t>캐릭터</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>(excluded: {0} — uncheck them in [Exclude] to include)</t>
+          <t>characters</t>
         </is>
       </c>
       <c r="E340" s="1" t="n"/>
@@ -7025,17 +7025,17 @@
       <c r="A341" s="1" t="n"/>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.UnlockHint</t>
+          <t>UI.Tool.KindEquip</t>
         </is>
       </c>
       <c r="C341" s="6" t="inlineStr">
         <is>
-          <t>잠금은 Ctrl+좌클릭으로 풀 수 있습니다.</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="D341" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Left-click to unlock.</t>
+          <t>gear</t>
         </is>
       </c>
       <c r="E341" s="1" t="n"/>
@@ -7044,17 +7044,17 @@
       <c r="A342" s="1" t="n"/>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.CharacterBlocked</t>
+          <t>UI.Tool.NItem</t>
         </is>
       </c>
       <c r="C342" s="6" t="inlineStr">
         <is>
-          <t>배치 중 · 장비 착용 · 마지막 캐릭터</t>
+          <t>{0}종</t>
         </is>
       </c>
       <c r="D342" s="6" t="inlineStr">
         <is>
-          <t>assigned · wearing gear · last character</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E342" s="1" t="n"/>
@@ -7063,17 +7063,17 @@
       <c r="A343" s="1" t="n"/>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.EquipBlocked</t>
+          <t>UI.Tool.NCharacter</t>
         </is>
       </c>
       <c r="C343" s="6" t="inlineStr">
         <is>
-          <t>캐릭터가 끼고 있는 장비</t>
+          <t>{0}명</t>
         </is>
       </c>
       <c r="D343" s="6" t="inlineStr">
         <is>
-          <t>equipped by a character</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E343" s="1" t="n"/>
@@ -7082,17 +7082,17 @@
       <c r="A344" s="1" t="n"/>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.ExcludeNone</t>
+          <t>UI.Tool.NEquip</t>
         </is>
       </c>
       <c r="C344" s="6" t="inlineStr">
         <is>
-          <t>제외 없음</t>
+          <t>{0}개</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
         <is>
-          <t>No Exclusions</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E344" s="1" t="n"/>
@@ -7101,17 +7101,17 @@
       <c r="A345" s="1" t="n"/>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.ExcludeCount</t>
+          <t>UI.Tool.LockedN</t>
         </is>
       </c>
       <c r="C345" s="6" t="inlineStr">
         <is>
-          <t>제외 {0}</t>
+          <t>잠금 {0}</t>
         </is>
       </c>
       <c r="D345" s="6" t="inlineStr">
         <is>
-          <t>Exclude {0}</t>
+          <t>{0} locked</t>
         </is>
       </c>
       <c r="E345" s="1" t="n"/>
@@ -7120,17 +7120,17 @@
       <c r="A346" s="1" t="n"/>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.TabResource</t>
+          <t>UI.Tool.ExcludedWrap</t>
         </is>
       </c>
       <c r="C346" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>({0} 제외)</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>(excluded: {0})</t>
         </is>
       </c>
       <c r="E346" s="1" t="n"/>
@@ -7139,17 +7139,17 @@
       <c r="A347" s="1" t="n"/>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.TabTrait</t>
+          <t>UI.Tool.SkippedWrap</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
         <is>
-          <t>특성</t>
+          <t>({0} 제외 — [제외]에서 체크를 풀면 함께 담깁니다)</t>
         </is>
       </c>
       <c r="D347" s="6" t="inlineStr">
         <is>
-          <t>Traits</t>
+          <t>(excluded: {0} — uncheck them in [Exclude] to include)</t>
         </is>
       </c>
       <c r="E347" s="1" t="n"/>
@@ -7158,17 +7158,17 @@
       <c r="A348" s="1" t="n"/>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.BulkAdd</t>
+          <t>UI.Tool.UnlockHint</t>
         </is>
       </c>
       <c r="C348" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>잠금은 Ctrl+좌클릭으로 풀 수 있습니다.</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
         <is>
-          <t>Add to Sell</t>
+          <t>Ctrl+Left-click to unlock.</t>
         </is>
       </c>
       <c r="E348" s="1" t="n"/>
@@ -7177,17 +7177,17 @@
       <c r="A349" s="1" t="n"/>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SearchName</t>
+          <t>UI.Tool.CharacterBlocked</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
         <is>
-          <t>이름 검색</t>
+          <t>배치 중 · 장비 착용 · 마지막 캐릭터</t>
         </is>
       </c>
       <c r="D349" s="6" t="inlineStr">
         <is>
-          <t>Search name</t>
+          <t>assigned · wearing gear · last character</t>
         </is>
       </c>
       <c r="E349" s="1" t="n"/>
@@ -7196,17 +7196,17 @@
       <c r="A350" s="1" t="n"/>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.Reset</t>
+          <t>UI.Tool.EquipBlocked</t>
         </is>
       </c>
       <c r="C350" s="6" t="inlineStr">
         <is>
-          <t>초기화</t>
+          <t>캐릭터가 끼고 있는 장비</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>equipped by a character</t>
         </is>
       </c>
       <c r="E350" s="1" t="n"/>
@@ -7215,17 +7215,17 @@
       <c r="A351" s="1" t="n"/>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoMatch</t>
+          <t>UI.Tool.ExcludeNone</t>
         </is>
       </c>
       <c r="C351" s="6" t="inlineStr">
         <is>
-          <t>조건에 맞는 항목이 없습니다</t>
+          <t>제외 없음</t>
         </is>
       </c>
       <c r="D351" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches</t>
+          <t>No Exclusions</t>
         </is>
       </c>
       <c r="E351" s="1" t="n"/>
@@ -7234,17 +7234,17 @@
       <c r="A352" s="1" t="n"/>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Empty</t>
+          <t>UI.Tool.ExcludeCount</t>
         </is>
       </c>
       <c r="C352" s="6" t="inlineStr">
         <is>
-          <t>자원을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다</t>
+          <t>제외 {0}</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>Right-click items to add — they sell instantly at the instant sell price</t>
+          <t>Exclude {0}</t>
         </is>
       </c>
       <c r="E352" s="1" t="n"/>
@@ -7253,17 +7253,17 @@
       <c r="A353" s="1" t="n"/>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Clear</t>
+          <t>UI.Inventory.TabResource</t>
         </is>
       </c>
       <c r="C353" s="6" t="inlineStr">
         <is>
-          <t>비우기</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D353" s="6" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="E353" s="1" t="n"/>
@@ -7272,17 +7272,17 @@
       <c r="A354" s="1" t="n"/>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.HighRarity</t>
+          <t>UI.Inventory.TabTrait</t>
         </is>
       </c>
       <c r="C354" s="6" t="inlineStr">
         <is>
-          <t>주의! 상위 등급 포함</t>
+          <t>특성</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>Caution! Includes high rarity</t>
+          <t>Traits</t>
         </is>
       </c>
       <c r="E354" s="1" t="n"/>
@@ -7291,17 +7291,17 @@
       <c r="A355" s="1" t="n"/>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.InstantSell</t>
+          <t>UI.Tool.BulkAdd</t>
         </is>
       </c>
       <c r="C355" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D355" s="6" t="inlineStr">
         <is>
-          <t>Instant Sell</t>
+          <t>Add to Sell</t>
         </is>
       </c>
       <c r="E355" s="1" t="n"/>
@@ -7310,17 +7310,17 @@
       <c r="A356" s="1" t="n"/>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.MarkSell</t>
+          <t>UI.Tool.SearchName</t>
         </is>
       </c>
       <c r="C356" s="6" t="inlineStr">
         <is>
-          <t>판</t>
+          <t>이름 검색</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Search name</t>
         </is>
       </c>
       <c r="E356" s="1" t="n"/>
@@ -7329,17 +7329,17 @@
       <c r="A357" s="1" t="n"/>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.MarkAssign</t>
+          <t>UI.Tool.Reset</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>초기화</t>
         </is>
       </c>
       <c r="D357" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="E357" s="1" t="n"/>
@@ -7348,17 +7348,17 @@
       <c r="A358" s="1" t="n"/>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.PendingSelect</t>
+          <t>UI.Inventory.NoMatch</t>
         </is>
       </c>
       <c r="C358" s="6" t="inlineStr">
         <is>
-          <t>선택 대기</t>
+          <t>조건에 맞는 항목이 없습니다</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Nothing matches</t>
         </is>
       </c>
       <c r="E358" s="1" t="n"/>
@@ -7367,17 +7367,17 @@
       <c r="A359" s="1" t="n"/>
       <c r="B359" s="6" t="inlineStr">
         <is>
-          <t>UI.Common.Waiting</t>
+          <t>UI.Sell.Empty</t>
         </is>
       </c>
       <c r="C359" s="6" t="inlineStr">
         <is>
-          <t>응답을 기다리는 중</t>
+          <t>자원을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다</t>
         </is>
       </c>
       <c r="D359" s="6" t="inlineStr">
         <is>
-          <t>Waiting for response</t>
+          <t>Right-click items to add — they sell instantly at the instant sell price</t>
         </is>
       </c>
       <c r="E359" s="1" t="n"/>
@@ -7386,17 +7386,17 @@
       <c r="A360" s="1" t="n"/>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.AlreadyMax</t>
+          <t>UI.Sell.Clear</t>
         </is>
       </c>
       <c r="C360" s="6" t="inlineStr">
         <is>
-          <t>이미 최고 단계입니다 — 더 넣을 수 없습니다.</t>
+          <t>비우기</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
         <is>
-          <t>Already at the top stage — nothing more can be added.</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="E360" s="1" t="n"/>
@@ -7405,17 +7405,17 @@
       <c r="A361" s="1" t="n"/>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.BusyMaterial</t>
+          <t>UI.Sell.HighRarity</t>
         </is>
       </c>
       <c r="C361" s="6" t="inlineStr">
         <is>
-          <t>배치됐거나 장비를 낀 캐릭터는 재료로 넣을 수 없습니다.</t>
+          <t>주의! 상위 등급 포함</t>
         </is>
       </c>
       <c r="D361" s="6" t="inlineStr">
         <is>
-          <t>Assigned or geared characters can't be used as material.</t>
+          <t>Caution! Includes high rarity</t>
         </is>
       </c>
       <c r="E361" s="1" t="n"/>
@@ -7424,17 +7424,17 @@
       <c r="A362" s="1" t="n"/>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.LockedMaterial</t>
+          <t>UI.Sell.InstantSell</t>
         </is>
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
-          <t>잠긴 캐릭터는 재료로 넣을 수 없습니다 — Ctrl+좌클릭으로 풀 수 있습니다.</t>
+          <t>즉시 판매</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>Locked characters can't be used as material — Ctrl+Left-click to unlock.</t>
+          <t>Instant Sell</t>
         </is>
       </c>
       <c r="E362" s="1" t="n"/>
@@ -7443,17 +7443,17 @@
       <c r="A363" s="1" t="n"/>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Info</t>
+          <t>UI.Inventory.MarkSell</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
         <is>
-          <t>응축 누적 {0} / {1}</t>
+          <t>판</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
         <is>
-          <t>Condensed {0} / {1}</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E363" s="1" t="n"/>
@@ -7462,17 +7462,17 @@
       <c r="A364" s="1" t="n"/>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Now</t>
+          <t>UI.Inventory.MarkAssign</t>
         </is>
       </c>
       <c r="C364" s="6" t="inlineStr">
         <is>
-          <t>지금 {0}성</t>
+          <t>배</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>Now {0}★</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E364" s="1" t="n"/>
@@ -7481,17 +7481,17 @@
       <c r="A365" s="1" t="n"/>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.After</t>
+          <t>UI.Inventory.PendingSelect</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
-          <t>응축 후 {0}성</t>
+          <t>선택 대기</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
         <is>
-          <t>After {0}★</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E365" s="1" t="n"/>
@@ -7500,17 +7500,17 @@
       <c r="A366" s="1" t="n"/>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.TotalPlus</t>
+          <t>UI.Common.Waiting</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
         <is>
-          <t>누적 {0} + {1} = {2}</t>
+          <t>응답을 기다리는 중</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
-          <t>Total {0} + {1} = {2}</t>
+          <t>Waiting for response</t>
         </is>
       </c>
       <c r="E366" s="1" t="n"/>
@@ -7519,17 +7519,17 @@
       <c r="A367" s="1" t="n"/>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Total</t>
+          <t>UI.Condense.AlreadyMax</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
         <is>
-          <t>누적 {0}</t>
+          <t>이미 최고 단계입니다 — 더 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D367" s="6" t="inlineStr">
         <is>
-          <t>Total {0}</t>
+          <t>Already at the top stage — nothing more can be added.</t>
         </is>
       </c>
       <c r="E367" s="1" t="n"/>
@@ -7538,17 +7538,17 @@
       <c r="A368" s="1" t="n"/>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.MaxStage</t>
+          <t>UI.Condense.BusyMaterial</t>
         </is>
       </c>
       <c r="C368" s="6" t="inlineStr">
         <is>
-          <t>최고 단계</t>
+          <t>배치됐거나 장비를 낀 캐릭터는 재료로 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>Max Stage</t>
+          <t>Assigned or geared characters can't be used as material.</t>
         </is>
       </c>
       <c r="E368" s="1" t="n"/>
@@ -7557,17 +7557,17 @@
       <c r="A369" s="1" t="n"/>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Reached</t>
+          <t>UI.Condense.LockedMaterial</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
-          <t>{0}성 도달</t>
+          <t>잠긴 캐릭터는 재료로 넣을 수 없습니다 — Ctrl+좌클릭으로 풀 수 있습니다.</t>
         </is>
       </c>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>Reaches {0}★</t>
+          <t>Locked characters can't be used as material — Ctrl+Left-click to unlock.</t>
         </is>
       </c>
       <c r="E369" s="1" t="n"/>
@@ -7576,17 +7576,17 @@
       <c r="A370" s="1" t="n"/>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ToNext</t>
+          <t>UI.Condense.Info</t>
         </is>
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>{0}성까지 {1}</t>
+          <t>응축 누적 {0} / {1}</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
         <is>
-          <t>{1} to {0}★</t>
+          <t>Condensed {0} / {1}</t>
         </is>
       </c>
       <c r="E370" s="1" t="n"/>
@@ -7595,17 +7595,17 @@
       <c r="A371" s="1" t="n"/>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Overflow</t>
+          <t>UI.Condense.Now</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
         <is>
-          <t>넘치는 재료 {0}마리는 효과 없이 사라집니다.</t>
+          <t>지금 {0}성</t>
         </is>
       </c>
       <c r="D371" s="6" t="inlineStr">
         <is>
-          <t>{0} excess material(s) will be lost with no effect.</t>
+          <t>Now {0}★</t>
         </is>
       </c>
       <c r="E371" s="1" t="n"/>
@@ -7614,17 +7614,17 @@
       <c r="A372" s="1" t="n"/>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialBusy</t>
+          <t>UI.Condense.After</t>
         </is>
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다 — {1}마리는 배치·착용 중입니다.</t>
+          <t>응축 후 {0}성</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material — {1} are assigned or geared.</t>
+          <t>After {0}★</t>
         </is>
       </c>
       <c r="E372" s="1" t="n"/>
@@ -7633,17 +7633,17 @@
       <c r="A373" s="1" t="n"/>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialSame</t>
+          <t>UI.Condense.TotalPlus</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다 — 같은 캐릭터끼리만 응축됩니다.</t>
+          <t>누적 {0} + {1} = {2}</t>
         </is>
       </c>
       <c r="D373" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material — only the same character can be condensed.</t>
+          <t>Total {0} + {1} = {2}</t>
         </is>
       </c>
       <c r="E373" s="1" t="n"/>
@@ -7652,17 +7652,17 @@
       <c r="A374" s="1" t="n"/>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.BusyCount</t>
+          <t>UI.Condense.Total</t>
         </is>
       </c>
       <c r="C374" s="6" t="inlineStr">
         <is>
-          <t>배치·착용 중인 {0} {1}마리는 재료로 넣을 수 없습니다.</t>
+          <t>누적 {0}</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>{1} assigned or geared {0} can't be used as material.</t>
+          <t>Total {0}</t>
         </is>
       </c>
       <c r="E374" s="1" t="n"/>
@@ -7671,17 +7671,17 @@
       <c r="A375" s="1" t="n"/>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickHint</t>
+          <t>UI.Condense.MaxStage</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터 칸을 눌러 재료로 담으세요.</t>
+          <t>최고 단계</t>
         </is>
       </c>
       <c r="D375" s="6" t="inlineStr">
         <is>
-          <t>Click slots of the same character to add them as material.</t>
+          <t>Max Stage</t>
         </is>
       </c>
       <c r="E375" s="1" t="n"/>
@@ -7690,17 +7690,17 @@
       <c r="A376" s="1" t="n"/>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickMaterial</t>
+          <t>UI.Condense.Reached</t>
         </is>
       </c>
       <c r="C376" s="6" t="inlineStr">
         <is>
-          <t>재료를 고르세요</t>
+          <t>{0}성 도달</t>
         </is>
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Choose Material</t>
+          <t>Reaches {0}★</t>
         </is>
       </c>
       <c r="E376" s="1" t="n"/>
@@ -7709,17 +7709,17 @@
       <c r="A377" s="1" t="n"/>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Confirm</t>
+          <t>UI.Condense.ToNext</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
-          <t>응축 ({0}마리)</t>
+          <t>{0}성까지 {1}</t>
         </is>
       </c>
       <c r="D377" s="6" t="inlineStr">
         <is>
-          <t>Condense ({0})</t>
+          <t>{1} to {0}★</t>
         </is>
       </c>
       <c r="E377" s="1" t="n"/>
@@ -7728,19 +7728,17 @@
       <c r="A378" s="1" t="n"/>
       <c r="B378" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialNotice</t>
+          <t>UI.Condense.Overflow</t>
         </is>
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다.
-같은 캐릭터끼리만 응축됩니다.</t>
+          <t>넘치는 재료 {0}마리는 효과 없이 사라집니다.</t>
         </is>
       </c>
       <c r="D378" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material.
-Only the same character can be condensed.</t>
+          <t>{0} excess material(s) will be lost with no effect.</t>
         </is>
       </c>
       <c r="E378" s="1" t="n"/>
@@ -7749,17 +7747,17 @@
       <c r="A379" s="1" t="n"/>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickFirst</t>
+          <t>UI.Condense.NoMaterialBusy</t>
         </is>
       </c>
       <c r="C379" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터 칸을 눌러 재료를 먼저 고르세요.</t>
+          <t>재료로 넣을 {0}이(가) 없습니다 — {1}마리는 배치·착용 중입니다.</t>
         </is>
       </c>
       <c r="D379" s="6" t="inlineStr">
         <is>
-          <t>Click slots of the same character to choose material first.</t>
+          <t>No {0} to use as material — {1} are assigned or geared.</t>
         </is>
       </c>
       <c r="E379" s="1" t="n"/>
@@ -7768,17 +7766,17 @@
       <c r="A380" s="1" t="n"/>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmText</t>
+          <t>UI.Condense.NoMaterialSame</t>
         </is>
       </c>
       <c r="C380" s="6" t="inlineStr">
         <is>
-          <t>재료 {0}마리를 녹여 {1}의 단계를 올립니다.</t>
+          <t>재료로 넣을 {0}이(가) 없습니다 — 같은 캐릭터끼리만 응축됩니다.</t>
         </is>
       </c>
       <c r="D380" s="6" t="inlineStr">
         <is>
-          <t>Melt {0} material(s) to raise {1}'s stage.</t>
+          <t>No {0} to use as material — only the same character can be condensed.</t>
         </is>
       </c>
       <c r="E380" s="1" t="n"/>
@@ -7787,17 +7785,17 @@
       <c r="A381" s="1" t="n"/>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmGrown</t>
+          <t>UI.Condense.BusyCount</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
         <is>
-          <t>Lv{0} 이상 재료 {1}마리의 레벨·경험치는 사라집니다.</t>
+          <t>배치·착용 중인 {0} {1}마리는 재료로 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D381" s="6" t="inlineStr">
         <is>
-          <t>Level and EXP of {1} material(s) at Lv{0}+ will be lost.</t>
+          <t>{1} assigned or geared {0} can't be used as material.</t>
         </is>
       </c>
       <c r="E381" s="1" t="n"/>
@@ -7806,17 +7804,17 @@
       <c r="A382" s="1" t="n"/>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.FillNext</t>
+          <t>UI.Condense.PickHint</t>
         </is>
       </c>
       <c r="C382" s="6" t="inlineStr">
         <is>
-          <t>다음 단계까지 채우기</t>
+          <t>같은 캐릭터 칸을 눌러 재료로 담으세요.</t>
         </is>
       </c>
       <c r="D382" s="6" t="inlineStr">
         <is>
-          <t>Fill to Next Stage</t>
+          <t>Click slots of the same character to add them as material.</t>
         </is>
       </c>
       <c r="E382" s="1" t="n"/>
@@ -7825,17 +7823,17 @@
       <c r="A383" s="1" t="n"/>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Speed</t>
+          <t>UI.Condense.PickMaterial</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
         <is>
-          <t>속도</t>
+          <t>재료를 고르세요</t>
         </is>
       </c>
       <c r="D383" s="6" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Choose Material</t>
         </is>
       </c>
       <c r="E383" s="1" t="n"/>
@@ -7844,17 +7842,17 @@
       <c r="A384" s="1" t="n"/>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Common</t>
+          <t>UI.Condense.Confirm</t>
         </is>
       </c>
       <c r="C384" s="6" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>응축 ({0}마리)</t>
         </is>
       </c>
       <c r="D384" s="6" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Condense ({0})</t>
         </is>
       </c>
       <c r="E384" s="1" t="n"/>
@@ -7863,17 +7861,19 @@
       <c r="A385" s="1" t="n"/>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Condition</t>
+          <t>UI.Condense.NoMaterialNotice</t>
         </is>
       </c>
       <c r="C385" s="6" t="inlineStr">
         <is>
-          <t>조건</t>
+          <t>재료로 넣을 {0}이(가) 없습니다.
+같은 캐릭터끼리만 응축됩니다.</t>
         </is>
       </c>
       <c r="D385" s="6" t="inlineStr">
         <is>
-          <t>Requires</t>
+          <t>No {0} to use as material.
+Only the same character can be condensed.</t>
         </is>
       </c>
       <c r="E385" s="1" t="n"/>
@@ -7882,17 +7882,17 @@
       <c r="A386" s="1" t="n"/>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentLevel</t>
+          <t>UI.Condense.PickFirst</t>
         </is>
       </c>
       <c r="C386" s="6" t="inlineStr">
         <is>
-          <t>(지금 {0})</t>
+          <t>같은 캐릭터 칸을 눌러 재료를 먼저 고르세요.</t>
         </is>
       </c>
       <c r="D386" s="6" t="inlineStr">
         <is>
-          <t>(now {0})</t>
+          <t>Click slots of the same character to choose material first.</t>
         </is>
       </c>
       <c r="E386" s="1" t="n"/>
@@ -7901,17 +7901,17 @@
       <c r="A387" s="1" t="n"/>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.LevelUp</t>
+          <t>UI.Condense.ConfirmText</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
         <is>
-          <t>레벨 올리기 ({0}점)</t>
+          <t>재료 {0}마리를 녹여 {1}의 단계를 올립니다.</t>
         </is>
       </c>
       <c r="D387" s="6" t="inlineStr">
         <is>
-          <t>Level Up ({0} pt)</t>
+          <t>Melt {0} material(s) to raise {1}'s stage.</t>
         </is>
       </c>
       <c r="E387" s="1" t="n"/>
@@ -7920,17 +7920,17 @@
       <c r="A388" s="1" t="n"/>
       <c r="B388" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentEffect</t>
+          <t>UI.Condense.ConfirmGrown</t>
         </is>
       </c>
       <c r="C388" s="6" t="inlineStr">
         <is>
-          <t>현재 효과</t>
+          <t>Lv{0} 이상 재료 {1}마리의 레벨·경험치는 사라집니다.</t>
         </is>
       </c>
       <c r="D388" s="6" t="inlineStr">
         <is>
-          <t>Current Effect</t>
+          <t>Level and EXP of {1} material(s) at Lv{0}+ will be lost.</t>
         </is>
       </c>
       <c r="E388" s="1" t="n"/>
@@ -7939,17 +7939,17 @@
       <c r="A389" s="1" t="n"/>
       <c r="B389" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NowLevel</t>
+          <t>UI.Condense.FillNext</t>
         </is>
       </c>
       <c r="C389" s="6" t="inlineStr">
         <is>
-          <t>지금 (Lv{0})</t>
+          <t>다음 단계까지 채우기</t>
         </is>
       </c>
       <c r="D389" s="6" t="inlineStr">
         <is>
-          <t>Now (Lv{0})</t>
+          <t>Fill to Next Stage</t>
         </is>
       </c>
       <c r="E389" s="1" t="n"/>
@@ -7958,17 +7958,17 @@
       <c r="A390" s="1" t="n"/>
       <c r="B390" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NextLevel</t>
+          <t>UI.Trait.Speed</t>
         </is>
       </c>
       <c r="C390" s="6" t="inlineStr">
         <is>
-          <t>다음 (Lv{0})</t>
+          <t>속도</t>
         </is>
       </c>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>Next (Lv{0})</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E390" s="1" t="n"/>
@@ -7977,17 +7977,17 @@
       <c r="A391" s="1" t="n"/>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Points</t>
+          <t>UI.Trait.Common</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
         <is>
-          <t>보유 포인트 {0}</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D391" s="6" t="inlineStr">
         <is>
-          <t>Points {0}</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E391" s="1" t="n"/>
@@ -7996,17 +7996,17 @@
       <c r="A392" s="1" t="n"/>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.UpTo</t>
+          <t>UI.Trait.Condition</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
         <is>
-          <t>{0}까지</t>
+          <t>조건</t>
         </is>
       </c>
       <c r="D392" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Requires</t>
         </is>
       </c>
       <c r="E392" s="1" t="n"/>
@@ -8015,17 +8015,17 @@
       <c r="A393" s="1" t="n"/>
       <c r="B393" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Opens</t>
+          <t>UI.Trait.CurrentLevel</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
         <is>
-          <t>{0} 열림</t>
+          <t>(지금 {0})</t>
         </is>
       </c>
       <c r="D393" s="6" t="inlineStr">
         <is>
-          <t>Opens {0}</t>
+          <t>(now {0})</t>
         </is>
       </c>
       <c r="E393" s="1" t="n"/>
@@ -8034,17 +8034,17 @@
       <c r="A394" s="1" t="n"/>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescUnlock</t>
+          <t>UI.Trait.LevelUp</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
         <is>
-          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
+          <t>레벨 올리기 ({0}점)</t>
         </is>
       </c>
       <c r="D394" s="6" t="inlineStr">
         <is>
-          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
+          <t>Level Up ({0} pt)</t>
         </is>
       </c>
       <c r="E394" s="1" t="n"/>
@@ -8053,17 +8053,17 @@
       <c r="A395" s="1" t="n"/>
       <c r="B395" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescSpeed</t>
+          <t>UI.Trait.CurrentEffect</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
         <is>
-          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
+          <t>현재 효과</t>
         </is>
       </c>
       <c r="D395" s="6" t="inlineStr">
         <is>
-          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
+          <t>Current Effect</t>
         </is>
       </c>
       <c r="E395" s="1" t="n"/>
@@ -8072,17 +8072,17 @@
       <c r="A396" s="1" t="n"/>
       <c r="B396" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYield</t>
+          <t>UI.Trait.NowLevel</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
         <is>
-          <t>판정 1회에 같은 자원이 더 나옵니다 (120%면 1개 + 20% 확률로 1개 더). 좋은 자원이 나올 확률은 그대로이고, 상자 · 경험치는 늘지 않습니다.</t>
+          <t>지금 (Lv{0})</t>
         </is>
       </c>
       <c r="D396" s="6" t="inlineStr">
         <is>
-          <t>Each roll yields more of the same resource (120% = 1 plus a 20% chance of 1 more). The odds of better resources stay the same, and boxes and EXP don't increase.</t>
+          <t>Now (Lv{0})</t>
         </is>
       </c>
       <c r="E396" s="1" t="n"/>
@@ -8091,17 +8091,17 @@
       <c r="A397" s="1" t="n"/>
       <c r="B397" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYieldAll</t>
+          <t>UI.Trait.NextLevel</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
         <is>
-          <t>모든 산업에 붙습니다.</t>
+          <t>다음 (Lv{0})</t>
         </is>
       </c>
       <c r="D397" s="6" t="inlineStr">
         <is>
-          <t>Applies to all industries.</t>
+          <t>Next (Lv{0})</t>
         </is>
       </c>
       <c r="E397" s="1" t="n"/>
@@ -8110,17 +8110,17 @@
       <c r="A398" s="1" t="n"/>
       <c r="B398" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.AlreadyMax</t>
+          <t>UI.Trait.Points</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
         <is>
-          <t>이미 최대 레벨입니다.</t>
+          <t>보유 포인트 {0}</t>
         </is>
       </c>
       <c r="D398" s="6" t="inlineStr">
         <is>
-          <t>Already at max level.</t>
+          <t>Points {0}</t>
         </is>
       </c>
       <c r="E398" s="1" t="n"/>
@@ -8129,17 +8129,17 @@
       <c r="A399" s="1" t="n"/>
       <c r="B399" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NotEnoughPoints</t>
+          <t>UI.Trait.UpTo</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
+          <t>{0}까지</t>
         </is>
       </c>
       <c r="D399" s="6" t="inlineStr">
         <is>
-          <t>Not enough trait points. ({0} pt required)</t>
+          <t>Up to {0}</t>
         </is>
       </c>
       <c r="E399" s="1" t="n"/>
@@ -8148,19 +8148,17 @@
       <c r="A400" s="1" t="n"/>
       <c r="B400" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.ConfirmLearn</t>
+          <t>UI.Trait.Opens</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트 {0}점을 사용합니다.
-'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
+          <t>{0} 열림</t>
         </is>
       </c>
       <c r="D400" s="6" t="inlineStr">
         <is>
-          <t>This uses {0} trait point(s).
-Raise '{1}' to Lv{2}?</t>
+          <t>Opens {0}</t>
         </is>
       </c>
       <c r="E400" s="1" t="n"/>
@@ -8169,17 +8167,17 @@
       <c r="A401" s="1" t="n"/>
       <c r="B401" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.WaitLearn</t>
+          <t>UI.Trait.DescUnlock</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
         <is>
-          <t>특성 레벨 올리기</t>
+          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
         </is>
       </c>
       <c r="D401" s="6" t="inlineStr">
         <is>
-          <t>Level Up Trait</t>
+          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
         </is>
       </c>
       <c r="E401" s="1" t="n"/>
@@ -8188,17 +8186,17 @@
       <c r="A402" s="1" t="n"/>
       <c r="B402" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.EmptyDetail</t>
+          <t>UI.Trait.DescSpeed</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
         <is>
-          <t>특성을 누르면 여기에 펼쳐집니다</t>
+          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
         </is>
       </c>
       <c r="D402" s="6" t="inlineStr">
         <is>
-          <t>Click a trait to see details here</t>
+          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
         </is>
       </c>
       <c r="E402" s="1" t="n"/>
@@ -8207,17 +8205,17 @@
       <c r="A403" s="1" t="n"/>
       <c r="B403" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Base</t>
+          <t>UI.Trait.DescYield</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>기본 {0}</t>
+          <t>판정 1회에 같은 자원이 더 나옵니다 (120%면 1개 + 20% 확률로 1개 더). 좋은 자원이 나올 확률은 그대로이고, 상자 · 경험치는 늘지 않습니다.</t>
         </is>
       </c>
       <c r="D403" s="6" t="inlineStr">
         <is>
-          <t>Base {0}</t>
+          <t>Each roll yields more of the same resource (120% = 1 plus a 20% chance of 1 more). The odds of better resources stay the same, and boxes and EXP don't increase.</t>
         </is>
       </c>
       <c r="E403" s="1" t="n"/>
@@ -8226,17 +8224,17 @@
       <c r="A404" s="1" t="n"/>
       <c r="B404" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.StatSlotCount</t>
+          <t>UI.Trait.DescYieldAll</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
         <is>
-          <t>능력치 칸 {0}개</t>
+          <t>모든 산업에 붙습니다.</t>
         </is>
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>{0} stat slots</t>
+          <t>Applies to all industries.</t>
         </is>
       </c>
       <c r="E404" s="1" t="n"/>
@@ -8245,17 +8243,17 @@
       <c r="A405" s="1" t="n"/>
       <c r="B405" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.GradeUp</t>
+          <t>UI.Trait.AlreadyMax</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
         <is>
-          <t>등급 상승!</t>
+          <t>이미 최대 레벨입니다.</t>
         </is>
       </c>
       <c r="D405" s="6" t="inlineStr">
         <is>
-          <t>Grade Up!</t>
+          <t>Already at max level.</t>
         </is>
       </c>
       <c r="E405" s="1" t="n"/>
@@ -8264,17 +8262,17 @@
       <c r="A406" s="1" t="n"/>
       <c r="B406" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CapAll</t>
+          <t>UI.Trait.NotEnoughPoints</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
         <is>
-          <t>보유 전부</t>
+          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
         </is>
       </c>
       <c r="D406" s="6" t="inlineStr">
         <is>
-          <t>All Owned</t>
+          <t>Not enough trait points. ({0} pt required)</t>
         </is>
       </c>
       <c r="E406" s="1" t="n"/>
@@ -8283,17 +8281,19 @@
       <c r="A407" s="1" t="n"/>
       <c r="B407" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.All</t>
+          <t>UI.Trait.ConfirmLearn</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>특성 포인트 {0}점을 사용합니다.
+'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
         </is>
       </c>
       <c r="D407" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>This uses {0} trait point(s).
+Raise '{1}' to Lv{2}?</t>
         </is>
       </c>
       <c r="E407" s="1" t="n"/>
@@ -8302,17 +8302,17 @@
       <c r="A408" s="1" t="n"/>
       <c r="B408" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.EveryCombo</t>
+          <t>UI.Trait.WaitLearn</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
         <is>
-          <t>칸마다 전체 또는 {0}</t>
+          <t>특성 레벨 올리기</t>
         </is>
       </c>
       <c r="D408" s="6" t="inlineStr">
         <is>
-          <t>Each slot: All or {0}</t>
+          <t>Level Up Trait</t>
         </is>
       </c>
       <c r="E408" s="1" t="n"/>
@@ -8321,17 +8321,17 @@
       <c r="A409" s="1" t="n"/>
       <c r="B409" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCombo</t>
+          <t>UI.Trait.EmptyDetail</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
         <is>
-          <t>칸 조합 없음</t>
+          <t>특성을 누르면 여기에 펼쳐집니다</t>
         </is>
       </c>
       <c r="D409" s="6" t="inlineStr">
         <is>
-          <t>No slot combos</t>
+          <t>Click a trait to see details here</t>
         </is>
       </c>
       <c r="E409" s="1" t="n"/>
@@ -8340,17 +8340,17 @@
       <c r="A410" s="1" t="n"/>
       <c r="B410" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combos</t>
+          <t>UI.Enchant.Base</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
         <is>
-          <t>칸 {0}</t>
+          <t>기본 {0}</t>
         </is>
       </c>
       <c r="D410" s="6" t="inlineStr">
         <is>
-          <t>Slots {0}</t>
+          <t>Base {0}</t>
         </is>
       </c>
       <c r="E410" s="1" t="n"/>
@@ -8359,19 +8359,17 @@
       <c r="A411" s="1" t="n"/>
       <c r="B411" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NotChosen</t>
+          <t>UI.Enchant.StatSlotCount</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
         <is>
-          <t>아직 선택하지 않았습니다.
-BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>능력치 칸 {0}개</t>
         </is>
       </c>
       <c r="D411" s="6" t="inlineStr">
         <is>
-          <t>You haven't chosen yet.
-Pick either BEFORE or AFTER.</t>
+          <t>{0} stat slots</t>
         </is>
       </c>
       <c r="E411" s="1" t="n"/>
@@ -8380,17 +8378,17 @@
       <c r="A412" s="1" t="n"/>
       <c r="B412" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WornBy</t>
+          <t>UI.Enchant.GradeUp</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
         <is>
-          <t>{0} 착용 중</t>
+          <t>등급 상승!</t>
         </is>
       </c>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>Worn by {0}</t>
+          <t>Grade Up!</t>
         </is>
       </c>
       <c r="E412" s="1" t="n"/>
@@ -8399,17 +8397,17 @@
       <c r="A413" s="1" t="n"/>
       <c r="B413" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ResultHere</t>
+          <t>UI.Enchant.CapAll</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
         <is>
-          <t>결과가 여기에 나옵니다</t>
+          <t>보유 전부</t>
         </is>
       </c>
       <c r="D413" s="6" t="inlineStr">
         <is>
-          <t>The result appears here</t>
+          <t>All Owned</t>
         </is>
       </c>
       <c r="E413" s="1" t="n"/>
@@ -8418,17 +8416,17 @@
       <c r="A414" s="1" t="n"/>
       <c r="B414" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoEnchant</t>
+          <t>UI.Enchant.All</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
         <is>
-          <t>인챈트 없음</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D414" s="6" t="inlineStr">
         <is>
-          <t>No Enchant</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E414" s="1" t="n"/>
@@ -8437,17 +8435,17 @@
       <c r="A415" s="1" t="n"/>
       <c r="B415" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PickOne</t>
+          <t>UI.Enchant.EveryCombo</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
         <is>
-          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
+          <t>칸마다 전체 또는 {0}</t>
         </is>
       </c>
       <c r="D415" s="6" t="inlineStr">
         <is>
-          <t>[Select] either BEFORE or AFTER.</t>
+          <t>Each slot: All or {0}</t>
         </is>
       </c>
       <c r="E415" s="1" t="n"/>
@@ -8456,17 +8454,17 @@
       <c r="A416" s="1" t="n"/>
       <c r="B416" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RerollKeepsBefore</t>
+          <t>UI.Enchant.NoCombo</t>
         </is>
       </c>
       <c r="C416" s="6" t="inlineStr">
         <is>
-          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
+          <t>칸 조합 없음</t>
         </is>
       </c>
       <c r="D416" s="6" t="inlineStr">
         <is>
-          <t>Using it again without choosing keeps BEFORE.</t>
+          <t>No slot combos</t>
         </is>
       </c>
       <c r="E416" s="1" t="n"/>
@@ -8475,17 +8473,17 @@
       <c r="A417" s="1" t="n"/>
       <c r="B417" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleFirst</t>
+          <t>UI.Enchant.Combos</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
         <is>
-          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
+          <t>칸 {0}</t>
         </is>
       </c>
       <c r="D417" s="6" t="inlineStr">
         <is>
-          <t>First use fills {1} slot(s) at {0} grade.</t>
+          <t>Slots {0}</t>
         </is>
       </c>
       <c r="E417" s="1" t="n"/>
@@ -8494,17 +8492,19 @@
       <c r="A418" s="1" t="n"/>
       <c r="B418" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleMythic</t>
+          <t>UI.Enchant.NotChosen</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
         <is>
-          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
+          <t>아직 선택하지 않았습니다.
+BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D418" s="6" t="inlineStr">
         <is>
-          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
+          <t>You haven't chosen yet.
+Pick either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E418" s="1" t="n"/>
@@ -8513,17 +8513,17 @@
       <c r="A419" s="1" t="n"/>
       <c r="B419" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleNormal</t>
+          <t>UI.Enchant.WornBy</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
+          <t>{0} 착용 중</t>
         </is>
       </c>
       <c r="D419" s="6" t="inlineStr">
         <is>
-          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
+          <t>Worn by {0}</t>
         </is>
       </c>
       <c r="E419" s="1" t="n"/>
@@ -8532,17 +8532,17 @@
       <c r="A420" s="1" t="n"/>
       <c r="B420" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleKeep</t>
+          <t>UI.Enchant.ResultHere</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
         <is>
-          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
+          <t>결과가 여기에 나옵니다</t>
         </is>
       </c>
       <c r="D420" s="6" t="inlineStr">
         <is>
-          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
+          <t>The result appears here</t>
         </is>
       </c>
       <c r="E420" s="1" t="n"/>
@@ -8551,17 +8551,17 @@
       <c r="A421" s="1" t="n"/>
       <c r="B421" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeFirst</t>
+          <t>UI.Enchant.NoEnchant</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
         <is>
-          <t>첫 사용 · 일반 확정</t>
+          <t>인챈트 없음</t>
         </is>
       </c>
       <c r="D421" s="6" t="inlineStr">
         <is>
-          <t>First use · Common guaranteed</t>
+          <t>No Enchant</t>
         </is>
       </c>
       <c r="E421" s="1" t="n"/>
@@ -8570,17 +8570,17 @@
       <c r="A422" s="1" t="n"/>
       <c r="B422" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOptionsOnly</t>
+          <t>UI.Enchant.PickOne</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
         <is>
-          <t>옵션만 다시 뽑기</t>
+          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
         </is>
       </c>
       <c r="D422" s="6" t="inlineStr">
         <is>
-          <t>Options reroll only</t>
+          <t>[Select] either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E422" s="1" t="n"/>
@@ -8589,17 +8589,17 @@
       <c r="A423" s="1" t="n"/>
       <c r="B423" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeUp</t>
+          <t>UI.Enchant.RerollKeepsBefore</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
         <is>
-          <t>{0} 상승 {1}</t>
+          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
         </is>
       </c>
       <c r="D423" s="6" t="inlineStr">
         <is>
-          <t>{0} up {1}</t>
+          <t>Using it again without choosing keeps BEFORE.</t>
         </is>
       </c>
       <c r="E423" s="1" t="n"/>
@@ -8608,17 +8608,17 @@
       <c r="A424" s="1" t="n"/>
       <c r="B424" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOwned</t>
+          <t>UI.Enchant.RuleFirst</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개</t>
+          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>First use fills {1} slot(s) at {0} grade.</t>
         </is>
       </c>
       <c r="E424" s="1" t="n"/>
@@ -8627,17 +8627,17 @@
       <c r="A425" s="1" t="n"/>
       <c r="B425" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeData</t>
+          <t>UI.Enchant.RuleMythic</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
         <is>
-          <t>큐브 정보가 없습니다</t>
+          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
         </is>
       </c>
       <c r="D425" s="6" t="inlineStr">
         <is>
-          <t>No cube data</t>
+          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
         </is>
       </c>
       <c r="E425" s="1" t="n"/>
@@ -8646,17 +8646,17 @@
       <c r="A426" s="1" t="n"/>
       <c r="B426" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UseCube</t>
+          <t>UI.Enchant.RuleNormal</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
         <is>
-          <t>{0} 사용</t>
+          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
         </is>
       </c>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>Use {0}</t>
+          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
         </is>
       </c>
       <c r="E426" s="1" t="n"/>
@@ -8665,17 +8665,17 @@
       <c r="A427" s="1" t="n"/>
       <c r="B427" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCube</t>
+          <t>UI.Enchant.RuleKeep</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다</t>
+          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
         </is>
       </c>
       <c r="D427" s="6" t="inlineStr">
         <is>
-          <t>No {0}</t>
+          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
         </is>
       </c>
       <c r="E427" s="1" t="n"/>
@@ -8684,17 +8684,17 @@
       <c r="A428" s="1" t="n"/>
       <c r="B428" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnequipAndUse</t>
+          <t>UI.Enchant.CubeFirst</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
         <is>
-          <t>해제하고 {0} 사용</t>
+          <t>첫 사용 · 일반 확정</t>
         </is>
       </c>
       <c r="D428" s="6" t="inlineStr">
         <is>
-          <t>Unequip and Use {0}</t>
+          <t>First use · Common guaranteed</t>
         </is>
       </c>
       <c r="E428" s="1" t="n"/>
@@ -8703,17 +8703,17 @@
       <c r="A429" s="1" t="n"/>
       <c r="B429" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeNotice</t>
+          <t>UI.Enchant.CubeOptionsOnly</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다.</t>
+          <t>옵션만 다시 뽑기</t>
         </is>
       </c>
       <c r="D429" s="6" t="inlineStr">
         <is>
-          <t>You have no {0}.</t>
+          <t>Options reroll only</t>
         </is>
       </c>
       <c r="E429" s="1" t="n"/>
@@ -8722,19 +8722,17 @@
       <c r="A430" s="1" t="n"/>
       <c r="B430" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ConfirmUnequip</t>
+          <t>UI.Enchant.CubeUp</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
         <is>
-          <t>{0}이(가) 끼고 있는 장비입니다.
-해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
+          <t>{0} 상승 {1}</t>
         </is>
       </c>
       <c r="D430" s="6" t="inlineStr">
         <is>
-          <t>{0} is wearing this gear.
-It will be unequipped before using the cube. (It won't be re-equipped.)</t>
+          <t>{0} up {1}</t>
         </is>
       </c>
       <c r="E430" s="1" t="n"/>
@@ -8743,17 +8741,17 @@
       <c r="A431" s="1" t="n"/>
       <c r="B431" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitUse</t>
+          <t>UI.Enchant.CubeOwned</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
         <is>
-          <t>큐브 사용</t>
+          <t>보유 {0}개</t>
         </is>
       </c>
       <c r="D431" s="6" t="inlineStr">
         <is>
-          <t>Use Cube</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E431" s="1" t="n"/>
@@ -8762,17 +8760,17 @@
       <c r="A432" s="1" t="n"/>
       <c r="B432" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitChoose</t>
+          <t>UI.Enchant.NoCubeData</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
         <is>
-          <t>큐브 결과 고르기</t>
+          <t>큐브 정보가 없습니다</t>
         </is>
       </c>
       <c r="D432" s="6" t="inlineStr">
         <is>
-          <t>Choose Cube Result</t>
+          <t>No cube data</t>
         </is>
       </c>
       <c r="E432" s="1" t="n"/>
@@ -8781,17 +8779,17 @@
       <c r="A433" s="1" t="n"/>
       <c r="B433" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ChooseFirst</t>
+          <t>UI.Enchant.UseCube</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
         <is>
-          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>{0} 사용</t>
         </is>
       </c>
       <c r="D433" s="6" t="inlineStr">
         <is>
-          <t>Pick BEFORE or AFTER first.</t>
+          <t>Use {0}</t>
         </is>
       </c>
       <c r="E433" s="1" t="n"/>
@@ -8800,17 +8798,17 @@
       <c r="A434" s="1" t="n"/>
       <c r="B434" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoAutoWorn</t>
+          <t>UI.Enchant.NoCube</t>
         </is>
       </c>
       <c r="C434" s="6" t="inlineStr">
         <is>
-          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
+          <t>{0}가 없습니다</t>
         </is>
       </c>
       <c r="D434" s="6" t="inlineStr">
         <is>
-          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
+          <t>No {0}</t>
         </is>
       </c>
       <c r="E434" s="1" t="n"/>
@@ -8819,17 +8817,17 @@
       <c r="A435" s="1" t="n"/>
       <c r="B435" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStart</t>
+          <t>UI.Enchant.UnequipAndUse</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
         <is>
-          <t>자동 시작 ▶</t>
+          <t>해제하고 {0} 사용</t>
         </is>
       </c>
       <c r="D435" s="6" t="inlineStr">
         <is>
-          <t>Start Auto ▶</t>
+          <t>Unequip and Use {0}</t>
         </is>
       </c>
       <c r="E435" s="1" t="n"/>
@@ -8838,17 +8836,17 @@
       <c r="A436" s="1" t="n"/>
       <c r="B436" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AlreadyMythic</t>
+          <t>UI.Enchant.NoCubeNotice</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
         <is>
-          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
+          <t>{0}가 없습니다.</t>
         </is>
       </c>
       <c r="D436" s="6" t="inlineStr">
         <is>
-          <t>Already Mythic. Pick an option to aim for.</t>
+          <t>You have no {0}.</t>
         </is>
       </c>
       <c r="E436" s="1" t="n"/>
@@ -8857,17 +8855,19 @@
       <c r="A437" s="1" t="n"/>
       <c r="B437" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NeedCombo</t>
+          <t>UI.Enchant.ConfirmUnequip</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
         <is>
-          <t>조합을 하나 이상 켜 주세요.</t>
+          <t>{0}이(가) 끼고 있는 장비입니다.
+해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
         </is>
       </c>
       <c r="D437" s="6" t="inlineStr">
         <is>
-          <t>Turn on at least one combo.</t>
+          <t>{0} is wearing this gear.
+It will be unequipped before using the cube. (It won't be re-equipped.)</t>
         </is>
       </c>
       <c r="E437" s="1" t="n"/>
@@ -8876,17 +8876,17 @@
       <c r="A438" s="1" t="n"/>
       <c r="B438" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.MeanCount</t>
+          <t>UI.Enchant.WaitUse</t>
         </is>
       </c>
       <c r="C438" s="6" t="inlineStr">
         <is>
-          <t>{0}개 (약 {1})</t>
+          <t>큐브 사용</t>
         </is>
       </c>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>{0} (about {1})</t>
+          <t>Use Cube</t>
         </is>
       </c>
       <c r="E438" s="1" t="n"/>
@@ -8895,17 +8895,17 @@
       <c r="A439" s="1" t="n"/>
       <c r="B439" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Within</t>
+          <t>UI.Enchant.WaitChoose</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
         <is>
-          <t>{0}개 안에 {1}</t>
+          <t>큐브 결과 고르기</t>
         </is>
       </c>
       <c r="D439" s="6" t="inlineStr">
         <is>
-          <t>{1} within {0}</t>
+          <t>Choose Cube Result</t>
         </is>
       </c>
       <c r="E439" s="1" t="n"/>
@@ -8914,17 +8914,17 @@
       <c r="A440" s="1" t="n"/>
       <c r="B440" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Mean</t>
+          <t>UI.Enchant.ChooseFirst</t>
         </is>
       </c>
       <c r="C440" s="6" t="inlineStr">
         <is>
-          <t>평균 {0}</t>
+          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D440" s="6" t="inlineStr">
         <is>
-          <t>avg {0}</t>
+          <t>Pick BEFORE or AFTER first.</t>
         </is>
       </c>
       <c r="E440" s="1" t="n"/>
@@ -8933,17 +8933,17 @@
       <c r="A441" s="1" t="n"/>
       <c r="B441" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnderMin</t>
+          <t>UI.Enchant.NoAutoWorn</t>
         </is>
       </c>
       <c r="C441" s="6" t="inlineStr">
         <is>
-          <t>0.01% 미만</t>
+          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
         </is>
       </c>
       <c r="D441" s="6" t="inlineStr">
         <is>
-          <t>under 0.01%</t>
+          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
         </is>
       </c>
       <c r="E441" s="1" t="n"/>
@@ -8952,17 +8952,17 @@
       <c r="A442" s="1" t="n"/>
       <c r="B442" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Minutes</t>
+          <t>UI.Enchant.AutoStart</t>
         </is>
       </c>
       <c r="C442" s="6" t="inlineStr">
         <is>
-          <t>{0}분</t>
+          <t>자동 시작 ▶</t>
         </is>
       </c>
       <c r="D442" s="6" t="inlineStr">
         <is>
-          <t>{0}m</t>
+          <t>Start Auto ▶</t>
         </is>
       </c>
       <c r="E442" s="1" t="n"/>
@@ -8971,17 +8971,17 @@
       <c r="A443" s="1" t="n"/>
       <c r="B443" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Hours</t>
+          <t>UI.Enchant.AlreadyMythic</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
         </is>
       </c>
       <c r="D443" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Already Mythic. Pick an option to aim for.</t>
         </is>
       </c>
       <c r="E443" s="1" t="n"/>
@@ -8990,17 +8990,17 @@
       <c r="A444" s="1" t="n"/>
       <c r="B444" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoRunning</t>
+          <t>UI.Enchant.NeedCombo</t>
         </is>
       </c>
       <c r="C444" s="6" t="inlineStr">
         <is>
-          <t>자동 진행 중 {0} / {1}개</t>
+          <t>조합을 하나 이상 켜 주세요.</t>
         </is>
       </c>
       <c r="D444" s="6" t="inlineStr">
         <is>
-          <t>Auto running {0} / {1}</t>
+          <t>Turn on at least one combo.</t>
         </is>
       </c>
       <c r="E444" s="1" t="n"/>
@@ -9009,17 +9009,17 @@
       <c r="A445" s="1" t="n"/>
       <c r="B445" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Goal</t>
+          <t>UI.Enchant.MeanCount</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
         <is>
-          <t>목표 {0} 이상</t>
+          <t>{0}개 (약 {1})</t>
         </is>
       </c>
       <c r="D445" s="6" t="inlineStr">
         <is>
-          <t>Goal: {0} or higher</t>
+          <t>{0} (about {1})</t>
         </is>
       </c>
       <c r="E445" s="1" t="n"/>
@@ -9028,17 +9028,17 @@
       <c r="A446" s="1" t="n"/>
       <c r="B446" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoSlotRule</t>
+          <t>UI.Enchant.Within</t>
         </is>
       </c>
       <c r="C446" s="6" t="inlineStr">
         <is>
-          <t>칸 조건 없음 — 등급만 봅니다</t>
+          <t>{0}개 안에 {1}</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
         <is>
-          <t>No slot condition — grade only</t>
+          <t>{1} within {0}</t>
         </is>
       </c>
       <c r="E446" s="1" t="n"/>
@@ -9047,17 +9047,17 @@
       <c r="A447" s="1" t="n"/>
       <c r="B447" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PerRoll</t>
+          <t>UI.Enchant.Mean</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}</t>
+          <t>평균 {0}</t>
         </is>
       </c>
       <c r="D447" s="6" t="inlineStr">
         <is>
-          <t>{0} per roll</t>
+          <t>avg {0}</t>
         </is>
       </c>
       <c r="E447" s="1" t="n"/>
@@ -9066,17 +9066,17 @@
       <c r="A448" s="1" t="n"/>
       <c r="B448" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStop</t>
+          <t>UI.Enchant.UnderMin</t>
         </is>
       </c>
       <c r="C448" s="6" t="inlineStr">
         <is>
-          <t>■ 멈춤</t>
+          <t>0.01% 미만</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
         <is>
-          <t>■ Stop</t>
+          <t>under 0.01%</t>
         </is>
       </c>
       <c r="E448" s="1" t="n"/>
@@ -9085,17 +9085,17 @@
       <c r="A449" s="1" t="n"/>
       <c r="B449" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Auto</t>
+          <t>UI.Enchant.Minutes</t>
         </is>
       </c>
       <c r="C449" s="6" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>{0}분</t>
         </is>
       </c>
       <c r="D449" s="6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>{0}m</t>
         </is>
       </c>
       <c r="E449" s="1" t="n"/>
@@ -9104,17 +9104,17 @@
       <c r="A450" s="1" t="n"/>
       <c r="B450" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndStopped</t>
+          <t>UI.Enchant.Hours</t>
         </is>
       </c>
       <c r="C450" s="6" t="inlineStr">
         <is>
-          <t>자동을 멈췄습니다</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
         <is>
-          <t>Auto stopped</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E450" s="1" t="n"/>
@@ -9123,17 +9123,17 @@
       <c r="A451" s="1" t="n"/>
       <c r="B451" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndCap</t>
+          <t>UI.Enchant.AutoRunning</t>
         </is>
       </c>
       <c r="C451" s="6" t="inlineStr">
         <is>
-          <t>상한에 닿아 멈췄습니다</t>
+          <t>자동 진행 중 {0} / {1}개</t>
         </is>
       </c>
       <c r="D451" s="6" t="inlineStr">
         <is>
-          <t>Stopped at the limit</t>
+          <t>Auto running {0} / {1}</t>
         </is>
       </c>
       <c r="E451" s="1" t="n"/>
@@ -9142,17 +9142,17 @@
       <c r="A452" s="1" t="n"/>
       <c r="B452" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndNoCube</t>
+          <t>UI.Enchant.Goal</t>
         </is>
       </c>
       <c r="C452" s="6" t="inlineStr">
         <is>
-          <t>큐브가 떨어져 멈췄습니다</t>
+          <t>목표 {0} 이상</t>
         </is>
       </c>
       <c r="D452" s="6" t="inlineStr">
         <is>
-          <t>Stopped — out of cubes</t>
+          <t>Goal: {0} or higher</t>
         </is>
       </c>
       <c r="E452" s="1" t="n"/>
@@ -9161,17 +9161,17 @@
       <c r="A453" s="1" t="n"/>
       <c r="B453" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndRejected</t>
+          <t>UI.Enchant.NoSlotRule</t>
         </is>
       </c>
       <c r="C453" s="6" t="inlineStr">
         <is>
-          <t>서버가 거절해 멈췄습니다</t>
+          <t>칸 조건 없음 — 등급만 봅니다</t>
         </is>
       </c>
       <c r="D453" s="6" t="inlineStr">
         <is>
-          <t>Stopped — server rejected</t>
+          <t>No slot condition — grade only</t>
         </is>
       </c>
       <c r="E453" s="1" t="n"/>
@@ -9180,17 +9180,17 @@
       <c r="A454" s="1" t="n"/>
       <c r="B454" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndGoal</t>
+          <t>UI.Enchant.PerRoll</t>
         </is>
       </c>
       <c r="C454" s="6" t="inlineStr">
         <is>
-          <t>목표 달성!</t>
+          <t>한 번에 {0}</t>
         </is>
       </c>
       <c r="D454" s="6" t="inlineStr">
         <is>
-          <t>Goal reached!</t>
+          <t>{0} per roll</t>
         </is>
       </c>
       <c r="E454" s="1" t="n"/>
@@ -9199,17 +9199,17 @@
       <c r="A455" s="1" t="n"/>
       <c r="B455" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndSummary</t>
+          <t>UI.Enchant.AutoStop</t>
         </is>
       </c>
       <c r="C455" s="6" t="inlineStr">
         <is>
-          <t>{0} — {1} {2}개 사용.</t>
+          <t>■ 멈춤</t>
         </is>
       </c>
       <c r="D455" s="6" t="inlineStr">
         <is>
-          <t>{0} — used {2} {1}.</t>
+          <t>■ Stop</t>
         </is>
       </c>
       <c r="E455" s="1" t="n"/>
@@ -9218,17 +9218,17 @@
       <c r="A456" s="1" t="n"/>
       <c r="B456" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.TargetGrade</t>
+          <t>UI.Enchant.Auto</t>
         </is>
       </c>
       <c r="C456" s="6" t="inlineStr">
         <is>
-          <t>목표 등급</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="D456" s="6" t="inlineStr">
         <is>
-          <t>Target Grade</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E456" s="1" t="n"/>
@@ -9237,17 +9237,17 @@
       <c r="A457" s="1" t="n"/>
       <c r="B457" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.FocusOption</t>
+          <t>UI.Enchant.AutoEndStopped</t>
         </is>
       </c>
       <c r="C457" s="6" t="inlineStr">
         <is>
-          <t>노릴 옵션</t>
+          <t>자동을 멈췄습니다</t>
         </is>
       </c>
       <c r="D457" s="6" t="inlineStr">
         <is>
-          <t>Aim For</t>
+          <t>Auto stopped</t>
         </is>
       </c>
       <c r="E457" s="1" t="n"/>
@@ -9256,17 +9256,17 @@
       <c r="A458" s="1" t="n"/>
       <c r="B458" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combo</t>
+          <t>UI.Enchant.AutoEndCap</t>
         </is>
       </c>
       <c r="C458" s="6" t="inlineStr">
         <is>
-          <t>조합</t>
+          <t>상한에 닿아 멈췄습니다</t>
         </is>
       </c>
       <c r="D458" s="6" t="inlineStr">
         <is>
-          <t>Combo</t>
+          <t>Stopped at the limit</t>
         </is>
       </c>
       <c r="E458" s="1" t="n"/>
@@ -9275,17 +9275,17 @@
       <c r="A459" s="1" t="n"/>
       <c r="B459" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Cap</t>
+          <t>UI.Enchant.AutoEndNoCube</t>
         </is>
       </c>
       <c r="C459" s="6" t="inlineStr">
         <is>
-          <t>상한</t>
+          <t>큐브가 떨어져 멈췄습니다</t>
         </is>
       </c>
       <c r="D459" s="6" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>Stopped — out of cubes</t>
         </is>
       </c>
       <c r="E459" s="1" t="n"/>
@@ -9294,17 +9294,17 @@
       <c r="A460" s="1" t="n"/>
       <c r="B460" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Select</t>
+          <t>UI.Enchant.AutoEndRejected</t>
         </is>
       </c>
       <c r="C460" s="6" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>서버가 거절해 멈췄습니다</t>
         </is>
       </c>
       <c r="D460" s="6" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Stopped — server rejected</t>
         </is>
       </c>
       <c r="E460" s="1" t="n"/>
@@ -9313,17 +9313,17 @@
       <c r="A461" s="1" t="n"/>
       <c r="B461" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Times</t>
+          <t>UI.Enchant.AutoEndGoal</t>
         </is>
       </c>
       <c r="C461" s="6" t="inlineStr">
         <is>
-          <t>{0}회</t>
+          <t>목표 달성!</t>
         </is>
       </c>
       <c r="D461" s="6" t="inlineStr">
         <is>
-          <t>x{0}</t>
+          <t>Goal reached!</t>
         </is>
       </c>
       <c r="E461" s="1" t="n"/>
@@ -9332,17 +9332,17 @@
       <c r="A462" s="1" t="n"/>
       <c r="B462" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Worker</t>
+          <t>UI.Enchant.AutoEndSummary</t>
         </is>
       </c>
       <c r="C462" s="6" t="inlineStr">
         <is>
-          <t>일꾼</t>
+          <t>{0} — {1} {2}개 사용.</t>
         </is>
       </c>
       <c r="D462" s="6" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>{0} — used {2} {1}.</t>
         </is>
       </c>
       <c r="E462" s="1" t="n"/>
@@ -9351,17 +9351,17 @@
       <c r="A463" s="1" t="n"/>
       <c r="B463" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.WorkSpeedUp</t>
+          <t>UI.Enchant.TargetGrade</t>
         </is>
       </c>
       <c r="C463" s="6" t="inlineStr">
         <is>
-          <t>작업속도 증가</t>
+          <t>목표 등급</t>
         </is>
       </c>
       <c r="D463" s="6" t="inlineStr">
         <is>
-          <t>Work Speed Up</t>
+          <t>Target Grade</t>
         </is>
       </c>
       <c r="E463" s="1" t="n"/>
@@ -9370,17 +9370,17 @@
       <c r="A464" s="1" t="n"/>
       <c r="B464" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Kinds</t>
+          <t>UI.Enchant.FocusOption</t>
         </is>
       </c>
       <c r="C464" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}종</t>
+          <t>노릴 옵션</t>
         </is>
       </c>
       <c r="D464" s="6" t="inlineStr">
         <is>
-          <t>{1} {0}</t>
+          <t>Aim For</t>
         </is>
       </c>
       <c r="E464" s="1" t="n"/>
@@ -9389,17 +9389,17 @@
       <c r="A465" s="1" t="n"/>
       <c r="B465" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.KindsOnly</t>
+          <t>UI.Enchant.Combo</t>
         </is>
       </c>
       <c r="C465" s="6" t="inlineStr">
         <is>
-          <t>{0}종</t>
+          <t>조합</t>
         </is>
       </c>
       <c r="D465" s="6" t="inlineStr">
         <is>
-          <t>{0} kinds</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="E465" s="1" t="n"/>
@@ -9408,17 +9408,17 @@
       <c r="A466" s="1" t="n"/>
       <c r="B466" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Item</t>
+          <t>UI.Enchant.Cap</t>
         </is>
       </c>
       <c r="C466" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="D466" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Limit</t>
         </is>
       </c>
       <c r="E466" s="1" t="n"/>
@@ -9427,17 +9427,17 @@
       <c r="A467" s="1" t="n"/>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.RateTitle</t>
+          <t>UI.Enchant.Select</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
         <is>
-          <t>{0} 확률</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="D467" s="6" t="inlineStr">
         <is>
-          <t>{0} Rates</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E467" s="1" t="n"/>
@@ -9446,17 +9446,17 @@
       <c r="A468" s="1" t="n"/>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoEntries</t>
+          <t>UI.Gacha.Times</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>뽑을 항목이 없다</t>
+          <t>{0}회</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
         <is>
-          <t>Nothing to draw</t>
+          <t>x{0}</t>
         </is>
       </c>
       <c r="E468" s="1" t="n"/>
@@ -9465,17 +9465,17 @@
       <c r="A469" s="1" t="n"/>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoRarity</t>
+          <t>UI.Gacha.Worker</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
         <is>
-          <t>등급 없음</t>
+          <t>일꾼</t>
         </is>
       </c>
       <c r="D469" s="6" t="inlineStr">
         <is>
-          <t>No Rarity</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="E469" s="1" t="n"/>
@@ -9484,17 +9484,17 @@
       <c r="A470" s="1" t="n"/>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SameRate</t>
+          <t>UI.Gacha.WorkSpeedUp</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
         <is>
-          <t>10회도 한 번마다 같은 확률</t>
+          <t>작업속도 증가</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
         <is>
-          <t>x10 uses the same odds for each draw</t>
+          <t>Work Speed Up</t>
         </is>
       </c>
       <c r="E470" s="1" t="n"/>
@@ -9503,17 +9503,17 @@
       <c r="A471" s="1" t="n"/>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Wait</t>
+          <t>UI.Gacha.Kinds</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
         <is>
-          <t>가챠 {0}회</t>
+          <t>{0} {1}종</t>
         </is>
       </c>
       <c r="D471" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0}</t>
+          <t>{1} {0}</t>
         </is>
       </c>
       <c r="E471" s="1" t="n"/>
@@ -9522,17 +9522,17 @@
       <c r="A472" s="1" t="n"/>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Source</t>
+          <t>UI.Gacha.KindsOnly</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
         <is>
-          <t>가챠</t>
+          <t>{0}종</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>{0} kinds</t>
         </is>
       </c>
       <c r="E472" s="1" t="n"/>
@@ -9541,17 +9541,17 @@
       <c r="A473" s="1" t="n"/>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceBox</t>
+          <t>UI.Gacha.Item</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
         <is>
-          <t>상자 개봉</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D473" s="6" t="inlineStr">
         <is>
-          <t>Box Opening</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E473" s="1" t="n"/>
@@ -9560,17 +9560,17 @@
       <c r="A474" s="1" t="n"/>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceMail</t>
+          <t>UI.Gacha.RateTitle</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
         <is>
-          <t>우편 수령</t>
+          <t>{0} 확률</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
         <is>
-          <t>Mail Claim</t>
+          <t>{0} Rates</t>
         </is>
       </c>
       <c r="E474" s="1" t="n"/>
@@ -9579,17 +9579,17 @@
       <c r="A475" s="1" t="n"/>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.ResultTitle</t>
+          <t>UI.Gacha.NoEntries</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
         <is>
-          <t>{0} 결과</t>
+          <t>뽑을 항목이 없다</t>
         </is>
       </c>
       <c r="D475" s="6" t="inlineStr">
         <is>
-          <t>{0} Results</t>
+          <t>Nothing to draw</t>
         </is>
       </c>
       <c r="E475" s="1" t="n"/>
@@ -9598,17 +9598,17 @@
       <c r="A476" s="1" t="n"/>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.DrawAgain</t>
+          <t>UI.Gacha.NoRarity</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
         <is>
-          <t>{0}회 더 뽑기</t>
+          <t>등급 없음</t>
         </is>
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0} Again</t>
+          <t>No Rarity</t>
         </is>
       </c>
       <c r="E476" s="1" t="n"/>
@@ -9617,17 +9617,17 @@
       <c r="A477" s="1" t="n"/>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Tab</t>
+          <t>UI.Gacha.SameRate</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>10회도 한 번마다 같은 확률</t>
         </is>
       </c>
       <c r="D477" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>x10 uses the same odds for each draw</t>
         </is>
       </c>
       <c r="E477" s="1" t="n"/>
@@ -9636,17 +9636,17 @@
       <c r="A478" s="1" t="n"/>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.CloseResult</t>
+          <t>UI.Gacha.Wait</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
         <is>
-          <t>[결과 닫기]</t>
+          <t>가챠 {0}회</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>[Close]</t>
+          <t>Draw x{0}</t>
         </is>
       </c>
       <c r="E478" s="1" t="n"/>
@@ -9655,17 +9655,17 @@
       <c r="A479" s="1" t="n"/>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Gacha.Source</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>가챠</t>
         </is>
       </c>
       <c r="D479" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E479" s="1" t="n"/>
@@ -9674,17 +9674,17 @@
       <c r="A480" s="1" t="n"/>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Gacha.SourceBox</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>상자 개봉</t>
         </is>
       </c>
       <c r="D480" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Box Opening</t>
         </is>
       </c>
       <c r="E480" s="1" t="n"/>
@@ -9693,17 +9693,17 @@
       <c r="A481" s="1" t="n"/>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Gacha.SourceMail</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>우편 수령</t>
         </is>
       </c>
       <c r="D481" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>Mail Claim</t>
         </is>
       </c>
       <c r="E481" s="1" t="n"/>
@@ -9712,17 +9712,17 @@
       <c r="A482" s="1" t="n"/>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Gacha.ResultTitle</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>{0} 결과</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>{0} Results</t>
         </is>
       </c>
       <c r="E482" s="1" t="n"/>
@@ -9731,17 +9731,17 @@
       <c r="A483" s="1" t="n"/>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Gacha.DrawAgain</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>{0}회 더 뽑기</t>
         </is>
       </c>
       <c r="D483" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>Draw x{0} Again</t>
         </is>
       </c>
       <c r="E483" s="1" t="n"/>
@@ -9750,17 +9750,17 @@
       <c r="A484" s="1" t="n"/>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Gacha.Tab</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="D484" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E484" s="1" t="n"/>
@@ -9769,17 +9769,17 @@
       <c r="A485" s="1" t="n"/>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Gacha.CloseResult</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>[결과 닫기]</t>
         </is>
       </c>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>[Close]</t>
         </is>
       </c>
       <c r="E485" s="1" t="n"/>
@@ -9788,17 +9788,17 @@
       <c r="A486" s="1" t="n"/>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E486" s="1" t="n"/>
@@ -9807,17 +9807,17 @@
       <c r="A487" s="1" t="n"/>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D487" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E487" s="1" t="n"/>
@@ -9826,17 +9826,17 @@
       <c r="A488" s="1" t="n"/>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D488" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E488" s="1" t="n"/>
@@ -9845,17 +9845,17 @@
       <c r="A489" s="1" t="n"/>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D489" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E489" s="1" t="n"/>
@@ -9864,17 +9864,17 @@
       <c r="A490" s="1" t="n"/>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D490" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E490" s="1" t="n"/>
@@ -9883,17 +9883,17 @@
       <c r="A491" s="1" t="n"/>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D491" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E491" s="1" t="n"/>
@@ -9902,17 +9902,17 @@
       <c r="A492" s="1" t="n"/>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D492" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E492" s="1" t="n"/>
@@ -9921,17 +9921,17 @@
       <c r="A493" s="1" t="n"/>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D493" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E493" s="1" t="n"/>
@@ -9940,17 +9940,17 @@
       <c r="A494" s="1" t="n"/>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D494" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E494" s="1" t="n"/>
@@ -9959,17 +9959,17 @@
       <c r="A495" s="1" t="n"/>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E495" s="1" t="n"/>
@@ -9978,17 +9978,17 @@
       <c r="A496" s="1" t="n"/>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D496" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E496" s="1" t="n"/>
@@ -9997,17 +9997,17 @@
       <c r="A497" s="1" t="n"/>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E497" s="1" t="n"/>
@@ -10016,17 +10016,17 @@
       <c r="A498" s="1" t="n"/>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D498" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E498" s="1" t="n"/>
@@ -10035,17 +10035,17 @@
       <c r="A499" s="1" t="n"/>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D499" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E499" s="1" t="n"/>
@@ -10054,17 +10054,17 @@
       <c r="A500" s="1" t="n"/>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D500" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E500" s="1" t="n"/>
@@ -10073,17 +10073,17 @@
       <c r="A501" s="1" t="n"/>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D501" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E501" s="1" t="n"/>
@@ -10092,17 +10092,17 @@
       <c r="A502" s="1" t="n"/>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D502" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E502" s="1" t="n"/>
@@ -10111,17 +10111,17 @@
       <c r="A503" s="1" t="n"/>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D503" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E503" s="1" t="n"/>
@@ -10130,17 +10130,17 @@
       <c r="A504" s="1" t="n"/>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D504" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E504" s="1" t="n"/>
@@ -10149,17 +10149,17 @@
       <c r="A505" s="1" t="n"/>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D505" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E505" s="1" t="n"/>
@@ -10168,17 +10168,17 @@
       <c r="A506" s="1" t="n"/>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D506" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E506" s="1" t="n"/>
@@ -10187,17 +10187,17 @@
       <c r="A507" s="1" t="n"/>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D507" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E507" s="1" t="n"/>
@@ -10206,17 +10206,17 @@
       <c r="A508" s="1" t="n"/>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D508" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E508" s="1" t="n"/>
@@ -10225,17 +10225,17 @@
       <c r="A509" s="1" t="n"/>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E509" s="1" t="n"/>
@@ -10244,17 +10244,17 @@
       <c r="A510" s="1" t="n"/>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D510" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E510" s="1" t="n"/>
@@ -10263,17 +10263,17 @@
       <c r="A511" s="1" t="n"/>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E511" s="1" t="n"/>
@@ -10282,17 +10282,17 @@
       <c r="A512" s="1" t="n"/>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E512" s="1" t="n"/>
@@ -10301,17 +10301,17 @@
       <c r="A513" s="1" t="n"/>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E513" s="1" t="n"/>
@@ -10320,17 +10320,17 @@
       <c r="A514" s="1" t="n"/>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D514" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E514" s="1" t="n"/>
@@ -10339,17 +10339,17 @@
       <c r="A515" s="1" t="n"/>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D515" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E515" s="1" t="n"/>
@@ -10358,17 +10358,17 @@
       <c r="A516" s="1" t="n"/>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D516" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E516" s="1" t="n"/>
@@ -10377,17 +10377,17 @@
       <c r="A517" s="1" t="n"/>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D517" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E517" s="1" t="n"/>
@@ -10396,17 +10396,17 @@
       <c r="A518" s="1" t="n"/>
       <c r="B518" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D518" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E518" s="1" t="n"/>
@@ -10415,17 +10415,17 @@
       <c r="A519" s="1" t="n"/>
       <c r="B519" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E519" s="1" t="n"/>
@@ -10434,17 +10434,17 @@
       <c r="A520" s="1" t="n"/>
       <c r="B520" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D520" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E520" s="1" t="n"/>
@@ -10453,17 +10453,17 @@
       <c r="A521" s="1" t="n"/>
       <c r="B521" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E521" s="1" t="n"/>
@@ -10472,17 +10472,17 @@
       <c r="A522" s="1" t="n"/>
       <c r="B522" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D522" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E522" s="1" t="n"/>
@@ -10491,17 +10491,17 @@
       <c r="A523" s="1" t="n"/>
       <c r="B523" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D523" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E523" s="1" t="n"/>
@@ -10510,17 +10510,17 @@
       <c r="A524" s="1" t="n"/>
       <c r="B524" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D524" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E524" s="1" t="n"/>
@@ -10529,17 +10529,17 @@
       <c r="A525" s="1" t="n"/>
       <c r="B525" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D525" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E525" s="1" t="n"/>
@@ -10548,17 +10548,17 @@
       <c r="A526" s="1" t="n"/>
       <c r="B526" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D526" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E526" s="1" t="n"/>
@@ -10567,17 +10567,17 @@
       <c r="A527" s="1" t="n"/>
       <c r="B527" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D527" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E527" s="1" t="n"/>
@@ -10586,17 +10586,17 @@
       <c r="A528" s="1" t="n"/>
       <c r="B528" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D528" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E528" s="1" t="n"/>
@@ -10605,17 +10605,17 @@
       <c r="A529" s="1" t="n"/>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D529" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E529" s="1" t="n"/>
@@ -10624,17 +10624,17 @@
       <c r="A530" s="1" t="n"/>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D530" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E530" s="1" t="n"/>
@@ -10643,17 +10643,17 @@
       <c r="A531" s="1" t="n"/>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D531" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E531" s="1" t="n"/>
@@ -10662,17 +10662,17 @@
       <c r="A532" s="1" t="n"/>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D532" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E532" s="1" t="n"/>
@@ -10681,17 +10681,17 @@
       <c r="A533" s="1" t="n"/>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D533" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E533" s="1" t="n"/>
@@ -10700,17 +10700,17 @@
       <c r="A534" s="1" t="n"/>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D534" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E534" s="1" t="n"/>
@@ -10719,17 +10719,17 @@
       <c r="A535" s="1" t="n"/>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D535" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E535" s="1" t="n"/>
@@ -10738,17 +10738,17 @@
       <c r="A536" s="1" t="n"/>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E536" s="1" t="n"/>
@@ -10757,17 +10757,17 @@
       <c r="A537" s="1" t="n"/>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E537" s="1" t="n"/>
@@ -10776,17 +10776,17 @@
       <c r="A538" s="1" t="n"/>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D538" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E538" s="1" t="n"/>
@@ -10795,17 +10795,17 @@
       <c r="A539" s="1" t="n"/>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D539" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E539" s="1" t="n"/>
@@ -10814,17 +10814,17 @@
       <c r="A540" s="1" t="n"/>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,19 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11633,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11652,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11671,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11690,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11709,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11728,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11747,17 +11745,19 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11766,17 +11766,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11785,17 +11785,17 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11804,17 +11804,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11823,19 +11823,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11844,17 +11842,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11863,19 +11861,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11884,17 +11880,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11903,17 +11899,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11922,17 +11918,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11941,17 +11937,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11960,17 +11956,19 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11979,17 +11977,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11998,17 +11996,19 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지 · 통째로만 팔립니다</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing · sold only as a whole</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12017,17 +12017,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12036,17 +12036,17 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12055,17 +12055,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12074,17 +12074,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12093,17 +12093,17 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12112,17 +12112,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12131,17 +12131,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지 · 통째로만 팔립니다</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>Owned {0} · up to {1} per listing · sold only as a whole</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12150,17 +12150,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12169,17 +12169,17 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E611" s="1" t="n"/>
@@ -12188,17 +12188,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12207,17 +12207,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12226,17 +12226,17 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12245,17 +12245,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12264,17 +12264,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12283,17 +12283,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12302,17 +12302,17 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12321,17 +12321,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12340,17 +12340,17 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12359,17 +12359,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12378,17 +12378,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12397,17 +12397,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12416,19 +12416,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12437,17 +12435,17 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12456,17 +12454,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12475,17 +12473,17 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12494,17 +12492,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12513,17 +12511,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12532,17 +12530,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12551,17 +12549,19 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12570,17 +12570,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12589,17 +12589,17 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12608,17 +12608,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.ChartTitle</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12627,17 +12627,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.ChartEmpty</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>최근 14일 동안 거래가 없습니다</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>No trades in the last 14 days</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12646,17 +12646,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.LevelsTitle</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12665,17 +12665,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.LevelsEmpty</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>지금 판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Nothing on sale right now</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12684,17 +12684,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.RegisterOpen</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>+ 판매 등록</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>+ List Item</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12703,17 +12703,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.ColItem</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12722,19 +12722,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.ColNet</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.
-끼고 있는 장비 · 일하는 캐릭터는 흐리게 보이고, 툴팁에 사유가 나옵니다.</t>
+          <t>팔리면 받는 금액</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.
-Worn gear and working characters are dimmed — the tooltip shows why.</t>
+          <t>You Get If Sold</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12743,17 +12741,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.ColDate</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12762,17 +12760,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.ColType</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12781,20 +12779,155 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
+          <t>UI.Auction.ColAmount</t>
+        </is>
+      </c>
+      <c r="C643" s="6" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="D643" s="6" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E643" s="1" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n"/>
+      <c r="B644" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColDest</t>
+        </is>
+      </c>
+      <c r="C644" s="6" t="inlineStr">
+        <is>
+          <t>받는 곳</t>
+        </is>
+      </c>
+      <c r="D644" s="6" t="inlineStr">
+        <is>
+          <t>Goes To</t>
+        </is>
+      </c>
+      <c r="E644" s="1" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n"/>
+      <c r="B645" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RegisterTitle</t>
+        </is>
+      </c>
+      <c r="C645" s="6" t="inlineStr">
+        <is>
+          <t>판매 등록</t>
+        </is>
+      </c>
+      <c r="D645" s="6" t="inlineStr">
+        <is>
+          <t>List an Item</t>
+        </is>
+      </c>
+      <c r="E645" s="1" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n"/>
+      <c r="B646" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.FindByName</t>
+        </is>
+      </c>
+      <c r="C646" s="6" t="inlineStr">
+        <is>
+          <t>이름으로 찾기</t>
+        </is>
+      </c>
+      <c r="D646" s="6" t="inlineStr">
+        <is>
+          <t>Find by name</t>
+        </is>
+      </c>
+      <c r="E646" s="1" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n"/>
+      <c r="B647" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RegisterEmptyCard</t>
+        </is>
+      </c>
+      <c r="C647" s="6" t="inlineStr">
+        <is>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.
+끼고 있는 장비 · 일하는 캐릭터는 흐리게 보이고, 툴팁에 사유가 나옵니다.</t>
+        </is>
+      </c>
+      <c r="D647" s="6" t="inlineStr">
+        <is>
+          <t>[Select] something to list on the left.
+Worn gear and working characters are dimmed — the tooltip shows why.</t>
+        </is>
+      </c>
+      <c r="E647" s="1" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n"/>
+      <c r="B648" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ShowPrice</t>
+        </is>
+      </c>
+      <c r="C648" s="6" t="inlineStr">
+        <is>
+          <t>시세 보기</t>
+        </is>
+      </c>
+      <c r="D648" s="6" t="inlineStr">
+        <is>
+          <t>View Prices</t>
+        </is>
+      </c>
+      <c r="E648" s="1" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n"/>
+      <c r="B649" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.MatchLowest</t>
+        </is>
+      </c>
+      <c r="C649" s="6" t="inlineStr">
+        <is>
+          <t>최저가에 맞춤</t>
+        </is>
+      </c>
+      <c r="D649" s="6" t="inlineStr">
+        <is>
+          <t>Match Lowest</t>
+        </is>
+      </c>
+      <c r="E649" s="1" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n"/>
+      <c r="B650" s="6" t="inlineStr">
+        <is>
           <t>UI.Auction.Register</t>
         </is>
       </c>
-      <c r="C643" s="6" t="inlineStr">
+      <c r="C650" s="6" t="inlineStr">
         <is>
           <t>등록</t>
         </is>
       </c>
-      <c r="D643" s="6" t="inlineStr">
+      <c r="D650" s="6" t="inlineStr">
         <is>
           <t>List</t>
         </is>
       </c>
-      <c r="E643" s="1" t="n"/>
+      <c r="E650" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E650"/>
+  <dimension ref="A1:E652"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7424,17 +7424,17 @@
       <c r="A362" s="1" t="n"/>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.InstantSell</t>
+          <t>UI.Sell.GrownWarning</t>
         </is>
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매</t>
+          <t>주의! 성장한 개체 {0}개 포함</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>Instant Sell</t>
+          <t>Caution! Includes {0} upgraded</t>
         </is>
       </c>
       <c r="E362" s="1" t="n"/>
@@ -7443,17 +7443,17 @@
       <c r="A363" s="1" t="n"/>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.MarkSell</t>
+          <t>UI.Sell.InstantSell</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
         <is>
-          <t>판</t>
+          <t>즉시 판매</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Instant Sell</t>
         </is>
       </c>
       <c r="E363" s="1" t="n"/>
@@ -7462,17 +7462,17 @@
       <c r="A364" s="1" t="n"/>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.MarkAssign</t>
+          <t>UI.Inventory.MarkSell</t>
         </is>
       </c>
       <c r="C364" s="6" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>판</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E364" s="1" t="n"/>
@@ -7481,17 +7481,17 @@
       <c r="A365" s="1" t="n"/>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.PendingSelect</t>
+          <t>UI.Inventory.MarkAssign</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
-          <t>선택 대기</t>
+          <t>배</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E365" s="1" t="n"/>
@@ -7500,17 +7500,17 @@
       <c r="A366" s="1" t="n"/>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>UI.Common.Waiting</t>
+          <t>UI.Inventory.PendingSelect</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
         <is>
-          <t>응답을 기다리는 중</t>
+          <t>선택 대기</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
-          <t>Waiting for response</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E366" s="1" t="n"/>
@@ -7519,17 +7519,17 @@
       <c r="A367" s="1" t="n"/>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.AlreadyMax</t>
+          <t>UI.Common.Waiting</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
         <is>
-          <t>이미 최고 단계입니다 — 더 넣을 수 없습니다.</t>
+          <t>응답을 기다리는 중</t>
         </is>
       </c>
       <c r="D367" s="6" t="inlineStr">
         <is>
-          <t>Already at the top stage — nothing more can be added.</t>
+          <t>Waiting for response</t>
         </is>
       </c>
       <c r="E367" s="1" t="n"/>
@@ -7538,17 +7538,17 @@
       <c r="A368" s="1" t="n"/>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.BusyMaterial</t>
+          <t>UI.Condense.AlreadyMax</t>
         </is>
       </c>
       <c r="C368" s="6" t="inlineStr">
         <is>
-          <t>배치됐거나 장비를 낀 캐릭터는 재료로 넣을 수 없습니다.</t>
+          <t>이미 최고 단계입니다 — 더 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>Assigned or geared characters can't be used as material.</t>
+          <t>Already at the top stage — nothing more can be added.</t>
         </is>
       </c>
       <c r="E368" s="1" t="n"/>
@@ -7557,17 +7557,17 @@
       <c r="A369" s="1" t="n"/>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.LockedMaterial</t>
+          <t>UI.Condense.BusyMaterial</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
-          <t>잠긴 캐릭터는 재료로 넣을 수 없습니다 — Ctrl+좌클릭으로 풀 수 있습니다.</t>
+          <t>배치됐거나 장비를 낀 캐릭터는 재료로 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>Locked characters can't be used as material — Ctrl+Left-click to unlock.</t>
+          <t>Assigned or geared characters can't be used as material.</t>
         </is>
       </c>
       <c r="E369" s="1" t="n"/>
@@ -7576,17 +7576,17 @@
       <c r="A370" s="1" t="n"/>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Info</t>
+          <t>UI.Condense.LockedMaterial</t>
         </is>
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>응축 누적 {0} / {1}</t>
+          <t>잠긴 캐릭터는 재료로 넣을 수 없습니다 — Ctrl+좌클릭으로 풀 수 있습니다.</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
         <is>
-          <t>Condensed {0} / {1}</t>
+          <t>Locked characters can't be used as material — Ctrl+Left-click to unlock.</t>
         </is>
       </c>
       <c r="E370" s="1" t="n"/>
@@ -7595,17 +7595,17 @@
       <c r="A371" s="1" t="n"/>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Now</t>
+          <t>UI.Condense.Info</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
         <is>
-          <t>지금 {0}성</t>
+          <t>응축 누적 {0} / {1}</t>
         </is>
       </c>
       <c r="D371" s="6" t="inlineStr">
         <is>
-          <t>Now {0}★</t>
+          <t>Condensed {0} / {1}</t>
         </is>
       </c>
       <c r="E371" s="1" t="n"/>
@@ -7614,17 +7614,17 @@
       <c r="A372" s="1" t="n"/>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.After</t>
+          <t>UI.Condense.Now</t>
         </is>
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
-          <t>응축 후 {0}성</t>
+          <t>지금 {0}성</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
-          <t>After {0}★</t>
+          <t>Now {0}★</t>
         </is>
       </c>
       <c r="E372" s="1" t="n"/>
@@ -7633,17 +7633,17 @@
       <c r="A373" s="1" t="n"/>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.TotalPlus</t>
+          <t>UI.Condense.After</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
         <is>
-          <t>누적 {0} + {1} = {2}</t>
+          <t>응축 후 {0}성</t>
         </is>
       </c>
       <c r="D373" s="6" t="inlineStr">
         <is>
-          <t>Total {0} + {1} = {2}</t>
+          <t>After {0}★</t>
         </is>
       </c>
       <c r="E373" s="1" t="n"/>
@@ -7652,17 +7652,17 @@
       <c r="A374" s="1" t="n"/>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Total</t>
+          <t>UI.Condense.TotalPlus</t>
         </is>
       </c>
       <c r="C374" s="6" t="inlineStr">
         <is>
-          <t>누적 {0}</t>
+          <t>누적 {0} + {1} = {2}</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>Total {0}</t>
+          <t>Total {0} + {1} = {2}</t>
         </is>
       </c>
       <c r="E374" s="1" t="n"/>
@@ -7671,17 +7671,17 @@
       <c r="A375" s="1" t="n"/>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.MaxStage</t>
+          <t>UI.Condense.Total</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
-          <t>최고 단계</t>
+          <t>누적 {0}</t>
         </is>
       </c>
       <c r="D375" s="6" t="inlineStr">
         <is>
-          <t>Max Stage</t>
+          <t>Total {0}</t>
         </is>
       </c>
       <c r="E375" s="1" t="n"/>
@@ -7690,17 +7690,17 @@
       <c r="A376" s="1" t="n"/>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Reached</t>
+          <t>UI.Condense.MaxStage</t>
         </is>
       </c>
       <c r="C376" s="6" t="inlineStr">
         <is>
-          <t>{0}성 도달</t>
+          <t>최고 단계</t>
         </is>
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Reaches {0}★</t>
+          <t>Max Stage</t>
         </is>
       </c>
       <c r="E376" s="1" t="n"/>
@@ -7709,17 +7709,17 @@
       <c r="A377" s="1" t="n"/>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ToNext</t>
+          <t>UI.Condense.Reached</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
-          <t>{0}성까지 {1}</t>
+          <t>{0}성 도달</t>
         </is>
       </c>
       <c r="D377" s="6" t="inlineStr">
         <is>
-          <t>{1} to {0}★</t>
+          <t>Reaches {0}★</t>
         </is>
       </c>
       <c r="E377" s="1" t="n"/>
@@ -7728,17 +7728,17 @@
       <c r="A378" s="1" t="n"/>
       <c r="B378" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Overflow</t>
+          <t>UI.Condense.ToNext</t>
         </is>
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
-          <t>넘치는 재료 {0}마리는 효과 없이 사라집니다.</t>
+          <t>{0}성까지 {1}</t>
         </is>
       </c>
       <c r="D378" s="6" t="inlineStr">
         <is>
-          <t>{0} excess material(s) will be lost with no effect.</t>
+          <t>{1} to {0}★</t>
         </is>
       </c>
       <c r="E378" s="1" t="n"/>
@@ -7747,17 +7747,17 @@
       <c r="A379" s="1" t="n"/>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialBusy</t>
+          <t>UI.Condense.Overflow</t>
         </is>
       </c>
       <c r="C379" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다 — {1}마리는 배치·착용 중입니다.</t>
+          <t>넘치는 재료 {0}마리는 효과 없이 사라집니다.</t>
         </is>
       </c>
       <c r="D379" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material — {1} are assigned or geared.</t>
+          <t>{0} excess material(s) will be lost with no effect.</t>
         </is>
       </c>
       <c r="E379" s="1" t="n"/>
@@ -7766,17 +7766,17 @@
       <c r="A380" s="1" t="n"/>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialSame</t>
+          <t>UI.Condense.NoMaterialBusy</t>
         </is>
       </c>
       <c r="C380" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다 — 같은 캐릭터끼리만 응축됩니다.</t>
+          <t>재료로 넣을 {0}이(가) 없습니다 — {1}마리는 배치·착용 중입니다.</t>
         </is>
       </c>
       <c r="D380" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material — only the same character can be condensed.</t>
+          <t>No {0} to use as material — {1} are assigned or geared.</t>
         </is>
       </c>
       <c r="E380" s="1" t="n"/>
@@ -7785,17 +7785,17 @@
       <c r="A381" s="1" t="n"/>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.BusyCount</t>
+          <t>UI.Condense.NoMaterialSame</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
         <is>
-          <t>배치·착용 중인 {0} {1}마리는 재료로 넣을 수 없습니다.</t>
+          <t>재료로 넣을 {0}이(가) 없습니다 — 같은 캐릭터끼리만 응축됩니다.</t>
         </is>
       </c>
       <c r="D381" s="6" t="inlineStr">
         <is>
-          <t>{1} assigned or geared {0} can't be used as material.</t>
+          <t>No {0} to use as material — only the same character can be condensed.</t>
         </is>
       </c>
       <c r="E381" s="1" t="n"/>
@@ -7804,17 +7804,17 @@
       <c r="A382" s="1" t="n"/>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickHint</t>
+          <t>UI.Condense.BusyCount</t>
         </is>
       </c>
       <c r="C382" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터 칸을 눌러 재료로 담으세요.</t>
+          <t>배치·착용 중인 {0} {1}마리는 재료로 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D382" s="6" t="inlineStr">
         <is>
-          <t>Click slots of the same character to add them as material.</t>
+          <t>{1} assigned or geared {0} can't be used as material.</t>
         </is>
       </c>
       <c r="E382" s="1" t="n"/>
@@ -7823,17 +7823,17 @@
       <c r="A383" s="1" t="n"/>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickMaterial</t>
+          <t>UI.Condense.PickHint</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
         <is>
-          <t>재료를 고르세요</t>
+          <t>같은 캐릭터 칸을 눌러 재료로 담으세요.</t>
         </is>
       </c>
       <c r="D383" s="6" t="inlineStr">
         <is>
-          <t>Choose Material</t>
+          <t>Click slots of the same character to add them as material.</t>
         </is>
       </c>
       <c r="E383" s="1" t="n"/>
@@ -7842,17 +7842,17 @@
       <c r="A384" s="1" t="n"/>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Confirm</t>
+          <t>UI.Condense.PickMaterial</t>
         </is>
       </c>
       <c r="C384" s="6" t="inlineStr">
         <is>
-          <t>응축 ({0}마리)</t>
+          <t>재료를 고르세요</t>
         </is>
       </c>
       <c r="D384" s="6" t="inlineStr">
         <is>
-          <t>Condense ({0})</t>
+          <t>Choose Material</t>
         </is>
       </c>
       <c r="E384" s="1" t="n"/>
@@ -7861,19 +7861,17 @@
       <c r="A385" s="1" t="n"/>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialNotice</t>
+          <t>UI.Condense.Confirm</t>
         </is>
       </c>
       <c r="C385" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다.
-같은 캐릭터끼리만 응축됩니다.</t>
+          <t>응축 ({0}마리)</t>
         </is>
       </c>
       <c r="D385" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material.
-Only the same character can be condensed.</t>
+          <t>Condense ({0})</t>
         </is>
       </c>
       <c r="E385" s="1" t="n"/>
@@ -7882,17 +7880,19 @@
       <c r="A386" s="1" t="n"/>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickFirst</t>
+          <t>UI.Condense.NoMaterialNotice</t>
         </is>
       </c>
       <c r="C386" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터 칸을 눌러 재료를 먼저 고르세요.</t>
+          <t>재료로 넣을 {0}이(가) 없습니다.
+같은 캐릭터끼리만 응축됩니다.</t>
         </is>
       </c>
       <c r="D386" s="6" t="inlineStr">
         <is>
-          <t>Click slots of the same character to choose material first.</t>
+          <t>No {0} to use as material.
+Only the same character can be condensed.</t>
         </is>
       </c>
       <c r="E386" s="1" t="n"/>
@@ -7901,17 +7901,17 @@
       <c r="A387" s="1" t="n"/>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmText</t>
+          <t>UI.Condense.PickFirst</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
         <is>
-          <t>재료 {0}마리를 녹여 {1}의 단계를 올립니다.</t>
+          <t>같은 캐릭터 칸을 눌러 재료를 먼저 고르세요.</t>
         </is>
       </c>
       <c r="D387" s="6" t="inlineStr">
         <is>
-          <t>Melt {0} material(s) to raise {1}'s stage.</t>
+          <t>Click slots of the same character to choose material first.</t>
         </is>
       </c>
       <c r="E387" s="1" t="n"/>
@@ -7920,17 +7920,17 @@
       <c r="A388" s="1" t="n"/>
       <c r="B388" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmGrown</t>
+          <t>UI.Condense.ConfirmText</t>
         </is>
       </c>
       <c r="C388" s="6" t="inlineStr">
         <is>
-          <t>Lv{0} 이상 재료 {1}마리의 레벨·경험치는 사라집니다.</t>
+          <t>재료 {0}마리를 녹여 {1}의 단계를 올립니다.</t>
         </is>
       </c>
       <c r="D388" s="6" t="inlineStr">
         <is>
-          <t>Level and EXP of {1} material(s) at Lv{0}+ will be lost.</t>
+          <t>Melt {0} material(s) to raise {1}'s stage.</t>
         </is>
       </c>
       <c r="E388" s="1" t="n"/>
@@ -7939,17 +7939,17 @@
       <c r="A389" s="1" t="n"/>
       <c r="B389" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.FillNext</t>
+          <t>UI.Condense.ConfirmGrown</t>
         </is>
       </c>
       <c r="C389" s="6" t="inlineStr">
         <is>
-          <t>다음 단계까지 채우기</t>
+          <t>Lv{0} 이상 재료 {1}마리의 레벨·경험치는 사라집니다.</t>
         </is>
       </c>
       <c r="D389" s="6" t="inlineStr">
         <is>
-          <t>Fill to Next Stage</t>
+          <t>Level and EXP of {1} material(s) at Lv{0}+ will be lost.</t>
         </is>
       </c>
       <c r="E389" s="1" t="n"/>
@@ -7958,17 +7958,17 @@
       <c r="A390" s="1" t="n"/>
       <c r="B390" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Speed</t>
+          <t>UI.Condense.ConfirmCondensed</t>
         </is>
       </c>
       <c r="C390" s="6" t="inlineStr">
         <is>
-          <t>속도</t>
+          <t>응축을 쌓은 재료 {0}마리의 응축 단계·누적도 사라집니다.</t>
         </is>
       </c>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Condense progress of {0} material(s) will also be lost.</t>
         </is>
       </c>
       <c r="E390" s="1" t="n"/>
@@ -7977,17 +7977,17 @@
       <c r="A391" s="1" t="n"/>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Common</t>
+          <t>UI.Condense.FillNext</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>다음 단계까지 채우기</t>
         </is>
       </c>
       <c r="D391" s="6" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Fill to Next Stage</t>
         </is>
       </c>
       <c r="E391" s="1" t="n"/>
@@ -7996,17 +7996,17 @@
       <c r="A392" s="1" t="n"/>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Condition</t>
+          <t>UI.Trait.Speed</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
         <is>
-          <t>조건</t>
+          <t>속도</t>
         </is>
       </c>
       <c r="D392" s="6" t="inlineStr">
         <is>
-          <t>Requires</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E392" s="1" t="n"/>
@@ -8015,17 +8015,17 @@
       <c r="A393" s="1" t="n"/>
       <c r="B393" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentLevel</t>
+          <t>UI.Trait.Common</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
         <is>
-          <t>(지금 {0})</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D393" s="6" t="inlineStr">
         <is>
-          <t>(now {0})</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E393" s="1" t="n"/>
@@ -8034,17 +8034,17 @@
       <c r="A394" s="1" t="n"/>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.LevelUp</t>
+          <t>UI.Trait.Condition</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
         <is>
-          <t>레벨 올리기 ({0}점)</t>
+          <t>조건</t>
         </is>
       </c>
       <c r="D394" s="6" t="inlineStr">
         <is>
-          <t>Level Up ({0} pt)</t>
+          <t>Requires</t>
         </is>
       </c>
       <c r="E394" s="1" t="n"/>
@@ -8053,17 +8053,17 @@
       <c r="A395" s="1" t="n"/>
       <c r="B395" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentEffect</t>
+          <t>UI.Trait.CurrentLevel</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
         <is>
-          <t>현재 효과</t>
+          <t>(지금 {0})</t>
         </is>
       </c>
       <c r="D395" s="6" t="inlineStr">
         <is>
-          <t>Current Effect</t>
+          <t>(now {0})</t>
         </is>
       </c>
       <c r="E395" s="1" t="n"/>
@@ -8072,17 +8072,17 @@
       <c r="A396" s="1" t="n"/>
       <c r="B396" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NowLevel</t>
+          <t>UI.Trait.LevelUp</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
         <is>
-          <t>지금 (Lv{0})</t>
+          <t>레벨 올리기 ({0}점)</t>
         </is>
       </c>
       <c r="D396" s="6" t="inlineStr">
         <is>
-          <t>Now (Lv{0})</t>
+          <t>Level Up ({0} pt)</t>
         </is>
       </c>
       <c r="E396" s="1" t="n"/>
@@ -8091,17 +8091,17 @@
       <c r="A397" s="1" t="n"/>
       <c r="B397" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NextLevel</t>
+          <t>UI.Trait.CurrentEffect</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
         <is>
-          <t>다음 (Lv{0})</t>
+          <t>현재 효과</t>
         </is>
       </c>
       <c r="D397" s="6" t="inlineStr">
         <is>
-          <t>Next (Lv{0})</t>
+          <t>Current Effect</t>
         </is>
       </c>
       <c r="E397" s="1" t="n"/>
@@ -8110,17 +8110,17 @@
       <c r="A398" s="1" t="n"/>
       <c r="B398" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Points</t>
+          <t>UI.Trait.NowLevel</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
         <is>
-          <t>보유 포인트 {0}</t>
+          <t>지금 (Lv{0})</t>
         </is>
       </c>
       <c r="D398" s="6" t="inlineStr">
         <is>
-          <t>Points {0}</t>
+          <t>Now (Lv{0})</t>
         </is>
       </c>
       <c r="E398" s="1" t="n"/>
@@ -8129,17 +8129,17 @@
       <c r="A399" s="1" t="n"/>
       <c r="B399" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.UpTo</t>
+          <t>UI.Trait.NextLevel</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
         <is>
-          <t>{0}까지</t>
+          <t>다음 (Lv{0})</t>
         </is>
       </c>
       <c r="D399" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Next (Lv{0})</t>
         </is>
       </c>
       <c r="E399" s="1" t="n"/>
@@ -8148,17 +8148,17 @@
       <c r="A400" s="1" t="n"/>
       <c r="B400" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Opens</t>
+          <t>UI.Trait.Points</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
         <is>
-          <t>{0} 열림</t>
+          <t>보유 포인트 {0}</t>
         </is>
       </c>
       <c r="D400" s="6" t="inlineStr">
         <is>
-          <t>Opens {0}</t>
+          <t>Points {0}</t>
         </is>
       </c>
       <c r="E400" s="1" t="n"/>
@@ -8167,17 +8167,17 @@
       <c r="A401" s="1" t="n"/>
       <c r="B401" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescUnlock</t>
+          <t>UI.Trait.UpTo</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
         <is>
-          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
+          <t>{0}까지</t>
         </is>
       </c>
       <c r="D401" s="6" t="inlineStr">
         <is>
-          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
+          <t>Up to {0}</t>
         </is>
       </c>
       <c r="E401" s="1" t="n"/>
@@ -8186,17 +8186,17 @@
       <c r="A402" s="1" t="n"/>
       <c r="B402" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescSpeed</t>
+          <t>UI.Trait.Opens</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
         <is>
-          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
+          <t>{0} 열림</t>
         </is>
       </c>
       <c r="D402" s="6" t="inlineStr">
         <is>
-          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
+          <t>Opens {0}</t>
         </is>
       </c>
       <c r="E402" s="1" t="n"/>
@@ -8205,17 +8205,17 @@
       <c r="A403" s="1" t="n"/>
       <c r="B403" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYield</t>
+          <t>UI.Trait.DescUnlock</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>판정 1회에 같은 자원이 더 나옵니다 (120%면 1개 + 20% 확률로 1개 더). 좋은 자원이 나올 확률은 그대로이고, 상자 · 경험치는 늘지 않습니다.</t>
+          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
         </is>
       </c>
       <c r="D403" s="6" t="inlineStr">
         <is>
-          <t>Each roll yields more of the same resource (120% = 1 plus a 20% chance of 1 more). The odds of better resources stay the same, and boxes and EXP don't increase.</t>
+          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
         </is>
       </c>
       <c r="E403" s="1" t="n"/>
@@ -8224,17 +8224,17 @@
       <c r="A404" s="1" t="n"/>
       <c r="B404" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYieldAll</t>
+          <t>UI.Trait.DescSpeed</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
         <is>
-          <t>모든 산업에 붙습니다.</t>
+          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
         </is>
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>Applies to all industries.</t>
+          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
         </is>
       </c>
       <c r="E404" s="1" t="n"/>
@@ -8243,17 +8243,17 @@
       <c r="A405" s="1" t="n"/>
       <c r="B405" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.AlreadyMax</t>
+          <t>UI.Trait.DescYield</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
         <is>
-          <t>이미 최대 레벨입니다.</t>
+          <t>판정 1회에 같은 자원이 더 나옵니다 (120%면 1개 + 20% 확률로 1개 더). 좋은 자원이 나올 확률은 그대로이고, 상자 · 경험치는 늘지 않습니다.</t>
         </is>
       </c>
       <c r="D405" s="6" t="inlineStr">
         <is>
-          <t>Already at max level.</t>
+          <t>Each roll yields more of the same resource (120% = 1 plus a 20% chance of 1 more). The odds of better resources stay the same, and boxes and EXP don't increase.</t>
         </is>
       </c>
       <c r="E405" s="1" t="n"/>
@@ -8262,17 +8262,17 @@
       <c r="A406" s="1" t="n"/>
       <c r="B406" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NotEnoughPoints</t>
+          <t>UI.Trait.DescYieldAll</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
+          <t>모든 산업에 붙습니다.</t>
         </is>
       </c>
       <c r="D406" s="6" t="inlineStr">
         <is>
-          <t>Not enough trait points. ({0} pt required)</t>
+          <t>Applies to all industries.</t>
         </is>
       </c>
       <c r="E406" s="1" t="n"/>
@@ -8281,19 +8281,17 @@
       <c r="A407" s="1" t="n"/>
       <c r="B407" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.ConfirmLearn</t>
+          <t>UI.Trait.AlreadyMax</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트 {0}점을 사용합니다.
-'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
+          <t>이미 최대 레벨입니다.</t>
         </is>
       </c>
       <c r="D407" s="6" t="inlineStr">
         <is>
-          <t>This uses {0} trait point(s).
-Raise '{1}' to Lv{2}?</t>
+          <t>Already at max level.</t>
         </is>
       </c>
       <c r="E407" s="1" t="n"/>
@@ -8302,17 +8300,17 @@
       <c r="A408" s="1" t="n"/>
       <c r="B408" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.WaitLearn</t>
+          <t>UI.Trait.NotEnoughPoints</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
         <is>
-          <t>특성 레벨 올리기</t>
+          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
         </is>
       </c>
       <c r="D408" s="6" t="inlineStr">
         <is>
-          <t>Level Up Trait</t>
+          <t>Not enough trait points. ({0} pt required)</t>
         </is>
       </c>
       <c r="E408" s="1" t="n"/>
@@ -8321,17 +8319,19 @@
       <c r="A409" s="1" t="n"/>
       <c r="B409" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.EmptyDetail</t>
+          <t>UI.Trait.ConfirmLearn</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
         <is>
-          <t>특성을 누르면 여기에 펼쳐집니다</t>
+          <t>특성 포인트 {0}점을 사용합니다.
+'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
         </is>
       </c>
       <c r="D409" s="6" t="inlineStr">
         <is>
-          <t>Click a trait to see details here</t>
+          <t>This uses {0} trait point(s).
+Raise '{1}' to Lv{2}?</t>
         </is>
       </c>
       <c r="E409" s="1" t="n"/>
@@ -8340,17 +8340,17 @@
       <c r="A410" s="1" t="n"/>
       <c r="B410" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Base</t>
+          <t>UI.Trait.WaitLearn</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
         <is>
-          <t>기본 {0}</t>
+          <t>특성 레벨 올리기</t>
         </is>
       </c>
       <c r="D410" s="6" t="inlineStr">
         <is>
-          <t>Base {0}</t>
+          <t>Level Up Trait</t>
         </is>
       </c>
       <c r="E410" s="1" t="n"/>
@@ -8359,17 +8359,17 @@
       <c r="A411" s="1" t="n"/>
       <c r="B411" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.StatSlotCount</t>
+          <t>UI.Trait.EmptyDetail</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
         <is>
-          <t>능력치 칸 {0}개</t>
+          <t>특성을 누르면 여기에 펼쳐집니다</t>
         </is>
       </c>
       <c r="D411" s="6" t="inlineStr">
         <is>
-          <t>{0} stat slots</t>
+          <t>Click a trait to see details here</t>
         </is>
       </c>
       <c r="E411" s="1" t="n"/>
@@ -8378,17 +8378,17 @@
       <c r="A412" s="1" t="n"/>
       <c r="B412" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.GradeUp</t>
+          <t>UI.Enchant.Base</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
         <is>
-          <t>등급 상승!</t>
+          <t>기본 {0}</t>
         </is>
       </c>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>Grade Up!</t>
+          <t>Base {0}</t>
         </is>
       </c>
       <c r="E412" s="1" t="n"/>
@@ -8397,17 +8397,17 @@
       <c r="A413" s="1" t="n"/>
       <c r="B413" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CapAll</t>
+          <t>UI.Enchant.StatSlotCount</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
         <is>
-          <t>보유 전부</t>
+          <t>능력치 칸 {0}개</t>
         </is>
       </c>
       <c r="D413" s="6" t="inlineStr">
         <is>
-          <t>All Owned</t>
+          <t>{0} stat slots</t>
         </is>
       </c>
       <c r="E413" s="1" t="n"/>
@@ -8416,17 +8416,17 @@
       <c r="A414" s="1" t="n"/>
       <c r="B414" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.All</t>
+          <t>UI.Enchant.GradeUp</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>등급 상승!</t>
         </is>
       </c>
       <c r="D414" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Grade Up!</t>
         </is>
       </c>
       <c r="E414" s="1" t="n"/>
@@ -8435,17 +8435,17 @@
       <c r="A415" s="1" t="n"/>
       <c r="B415" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.EveryCombo</t>
+          <t>UI.Enchant.CapAll</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
         <is>
-          <t>칸마다 전체 또는 {0}</t>
+          <t>보유 전부</t>
         </is>
       </c>
       <c r="D415" s="6" t="inlineStr">
         <is>
-          <t>Each slot: All or {0}</t>
+          <t>All Owned</t>
         </is>
       </c>
       <c r="E415" s="1" t="n"/>
@@ -8454,17 +8454,17 @@
       <c r="A416" s="1" t="n"/>
       <c r="B416" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCombo</t>
+          <t>UI.Enchant.All</t>
         </is>
       </c>
       <c r="C416" s="6" t="inlineStr">
         <is>
-          <t>칸 조합 없음</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D416" s="6" t="inlineStr">
         <is>
-          <t>No slot combos</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E416" s="1" t="n"/>
@@ -8473,17 +8473,17 @@
       <c r="A417" s="1" t="n"/>
       <c r="B417" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combos</t>
+          <t>UI.Enchant.EveryCombo</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
         <is>
-          <t>칸 {0}</t>
+          <t>칸마다 전체 또는 {0}</t>
         </is>
       </c>
       <c r="D417" s="6" t="inlineStr">
         <is>
-          <t>Slots {0}</t>
+          <t>Each slot: All or {0}</t>
         </is>
       </c>
       <c r="E417" s="1" t="n"/>
@@ -8492,19 +8492,17 @@
       <c r="A418" s="1" t="n"/>
       <c r="B418" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NotChosen</t>
+          <t>UI.Enchant.NoCombo</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
         <is>
-          <t>아직 선택하지 않았습니다.
-BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>칸 조합 없음</t>
         </is>
       </c>
       <c r="D418" s="6" t="inlineStr">
         <is>
-          <t>You haven't chosen yet.
-Pick either BEFORE or AFTER.</t>
+          <t>No slot combos</t>
         </is>
       </c>
       <c r="E418" s="1" t="n"/>
@@ -8513,17 +8511,17 @@
       <c r="A419" s="1" t="n"/>
       <c r="B419" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WornBy</t>
+          <t>UI.Enchant.Combos</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>{0} 착용 중</t>
+          <t>칸 {0}</t>
         </is>
       </c>
       <c r="D419" s="6" t="inlineStr">
         <is>
-          <t>Worn by {0}</t>
+          <t>Slots {0}</t>
         </is>
       </c>
       <c r="E419" s="1" t="n"/>
@@ -8532,17 +8530,19 @@
       <c r="A420" s="1" t="n"/>
       <c r="B420" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ResultHere</t>
+          <t>UI.Enchant.NotChosen</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
         <is>
-          <t>결과가 여기에 나옵니다</t>
+          <t>아직 선택하지 않았습니다.
+BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D420" s="6" t="inlineStr">
         <is>
-          <t>The result appears here</t>
+          <t>You haven't chosen yet.
+Pick either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E420" s="1" t="n"/>
@@ -8551,17 +8551,17 @@
       <c r="A421" s="1" t="n"/>
       <c r="B421" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoEnchant</t>
+          <t>UI.Enchant.WornBy</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
         <is>
-          <t>인챈트 없음</t>
+          <t>{0} 착용 중</t>
         </is>
       </c>
       <c r="D421" s="6" t="inlineStr">
         <is>
-          <t>No Enchant</t>
+          <t>Worn by {0}</t>
         </is>
       </c>
       <c r="E421" s="1" t="n"/>
@@ -8570,17 +8570,17 @@
       <c r="A422" s="1" t="n"/>
       <c r="B422" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PickOne</t>
+          <t>UI.Enchant.ResultHere</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
         <is>
-          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
+          <t>결과가 여기에 나옵니다</t>
         </is>
       </c>
       <c r="D422" s="6" t="inlineStr">
         <is>
-          <t>[Select] either BEFORE or AFTER.</t>
+          <t>The result appears here</t>
         </is>
       </c>
       <c r="E422" s="1" t="n"/>
@@ -8589,17 +8589,17 @@
       <c r="A423" s="1" t="n"/>
       <c r="B423" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RerollKeepsBefore</t>
+          <t>UI.Enchant.NoEnchant</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
         <is>
-          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
+          <t>인챈트 없음</t>
         </is>
       </c>
       <c r="D423" s="6" t="inlineStr">
         <is>
-          <t>Using it again without choosing keeps BEFORE.</t>
+          <t>No Enchant</t>
         </is>
       </c>
       <c r="E423" s="1" t="n"/>
@@ -8608,17 +8608,17 @@
       <c r="A424" s="1" t="n"/>
       <c r="B424" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleFirst</t>
+          <t>UI.Enchant.PickOne</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
+          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
         <is>
-          <t>First use fills {1} slot(s) at {0} grade.</t>
+          <t>[Select] either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E424" s="1" t="n"/>
@@ -8627,17 +8627,17 @@
       <c r="A425" s="1" t="n"/>
       <c r="B425" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleMythic</t>
+          <t>UI.Enchant.RerollKeepsBefore</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
         <is>
-          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
+          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
         </is>
       </c>
       <c r="D425" s="6" t="inlineStr">
         <is>
-          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
+          <t>Using it again without choosing keeps BEFORE.</t>
         </is>
       </c>
       <c r="E425" s="1" t="n"/>
@@ -8646,17 +8646,17 @@
       <c r="A426" s="1" t="n"/>
       <c r="B426" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleNormal</t>
+          <t>UI.Enchant.RuleFirst</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
         <is>
-          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
+          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
         </is>
       </c>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
+          <t>First use fills {1} slot(s) at {0} grade.</t>
         </is>
       </c>
       <c r="E426" s="1" t="n"/>
@@ -8665,17 +8665,17 @@
       <c r="A427" s="1" t="n"/>
       <c r="B427" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleKeep</t>
+          <t>UI.Enchant.RuleMythic</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
         <is>
-          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
+          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
         </is>
       </c>
       <c r="D427" s="6" t="inlineStr">
         <is>
-          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
+          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
         </is>
       </c>
       <c r="E427" s="1" t="n"/>
@@ -8684,17 +8684,17 @@
       <c r="A428" s="1" t="n"/>
       <c r="B428" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeFirst</t>
+          <t>UI.Enchant.RuleNormal</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
         <is>
-          <t>첫 사용 · 일반 확정</t>
+          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
         </is>
       </c>
       <c r="D428" s="6" t="inlineStr">
         <is>
-          <t>First use · Common guaranteed</t>
+          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
         </is>
       </c>
       <c r="E428" s="1" t="n"/>
@@ -8703,17 +8703,17 @@
       <c r="A429" s="1" t="n"/>
       <c r="B429" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOptionsOnly</t>
+          <t>UI.Enchant.RuleKeep</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
         <is>
-          <t>옵션만 다시 뽑기</t>
+          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
         </is>
       </c>
       <c r="D429" s="6" t="inlineStr">
         <is>
-          <t>Options reroll only</t>
+          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
         </is>
       </c>
       <c r="E429" s="1" t="n"/>
@@ -8722,17 +8722,17 @@
       <c r="A430" s="1" t="n"/>
       <c r="B430" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeUp</t>
+          <t>UI.Enchant.CubeFirst</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
         <is>
-          <t>{0} 상승 {1}</t>
+          <t>첫 사용 · 일반 확정</t>
         </is>
       </c>
       <c r="D430" s="6" t="inlineStr">
         <is>
-          <t>{0} up {1}</t>
+          <t>First use · Common guaranteed</t>
         </is>
       </c>
       <c r="E430" s="1" t="n"/>
@@ -8741,17 +8741,17 @@
       <c r="A431" s="1" t="n"/>
       <c r="B431" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOwned</t>
+          <t>UI.Enchant.CubeOptionsOnly</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개</t>
+          <t>옵션만 다시 뽑기</t>
         </is>
       </c>
       <c r="D431" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>Options reroll only</t>
         </is>
       </c>
       <c r="E431" s="1" t="n"/>
@@ -8760,17 +8760,17 @@
       <c r="A432" s="1" t="n"/>
       <c r="B432" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeData</t>
+          <t>UI.Enchant.CubeUp</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
         <is>
-          <t>큐브 정보가 없습니다</t>
+          <t>{0} 상승 {1}</t>
         </is>
       </c>
       <c r="D432" s="6" t="inlineStr">
         <is>
-          <t>No cube data</t>
+          <t>{0} up {1}</t>
         </is>
       </c>
       <c r="E432" s="1" t="n"/>
@@ -8779,17 +8779,17 @@
       <c r="A433" s="1" t="n"/>
       <c r="B433" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UseCube</t>
+          <t>UI.Enchant.CubeOwned</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
         <is>
-          <t>{0} 사용</t>
+          <t>보유 {0}개</t>
         </is>
       </c>
       <c r="D433" s="6" t="inlineStr">
         <is>
-          <t>Use {0}</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E433" s="1" t="n"/>
@@ -8798,17 +8798,17 @@
       <c r="A434" s="1" t="n"/>
       <c r="B434" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCube</t>
+          <t>UI.Enchant.NoCubeData</t>
         </is>
       </c>
       <c r="C434" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다</t>
+          <t>큐브 정보가 없습니다</t>
         </is>
       </c>
       <c r="D434" s="6" t="inlineStr">
         <is>
-          <t>No {0}</t>
+          <t>No cube data</t>
         </is>
       </c>
       <c r="E434" s="1" t="n"/>
@@ -8817,17 +8817,17 @@
       <c r="A435" s="1" t="n"/>
       <c r="B435" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnequipAndUse</t>
+          <t>UI.Enchant.UseCube</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
         <is>
-          <t>해제하고 {0} 사용</t>
+          <t>{0} 사용</t>
         </is>
       </c>
       <c r="D435" s="6" t="inlineStr">
         <is>
-          <t>Unequip and Use {0}</t>
+          <t>Use {0}</t>
         </is>
       </c>
       <c r="E435" s="1" t="n"/>
@@ -8836,17 +8836,17 @@
       <c r="A436" s="1" t="n"/>
       <c r="B436" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeNotice</t>
+          <t>UI.Enchant.NoCube</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다.</t>
+          <t>{0}가 없습니다</t>
         </is>
       </c>
       <c r="D436" s="6" t="inlineStr">
         <is>
-          <t>You have no {0}.</t>
+          <t>No {0}</t>
         </is>
       </c>
       <c r="E436" s="1" t="n"/>
@@ -8855,19 +8855,17 @@
       <c r="A437" s="1" t="n"/>
       <c r="B437" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ConfirmUnequip</t>
+          <t>UI.Enchant.UnequipAndUse</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
         <is>
-          <t>{0}이(가) 끼고 있는 장비입니다.
-해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
+          <t>해제하고 {0} 사용</t>
         </is>
       </c>
       <c r="D437" s="6" t="inlineStr">
         <is>
-          <t>{0} is wearing this gear.
-It will be unequipped before using the cube. (It won't be re-equipped.)</t>
+          <t>Unequip and Use {0}</t>
         </is>
       </c>
       <c r="E437" s="1" t="n"/>
@@ -8876,17 +8874,17 @@
       <c r="A438" s="1" t="n"/>
       <c r="B438" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitUse</t>
+          <t>UI.Enchant.NoCubeNotice</t>
         </is>
       </c>
       <c r="C438" s="6" t="inlineStr">
         <is>
-          <t>큐브 사용</t>
+          <t>{0}가 없습니다.</t>
         </is>
       </c>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>Use Cube</t>
+          <t>You have no {0}.</t>
         </is>
       </c>
       <c r="E438" s="1" t="n"/>
@@ -8895,17 +8893,19 @@
       <c r="A439" s="1" t="n"/>
       <c r="B439" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitChoose</t>
+          <t>UI.Enchant.ConfirmUnequip</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
         <is>
-          <t>큐브 결과 고르기</t>
+          <t>{0}이(가) 끼고 있는 장비입니다.
+해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
         </is>
       </c>
       <c r="D439" s="6" t="inlineStr">
         <is>
-          <t>Choose Cube Result</t>
+          <t>{0} is wearing this gear.
+It will be unequipped before using the cube. (It won't be re-equipped.)</t>
         </is>
       </c>
       <c r="E439" s="1" t="n"/>
@@ -8914,17 +8914,17 @@
       <c r="A440" s="1" t="n"/>
       <c r="B440" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ChooseFirst</t>
+          <t>UI.Enchant.WaitUse</t>
         </is>
       </c>
       <c r="C440" s="6" t="inlineStr">
         <is>
-          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>큐브 사용</t>
         </is>
       </c>
       <c r="D440" s="6" t="inlineStr">
         <is>
-          <t>Pick BEFORE or AFTER first.</t>
+          <t>Use Cube</t>
         </is>
       </c>
       <c r="E440" s="1" t="n"/>
@@ -8933,17 +8933,17 @@
       <c r="A441" s="1" t="n"/>
       <c r="B441" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoAutoWorn</t>
+          <t>UI.Enchant.WaitChoose</t>
         </is>
       </c>
       <c r="C441" s="6" t="inlineStr">
         <is>
-          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
+          <t>큐브 결과 고르기</t>
         </is>
       </c>
       <c r="D441" s="6" t="inlineStr">
         <is>
-          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
+          <t>Choose Cube Result</t>
         </is>
       </c>
       <c r="E441" s="1" t="n"/>
@@ -8952,17 +8952,17 @@
       <c r="A442" s="1" t="n"/>
       <c r="B442" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStart</t>
+          <t>UI.Enchant.ChooseFirst</t>
         </is>
       </c>
       <c r="C442" s="6" t="inlineStr">
         <is>
-          <t>자동 시작 ▶</t>
+          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D442" s="6" t="inlineStr">
         <is>
-          <t>Start Auto ▶</t>
+          <t>Pick BEFORE or AFTER first.</t>
         </is>
       </c>
       <c r="E442" s="1" t="n"/>
@@ -8971,17 +8971,17 @@
       <c r="A443" s="1" t="n"/>
       <c r="B443" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AlreadyMythic</t>
+          <t>UI.Enchant.NoAutoWorn</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
         <is>
-          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
+          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
         </is>
       </c>
       <c r="D443" s="6" t="inlineStr">
         <is>
-          <t>Already Mythic. Pick an option to aim for.</t>
+          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
         </is>
       </c>
       <c r="E443" s="1" t="n"/>
@@ -8990,17 +8990,17 @@
       <c r="A444" s="1" t="n"/>
       <c r="B444" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NeedCombo</t>
+          <t>UI.Enchant.AutoStart</t>
         </is>
       </c>
       <c r="C444" s="6" t="inlineStr">
         <is>
-          <t>조합을 하나 이상 켜 주세요.</t>
+          <t>자동 시작 ▶</t>
         </is>
       </c>
       <c r="D444" s="6" t="inlineStr">
         <is>
-          <t>Turn on at least one combo.</t>
+          <t>Start Auto ▶</t>
         </is>
       </c>
       <c r="E444" s="1" t="n"/>
@@ -9009,17 +9009,17 @@
       <c r="A445" s="1" t="n"/>
       <c r="B445" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.MeanCount</t>
+          <t>UI.Enchant.AlreadyMythic</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
         <is>
-          <t>{0}개 (약 {1})</t>
+          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
         </is>
       </c>
       <c r="D445" s="6" t="inlineStr">
         <is>
-          <t>{0} (about {1})</t>
+          <t>Already Mythic. Pick an option to aim for.</t>
         </is>
       </c>
       <c r="E445" s="1" t="n"/>
@@ -9028,17 +9028,17 @@
       <c r="A446" s="1" t="n"/>
       <c r="B446" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Within</t>
+          <t>UI.Enchant.NeedCombo</t>
         </is>
       </c>
       <c r="C446" s="6" t="inlineStr">
         <is>
-          <t>{0}개 안에 {1}</t>
+          <t>조합을 하나 이상 켜 주세요.</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
         <is>
-          <t>{1} within {0}</t>
+          <t>Turn on at least one combo.</t>
         </is>
       </c>
       <c r="E446" s="1" t="n"/>
@@ -9047,17 +9047,17 @@
       <c r="A447" s="1" t="n"/>
       <c r="B447" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Mean</t>
+          <t>UI.Enchant.MeanCount</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
         <is>
-          <t>평균 {0}</t>
+          <t>{0}개 (약 {1})</t>
         </is>
       </c>
       <c r="D447" s="6" t="inlineStr">
         <is>
-          <t>avg {0}</t>
+          <t>{0} (about {1})</t>
         </is>
       </c>
       <c r="E447" s="1" t="n"/>
@@ -9066,17 +9066,17 @@
       <c r="A448" s="1" t="n"/>
       <c r="B448" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnderMin</t>
+          <t>UI.Enchant.Within</t>
         </is>
       </c>
       <c r="C448" s="6" t="inlineStr">
         <is>
-          <t>0.01% 미만</t>
+          <t>{0}개 안에 {1}</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
         <is>
-          <t>under 0.01%</t>
+          <t>{1} within {0}</t>
         </is>
       </c>
       <c r="E448" s="1" t="n"/>
@@ -9085,17 +9085,17 @@
       <c r="A449" s="1" t="n"/>
       <c r="B449" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Minutes</t>
+          <t>UI.Enchant.Mean</t>
         </is>
       </c>
       <c r="C449" s="6" t="inlineStr">
         <is>
-          <t>{0}분</t>
+          <t>평균 {0}</t>
         </is>
       </c>
       <c r="D449" s="6" t="inlineStr">
         <is>
-          <t>{0}m</t>
+          <t>avg {0}</t>
         </is>
       </c>
       <c r="E449" s="1" t="n"/>
@@ -9104,17 +9104,17 @@
       <c r="A450" s="1" t="n"/>
       <c r="B450" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Hours</t>
+          <t>UI.Enchant.UnderMin</t>
         </is>
       </c>
       <c r="C450" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>0.01% 미만</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>under 0.01%</t>
         </is>
       </c>
       <c r="E450" s="1" t="n"/>
@@ -9123,17 +9123,17 @@
       <c r="A451" s="1" t="n"/>
       <c r="B451" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoRunning</t>
+          <t>UI.Enchant.Minutes</t>
         </is>
       </c>
       <c r="C451" s="6" t="inlineStr">
         <is>
-          <t>자동 진행 중 {0} / {1}개</t>
+          <t>{0}분</t>
         </is>
       </c>
       <c r="D451" s="6" t="inlineStr">
         <is>
-          <t>Auto running {0} / {1}</t>
+          <t>{0}m</t>
         </is>
       </c>
       <c r="E451" s="1" t="n"/>
@@ -9142,17 +9142,17 @@
       <c r="A452" s="1" t="n"/>
       <c r="B452" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Goal</t>
+          <t>UI.Enchant.Hours</t>
         </is>
       </c>
       <c r="C452" s="6" t="inlineStr">
         <is>
-          <t>목표 {0} 이상</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D452" s="6" t="inlineStr">
         <is>
-          <t>Goal: {0} or higher</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E452" s="1" t="n"/>
@@ -9161,17 +9161,17 @@
       <c r="A453" s="1" t="n"/>
       <c r="B453" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoSlotRule</t>
+          <t>UI.Enchant.AutoRunning</t>
         </is>
       </c>
       <c r="C453" s="6" t="inlineStr">
         <is>
-          <t>칸 조건 없음 — 등급만 봅니다</t>
+          <t>자동 진행 중 {0} / {1}개</t>
         </is>
       </c>
       <c r="D453" s="6" t="inlineStr">
         <is>
-          <t>No slot condition — grade only</t>
+          <t>Auto running {0} / {1}</t>
         </is>
       </c>
       <c r="E453" s="1" t="n"/>
@@ -9180,17 +9180,17 @@
       <c r="A454" s="1" t="n"/>
       <c r="B454" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PerRoll</t>
+          <t>UI.Enchant.Goal</t>
         </is>
       </c>
       <c r="C454" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}</t>
+          <t>목표 {0} 이상</t>
         </is>
       </c>
       <c r="D454" s="6" t="inlineStr">
         <is>
-          <t>{0} per roll</t>
+          <t>Goal: {0} or higher</t>
         </is>
       </c>
       <c r="E454" s="1" t="n"/>
@@ -9199,17 +9199,17 @@
       <c r="A455" s="1" t="n"/>
       <c r="B455" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStop</t>
+          <t>UI.Enchant.NoSlotRule</t>
         </is>
       </c>
       <c r="C455" s="6" t="inlineStr">
         <is>
-          <t>■ 멈춤</t>
+          <t>칸 조건 없음 — 등급만 봅니다</t>
         </is>
       </c>
       <c r="D455" s="6" t="inlineStr">
         <is>
-          <t>■ Stop</t>
+          <t>No slot condition — grade only</t>
         </is>
       </c>
       <c r="E455" s="1" t="n"/>
@@ -9218,17 +9218,17 @@
       <c r="A456" s="1" t="n"/>
       <c r="B456" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Auto</t>
+          <t>UI.Enchant.PerRoll</t>
         </is>
       </c>
       <c r="C456" s="6" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>한 번에 {0}</t>
         </is>
       </c>
       <c r="D456" s="6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>{0} per roll</t>
         </is>
       </c>
       <c r="E456" s="1" t="n"/>
@@ -9237,17 +9237,17 @@
       <c r="A457" s="1" t="n"/>
       <c r="B457" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndStopped</t>
+          <t>UI.Enchant.AutoStop</t>
         </is>
       </c>
       <c r="C457" s="6" t="inlineStr">
         <is>
-          <t>자동을 멈췄습니다</t>
+          <t>■ 멈춤</t>
         </is>
       </c>
       <c r="D457" s="6" t="inlineStr">
         <is>
-          <t>Auto stopped</t>
+          <t>■ Stop</t>
         </is>
       </c>
       <c r="E457" s="1" t="n"/>
@@ -9256,17 +9256,17 @@
       <c r="A458" s="1" t="n"/>
       <c r="B458" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndCap</t>
+          <t>UI.Enchant.Auto</t>
         </is>
       </c>
       <c r="C458" s="6" t="inlineStr">
         <is>
-          <t>상한에 닿아 멈췄습니다</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="D458" s="6" t="inlineStr">
         <is>
-          <t>Stopped at the limit</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E458" s="1" t="n"/>
@@ -9275,17 +9275,17 @@
       <c r="A459" s="1" t="n"/>
       <c r="B459" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndNoCube</t>
+          <t>UI.Enchant.AutoEndStopped</t>
         </is>
       </c>
       <c r="C459" s="6" t="inlineStr">
         <is>
-          <t>큐브가 떨어져 멈췄습니다</t>
+          <t>자동을 멈췄습니다</t>
         </is>
       </c>
       <c r="D459" s="6" t="inlineStr">
         <is>
-          <t>Stopped — out of cubes</t>
+          <t>Auto stopped</t>
         </is>
       </c>
       <c r="E459" s="1" t="n"/>
@@ -9294,17 +9294,17 @@
       <c r="A460" s="1" t="n"/>
       <c r="B460" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndRejected</t>
+          <t>UI.Enchant.AutoEndCap</t>
         </is>
       </c>
       <c r="C460" s="6" t="inlineStr">
         <is>
-          <t>서버가 거절해 멈췄습니다</t>
+          <t>상한에 닿아 멈췄습니다</t>
         </is>
       </c>
       <c r="D460" s="6" t="inlineStr">
         <is>
-          <t>Stopped — server rejected</t>
+          <t>Stopped at the limit</t>
         </is>
       </c>
       <c r="E460" s="1" t="n"/>
@@ -9313,17 +9313,17 @@
       <c r="A461" s="1" t="n"/>
       <c r="B461" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndGoal</t>
+          <t>UI.Enchant.AutoEndNoCube</t>
         </is>
       </c>
       <c r="C461" s="6" t="inlineStr">
         <is>
-          <t>목표 달성!</t>
+          <t>큐브가 떨어져 멈췄습니다</t>
         </is>
       </c>
       <c r="D461" s="6" t="inlineStr">
         <is>
-          <t>Goal reached!</t>
+          <t>Stopped — out of cubes</t>
         </is>
       </c>
       <c r="E461" s="1" t="n"/>
@@ -9332,17 +9332,17 @@
       <c r="A462" s="1" t="n"/>
       <c r="B462" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndSummary</t>
+          <t>UI.Enchant.AutoEndRejected</t>
         </is>
       </c>
       <c r="C462" s="6" t="inlineStr">
         <is>
-          <t>{0} — {1} {2}개 사용.</t>
+          <t>서버가 거절해 멈췄습니다</t>
         </is>
       </c>
       <c r="D462" s="6" t="inlineStr">
         <is>
-          <t>{0} — used {2} {1}.</t>
+          <t>Stopped — server rejected</t>
         </is>
       </c>
       <c r="E462" s="1" t="n"/>
@@ -9351,17 +9351,17 @@
       <c r="A463" s="1" t="n"/>
       <c r="B463" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.TargetGrade</t>
+          <t>UI.Enchant.AutoEndGoal</t>
         </is>
       </c>
       <c r="C463" s="6" t="inlineStr">
         <is>
-          <t>목표 등급</t>
+          <t>목표 달성!</t>
         </is>
       </c>
       <c r="D463" s="6" t="inlineStr">
         <is>
-          <t>Target Grade</t>
+          <t>Goal reached!</t>
         </is>
       </c>
       <c r="E463" s="1" t="n"/>
@@ -9370,17 +9370,17 @@
       <c r="A464" s="1" t="n"/>
       <c r="B464" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.FocusOption</t>
+          <t>UI.Enchant.AutoEndSummary</t>
         </is>
       </c>
       <c r="C464" s="6" t="inlineStr">
         <is>
-          <t>노릴 옵션</t>
+          <t>{0} — {1} {2}개 사용.</t>
         </is>
       </c>
       <c r="D464" s="6" t="inlineStr">
         <is>
-          <t>Aim For</t>
+          <t>{0} — used {2} {1}.</t>
         </is>
       </c>
       <c r="E464" s="1" t="n"/>
@@ -9389,17 +9389,17 @@
       <c r="A465" s="1" t="n"/>
       <c r="B465" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combo</t>
+          <t>UI.Enchant.TargetGrade</t>
         </is>
       </c>
       <c r="C465" s="6" t="inlineStr">
         <is>
-          <t>조합</t>
+          <t>목표 등급</t>
         </is>
       </c>
       <c r="D465" s="6" t="inlineStr">
         <is>
-          <t>Combo</t>
+          <t>Target Grade</t>
         </is>
       </c>
       <c r="E465" s="1" t="n"/>
@@ -9408,17 +9408,17 @@
       <c r="A466" s="1" t="n"/>
       <c r="B466" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Cap</t>
+          <t>UI.Enchant.FocusOption</t>
         </is>
       </c>
       <c r="C466" s="6" t="inlineStr">
         <is>
-          <t>상한</t>
+          <t>노릴 옵션</t>
         </is>
       </c>
       <c r="D466" s="6" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>Aim For</t>
         </is>
       </c>
       <c r="E466" s="1" t="n"/>
@@ -9427,17 +9427,17 @@
       <c r="A467" s="1" t="n"/>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Select</t>
+          <t>UI.Enchant.Combo</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>조합</t>
         </is>
       </c>
       <c r="D467" s="6" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="E467" s="1" t="n"/>
@@ -9446,17 +9446,17 @@
       <c r="A468" s="1" t="n"/>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Times</t>
+          <t>UI.Enchant.Cap</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>{0}회</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
         <is>
-          <t>x{0}</t>
+          <t>Limit</t>
         </is>
       </c>
       <c r="E468" s="1" t="n"/>
@@ -9465,17 +9465,17 @@
       <c r="A469" s="1" t="n"/>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Worker</t>
+          <t>UI.Enchant.Select</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
         <is>
-          <t>일꾼</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="D469" s="6" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E469" s="1" t="n"/>
@@ -9484,17 +9484,17 @@
       <c r="A470" s="1" t="n"/>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.WorkSpeedUp</t>
+          <t>UI.Gacha.Times</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
         <is>
-          <t>작업속도 증가</t>
+          <t>{0}회</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
         <is>
-          <t>Work Speed Up</t>
+          <t>x{0}</t>
         </is>
       </c>
       <c r="E470" s="1" t="n"/>
@@ -9503,17 +9503,17 @@
       <c r="A471" s="1" t="n"/>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Kinds</t>
+          <t>UI.Gacha.Worker</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}종</t>
+          <t>일꾼</t>
         </is>
       </c>
       <c r="D471" s="6" t="inlineStr">
         <is>
-          <t>{1} {0}</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="E471" s="1" t="n"/>
@@ -9522,17 +9522,17 @@
       <c r="A472" s="1" t="n"/>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.KindsOnly</t>
+          <t>UI.Gacha.WorkSpeedUp</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
         <is>
-          <t>{0}종</t>
+          <t>작업속도 증가</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
         <is>
-          <t>{0} kinds</t>
+          <t>Work Speed Up</t>
         </is>
       </c>
       <c r="E472" s="1" t="n"/>
@@ -9541,17 +9541,17 @@
       <c r="A473" s="1" t="n"/>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Item</t>
+          <t>UI.Gacha.Kinds</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>{0} {1}종</t>
         </is>
       </c>
       <c r="D473" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>{1} {0}</t>
         </is>
       </c>
       <c r="E473" s="1" t="n"/>
@@ -9560,17 +9560,17 @@
       <c r="A474" s="1" t="n"/>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.RateTitle</t>
+          <t>UI.Gacha.KindsOnly</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
         <is>
-          <t>{0} 확률</t>
+          <t>{0}종</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
         <is>
-          <t>{0} Rates</t>
+          <t>{0} kinds</t>
         </is>
       </c>
       <c r="E474" s="1" t="n"/>
@@ -9579,17 +9579,17 @@
       <c r="A475" s="1" t="n"/>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoEntries</t>
+          <t>UI.Gacha.Item</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
         <is>
-          <t>뽑을 항목이 없다</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D475" s="6" t="inlineStr">
         <is>
-          <t>Nothing to draw</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E475" s="1" t="n"/>
@@ -9598,17 +9598,17 @@
       <c r="A476" s="1" t="n"/>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoRarity</t>
+          <t>UI.Gacha.RateTitle</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
         <is>
-          <t>등급 없음</t>
+          <t>{0} 확률</t>
         </is>
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>No Rarity</t>
+          <t>{0} Rates</t>
         </is>
       </c>
       <c r="E476" s="1" t="n"/>
@@ -9617,17 +9617,17 @@
       <c r="A477" s="1" t="n"/>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SameRate</t>
+          <t>UI.Gacha.NoEntries</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
         <is>
-          <t>10회도 한 번마다 같은 확률</t>
+          <t>뽑을 항목이 없다</t>
         </is>
       </c>
       <c r="D477" s="6" t="inlineStr">
         <is>
-          <t>x10 uses the same odds for each draw</t>
+          <t>Nothing to draw</t>
         </is>
       </c>
       <c r="E477" s="1" t="n"/>
@@ -9636,17 +9636,17 @@
       <c r="A478" s="1" t="n"/>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Wait</t>
+          <t>UI.Gacha.NoRarity</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
         <is>
-          <t>가챠 {0}회</t>
+          <t>등급 없음</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0}</t>
+          <t>No Rarity</t>
         </is>
       </c>
       <c r="E478" s="1" t="n"/>
@@ -9655,17 +9655,17 @@
       <c r="A479" s="1" t="n"/>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Source</t>
+          <t>UI.Gacha.SameRate</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
         <is>
-          <t>가챠</t>
+          <t>10회도 한 번마다 같은 확률</t>
         </is>
       </c>
       <c r="D479" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>x10 uses the same odds for each draw</t>
         </is>
       </c>
       <c r="E479" s="1" t="n"/>
@@ -9674,17 +9674,17 @@
       <c r="A480" s="1" t="n"/>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceBox</t>
+          <t>UI.Gacha.Wait</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
         <is>
-          <t>상자 개봉</t>
+          <t>가챠 {0}회</t>
         </is>
       </c>
       <c r="D480" s="6" t="inlineStr">
         <is>
-          <t>Box Opening</t>
+          <t>Draw x{0}</t>
         </is>
       </c>
       <c r="E480" s="1" t="n"/>
@@ -9693,17 +9693,17 @@
       <c r="A481" s="1" t="n"/>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceMail</t>
+          <t>UI.Gacha.Source</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
         <is>
-          <t>우편 수령</t>
+          <t>가챠</t>
         </is>
       </c>
       <c r="D481" s="6" t="inlineStr">
         <is>
-          <t>Mail Claim</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E481" s="1" t="n"/>
@@ -9712,17 +9712,17 @@
       <c r="A482" s="1" t="n"/>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.ResultTitle</t>
+          <t>UI.Gacha.SourceBox</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>{0} 결과</t>
+          <t>상자 개봉</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
         <is>
-          <t>{0} Results</t>
+          <t>Box Opening</t>
         </is>
       </c>
       <c r="E482" s="1" t="n"/>
@@ -9731,17 +9731,17 @@
       <c r="A483" s="1" t="n"/>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.DrawAgain</t>
+          <t>UI.Gacha.SourceMail</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
         <is>
-          <t>{0}회 더 뽑기</t>
+          <t>우편 수령</t>
         </is>
       </c>
       <c r="D483" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0} Again</t>
+          <t>Mail Claim</t>
         </is>
       </c>
       <c r="E483" s="1" t="n"/>
@@ -9750,17 +9750,17 @@
       <c r="A484" s="1" t="n"/>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Tab</t>
+          <t>UI.Gacha.ResultTitle</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>{0} 결과</t>
         </is>
       </c>
       <c r="D484" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>{0} Results</t>
         </is>
       </c>
       <c r="E484" s="1" t="n"/>
@@ -9769,17 +9769,17 @@
       <c r="A485" s="1" t="n"/>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.CloseResult</t>
+          <t>UI.Gacha.DrawAgain</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
         <is>
-          <t>[결과 닫기]</t>
+          <t>{0}회 더 뽑기</t>
         </is>
       </c>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>[Close]</t>
+          <t>Draw x{0} Again</t>
         </is>
       </c>
       <c r="E485" s="1" t="n"/>
@@ -9788,17 +9788,17 @@
       <c r="A486" s="1" t="n"/>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Gacha.Tab</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E486" s="1" t="n"/>
@@ -9807,17 +9807,17 @@
       <c r="A487" s="1" t="n"/>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Gacha.CloseResult</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>[결과 닫기]</t>
         </is>
       </c>
       <c r="D487" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>[Close]</t>
         </is>
       </c>
       <c r="E487" s="1" t="n"/>
@@ -9826,17 +9826,17 @@
       <c r="A488" s="1" t="n"/>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D488" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E488" s="1" t="n"/>
@@ -9845,17 +9845,17 @@
       <c r="A489" s="1" t="n"/>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D489" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E489" s="1" t="n"/>
@@ -9864,17 +9864,17 @@
       <c r="A490" s="1" t="n"/>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D490" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E490" s="1" t="n"/>
@@ -9883,17 +9883,17 @@
       <c r="A491" s="1" t="n"/>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D491" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E491" s="1" t="n"/>
@@ -9902,17 +9902,17 @@
       <c r="A492" s="1" t="n"/>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D492" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E492" s="1" t="n"/>
@@ -9921,17 +9921,17 @@
       <c r="A493" s="1" t="n"/>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D493" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E493" s="1" t="n"/>
@@ -9940,17 +9940,17 @@
       <c r="A494" s="1" t="n"/>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D494" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E494" s="1" t="n"/>
@@ -9959,17 +9959,17 @@
       <c r="A495" s="1" t="n"/>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E495" s="1" t="n"/>
@@ -9978,17 +9978,17 @@
       <c r="A496" s="1" t="n"/>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D496" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E496" s="1" t="n"/>
@@ -9997,17 +9997,17 @@
       <c r="A497" s="1" t="n"/>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E497" s="1" t="n"/>
@@ -10016,17 +10016,17 @@
       <c r="A498" s="1" t="n"/>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D498" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E498" s="1" t="n"/>
@@ -10035,17 +10035,17 @@
       <c r="A499" s="1" t="n"/>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D499" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E499" s="1" t="n"/>
@@ -10054,17 +10054,17 @@
       <c r="A500" s="1" t="n"/>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D500" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E500" s="1" t="n"/>
@@ -10073,17 +10073,17 @@
       <c r="A501" s="1" t="n"/>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D501" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E501" s="1" t="n"/>
@@ -10092,17 +10092,17 @@
       <c r="A502" s="1" t="n"/>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D502" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E502" s="1" t="n"/>
@@ -10111,17 +10111,17 @@
       <c r="A503" s="1" t="n"/>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D503" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E503" s="1" t="n"/>
@@ -10130,17 +10130,17 @@
       <c r="A504" s="1" t="n"/>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D504" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E504" s="1" t="n"/>
@@ -10149,17 +10149,17 @@
       <c r="A505" s="1" t="n"/>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D505" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E505" s="1" t="n"/>
@@ -10168,17 +10168,17 @@
       <c r="A506" s="1" t="n"/>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D506" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E506" s="1" t="n"/>
@@ -10187,17 +10187,17 @@
       <c r="A507" s="1" t="n"/>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D507" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E507" s="1" t="n"/>
@@ -10206,17 +10206,17 @@
       <c r="A508" s="1" t="n"/>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D508" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E508" s="1" t="n"/>
@@ -10225,17 +10225,17 @@
       <c r="A509" s="1" t="n"/>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E509" s="1" t="n"/>
@@ -10244,17 +10244,17 @@
       <c r="A510" s="1" t="n"/>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D510" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E510" s="1" t="n"/>
@@ -10263,17 +10263,17 @@
       <c r="A511" s="1" t="n"/>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E511" s="1" t="n"/>
@@ -10282,17 +10282,17 @@
       <c r="A512" s="1" t="n"/>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E512" s="1" t="n"/>
@@ -10301,17 +10301,17 @@
       <c r="A513" s="1" t="n"/>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E513" s="1" t="n"/>
@@ -10320,17 +10320,17 @@
       <c r="A514" s="1" t="n"/>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D514" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E514" s="1" t="n"/>
@@ -10339,17 +10339,17 @@
       <c r="A515" s="1" t="n"/>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D515" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E515" s="1" t="n"/>
@@ -10358,17 +10358,17 @@
       <c r="A516" s="1" t="n"/>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D516" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E516" s="1" t="n"/>
@@ -10377,17 +10377,17 @@
       <c r="A517" s="1" t="n"/>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D517" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E517" s="1" t="n"/>
@@ -10396,17 +10396,17 @@
       <c r="A518" s="1" t="n"/>
       <c r="B518" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D518" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E518" s="1" t="n"/>
@@ -10415,17 +10415,17 @@
       <c r="A519" s="1" t="n"/>
       <c r="B519" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E519" s="1" t="n"/>
@@ -10434,17 +10434,17 @@
       <c r="A520" s="1" t="n"/>
       <c r="B520" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D520" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E520" s="1" t="n"/>
@@ -10453,17 +10453,17 @@
       <c r="A521" s="1" t="n"/>
       <c r="B521" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E521" s="1" t="n"/>
@@ -10472,17 +10472,17 @@
       <c r="A522" s="1" t="n"/>
       <c r="B522" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D522" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E522" s="1" t="n"/>
@@ -10491,17 +10491,17 @@
       <c r="A523" s="1" t="n"/>
       <c r="B523" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D523" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E523" s="1" t="n"/>
@@ -10510,17 +10510,17 @@
       <c r="A524" s="1" t="n"/>
       <c r="B524" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D524" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E524" s="1" t="n"/>
@@ -10529,17 +10529,17 @@
       <c r="A525" s="1" t="n"/>
       <c r="B525" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D525" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E525" s="1" t="n"/>
@@ -10548,17 +10548,17 @@
       <c r="A526" s="1" t="n"/>
       <c r="B526" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D526" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E526" s="1" t="n"/>
@@ -10567,17 +10567,17 @@
       <c r="A527" s="1" t="n"/>
       <c r="B527" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D527" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E527" s="1" t="n"/>
@@ -10586,17 +10586,17 @@
       <c r="A528" s="1" t="n"/>
       <c r="B528" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D528" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E528" s="1" t="n"/>
@@ -10605,17 +10605,17 @@
       <c r="A529" s="1" t="n"/>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D529" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E529" s="1" t="n"/>
@@ -10624,17 +10624,17 @@
       <c r="A530" s="1" t="n"/>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D530" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E530" s="1" t="n"/>
@@ -10643,17 +10643,17 @@
       <c r="A531" s="1" t="n"/>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D531" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E531" s="1" t="n"/>
@@ -10662,17 +10662,17 @@
       <c r="A532" s="1" t="n"/>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D532" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E532" s="1" t="n"/>
@@ -10681,17 +10681,17 @@
       <c r="A533" s="1" t="n"/>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D533" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E533" s="1" t="n"/>
@@ -10700,17 +10700,17 @@
       <c r="A534" s="1" t="n"/>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D534" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E534" s="1" t="n"/>
@@ -10719,17 +10719,17 @@
       <c r="A535" s="1" t="n"/>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D535" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E535" s="1" t="n"/>
@@ -10738,17 +10738,17 @@
       <c r="A536" s="1" t="n"/>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E536" s="1" t="n"/>
@@ -10757,17 +10757,17 @@
       <c r="A537" s="1" t="n"/>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E537" s="1" t="n"/>
@@ -10776,17 +10776,17 @@
       <c r="A538" s="1" t="n"/>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D538" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E538" s="1" t="n"/>
@@ -10795,17 +10795,17 @@
       <c r="A539" s="1" t="n"/>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D539" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E539" s="1" t="n"/>
@@ -10814,17 +10814,17 @@
       <c r="A540" s="1" t="n"/>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,17 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11631,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11650,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11669,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11688,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11707,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11726,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11745,19 +11745,17 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11766,17 +11764,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11785,17 +11783,19 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11804,17 +11804,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11823,17 +11823,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11842,17 +11842,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11861,17 +11861,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11880,17 +11880,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11899,17 +11899,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11918,17 +11918,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11937,17 +11937,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11956,19 +11956,17 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11977,17 +11975,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11996,19 +11994,19 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12017,17 +12015,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12036,17 +12034,19 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12055,17 +12055,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12074,17 +12074,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12093,17 +12093,17 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12112,17 +12112,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12131,17 +12131,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지 · 통째로만 팔립니다</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing · sold only as a whole</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12150,17 +12150,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12169,17 +12169,17 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지 · 통째로만 팔립니다</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Owned {0} · up to {1} per listing · sold only as a whole</t>
         </is>
       </c>
       <c r="E611" s="1" t="n"/>
@@ -12188,17 +12188,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12207,17 +12207,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12226,17 +12226,17 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12245,17 +12245,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12264,17 +12264,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12283,17 +12283,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12302,17 +12302,17 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12321,17 +12321,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12340,17 +12340,17 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12359,17 +12359,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12378,17 +12378,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12397,17 +12397,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12416,17 +12416,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12435,17 +12435,17 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12454,17 +12454,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12473,17 +12473,17 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12492,17 +12492,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12511,17 +12511,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12530,17 +12530,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12549,19 +12549,17 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12570,17 +12568,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12589,17 +12587,19 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12608,17 +12608,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12627,17 +12627,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12646,17 +12646,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.ChartTitle</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12665,17 +12665,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.ChartEmpty</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>최근 14일 동안 거래가 없습니다</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>No trades in the last 14 days</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12684,17 +12684,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.LevelsTitle</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12703,17 +12703,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.LevelsEmpty</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>지금 판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Nothing on sale right now</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12722,17 +12722,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.RegisterOpen</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>+ 판매 등록</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>+ List Item</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12741,17 +12741,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.ColItem</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12760,17 +12760,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.ColNet</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>팔리면 받는 금액</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>You Get If Sold</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12779,17 +12779,17 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.ColDate</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E643" s="1" t="n"/>
@@ -12798,17 +12798,17 @@
       <c r="A644" s="1" t="n"/>
       <c r="B644" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.ColType</t>
         </is>
       </c>
       <c r="C644" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="D644" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E644" s="1" t="n"/>
@@ -12817,17 +12817,17 @@
       <c r="A645" s="1" t="n"/>
       <c r="B645" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.ColAmount</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E645" s="1" t="n"/>
@@ -12836,17 +12836,17 @@
       <c r="A646" s="1" t="n"/>
       <c r="B646" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.ColDest</t>
         </is>
       </c>
       <c r="C646" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>받는 곳</t>
         </is>
       </c>
       <c r="D646" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>Goes To</t>
         </is>
       </c>
       <c r="E646" s="1" t="n"/>
@@ -12855,19 +12855,17 @@
       <c r="A647" s="1" t="n"/>
       <c r="B647" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.RegisterTitle</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.
-끼고 있는 장비 · 일하는 캐릭터는 흐리게 보이고, 툴팁에 사유가 나옵니다.</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D647" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.
-Worn gear and working characters are dimmed — the tooltip shows why.</t>
+          <t>List an Item</t>
         </is>
       </c>
       <c r="E647" s="1" t="n"/>
@@ -12876,17 +12874,17 @@
       <c r="A648" s="1" t="n"/>
       <c r="B648" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.FindByName</t>
         </is>
       </c>
       <c r="C648" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>이름으로 찾기</t>
         </is>
       </c>
       <c r="D648" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>Find by name</t>
         </is>
       </c>
       <c r="E648" s="1" t="n"/>
@@ -12895,17 +12893,19 @@
       <c r="A649" s="1" t="n"/>
       <c r="B649" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.RegisterEmptyCard</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.
+끼고 있는 장비 · 일하는 캐릭터는 흐리게 보이고, 툴팁에 사유가 나옵니다.</t>
         </is>
       </c>
       <c r="D649" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>[Select] something to list on the left.
+Worn gear and working characters are dimmed — the tooltip shows why.</t>
         </is>
       </c>
       <c r="E649" s="1" t="n"/>
@@ -12914,20 +12914,58 @@
       <c r="A650" s="1" t="n"/>
       <c r="B650" s="6" t="inlineStr">
         <is>
+          <t>UI.Auction.ShowPrice</t>
+        </is>
+      </c>
+      <c r="C650" s="6" t="inlineStr">
+        <is>
+          <t>시세 보기</t>
+        </is>
+      </c>
+      <c r="D650" s="6" t="inlineStr">
+        <is>
+          <t>View Prices</t>
+        </is>
+      </c>
+      <c r="E650" s="1" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n"/>
+      <c r="B651" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.MatchLowest</t>
+        </is>
+      </c>
+      <c r="C651" s="6" t="inlineStr">
+        <is>
+          <t>최저가에 맞춤</t>
+        </is>
+      </c>
+      <c r="D651" s="6" t="inlineStr">
+        <is>
+          <t>Match Lowest</t>
+        </is>
+      </c>
+      <c r="E651" s="1" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n"/>
+      <c r="B652" s="6" t="inlineStr">
+        <is>
           <t>UI.Auction.Register</t>
         </is>
       </c>
-      <c r="C650" s="6" t="inlineStr">
+      <c r="C652" s="6" t="inlineStr">
         <is>
           <t>등록</t>
         </is>
       </c>
-      <c r="D650" s="6" t="inlineStr">
+      <c r="D652" s="6" t="inlineStr">
         <is>
           <t>List</t>
         </is>
       </c>
-      <c r="E650" s="1" t="n"/>
+      <c r="E652" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E652"/>
+  <dimension ref="A1:E684"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7996,17 +7996,17 @@
       <c r="A392" s="1" t="n"/>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Speed</t>
+          <t>UI.Condense.HelpTitle</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
         <is>
-          <t>속도</t>
+          <t>응축</t>
         </is>
       </c>
       <c r="D392" s="6" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Condense</t>
         </is>
       </c>
       <c r="E392" s="1" t="n"/>
@@ -8015,17 +8015,17 @@
       <c r="A393" s="1" t="n"/>
       <c r="B393" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Common</t>
+          <t>UI.Condense.HelpSame</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>같은 캐릭터를 재료로 녹여 누적을 쌓습니다 — 재료 1마리 = 누적 +1</t>
         </is>
       </c>
       <c r="D393" s="6" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Melt duplicates of the same character to build up the total — 1 material = +1</t>
         </is>
       </c>
       <c r="E393" s="1" t="n"/>
@@ -8034,17 +8034,17 @@
       <c r="A394" s="1" t="n"/>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Condition</t>
+          <t>UI.Condense.HelpStar</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
         <is>
-          <t>조건</t>
+          <t>누적이 단계 기준에 닿으면 ★이 오르고 작업속도가 늘어납니다</t>
         </is>
       </c>
       <c r="D394" s="6" t="inlineStr">
         <is>
-          <t>Requires</t>
+          <t>Reaching a stage total raises the stars and work speed</t>
         </is>
       </c>
       <c r="E394" s="1" t="n"/>
@@ -8053,17 +8053,17 @@
       <c r="A395" s="1" t="n"/>
       <c r="B395" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentLevel</t>
+          <t>UI.Condense.HelpLost</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
         <is>
-          <t>(지금 {0})</t>
+          <t>재료의 레벨 · 경험치 · 응축은 사라지고 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D395" s="6" t="inlineStr">
         <is>
-          <t>(now {0})</t>
+          <t>Materials lose their level, EXP and condense — this can't be undone</t>
         </is>
       </c>
       <c r="E395" s="1" t="n"/>
@@ -8072,17 +8072,17 @@
       <c r="A396" s="1" t="n"/>
       <c r="B396" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.LevelUp</t>
+          <t>UI.Condense.HelpOverflow</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
         <is>
-          <t>레벨 올리기 ({0}점)</t>
+          <t>최고 단계를 넘는 재료는 효과 없이 사라집니다</t>
         </is>
       </c>
       <c r="D396" s="6" t="inlineStr">
         <is>
-          <t>Level Up ({0} pt)</t>
+          <t>Materials beyond the top stage are consumed with no effect</t>
         </is>
       </c>
       <c r="E396" s="1" t="n"/>
@@ -8091,17 +8091,17 @@
       <c r="A397" s="1" t="n"/>
       <c r="B397" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentEffect</t>
+          <t>UI.Condense.HelpBusy</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
         <is>
-          <t>현재 효과</t>
+          <t>배치 · 장비 착용 · 잠긴 캐릭터는 재료로 넣을 수 없습니다</t>
         </is>
       </c>
       <c r="D397" s="6" t="inlineStr">
         <is>
-          <t>Current Effect</t>
+          <t>Assigned, gear-wearing or locked characters can't be materials</t>
         </is>
       </c>
       <c r="E397" s="1" t="n"/>
@@ -8110,17 +8110,17 @@
       <c r="A398" s="1" t="n"/>
       <c r="B398" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NowLevel</t>
+          <t>UI.Condense.HelpStage</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
         <is>
-          <t>지금 (Lv{0})</t>
+          <t>■ 단계</t>
         </is>
       </c>
       <c r="D398" s="6" t="inlineStr">
         <is>
-          <t>Now (Lv{0})</t>
+          <t>■ Stage</t>
         </is>
       </c>
       <c r="E398" s="1" t="n"/>
@@ -8129,17 +8129,17 @@
       <c r="A399" s="1" t="n"/>
       <c r="B399" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NextLevel</t>
+          <t>UI.Condense.HelpTotal</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
         <is>
-          <t>다음 (Lv{0})</t>
+          <t>누적</t>
         </is>
       </c>
       <c r="D399" s="6" t="inlineStr">
         <is>
-          <t>Next (Lv{0})</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E399" s="1" t="n"/>
@@ -8148,17 +8148,17 @@
       <c r="A400" s="1" t="n"/>
       <c r="B400" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Points</t>
+          <t>UI.Condense.StarN</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
         <is>
-          <t>보유 포인트 {0}</t>
+          <t>{0}성</t>
         </is>
       </c>
       <c r="D400" s="6" t="inlineStr">
         <is>
-          <t>Points {0}</t>
+          <t>{0}-Star</t>
         </is>
       </c>
       <c r="E400" s="1" t="n"/>
@@ -8167,17 +8167,17 @@
       <c r="A401" s="1" t="n"/>
       <c r="B401" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.UpTo</t>
+          <t>UI.Trait.Speed</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
         <is>
-          <t>{0}까지</t>
+          <t>속도</t>
         </is>
       </c>
       <c r="D401" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E401" s="1" t="n"/>
@@ -8186,17 +8186,17 @@
       <c r="A402" s="1" t="n"/>
       <c r="B402" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Opens</t>
+          <t>UI.Trait.Common</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
         <is>
-          <t>{0} 열림</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D402" s="6" t="inlineStr">
         <is>
-          <t>Opens {0}</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E402" s="1" t="n"/>
@@ -8205,17 +8205,17 @@
       <c r="A403" s="1" t="n"/>
       <c r="B403" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescUnlock</t>
+          <t>UI.Trait.Condition</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
+          <t>조건</t>
         </is>
       </c>
       <c r="D403" s="6" t="inlineStr">
         <is>
-          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
+          <t>Requires</t>
         </is>
       </c>
       <c r="E403" s="1" t="n"/>
@@ -8224,17 +8224,17 @@
       <c r="A404" s="1" t="n"/>
       <c r="B404" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescSpeed</t>
+          <t>UI.Trait.CurrentLevel</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
         <is>
-          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
+          <t>(지금 {0})</t>
         </is>
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
+          <t>(now {0})</t>
         </is>
       </c>
       <c r="E404" s="1" t="n"/>
@@ -8243,17 +8243,17 @@
       <c r="A405" s="1" t="n"/>
       <c r="B405" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYield</t>
+          <t>UI.Trait.LevelUp</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
         <is>
-          <t>판정 1회에 같은 자원이 더 나옵니다 (120%면 1개 + 20% 확률로 1개 더). 좋은 자원이 나올 확률은 그대로이고, 상자 · 경험치는 늘지 않습니다.</t>
+          <t>레벨 올리기 ({0}점)</t>
         </is>
       </c>
       <c r="D405" s="6" t="inlineStr">
         <is>
-          <t>Each roll yields more of the same resource (120% = 1 plus a 20% chance of 1 more). The odds of better resources stay the same, and boxes and EXP don't increase.</t>
+          <t>Level Up ({0} pt)</t>
         </is>
       </c>
       <c r="E405" s="1" t="n"/>
@@ -8262,17 +8262,17 @@
       <c r="A406" s="1" t="n"/>
       <c r="B406" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYieldAll</t>
+          <t>UI.Trait.CurrentEffect</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
         <is>
-          <t>모든 산업에 붙습니다.</t>
+          <t>현재 효과</t>
         </is>
       </c>
       <c r="D406" s="6" t="inlineStr">
         <is>
-          <t>Applies to all industries.</t>
+          <t>Current Effect</t>
         </is>
       </c>
       <c r="E406" s="1" t="n"/>
@@ -8281,17 +8281,17 @@
       <c r="A407" s="1" t="n"/>
       <c r="B407" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.AlreadyMax</t>
+          <t>UI.Trait.NowLevel</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
         <is>
-          <t>이미 최대 레벨입니다.</t>
+          <t>지금 (Lv{0})</t>
         </is>
       </c>
       <c r="D407" s="6" t="inlineStr">
         <is>
-          <t>Already at max level.</t>
+          <t>Now (Lv{0})</t>
         </is>
       </c>
       <c r="E407" s="1" t="n"/>
@@ -8300,17 +8300,17 @@
       <c r="A408" s="1" t="n"/>
       <c r="B408" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NotEnoughPoints</t>
+          <t>UI.Trait.NextLevel</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
+          <t>다음 (Lv{0})</t>
         </is>
       </c>
       <c r="D408" s="6" t="inlineStr">
         <is>
-          <t>Not enough trait points. ({0} pt required)</t>
+          <t>Next (Lv{0})</t>
         </is>
       </c>
       <c r="E408" s="1" t="n"/>
@@ -8319,19 +8319,17 @@
       <c r="A409" s="1" t="n"/>
       <c r="B409" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.ConfirmLearn</t>
+          <t>UI.Trait.Points</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트 {0}점을 사용합니다.
-'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
+          <t>보유 포인트 {0}</t>
         </is>
       </c>
       <c r="D409" s="6" t="inlineStr">
         <is>
-          <t>This uses {0} trait point(s).
-Raise '{1}' to Lv{2}?</t>
+          <t>Points {0}</t>
         </is>
       </c>
       <c r="E409" s="1" t="n"/>
@@ -8340,17 +8338,17 @@
       <c r="A410" s="1" t="n"/>
       <c r="B410" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.WaitLearn</t>
+          <t>UI.Trait.UpTo</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
         <is>
-          <t>특성 레벨 올리기</t>
+          <t>{0}까지</t>
         </is>
       </c>
       <c r="D410" s="6" t="inlineStr">
         <is>
-          <t>Level Up Trait</t>
+          <t>Up to {0}</t>
         </is>
       </c>
       <c r="E410" s="1" t="n"/>
@@ -8359,17 +8357,17 @@
       <c r="A411" s="1" t="n"/>
       <c r="B411" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.EmptyDetail</t>
+          <t>UI.Trait.Opens</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
         <is>
-          <t>특성을 누르면 여기에 펼쳐집니다</t>
+          <t>{0} 열림</t>
         </is>
       </c>
       <c r="D411" s="6" t="inlineStr">
         <is>
-          <t>Click a trait to see details here</t>
+          <t>Opens {0}</t>
         </is>
       </c>
       <c r="E411" s="1" t="n"/>
@@ -8378,17 +8376,17 @@
       <c r="A412" s="1" t="n"/>
       <c r="B412" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Base</t>
+          <t>UI.Trait.DescUnlock</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
         <is>
-          <t>기본 {0}</t>
+          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
         </is>
       </c>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>Base {0}</t>
+          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
         </is>
       </c>
       <c r="E412" s="1" t="n"/>
@@ -8397,17 +8395,17 @@
       <c r="A413" s="1" t="n"/>
       <c r="B413" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.StatSlotCount</t>
+          <t>UI.Trait.DescSpeed</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
         <is>
-          <t>능력치 칸 {0}개</t>
+          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
         </is>
       </c>
       <c r="D413" s="6" t="inlineStr">
         <is>
-          <t>{0} stat slots</t>
+          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
         </is>
       </c>
       <c r="E413" s="1" t="n"/>
@@ -8416,17 +8414,17 @@
       <c r="A414" s="1" t="n"/>
       <c r="B414" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.GradeUp</t>
+          <t>UI.Trait.DescYield</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
         <is>
-          <t>등급 상승!</t>
+          <t>판정 1회에 같은 자원이 더 나옵니다. 상자 · 경험치는 늘지 않습니다.</t>
         </is>
       </c>
       <c r="D414" s="6" t="inlineStr">
         <is>
-          <t>Grade Up!</t>
+          <t>Each roll yields more of the same resource. Boxes and EXP don't increase.</t>
         </is>
       </c>
       <c r="E414" s="1" t="n"/>
@@ -8435,17 +8433,17 @@
       <c r="A415" s="1" t="n"/>
       <c r="B415" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CapAll</t>
+          <t>UI.Trait.DescYieldAll</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
         <is>
-          <t>보유 전부</t>
+          <t>모든 산업에 붙습니다.</t>
         </is>
       </c>
       <c r="D415" s="6" t="inlineStr">
         <is>
-          <t>All Owned</t>
+          <t>Applies to all industries.</t>
         </is>
       </c>
       <c r="E415" s="1" t="n"/>
@@ -8454,17 +8452,17 @@
       <c r="A416" s="1" t="n"/>
       <c r="B416" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.All</t>
+          <t>UI.Trait.AlreadyMax</t>
         </is>
       </c>
       <c r="C416" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>이미 최대 레벨입니다.</t>
         </is>
       </c>
       <c r="D416" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Already at max level.</t>
         </is>
       </c>
       <c r="E416" s="1" t="n"/>
@@ -8473,17 +8471,17 @@
       <c r="A417" s="1" t="n"/>
       <c r="B417" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.EveryCombo</t>
+          <t>UI.Trait.NotEnoughPoints</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
         <is>
-          <t>칸마다 전체 또는 {0}</t>
+          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
         </is>
       </c>
       <c r="D417" s="6" t="inlineStr">
         <is>
-          <t>Each slot: All or {0}</t>
+          <t>Not enough trait points. ({0} pt required)</t>
         </is>
       </c>
       <c r="E417" s="1" t="n"/>
@@ -8492,17 +8490,19 @@
       <c r="A418" s="1" t="n"/>
       <c r="B418" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCombo</t>
+          <t>UI.Trait.ConfirmLearn</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
         <is>
-          <t>칸 조합 없음</t>
+          <t>특성 포인트 {0}점을 사용합니다.
+'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
         </is>
       </c>
       <c r="D418" s="6" t="inlineStr">
         <is>
-          <t>No slot combos</t>
+          <t>This uses {0} trait point(s).
+Raise '{1}' to Lv{2}?</t>
         </is>
       </c>
       <c r="E418" s="1" t="n"/>
@@ -8511,17 +8511,17 @@
       <c r="A419" s="1" t="n"/>
       <c r="B419" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combos</t>
+          <t>UI.Trait.WaitLearn</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>칸 {0}</t>
+          <t>특성 레벨 올리기</t>
         </is>
       </c>
       <c r="D419" s="6" t="inlineStr">
         <is>
-          <t>Slots {0}</t>
+          <t>Level Up Trait</t>
         </is>
       </c>
       <c r="E419" s="1" t="n"/>
@@ -8530,19 +8530,17 @@
       <c r="A420" s="1" t="n"/>
       <c r="B420" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NotChosen</t>
+          <t>UI.Trait.EmptyDetail</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
         <is>
-          <t>아직 선택하지 않았습니다.
-BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>특성을 누르면 여기에 펼쳐집니다</t>
         </is>
       </c>
       <c r="D420" s="6" t="inlineStr">
         <is>
-          <t>You haven't chosen yet.
-Pick either BEFORE or AFTER.</t>
+          <t>Click a trait to see details here</t>
         </is>
       </c>
       <c r="E420" s="1" t="n"/>
@@ -8551,17 +8549,17 @@
       <c r="A421" s="1" t="n"/>
       <c r="B421" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WornBy</t>
+          <t>UI.Trait.HelpTitle</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
         <is>
-          <t>{0} 착용 중</t>
+          <t>특성</t>
         </is>
       </c>
       <c r="D421" s="6" t="inlineStr">
         <is>
-          <t>Worn by {0}</t>
+          <t>Traits</t>
         </is>
       </c>
       <c r="E421" s="1" t="n"/>
@@ -8570,17 +8568,17 @@
       <c r="A422" s="1" t="n"/>
       <c r="B422" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ResultHere</t>
+          <t>UI.Trait.HelpPoint</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
         <is>
-          <t>결과가 여기에 나옵니다</t>
+          <t>계정 레벨이 오르면 특성 포인트를 얻습니다</t>
         </is>
       </c>
       <c r="D422" s="6" t="inlineStr">
         <is>
-          <t>The result appears here</t>
+          <t>You earn trait points as your account level rises</t>
         </is>
       </c>
       <c r="E422" s="1" t="n"/>
@@ -8589,17 +8587,17 @@
       <c r="A423" s="1" t="n"/>
       <c r="B423" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoEnchant</t>
+          <t>UI.Trait.HelpLevel</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
         <is>
-          <t>인챈트 없음</t>
+          <t>레벨을 올리려면 포인트와 계정 레벨 조건이 함께 필요합니다</t>
         </is>
       </c>
       <c r="D423" s="6" t="inlineStr">
         <is>
-          <t>No Enchant</t>
+          <t>Leveling up needs both points and the account level requirement</t>
         </is>
       </c>
       <c r="E423" s="1" t="n"/>
@@ -8608,17 +8606,17 @@
       <c r="A424" s="1" t="n"/>
       <c r="B424" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PickOne</t>
+          <t>UI.Trait.HelpChoose</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
+          <t>포인트로 전부 올릴 수는 없습니다 — 키울 산업을 고르세요</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
         <is>
-          <t>[Select] either BEFORE or AFTER.</t>
+          <t>Points can't max everything — choose which industries to grow</t>
         </is>
       </c>
       <c r="E424" s="1" t="n"/>
@@ -8627,17 +8625,17 @@
       <c r="A425" s="1" t="n"/>
       <c r="B425" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RerollKeepsBefore</t>
+          <t>UI.Trait.HelpKinds</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
         <is>
-          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
+          <t>종류</t>
         </is>
       </c>
       <c r="D425" s="6" t="inlineStr">
         <is>
-          <t>Using it again without choosing keeps BEFORE.</t>
+          <t>Types</t>
         </is>
       </c>
       <c r="E425" s="1" t="n"/>
@@ -8646,17 +8644,17 @@
       <c r="A426" s="1" t="n"/>
       <c r="B426" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleFirst</t>
+          <t>UI.Trait.HelpYieldCalc</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
         <is>
-          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
+          <t>산출량 120%면 1개 + 20% 확률로 1개 더</t>
         </is>
       </c>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>First use fills {1} slot(s) at {0} grade.</t>
+          <t>Yield 120% = 1 plus a 20% chance of 1 more</t>
         </is>
       </c>
       <c r="E426" s="1" t="n"/>
@@ -8665,17 +8663,17 @@
       <c r="A427" s="1" t="n"/>
       <c r="B427" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleMythic</t>
+          <t>UI.Trait.HelpYieldRarity</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
         <is>
-          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
+          <t>산출량이 올라도 좋은 자원이 나올 확률은 그대로입니다</t>
         </is>
       </c>
       <c r="D427" s="6" t="inlineStr">
         <is>
-          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
+          <t>Yield doesn't change the odds of better resources</t>
         </is>
       </c>
       <c r="E427" s="1" t="n"/>
@@ -8684,17 +8682,17 @@
       <c r="A428" s="1" t="n"/>
       <c r="B428" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleNormal</t>
+          <t>UI.Enchant.Base</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
         <is>
-          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
+          <t>기본 {0}</t>
         </is>
       </c>
       <c r="D428" s="6" t="inlineStr">
         <is>
-          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
+          <t>Base {0}</t>
         </is>
       </c>
       <c r="E428" s="1" t="n"/>
@@ -8703,17 +8701,17 @@
       <c r="A429" s="1" t="n"/>
       <c r="B429" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleKeep</t>
+          <t>UI.Enchant.StatSlotCount</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
         <is>
-          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
+          <t>능력치 칸 {0}개</t>
         </is>
       </c>
       <c r="D429" s="6" t="inlineStr">
         <is>
-          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
+          <t>{0} stat slots</t>
         </is>
       </c>
       <c r="E429" s="1" t="n"/>
@@ -8722,17 +8720,17 @@
       <c r="A430" s="1" t="n"/>
       <c r="B430" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeFirst</t>
+          <t>UI.Enchant.GradeUp</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
         <is>
-          <t>첫 사용 · 일반 확정</t>
+          <t>등급 상승!</t>
         </is>
       </c>
       <c r="D430" s="6" t="inlineStr">
         <is>
-          <t>First use · Common guaranteed</t>
+          <t>Grade Up!</t>
         </is>
       </c>
       <c r="E430" s="1" t="n"/>
@@ -8741,17 +8739,17 @@
       <c r="A431" s="1" t="n"/>
       <c r="B431" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOptionsOnly</t>
+          <t>UI.Enchant.CapAll</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
         <is>
-          <t>옵션만 다시 뽑기</t>
+          <t>보유 전부</t>
         </is>
       </c>
       <c r="D431" s="6" t="inlineStr">
         <is>
-          <t>Options reroll only</t>
+          <t>All Owned</t>
         </is>
       </c>
       <c r="E431" s="1" t="n"/>
@@ -8760,17 +8758,17 @@
       <c r="A432" s="1" t="n"/>
       <c r="B432" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeUp</t>
+          <t>UI.Enchant.All</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
         <is>
-          <t>{0} 상승 {1}</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D432" s="6" t="inlineStr">
         <is>
-          <t>{0} up {1}</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E432" s="1" t="n"/>
@@ -8779,17 +8777,17 @@
       <c r="A433" s="1" t="n"/>
       <c r="B433" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOwned</t>
+          <t>UI.Enchant.EveryCombo</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개</t>
+          <t>칸마다 전체 또는 {0}</t>
         </is>
       </c>
       <c r="D433" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>Each slot: All or {0}</t>
         </is>
       </c>
       <c r="E433" s="1" t="n"/>
@@ -8798,17 +8796,17 @@
       <c r="A434" s="1" t="n"/>
       <c r="B434" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeData</t>
+          <t>UI.Enchant.NoCombo</t>
         </is>
       </c>
       <c r="C434" s="6" t="inlineStr">
         <is>
-          <t>큐브 정보가 없습니다</t>
+          <t>칸 조합 없음</t>
         </is>
       </c>
       <c r="D434" s="6" t="inlineStr">
         <is>
-          <t>No cube data</t>
+          <t>No slot combos</t>
         </is>
       </c>
       <c r="E434" s="1" t="n"/>
@@ -8817,17 +8815,17 @@
       <c r="A435" s="1" t="n"/>
       <c r="B435" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UseCube</t>
+          <t>UI.Enchant.Combos</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
         <is>
-          <t>{0} 사용</t>
+          <t>칸 {0}</t>
         </is>
       </c>
       <c r="D435" s="6" t="inlineStr">
         <is>
-          <t>Use {0}</t>
+          <t>Slots {0}</t>
         </is>
       </c>
       <c r="E435" s="1" t="n"/>
@@ -8836,17 +8834,19 @@
       <c r="A436" s="1" t="n"/>
       <c r="B436" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCube</t>
+          <t>UI.Enchant.NotChosen</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다</t>
+          <t>아직 선택하지 않았습니다.
+BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D436" s="6" t="inlineStr">
         <is>
-          <t>No {0}</t>
+          <t>You haven't chosen yet.
+Pick either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E436" s="1" t="n"/>
@@ -8855,17 +8855,17 @@
       <c r="A437" s="1" t="n"/>
       <c r="B437" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnequipAndUse</t>
+          <t>UI.Enchant.WornBy</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
         <is>
-          <t>해제하고 {0} 사용</t>
+          <t>{0} 착용 중</t>
         </is>
       </c>
       <c r="D437" s="6" t="inlineStr">
         <is>
-          <t>Unequip and Use {0}</t>
+          <t>Worn by {0}</t>
         </is>
       </c>
       <c r="E437" s="1" t="n"/>
@@ -8874,17 +8874,17 @@
       <c r="A438" s="1" t="n"/>
       <c r="B438" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeNotice</t>
+          <t>UI.Enchant.ResultHere</t>
         </is>
       </c>
       <c r="C438" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다.</t>
+          <t>결과가 여기에 나옵니다</t>
         </is>
       </c>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>You have no {0}.</t>
+          <t>The result appears here</t>
         </is>
       </c>
       <c r="E438" s="1" t="n"/>
@@ -8893,19 +8893,17 @@
       <c r="A439" s="1" t="n"/>
       <c r="B439" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ConfirmUnequip</t>
+          <t>UI.Enchant.NoEnchant</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
         <is>
-          <t>{0}이(가) 끼고 있는 장비입니다.
-해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
+          <t>인챈트 없음</t>
         </is>
       </c>
       <c r="D439" s="6" t="inlineStr">
         <is>
-          <t>{0} is wearing this gear.
-It will be unequipped before using the cube. (It won't be re-equipped.)</t>
+          <t>No Enchant</t>
         </is>
       </c>
       <c r="E439" s="1" t="n"/>
@@ -8914,17 +8912,17 @@
       <c r="A440" s="1" t="n"/>
       <c r="B440" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitUse</t>
+          <t>UI.Enchant.PickOne</t>
         </is>
       </c>
       <c r="C440" s="6" t="inlineStr">
         <is>
-          <t>큐브 사용</t>
+          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
         </is>
       </c>
       <c r="D440" s="6" t="inlineStr">
         <is>
-          <t>Use Cube</t>
+          <t>[Select] either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E440" s="1" t="n"/>
@@ -8933,17 +8931,17 @@
       <c r="A441" s="1" t="n"/>
       <c r="B441" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitChoose</t>
+          <t>UI.Enchant.RerollKeepsBefore</t>
         </is>
       </c>
       <c r="C441" s="6" t="inlineStr">
         <is>
-          <t>큐브 결과 고르기</t>
+          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
         </is>
       </c>
       <c r="D441" s="6" t="inlineStr">
         <is>
-          <t>Choose Cube Result</t>
+          <t>Using it again without choosing keeps BEFORE.</t>
         </is>
       </c>
       <c r="E441" s="1" t="n"/>
@@ -8952,17 +8950,17 @@
       <c r="A442" s="1" t="n"/>
       <c r="B442" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ChooseFirst</t>
+          <t>UI.Enchant.RuleFirst</t>
         </is>
       </c>
       <c r="C442" s="6" t="inlineStr">
         <is>
-          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
         </is>
       </c>
       <c r="D442" s="6" t="inlineStr">
         <is>
-          <t>Pick BEFORE or AFTER first.</t>
+          <t>First use fills {1} slot(s) at {0} grade.</t>
         </is>
       </c>
       <c r="E442" s="1" t="n"/>
@@ -8971,17 +8969,17 @@
       <c r="A443" s="1" t="n"/>
       <c r="B443" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoAutoWorn</t>
+          <t>UI.Enchant.RuleMythic</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
         <is>
-          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
+          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
         </is>
       </c>
       <c r="D443" s="6" t="inlineStr">
         <is>
-          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
+          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
         </is>
       </c>
       <c r="E443" s="1" t="n"/>
@@ -8990,17 +8988,17 @@
       <c r="A444" s="1" t="n"/>
       <c r="B444" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStart</t>
+          <t>UI.Enchant.RuleNormal</t>
         </is>
       </c>
       <c r="C444" s="6" t="inlineStr">
         <is>
-          <t>자동 시작 ▶</t>
+          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
         </is>
       </c>
       <c r="D444" s="6" t="inlineStr">
         <is>
-          <t>Start Auto ▶</t>
+          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
         </is>
       </c>
       <c r="E444" s="1" t="n"/>
@@ -9009,17 +9007,17 @@
       <c r="A445" s="1" t="n"/>
       <c r="B445" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AlreadyMythic</t>
+          <t>UI.Enchant.RuleKeep</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
         <is>
-          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
+          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
         </is>
       </c>
       <c r="D445" s="6" t="inlineStr">
         <is>
-          <t>Already Mythic. Pick an option to aim for.</t>
+          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
         </is>
       </c>
       <c r="E445" s="1" t="n"/>
@@ -9028,17 +9026,17 @@
       <c r="A446" s="1" t="n"/>
       <c r="B446" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NeedCombo</t>
+          <t>UI.Enchant.CubeFirst</t>
         </is>
       </c>
       <c r="C446" s="6" t="inlineStr">
         <is>
-          <t>조합을 하나 이상 켜 주세요.</t>
+          <t>첫 사용 · 일반 확정</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
         <is>
-          <t>Turn on at least one combo.</t>
+          <t>First use · Common guaranteed</t>
         </is>
       </c>
       <c r="E446" s="1" t="n"/>
@@ -9047,17 +9045,17 @@
       <c r="A447" s="1" t="n"/>
       <c r="B447" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.MeanCount</t>
+          <t>UI.Enchant.CubeOptionsOnly</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
         <is>
-          <t>{0}개 (약 {1})</t>
+          <t>옵션만 다시 뽑기</t>
         </is>
       </c>
       <c r="D447" s="6" t="inlineStr">
         <is>
-          <t>{0} (about {1})</t>
+          <t>Options reroll only</t>
         </is>
       </c>
       <c r="E447" s="1" t="n"/>
@@ -9066,17 +9064,17 @@
       <c r="A448" s="1" t="n"/>
       <c r="B448" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Within</t>
+          <t>UI.Enchant.CubeUp</t>
         </is>
       </c>
       <c r="C448" s="6" t="inlineStr">
         <is>
-          <t>{0}개 안에 {1}</t>
+          <t>{0} 상승 {1}</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
         <is>
-          <t>{1} within {0}</t>
+          <t>{0} up {1}</t>
         </is>
       </c>
       <c r="E448" s="1" t="n"/>
@@ -9085,17 +9083,17 @@
       <c r="A449" s="1" t="n"/>
       <c r="B449" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Mean</t>
+          <t>UI.Enchant.CubeOwned</t>
         </is>
       </c>
       <c r="C449" s="6" t="inlineStr">
         <is>
-          <t>평균 {0}</t>
+          <t>보유 {0}개</t>
         </is>
       </c>
       <c r="D449" s="6" t="inlineStr">
         <is>
-          <t>avg {0}</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E449" s="1" t="n"/>
@@ -9104,17 +9102,17 @@
       <c r="A450" s="1" t="n"/>
       <c r="B450" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnderMin</t>
+          <t>UI.Enchant.NoCubeData</t>
         </is>
       </c>
       <c r="C450" s="6" t="inlineStr">
         <is>
-          <t>0.01% 미만</t>
+          <t>큐브 정보가 없습니다</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
         <is>
-          <t>under 0.01%</t>
+          <t>No cube data</t>
         </is>
       </c>
       <c r="E450" s="1" t="n"/>
@@ -9123,17 +9121,17 @@
       <c r="A451" s="1" t="n"/>
       <c r="B451" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Minutes</t>
+          <t>UI.Enchant.UseCube</t>
         </is>
       </c>
       <c r="C451" s="6" t="inlineStr">
         <is>
-          <t>{0}분</t>
+          <t>{0} 사용</t>
         </is>
       </c>
       <c r="D451" s="6" t="inlineStr">
         <is>
-          <t>{0}m</t>
+          <t>Use {0}</t>
         </is>
       </c>
       <c r="E451" s="1" t="n"/>
@@ -9142,17 +9140,17 @@
       <c r="A452" s="1" t="n"/>
       <c r="B452" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Hours</t>
+          <t>UI.Enchant.NoCube</t>
         </is>
       </c>
       <c r="C452" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>{0}가 없습니다</t>
         </is>
       </c>
       <c r="D452" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>No {0}</t>
         </is>
       </c>
       <c r="E452" s="1" t="n"/>
@@ -9161,17 +9159,17 @@
       <c r="A453" s="1" t="n"/>
       <c r="B453" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoRunning</t>
+          <t>UI.Enchant.UnequipAndUse</t>
         </is>
       </c>
       <c r="C453" s="6" t="inlineStr">
         <is>
-          <t>자동 진행 중 {0} / {1}개</t>
+          <t>해제하고 {0} 사용</t>
         </is>
       </c>
       <c r="D453" s="6" t="inlineStr">
         <is>
-          <t>Auto running {0} / {1}</t>
+          <t>Unequip and Use {0}</t>
         </is>
       </c>
       <c r="E453" s="1" t="n"/>
@@ -9180,17 +9178,17 @@
       <c r="A454" s="1" t="n"/>
       <c r="B454" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Goal</t>
+          <t>UI.Enchant.NoCubeNotice</t>
         </is>
       </c>
       <c r="C454" s="6" t="inlineStr">
         <is>
-          <t>목표 {0} 이상</t>
+          <t>{0}가 없습니다.</t>
         </is>
       </c>
       <c r="D454" s="6" t="inlineStr">
         <is>
-          <t>Goal: {0} or higher</t>
+          <t>You have no {0}.</t>
         </is>
       </c>
       <c r="E454" s="1" t="n"/>
@@ -9199,17 +9197,19 @@
       <c r="A455" s="1" t="n"/>
       <c r="B455" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoSlotRule</t>
+          <t>UI.Enchant.ConfirmUnequip</t>
         </is>
       </c>
       <c r="C455" s="6" t="inlineStr">
         <is>
-          <t>칸 조건 없음 — 등급만 봅니다</t>
+          <t>{0}이(가) 끼고 있는 장비입니다.
+해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
         </is>
       </c>
       <c r="D455" s="6" t="inlineStr">
         <is>
-          <t>No slot condition — grade only</t>
+          <t>{0} is wearing this gear.
+It will be unequipped before using the cube. (It won't be re-equipped.)</t>
         </is>
       </c>
       <c r="E455" s="1" t="n"/>
@@ -9218,17 +9218,17 @@
       <c r="A456" s="1" t="n"/>
       <c r="B456" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PerRoll</t>
+          <t>UI.Enchant.WaitUse</t>
         </is>
       </c>
       <c r="C456" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}</t>
+          <t>큐브 사용</t>
         </is>
       </c>
       <c r="D456" s="6" t="inlineStr">
         <is>
-          <t>{0} per roll</t>
+          <t>Use Cube</t>
         </is>
       </c>
       <c r="E456" s="1" t="n"/>
@@ -9237,17 +9237,17 @@
       <c r="A457" s="1" t="n"/>
       <c r="B457" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStop</t>
+          <t>UI.Enchant.WaitChoose</t>
         </is>
       </c>
       <c r="C457" s="6" t="inlineStr">
         <is>
-          <t>■ 멈춤</t>
+          <t>큐브 결과 고르기</t>
         </is>
       </c>
       <c r="D457" s="6" t="inlineStr">
         <is>
-          <t>■ Stop</t>
+          <t>Choose Cube Result</t>
         </is>
       </c>
       <c r="E457" s="1" t="n"/>
@@ -9256,17 +9256,17 @@
       <c r="A458" s="1" t="n"/>
       <c r="B458" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Auto</t>
+          <t>UI.Enchant.ChooseFirst</t>
         </is>
       </c>
       <c r="C458" s="6" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D458" s="6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Pick BEFORE or AFTER first.</t>
         </is>
       </c>
       <c r="E458" s="1" t="n"/>
@@ -9275,17 +9275,17 @@
       <c r="A459" s="1" t="n"/>
       <c r="B459" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndStopped</t>
+          <t>UI.Enchant.NoAutoWorn</t>
         </is>
       </c>
       <c r="C459" s="6" t="inlineStr">
         <is>
-          <t>자동을 멈췄습니다</t>
+          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
         </is>
       </c>
       <c r="D459" s="6" t="inlineStr">
         <is>
-          <t>Auto stopped</t>
+          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
         </is>
       </c>
       <c r="E459" s="1" t="n"/>
@@ -9294,17 +9294,17 @@
       <c r="A460" s="1" t="n"/>
       <c r="B460" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndCap</t>
+          <t>UI.Enchant.AutoStart</t>
         </is>
       </c>
       <c r="C460" s="6" t="inlineStr">
         <is>
-          <t>상한에 닿아 멈췄습니다</t>
+          <t>자동 시작 ▶</t>
         </is>
       </c>
       <c r="D460" s="6" t="inlineStr">
         <is>
-          <t>Stopped at the limit</t>
+          <t>Start Auto ▶</t>
         </is>
       </c>
       <c r="E460" s="1" t="n"/>
@@ -9313,17 +9313,17 @@
       <c r="A461" s="1" t="n"/>
       <c r="B461" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndNoCube</t>
+          <t>UI.Enchant.AlreadyMythic</t>
         </is>
       </c>
       <c r="C461" s="6" t="inlineStr">
         <is>
-          <t>큐브가 떨어져 멈췄습니다</t>
+          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
         </is>
       </c>
       <c r="D461" s="6" t="inlineStr">
         <is>
-          <t>Stopped — out of cubes</t>
+          <t>Already Mythic. Pick an option to aim for.</t>
         </is>
       </c>
       <c r="E461" s="1" t="n"/>
@@ -9332,17 +9332,17 @@
       <c r="A462" s="1" t="n"/>
       <c r="B462" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndRejected</t>
+          <t>UI.Enchant.NeedCombo</t>
         </is>
       </c>
       <c r="C462" s="6" t="inlineStr">
         <is>
-          <t>서버가 거절해 멈췄습니다</t>
+          <t>조합을 하나 이상 켜 주세요.</t>
         </is>
       </c>
       <c r="D462" s="6" t="inlineStr">
         <is>
-          <t>Stopped — server rejected</t>
+          <t>Turn on at least one combo.</t>
         </is>
       </c>
       <c r="E462" s="1" t="n"/>
@@ -9351,17 +9351,17 @@
       <c r="A463" s="1" t="n"/>
       <c r="B463" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndGoal</t>
+          <t>UI.Enchant.MeanCount</t>
         </is>
       </c>
       <c r="C463" s="6" t="inlineStr">
         <is>
-          <t>목표 달성!</t>
+          <t>{0}개 (약 {1})</t>
         </is>
       </c>
       <c r="D463" s="6" t="inlineStr">
         <is>
-          <t>Goal reached!</t>
+          <t>{0} (about {1})</t>
         </is>
       </c>
       <c r="E463" s="1" t="n"/>
@@ -9370,17 +9370,17 @@
       <c r="A464" s="1" t="n"/>
       <c r="B464" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndSummary</t>
+          <t>UI.Enchant.Within</t>
         </is>
       </c>
       <c r="C464" s="6" t="inlineStr">
         <is>
-          <t>{0} — {1} {2}개 사용.</t>
+          <t>{0}개 안에 {1}</t>
         </is>
       </c>
       <c r="D464" s="6" t="inlineStr">
         <is>
-          <t>{0} — used {2} {1}.</t>
+          <t>{1} within {0}</t>
         </is>
       </c>
       <c r="E464" s="1" t="n"/>
@@ -9389,17 +9389,17 @@
       <c r="A465" s="1" t="n"/>
       <c r="B465" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.TargetGrade</t>
+          <t>UI.Enchant.Mean</t>
         </is>
       </c>
       <c r="C465" s="6" t="inlineStr">
         <is>
-          <t>목표 등급</t>
+          <t>평균 {0}</t>
         </is>
       </c>
       <c r="D465" s="6" t="inlineStr">
         <is>
-          <t>Target Grade</t>
+          <t>avg {0}</t>
         </is>
       </c>
       <c r="E465" s="1" t="n"/>
@@ -9408,17 +9408,17 @@
       <c r="A466" s="1" t="n"/>
       <c r="B466" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.FocusOption</t>
+          <t>UI.Enchant.UnderMin</t>
         </is>
       </c>
       <c r="C466" s="6" t="inlineStr">
         <is>
-          <t>노릴 옵션</t>
+          <t>0.01% 미만</t>
         </is>
       </c>
       <c r="D466" s="6" t="inlineStr">
         <is>
-          <t>Aim For</t>
+          <t>under 0.01%</t>
         </is>
       </c>
       <c r="E466" s="1" t="n"/>
@@ -9427,17 +9427,17 @@
       <c r="A467" s="1" t="n"/>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combo</t>
+          <t>UI.Enchant.Minutes</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
         <is>
-          <t>조합</t>
+          <t>{0}분</t>
         </is>
       </c>
       <c r="D467" s="6" t="inlineStr">
         <is>
-          <t>Combo</t>
+          <t>{0}m</t>
         </is>
       </c>
       <c r="E467" s="1" t="n"/>
@@ -9446,17 +9446,17 @@
       <c r="A468" s="1" t="n"/>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Cap</t>
+          <t>UI.Enchant.Hours</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>상한</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E468" s="1" t="n"/>
@@ -9465,17 +9465,17 @@
       <c r="A469" s="1" t="n"/>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Select</t>
+          <t>UI.Enchant.AutoRunning</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>자동 진행 중 {0} / {1}개</t>
         </is>
       </c>
       <c r="D469" s="6" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Auto running {0} / {1}</t>
         </is>
       </c>
       <c r="E469" s="1" t="n"/>
@@ -9484,17 +9484,17 @@
       <c r="A470" s="1" t="n"/>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Times</t>
+          <t>UI.Enchant.Goal</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
         <is>
-          <t>{0}회</t>
+          <t>목표 {0} 이상</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
         <is>
-          <t>x{0}</t>
+          <t>Goal: {0} or higher</t>
         </is>
       </c>
       <c r="E470" s="1" t="n"/>
@@ -9503,17 +9503,17 @@
       <c r="A471" s="1" t="n"/>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Worker</t>
+          <t>UI.Enchant.NoSlotRule</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
         <is>
-          <t>일꾼</t>
+          <t>칸 조건 없음 — 등급만 봅니다</t>
         </is>
       </c>
       <c r="D471" s="6" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>No slot condition — grade only</t>
         </is>
       </c>
       <c r="E471" s="1" t="n"/>
@@ -9522,17 +9522,17 @@
       <c r="A472" s="1" t="n"/>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.WorkSpeedUp</t>
+          <t>UI.Enchant.PerRoll</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
         <is>
-          <t>작업속도 증가</t>
+          <t>한 번에 {0}</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
         <is>
-          <t>Work Speed Up</t>
+          <t>{0} per roll</t>
         </is>
       </c>
       <c r="E472" s="1" t="n"/>
@@ -9541,17 +9541,17 @@
       <c r="A473" s="1" t="n"/>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Kinds</t>
+          <t>UI.Enchant.AutoStop</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}종</t>
+          <t>■ 멈춤</t>
         </is>
       </c>
       <c r="D473" s="6" t="inlineStr">
         <is>
-          <t>{1} {0}</t>
+          <t>■ Stop</t>
         </is>
       </c>
       <c r="E473" s="1" t="n"/>
@@ -9560,17 +9560,17 @@
       <c r="A474" s="1" t="n"/>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.KindsOnly</t>
+          <t>UI.Enchant.Auto</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
         <is>
-          <t>{0}종</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
         <is>
-          <t>{0} kinds</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E474" s="1" t="n"/>
@@ -9579,17 +9579,17 @@
       <c r="A475" s="1" t="n"/>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Item</t>
+          <t>UI.Enchant.AutoEndStopped</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>자동을 멈췄습니다</t>
         </is>
       </c>
       <c r="D475" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Auto stopped</t>
         </is>
       </c>
       <c r="E475" s="1" t="n"/>
@@ -9598,17 +9598,17 @@
       <c r="A476" s="1" t="n"/>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.RateTitle</t>
+          <t>UI.Enchant.AutoEndCap</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
         <is>
-          <t>{0} 확률</t>
+          <t>상한에 닿아 멈췄습니다</t>
         </is>
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>{0} Rates</t>
+          <t>Stopped at the limit</t>
         </is>
       </c>
       <c r="E476" s="1" t="n"/>
@@ -9617,17 +9617,17 @@
       <c r="A477" s="1" t="n"/>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoEntries</t>
+          <t>UI.Enchant.AutoEndNoCube</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
         <is>
-          <t>뽑을 항목이 없다</t>
+          <t>큐브가 떨어져 멈췄습니다</t>
         </is>
       </c>
       <c r="D477" s="6" t="inlineStr">
         <is>
-          <t>Nothing to draw</t>
+          <t>Stopped — out of cubes</t>
         </is>
       </c>
       <c r="E477" s="1" t="n"/>
@@ -9636,17 +9636,17 @@
       <c r="A478" s="1" t="n"/>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoRarity</t>
+          <t>UI.Enchant.AutoEndRejected</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
         <is>
-          <t>등급 없음</t>
+          <t>서버가 거절해 멈췄습니다</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>No Rarity</t>
+          <t>Stopped — server rejected</t>
         </is>
       </c>
       <c r="E478" s="1" t="n"/>
@@ -9655,17 +9655,17 @@
       <c r="A479" s="1" t="n"/>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SameRate</t>
+          <t>UI.Enchant.AutoEndGoal</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
         <is>
-          <t>10회도 한 번마다 같은 확률</t>
+          <t>목표 달성!</t>
         </is>
       </c>
       <c r="D479" s="6" t="inlineStr">
         <is>
-          <t>x10 uses the same odds for each draw</t>
+          <t>Goal reached!</t>
         </is>
       </c>
       <c r="E479" s="1" t="n"/>
@@ -9674,17 +9674,17 @@
       <c r="A480" s="1" t="n"/>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Wait</t>
+          <t>UI.Enchant.AutoEndSummary</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
         <is>
-          <t>가챠 {0}회</t>
+          <t>{0} — {1} {2}개 사용.</t>
         </is>
       </c>
       <c r="D480" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0}</t>
+          <t>{0} — used {2} {1}.</t>
         </is>
       </c>
       <c r="E480" s="1" t="n"/>
@@ -9693,17 +9693,17 @@
       <c r="A481" s="1" t="n"/>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Source</t>
+          <t>UI.Enchant.TargetGrade</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
         <is>
-          <t>가챠</t>
+          <t>목표 등급</t>
         </is>
       </c>
       <c r="D481" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Target Grade</t>
         </is>
       </c>
       <c r="E481" s="1" t="n"/>
@@ -9712,17 +9712,17 @@
       <c r="A482" s="1" t="n"/>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceBox</t>
+          <t>UI.Enchant.FocusOption</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>상자 개봉</t>
+          <t>노릴 옵션</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
         <is>
-          <t>Box Opening</t>
+          <t>Aim For</t>
         </is>
       </c>
       <c r="E482" s="1" t="n"/>
@@ -9731,17 +9731,17 @@
       <c r="A483" s="1" t="n"/>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceMail</t>
+          <t>UI.Enchant.Combo</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
         <is>
-          <t>우편 수령</t>
+          <t>조합</t>
         </is>
       </c>
       <c r="D483" s="6" t="inlineStr">
         <is>
-          <t>Mail Claim</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="E483" s="1" t="n"/>
@@ -9750,17 +9750,17 @@
       <c r="A484" s="1" t="n"/>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.ResultTitle</t>
+          <t>UI.Enchant.Cap</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
         <is>
-          <t>{0} 결과</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="D484" s="6" t="inlineStr">
         <is>
-          <t>{0} Results</t>
+          <t>Limit</t>
         </is>
       </c>
       <c r="E484" s="1" t="n"/>
@@ -9769,17 +9769,17 @@
       <c r="A485" s="1" t="n"/>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.DrawAgain</t>
+          <t>UI.Enchant.Select</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
         <is>
-          <t>{0}회 더 뽑기</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0} Again</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E485" s="1" t="n"/>
@@ -9788,17 +9788,17 @@
       <c r="A486" s="1" t="n"/>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Tab</t>
+          <t>UI.Gacha.Times</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>{0}회</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>x{0}</t>
         </is>
       </c>
       <c r="E486" s="1" t="n"/>
@@ -9807,17 +9807,17 @@
       <c r="A487" s="1" t="n"/>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.CloseResult</t>
+          <t>UI.Gacha.Worker</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
         <is>
-          <t>[결과 닫기]</t>
+          <t>일꾼</t>
         </is>
       </c>
       <c r="D487" s="6" t="inlineStr">
         <is>
-          <t>[Close]</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="E487" s="1" t="n"/>
@@ -9826,17 +9826,17 @@
       <c r="A488" s="1" t="n"/>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Gacha.WorkSpeedUp</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>작업속도 증가</t>
         </is>
       </c>
       <c r="D488" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>Work Speed Up</t>
         </is>
       </c>
       <c r="E488" s="1" t="n"/>
@@ -9845,17 +9845,17 @@
       <c r="A489" s="1" t="n"/>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Gacha.Kinds</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>{0} {1}종</t>
         </is>
       </c>
       <c r="D489" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>{1} {0}</t>
         </is>
       </c>
       <c r="E489" s="1" t="n"/>
@@ -9864,17 +9864,17 @@
       <c r="A490" s="1" t="n"/>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Gacha.KindsOnly</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>{0}종</t>
         </is>
       </c>
       <c r="D490" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>{0} kinds</t>
         </is>
       </c>
       <c r="E490" s="1" t="n"/>
@@ -9883,17 +9883,17 @@
       <c r="A491" s="1" t="n"/>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Gacha.Item</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D491" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E491" s="1" t="n"/>
@@ -9902,17 +9902,17 @@
       <c r="A492" s="1" t="n"/>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Gacha.RateTitle</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>{0} 확률</t>
         </is>
       </c>
       <c r="D492" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>{0} Rates</t>
         </is>
       </c>
       <c r="E492" s="1" t="n"/>
@@ -9921,17 +9921,17 @@
       <c r="A493" s="1" t="n"/>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Gacha.NoEntries</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>뽑을 항목이 없다</t>
         </is>
       </c>
       <c r="D493" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Nothing to draw</t>
         </is>
       </c>
       <c r="E493" s="1" t="n"/>
@@ -9940,17 +9940,17 @@
       <c r="A494" s="1" t="n"/>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Gacha.NoRarity</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>등급 없음</t>
         </is>
       </c>
       <c r="D494" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>No Rarity</t>
         </is>
       </c>
       <c r="E494" s="1" t="n"/>
@@ -9959,17 +9959,17 @@
       <c r="A495" s="1" t="n"/>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Gacha.SameRate</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>10회도 한 번마다 같은 확률</t>
         </is>
       </c>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>x10 uses the same odds for each draw</t>
         </is>
       </c>
       <c r="E495" s="1" t="n"/>
@@ -9978,17 +9978,17 @@
       <c r="A496" s="1" t="n"/>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Gacha.Wait</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>가챠 {0}회</t>
         </is>
       </c>
       <c r="D496" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>Draw x{0}</t>
         </is>
       </c>
       <c r="E496" s="1" t="n"/>
@@ -9997,17 +9997,17 @@
       <c r="A497" s="1" t="n"/>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Gacha.Source</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>가챠</t>
         </is>
       </c>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E497" s="1" t="n"/>
@@ -10016,17 +10016,17 @@
       <c r="A498" s="1" t="n"/>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Gacha.SourceBox</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>상자 개봉</t>
         </is>
       </c>
       <c r="D498" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>Box Opening</t>
         </is>
       </c>
       <c r="E498" s="1" t="n"/>
@@ -10035,17 +10035,17 @@
       <c r="A499" s="1" t="n"/>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Gacha.SourceMail</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>우편 수령</t>
         </is>
       </c>
       <c r="D499" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Mail Claim</t>
         </is>
       </c>
       <c r="E499" s="1" t="n"/>
@@ -10054,17 +10054,17 @@
       <c r="A500" s="1" t="n"/>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Gacha.ResultTitle</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>{0} 결과</t>
         </is>
       </c>
       <c r="D500" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>{0} Results</t>
         </is>
       </c>
       <c r="E500" s="1" t="n"/>
@@ -10073,17 +10073,17 @@
       <c r="A501" s="1" t="n"/>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Gacha.DrawAgain</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>{0}회 더 뽑기</t>
         </is>
       </c>
       <c r="D501" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>Draw x{0} Again</t>
         </is>
       </c>
       <c r="E501" s="1" t="n"/>
@@ -10092,17 +10092,17 @@
       <c r="A502" s="1" t="n"/>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Gacha.Tab</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="D502" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E502" s="1" t="n"/>
@@ -10111,17 +10111,17 @@
       <c r="A503" s="1" t="n"/>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Gacha.CloseResult</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>[결과 닫기]</t>
         </is>
       </c>
       <c r="D503" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>[Close]</t>
         </is>
       </c>
       <c r="E503" s="1" t="n"/>
@@ -10130,17 +10130,17 @@
       <c r="A504" s="1" t="n"/>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D504" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E504" s="1" t="n"/>
@@ -10149,17 +10149,17 @@
       <c r="A505" s="1" t="n"/>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D505" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E505" s="1" t="n"/>
@@ -10168,17 +10168,17 @@
       <c r="A506" s="1" t="n"/>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D506" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E506" s="1" t="n"/>
@@ -10187,17 +10187,17 @@
       <c r="A507" s="1" t="n"/>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D507" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E507" s="1" t="n"/>
@@ -10206,17 +10206,17 @@
       <c r="A508" s="1" t="n"/>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D508" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E508" s="1" t="n"/>
@@ -10225,17 +10225,17 @@
       <c r="A509" s="1" t="n"/>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E509" s="1" t="n"/>
@@ -10244,17 +10244,17 @@
       <c r="A510" s="1" t="n"/>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D510" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E510" s="1" t="n"/>
@@ -10263,17 +10263,17 @@
       <c r="A511" s="1" t="n"/>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E511" s="1" t="n"/>
@@ -10282,17 +10282,17 @@
       <c r="A512" s="1" t="n"/>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E512" s="1" t="n"/>
@@ -10301,17 +10301,17 @@
       <c r="A513" s="1" t="n"/>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E513" s="1" t="n"/>
@@ -10320,17 +10320,17 @@
       <c r="A514" s="1" t="n"/>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D514" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E514" s="1" t="n"/>
@@ -10339,17 +10339,17 @@
       <c r="A515" s="1" t="n"/>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D515" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E515" s="1" t="n"/>
@@ -10358,17 +10358,17 @@
       <c r="A516" s="1" t="n"/>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D516" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E516" s="1" t="n"/>
@@ -10377,17 +10377,17 @@
       <c r="A517" s="1" t="n"/>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D517" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E517" s="1" t="n"/>
@@ -10396,17 +10396,17 @@
       <c r="A518" s="1" t="n"/>
       <c r="B518" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D518" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E518" s="1" t="n"/>
@@ -10415,17 +10415,17 @@
       <c r="A519" s="1" t="n"/>
       <c r="B519" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E519" s="1" t="n"/>
@@ -10434,17 +10434,17 @@
       <c r="A520" s="1" t="n"/>
       <c r="B520" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D520" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E520" s="1" t="n"/>
@@ -10453,17 +10453,17 @@
       <c r="A521" s="1" t="n"/>
       <c r="B521" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E521" s="1" t="n"/>
@@ -10472,17 +10472,17 @@
       <c r="A522" s="1" t="n"/>
       <c r="B522" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D522" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E522" s="1" t="n"/>
@@ -10491,17 +10491,17 @@
       <c r="A523" s="1" t="n"/>
       <c r="B523" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D523" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E523" s="1" t="n"/>
@@ -10510,17 +10510,17 @@
       <c r="A524" s="1" t="n"/>
       <c r="B524" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D524" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E524" s="1" t="n"/>
@@ -10529,17 +10529,17 @@
       <c r="A525" s="1" t="n"/>
       <c r="B525" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D525" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E525" s="1" t="n"/>
@@ -10548,17 +10548,17 @@
       <c r="A526" s="1" t="n"/>
       <c r="B526" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D526" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E526" s="1" t="n"/>
@@ -10567,17 +10567,17 @@
       <c r="A527" s="1" t="n"/>
       <c r="B527" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D527" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E527" s="1" t="n"/>
@@ -10586,17 +10586,17 @@
       <c r="A528" s="1" t="n"/>
       <c r="B528" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D528" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E528" s="1" t="n"/>
@@ -10605,17 +10605,17 @@
       <c r="A529" s="1" t="n"/>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D529" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E529" s="1" t="n"/>
@@ -10624,17 +10624,17 @@
       <c r="A530" s="1" t="n"/>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D530" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E530" s="1" t="n"/>
@@ -10643,17 +10643,17 @@
       <c r="A531" s="1" t="n"/>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D531" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E531" s="1" t="n"/>
@@ -10662,17 +10662,17 @@
       <c r="A532" s="1" t="n"/>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D532" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E532" s="1" t="n"/>
@@ -10681,17 +10681,17 @@
       <c r="A533" s="1" t="n"/>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D533" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E533" s="1" t="n"/>
@@ -10700,17 +10700,17 @@
       <c r="A534" s="1" t="n"/>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D534" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E534" s="1" t="n"/>
@@ -10719,17 +10719,17 @@
       <c r="A535" s="1" t="n"/>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D535" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E535" s="1" t="n"/>
@@ -10738,17 +10738,17 @@
       <c r="A536" s="1" t="n"/>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E536" s="1" t="n"/>
@@ -10757,17 +10757,17 @@
       <c r="A537" s="1" t="n"/>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E537" s="1" t="n"/>
@@ -10776,17 +10776,17 @@
       <c r="A538" s="1" t="n"/>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D538" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E538" s="1" t="n"/>
@@ -10795,17 +10795,17 @@
       <c r="A539" s="1" t="n"/>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D539" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E539" s="1" t="n"/>
@@ -10814,17 +10814,17 @@
       <c r="A540" s="1" t="n"/>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,17 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11631,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11650,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11669,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11688,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11707,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11726,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11745,17 +11745,17 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11764,17 +11764,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11783,19 +11783,17 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11804,17 +11802,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11823,17 +11821,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11842,17 +11840,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11861,17 +11859,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11880,17 +11878,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11899,17 +11897,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11918,17 +11916,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11937,17 +11935,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11956,17 +11954,17 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11975,17 +11973,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11994,19 +11992,17 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12015,17 +12011,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12034,19 +12030,17 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12055,17 +12049,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12074,17 +12068,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12093,17 +12087,19 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12112,17 +12108,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12131,17 +12127,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12150,17 +12146,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12169,17 +12165,17 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지 · 통째로만 팔립니다</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing · sold only as a whole</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E611" s="1" t="n"/>
@@ -12188,17 +12184,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12207,17 +12203,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12226,17 +12222,17 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12245,17 +12241,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12264,17 +12260,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12283,17 +12279,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12302,17 +12298,19 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12321,17 +12319,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12340,17 +12338,19 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12359,17 +12359,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12378,17 +12378,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12397,17 +12397,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12416,17 +12416,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12435,17 +12435,17 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12454,17 +12454,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12473,17 +12473,17 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Owned {0} · up to {1} per listing</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12492,17 +12492,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12511,17 +12511,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12530,17 +12530,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12549,17 +12549,17 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12568,17 +12568,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12587,19 +12587,17 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12608,17 +12606,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12627,17 +12625,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12646,17 +12644,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12665,17 +12663,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12684,17 +12682,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12703,17 +12701,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12722,17 +12720,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12741,17 +12739,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12760,17 +12758,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12779,17 +12777,17 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E643" s="1" t="n"/>
@@ -12798,17 +12796,17 @@
       <c r="A644" s="1" t="n"/>
       <c r="B644" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C644" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D644" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E644" s="1" t="n"/>
@@ -12817,17 +12815,17 @@
       <c r="A645" s="1" t="n"/>
       <c r="B645" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E645" s="1" t="n"/>
@@ -12836,17 +12834,17 @@
       <c r="A646" s="1" t="n"/>
       <c r="B646" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C646" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D646" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E646" s="1" t="n"/>
@@ -12855,17 +12853,17 @@
       <c r="A647" s="1" t="n"/>
       <c r="B647" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D647" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E647" s="1" t="n"/>
@@ -12874,17 +12872,17 @@
       <c r="A648" s="1" t="n"/>
       <c r="B648" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C648" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D648" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E648" s="1" t="n"/>
@@ -12893,19 +12891,19 @@
       <c r="A649" s="1" t="n"/>
       <c r="B649" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.
-끼고 있는 장비 · 일하는 캐릭터는 흐리게 보이고, 툴팁에 사유가 나옵니다.</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D649" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.
-Worn gear and working characters are dimmed — the tooltip shows why.</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E649" s="1" t="n"/>
@@ -12914,17 +12912,17 @@
       <c r="A650" s="1" t="n"/>
       <c r="B650" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C650" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D650" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E650" s="1" t="n"/>
@@ -12933,17 +12931,17 @@
       <c r="A651" s="1" t="n"/>
       <c r="B651" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C651" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E651" s="1" t="n"/>
@@ -12952,20 +12950,628 @@
       <c r="A652" s="1" t="n"/>
       <c r="B652" s="6" t="inlineStr">
         <is>
+          <t>UI.Auction.ChartTitle</t>
+        </is>
+      </c>
+      <c r="C652" s="6" t="inlineStr">
+        <is>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+        </is>
+      </c>
+      <c r="D652" s="6" t="inlineStr">
+        <is>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
+        </is>
+      </c>
+      <c r="E652" s="1" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n"/>
+      <c r="B653" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ChartEmpty</t>
+        </is>
+      </c>
+      <c r="C653" s="6" t="inlineStr">
+        <is>
+          <t>최근 14일 동안 거래가 없습니다</t>
+        </is>
+      </c>
+      <c r="D653" s="6" t="inlineStr">
+        <is>
+          <t>No trades in the last 14 days</t>
+        </is>
+      </c>
+      <c r="E653" s="1" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n"/>
+      <c r="B654" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.LevelsTitle</t>
+        </is>
+      </c>
+      <c r="C654" s="6" t="inlineStr">
+        <is>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+        </is>
+      </c>
+      <c r="D654" s="6" t="inlineStr">
+        <is>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
+        </is>
+      </c>
+      <c r="E654" s="1" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n"/>
+      <c r="B655" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.LevelsEmpty</t>
+        </is>
+      </c>
+      <c r="C655" s="6" t="inlineStr">
+        <is>
+          <t>지금 판매 중인 매물이 없습니다</t>
+        </is>
+      </c>
+      <c r="D655" s="6" t="inlineStr">
+        <is>
+          <t>Nothing on sale right now</t>
+        </is>
+      </c>
+      <c r="E655" s="1" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n"/>
+      <c r="B656" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RegisterOpen</t>
+        </is>
+      </c>
+      <c r="C656" s="6" t="inlineStr">
+        <is>
+          <t>+ 판매 등록</t>
+        </is>
+      </c>
+      <c r="D656" s="6" t="inlineStr">
+        <is>
+          <t>+ List Item</t>
+        </is>
+      </c>
+      <c r="E656" s="1" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n"/>
+      <c r="B657" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColItem</t>
+        </is>
+      </c>
+      <c r="C657" s="6" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+      <c r="D657" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="E657" s="1" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n"/>
+      <c r="B658" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColNet</t>
+        </is>
+      </c>
+      <c r="C658" s="6" t="inlineStr">
+        <is>
+          <t>팔리면 받는 금액</t>
+        </is>
+      </c>
+      <c r="D658" s="6" t="inlineStr">
+        <is>
+          <t>You Get If Sold</t>
+        </is>
+      </c>
+      <c r="E658" s="1" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n"/>
+      <c r="B659" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColDate</t>
+        </is>
+      </c>
+      <c r="C659" s="6" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="D659" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E659" s="1" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n"/>
+      <c r="B660" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColType</t>
+        </is>
+      </c>
+      <c r="C660" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D660" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E660" s="1" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n"/>
+      <c r="B661" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColAmount</t>
+        </is>
+      </c>
+      <c r="C661" s="6" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="D661" s="6" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E661" s="1" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n"/>
+      <c r="B662" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ColDest</t>
+        </is>
+      </c>
+      <c r="C662" s="6" t="inlineStr">
+        <is>
+          <t>받는 곳</t>
+        </is>
+      </c>
+      <c r="D662" s="6" t="inlineStr">
+        <is>
+          <t>Goes To</t>
+        </is>
+      </c>
+      <c r="E662" s="1" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n"/>
+      <c r="B663" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RegisterTitle</t>
+        </is>
+      </c>
+      <c r="C663" s="6" t="inlineStr">
+        <is>
+          <t>판매 등록</t>
+        </is>
+      </c>
+      <c r="D663" s="6" t="inlineStr">
+        <is>
+          <t>List an Item</t>
+        </is>
+      </c>
+      <c r="E663" s="1" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n"/>
+      <c r="B664" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.FindByName</t>
+        </is>
+      </c>
+      <c r="C664" s="6" t="inlineStr">
+        <is>
+          <t>이름으로 찾기</t>
+        </is>
+      </c>
+      <c r="D664" s="6" t="inlineStr">
+        <is>
+          <t>Find by name</t>
+        </is>
+      </c>
+      <c r="E664" s="1" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n"/>
+      <c r="B665" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RegisterEmptyCard</t>
+        </is>
+      </c>
+      <c r="C665" s="6" t="inlineStr">
+        <is>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
+        </is>
+      </c>
+      <c r="D665" s="6" t="inlineStr">
+        <is>
+          <t>[Select] something to list on the left.</t>
+        </is>
+      </c>
+      <c r="E665" s="1" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n"/>
+      <c r="B666" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.ShowPrice</t>
+        </is>
+      </c>
+      <c r="C666" s="6" t="inlineStr">
+        <is>
+          <t>시세 보기</t>
+        </is>
+      </c>
+      <c r="D666" s="6" t="inlineStr">
+        <is>
+          <t>View Prices</t>
+        </is>
+      </c>
+      <c r="E666" s="1" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n"/>
+      <c r="B667" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.MatchLowest</t>
+        </is>
+      </c>
+      <c r="C667" s="6" t="inlineStr">
+        <is>
+          <t>최저가에 맞춤</t>
+        </is>
+      </c>
+      <c r="D667" s="6" t="inlineStr">
+        <is>
+          <t>Match Lowest</t>
+        </is>
+      </c>
+      <c r="E667" s="1" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n"/>
+      <c r="B668" s="6" t="inlineStr">
+        <is>
           <t>UI.Auction.Register</t>
         </is>
       </c>
-      <c r="C652" s="6" t="inlineStr">
+      <c r="C668" s="6" t="inlineStr">
         <is>
           <t>등록</t>
         </is>
       </c>
-      <c r="D652" s="6" t="inlineStr">
+      <c r="D668" s="6" t="inlineStr">
         <is>
           <t>List</t>
         </is>
       </c>
-      <c r="E652" s="1" t="n"/>
+      <c r="E668" s="1" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n"/>
+      <c r="B669" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.GuideTitle</t>
+        </is>
+      </c>
+      <c r="C669" s="6" t="inlineStr">
+        <is>
+          <t>경매장</t>
+        </is>
+      </c>
+      <c r="D669" s="6" t="inlineStr">
+        <is>
+          <t>Auction House</t>
+        </is>
+      </c>
+      <c r="E669" s="1" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n"/>
+      <c r="B670" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.GuideBuyWhole</t>
+        </is>
+      </c>
+      <c r="C670" s="6" t="inlineStr">
+        <is>
+          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
+        </is>
+      </c>
+      <c r="D670" s="6" t="inlineStr">
+        <is>
+          <t>Listings are bought whole — no partial purchases</t>
+        </is>
+      </c>
+      <c r="E670" s="1" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n"/>
+      <c r="B671" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.GuideBuyOwn</t>
+        </is>
+      </c>
+      <c r="C671" s="6" t="inlineStr">
+        <is>
+          <t>내 매물은 살 수 없습니다</t>
+        </is>
+      </c>
+      <c r="D671" s="6" t="inlineStr">
+        <is>
+          <t>You can't buy your own listings</t>
+        </is>
+      </c>
+      <c r="E671" s="1" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n"/>
+      <c r="B672" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.GuideMailHeader</t>
+        </is>
+      </c>
+      <c r="C672" s="6" t="inlineStr">
+        <is>
+          <t>우편</t>
+        </is>
+      </c>
+      <c r="D672" s="6" t="inlineStr">
+        <is>
+          <t>Mail</t>
+        </is>
+      </c>
+      <c r="E672" s="1" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n"/>
+      <c r="B673" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.GuideMail</t>
+        </is>
+      </c>
+      <c r="C673" s="6" t="inlineStr">
+        <is>
+          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
+        </is>
+      </c>
+      <c r="D673" s="6" t="inlineStr">
+        <is>
+          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
+        </is>
+      </c>
+      <c r="E673" s="1" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n"/>
+      <c r="B674" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.GuideSellHint</t>
+        </is>
+      </c>
+      <c r="C674" s="6" t="inlineStr">
+        <is>
+          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
+        </is>
+      </c>
+      <c r="D674" s="6" t="inlineStr">
+        <is>
+          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
+        </is>
+      </c>
+      <c r="E674" s="1" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n"/>
+      <c r="B675" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleAuction</t>
+        </is>
+      </c>
+      <c r="C675" s="6" t="inlineStr">
+        <is>
+          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
+        </is>
+      </c>
+      <c r="D675" s="6" t="inlineStr">
+        <is>
+          <t>Auction — sell to other players at your price · wait until it sells</t>
+        </is>
+      </c>
+      <c r="E675" s="1" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n"/>
+      <c r="B676" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleInstant</t>
+        </is>
+      </c>
+      <c r="C676" s="6" t="inlineStr">
+        <is>
+          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
+        </is>
+      </c>
+      <c r="D676" s="6" t="inlineStr">
+        <is>
+          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
+        </is>
+      </c>
+      <c r="E676" s="1" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n"/>
+      <c r="B677" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleHeader</t>
+        </is>
+      </c>
+      <c r="C677" s="6" t="inlineStr">
+        <is>
+          <t>등록 규칙</t>
+        </is>
+      </c>
+      <c r="D677" s="6" t="inlineStr">
+        <is>
+          <t>Listing Rules</t>
+        </is>
+      </c>
+      <c r="E677" s="1" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n"/>
+      <c r="B678" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RulePrice</t>
+        </is>
+      </c>
+      <c r="C678" s="6" t="inlineStr">
+        <is>
+          <t>즉시 판매가 이상 ~ {0} G</t>
+        </is>
+      </c>
+      <c r="D678" s="6" t="inlineStr">
+        <is>
+          <t>From the instant price ~ {0} G</t>
+        </is>
+      </c>
+      <c r="E678" s="1" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n"/>
+      <c r="B679" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleCountLabel</t>
+        </is>
+      </c>
+      <c r="C679" s="6" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D679" s="6" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="E679" s="1" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n"/>
+      <c r="B680" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleCount</t>
+        </is>
+      </c>
+      <c r="C680" s="6" t="inlineStr">
+        <is>
+          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
+        </is>
+      </c>
+      <c r="D680" s="6" t="inlineStr">
+        <is>
+          <t>Up to {0} per listing · sold only whole</t>
+        </is>
+      </c>
+      <c r="E680" s="1" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n"/>
+      <c r="B681" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleSlots</t>
+        </is>
+      </c>
+      <c r="C681" s="6" t="inlineStr">
+        <is>
+          <t>최대 {0}건</t>
+        </is>
+      </c>
+      <c r="D681" s="6" t="inlineStr">
+        <is>
+          <t>Up to {0}</t>
+        </is>
+      </c>
+      <c r="E681" s="1" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n"/>
+      <c r="B682" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleListingFee</t>
+        </is>
+      </c>
+      <c r="C682" s="6" t="inlineStr">
+        <is>
+          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+        </is>
+      </c>
+      <c r="D682" s="6" t="inlineStr">
+        <is>
+          <t>Paid on listing · refunded on expiry, not on cancel</t>
+        </is>
+      </c>
+      <c r="E682" s="1" t="n"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n"/>
+      <c r="B683" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleSaleFee</t>
+        </is>
+      </c>
+      <c r="C683" s="6" t="inlineStr">
+        <is>
+          <t>팔린 금액에서 뗌</t>
+        </is>
+      </c>
+      <c r="D683" s="6" t="inlineStr">
+        <is>
+          <t>Deducted from the sale</t>
+        </is>
+      </c>
+      <c r="E683" s="1" t="n"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n"/>
+      <c r="B684" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleCantList</t>
+        </is>
+      </c>
+      <c r="C684" s="6" t="inlineStr">
+        <is>
+          <t>끼고 있는 장비 · 일하는 캐릭터 · 잠긴 것은 올릴 수 없습니다 (흐린 줄 — 올리면 사유)</t>
+        </is>
+      </c>
+      <c r="D684" s="6" t="inlineStr">
+        <is>
+          <t>Worn gear, working characters and locked items can't be listed (dimmed — hover for why)</t>
+        </is>
+      </c>
+      <c r="E684" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E684"/>
+  <dimension ref="A1:E691"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6415,17 +6415,17 @@
       <c r="A309" s="1" t="n"/>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CantList</t>
+          <t>UI.Inventory.WaitMerge</t>
         </is>
       </c>
       <c r="C309" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없습니다 — {0}</t>
+          <t>{0} 합치기</t>
         </is>
       </c>
       <c r="D309" s="6" t="inlineStr">
         <is>
-          <t>Can't list — {0}</t>
+          <t>Merge {0}</t>
         </is>
       </c>
       <c r="E309" s="1" t="n"/>
@@ -6434,17 +6434,17 @@
       <c r="A310" s="1" t="n"/>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.CantSell</t>
+          <t>UI.Inventory.CantList</t>
         </is>
       </c>
       <c r="C310" s="6" t="inlineStr">
         <is>
-          <t>팔 수 없습니다 — {0}</t>
+          <t>올릴 수 없습니다 — {0}</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Can't sell — {0}</t>
+          <t>Can't list — {0}</t>
         </is>
       </c>
       <c r="E310" s="1" t="n"/>
@@ -6453,17 +6453,17 @@
       <c r="A311" s="1" t="n"/>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskSell</t>
+          <t>UI.Inventory.CantSell</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 팔까?</t>
+          <t>팔 수 없습니다 — {0}</t>
         </is>
       </c>
       <c r="D311" s="6" t="inlineStr">
         <is>
-          <t>How many to sell?</t>
+          <t>Can't sell — {0}</t>
         </is>
       </c>
       <c r="E311" s="1" t="n"/>
@@ -6472,17 +6472,17 @@
       <c r="A312" s="1" t="n"/>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskOpen</t>
+          <t>UI.Inventory.AskSell</t>
         </is>
       </c>
       <c r="C312" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 열까?</t>
+          <t>몇 개를 팔까?</t>
         </is>
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>How many to open?</t>
+          <t>How many to sell?</t>
         </is>
       </c>
       <c r="E312" s="1" t="n"/>
@@ -6491,17 +6491,17 @@
       <c r="A313" s="1" t="n"/>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskStore</t>
+          <t>UI.Inventory.AskOpen</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 창고에 넣을까?</t>
+          <t>몇 개를 열까?</t>
         </is>
       </c>
       <c r="D313" s="6" t="inlineStr">
         <is>
-          <t>How many to store?</t>
+          <t>How many to open?</t>
         </is>
       </c>
       <c r="E313" s="1" t="n"/>
@@ -6510,17 +6510,17 @@
       <c r="A314" s="1" t="n"/>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.AskTakeOut</t>
+          <t>UI.Inventory.AskStore</t>
         </is>
       </c>
       <c r="C314" s="6" t="inlineStr">
         <is>
-          <t>몇 개를 꺼낼까?</t>
+          <t>몇 개를 창고에 넣을까?</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>How many to take out?</t>
+          <t>How many to store?</t>
         </is>
       </c>
       <c r="E314" s="1" t="n"/>
@@ -6529,17 +6529,17 @@
       <c r="A315" s="1" t="n"/>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitStore</t>
+          <t>UI.Inventory.AskTakeOut</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
         <is>
-          <t>창고에 넣기</t>
+          <t>몇 개를 꺼낼까?</t>
         </is>
       </c>
       <c r="D315" s="6" t="inlineStr">
         <is>
-          <t>Store in Warehouse</t>
+          <t>How many to take out?</t>
         </is>
       </c>
       <c r="E315" s="1" t="n"/>
@@ -6548,17 +6548,17 @@
       <c r="A316" s="1" t="n"/>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitTakeOut</t>
+          <t>UI.Inventory.WaitStore</t>
         </is>
       </c>
       <c r="C316" s="6" t="inlineStr">
         <is>
-          <t>창고에서 꺼내기</t>
+          <t>창고에 넣기</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>Take Out of Warehouse</t>
+          <t>Store in Warehouse</t>
         </is>
       </c>
       <c r="E316" s="1" t="n"/>
@@ -6567,17 +6567,17 @@
       <c r="A317" s="1" t="n"/>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.WaitOpenBox</t>
+          <t>UI.Inventory.WaitTakeOut</t>
         </is>
       </c>
       <c r="C317" s="6" t="inlineStr">
         <is>
-          <t>상자 개봉 {0}개</t>
+          <t>창고에서 꺼내기</t>
         </is>
       </c>
       <c r="D317" s="6" t="inlineStr">
         <is>
-          <t>Open {0} Box(es)</t>
+          <t>Take Out of Warehouse</t>
         </is>
       </c>
       <c r="E317" s="1" t="n"/>
@@ -6586,17 +6586,17 @@
       <c r="A318" s="1" t="n"/>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoMoveWhileFiltering</t>
+          <t>UI.Inventory.WaitOpenBox</t>
         </is>
       </c>
       <c r="C318" s="6" t="inlineStr">
         <is>
-          <t>찾기 중에는 칸을 옮길 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
+          <t>상자 개봉 {0}개</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>You can't move slots while searching. Clear the search first.</t>
+          <t>Open {0} Box(es)</t>
         </is>
       </c>
       <c r="E318" s="1" t="n"/>
@@ -6605,17 +6605,17 @@
       <c r="A319" s="1" t="n"/>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoDropWhileFiltering</t>
+          <t>UI.Inventory.NoMoveWhileFiltering</t>
         </is>
       </c>
       <c r="C319" s="6" t="inlineStr">
         <is>
-          <t>찾기 중에는 넣을 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
+          <t>찾기 중에는 칸을 옮길 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
         </is>
       </c>
       <c r="D319" s="6" t="inlineStr">
         <is>
-          <t>You can't drop items while searching. Clear the search first.</t>
+          <t>You can't move slots while searching. Clear the search first.</t>
         </is>
       </c>
       <c r="E319" s="1" t="n"/>
@@ -6624,17 +6624,17 @@
       <c r="A320" s="1" t="n"/>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoEmptySlot</t>
+          <t>UI.Inventory.NoDropWhileFiltering</t>
         </is>
       </c>
       <c r="C320" s="6" t="inlineStr">
         <is>
-          <t>{0}에 빈 칸이 없습니다.</t>
+          <t>찾기 중에는 넣을 수 없습니다. 찾기를 비운 뒤 옮겨 주세요.</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>No empty slot in {0}.</t>
+          <t>You can't drop items while searching. Clear the search first.</t>
         </is>
       </c>
       <c r="E320" s="1" t="n"/>
@@ -6643,19 +6643,17 @@
       <c r="A321" s="1" t="n"/>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.RewardToMail</t>
+          <t>UI.Inventory.NoEmptySlot</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
         <is>
-          <t>인벤토리가 가득 차 보상을 우편함에 보관했습니다.
-우편함에서 받아 주세요.</t>
+          <t>{0}에 빈 칸이 없습니다.</t>
         </is>
       </c>
       <c r="D321" s="6" t="inlineStr">
         <is>
-          <t>Inventory is full, so rewards were sent to your mailbox.
-Claim them from the mailbox.</t>
+          <t>No empty slot in {0}.</t>
         </is>
       </c>
       <c r="E321" s="1" t="n"/>
@@ -6664,17 +6662,19 @@
       <c r="A322" s="1" t="n"/>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.CartCount</t>
+          <t>UI.Inventory.RewardToMail</t>
         </is>
       </c>
       <c r="C322" s="6" t="inlineStr">
         <is>
-          <t>담은 수량</t>
+          <t>인벤토리가 가득 차 보상을 우편함에 보관했습니다.
+우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
-          <t>In Cart</t>
+          <t>Inventory is full, so rewards were sent to your mailbox.
+Claim them from the mailbox.</t>
         </is>
       </c>
       <c r="E322" s="1" t="n"/>
@@ -6683,17 +6683,17 @@
       <c r="A323" s="1" t="n"/>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Each</t>
+          <t>UI.Sell.CartCount</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
         <is>
-          <t>개당</t>
+          <t>담은 수량</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>In Cart</t>
         </is>
       </c>
       <c r="E323" s="1" t="n"/>
@@ -6702,17 +6702,17 @@
       <c r="A324" s="1" t="n"/>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.GoldToGet</t>
+          <t>UI.Sell.Each</t>
         </is>
       </c>
       <c r="C324" s="6" t="inlineStr">
         <is>
-          <t>받을 골드</t>
+          <t>개당</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>Gold to Receive</t>
+          <t>each</t>
         </is>
       </c>
       <c r="E324" s="1" t="n"/>
@@ -6721,17 +6721,17 @@
       <c r="A325" s="1" t="n"/>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.IfAuctioned</t>
+          <t>UI.Sell.GoldToGet</t>
         </is>
       </c>
       <c r="C325" s="6" t="inlineStr">
         <is>
-          <t>경매로 올리면</t>
+          <t>받을 골드</t>
         </is>
       </c>
       <c r="D325" s="6" t="inlineStr">
         <is>
-          <t>If Listed on Auction</t>
+          <t>Gold to Receive</t>
         </is>
       </c>
       <c r="E325" s="1" t="n"/>
@@ -6740,17 +6740,17 @@
       <c r="A326" s="1" t="n"/>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.UnitPrice</t>
+          <t>UI.Sell.IfAuctioned</t>
         </is>
       </c>
       <c r="C326" s="6" t="inlineStr">
         <is>
-          <t>개당 단가</t>
+          <t>경매로 올리면</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>unit price</t>
+          <t>If Listed on Auction</t>
         </is>
       </c>
       <c r="E326" s="1" t="n"/>
@@ -6759,17 +6759,17 @@
       <c r="A327" s="1" t="n"/>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.SetInAuction</t>
+          <t>UI.Sell.UnitPrice</t>
         </is>
       </c>
       <c r="C327" s="6" t="inlineStr">
         <is>
-          <t>경매장 [등록] 탭에서 직접 정합니다</t>
+          <t>개당 단가</t>
         </is>
       </c>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>Set it yourself in the Auction [List] tab</t>
+          <t>unit price</t>
         </is>
       </c>
       <c r="E327" s="1" t="n"/>
@@ -6778,17 +6778,17 @@
       <c r="A328" s="1" t="n"/>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Total</t>
+          <t>UI.Sell.SetInAuction</t>
         </is>
       </c>
       <c r="C328" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매 {0} G</t>
+          <t>경매장 [등록] 탭에서 직접 정합니다</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>Instant Sell {0} G</t>
+          <t>Set it yourself in the Auction [List] tab</t>
         </is>
       </c>
       <c r="E328" s="1" t="n"/>
@@ -6797,17 +6797,17 @@
       <c r="A329" s="1" t="n"/>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Wait</t>
+          <t>UI.Sell.Total</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
         <is>
-          <t>판매</t>
+          <t>즉시 판매 {0} G</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Instant Sell {0} G</t>
         </is>
       </c>
       <c r="E329" s="1" t="n"/>
@@ -6816,17 +6816,17 @@
       <c r="A330" s="1" t="n"/>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SortRarity</t>
+          <t>UI.Sell.Wait</t>
         </is>
       </c>
       <c r="C330" s="6" t="inlineStr">
         <is>
-          <t>등급순</t>
+          <t>판매</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>By Rarity</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="E330" s="1" t="n"/>
@@ -6835,17 +6835,17 @@
       <c r="A331" s="1" t="n"/>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SortName</t>
+          <t>UI.Tool.SortRarity</t>
         </is>
       </c>
       <c r="C331" s="6" t="inlineStr">
         <is>
-          <t>이름순</t>
+          <t>등급순</t>
         </is>
       </c>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>By Name</t>
+          <t>By Rarity</t>
         </is>
       </c>
       <c r="E331" s="1" t="n"/>
@@ -6854,17 +6854,17 @@
       <c r="A332" s="1" t="n"/>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SortCount</t>
+          <t>UI.Tool.SortName</t>
         </is>
       </c>
       <c r="C332" s="6" t="inlineStr">
         <is>
-          <t>수량순</t>
+          <t>이름순</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>By Count</t>
+          <t>By Name</t>
         </is>
       </c>
       <c r="E332" s="1" t="n"/>
@@ -6873,17 +6873,17 @@
       <c r="A333" s="1" t="n"/>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.RarityOrBelow</t>
+          <t>UI.Tool.SortCount</t>
         </is>
       </c>
       <c r="C333" s="6" t="inlineStr">
         <is>
-          <t>{0} 이하</t>
+          <t>수량순</t>
         </is>
       </c>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>{0} or lower</t>
+          <t>By Count</t>
         </is>
       </c>
       <c r="E333" s="1" t="n"/>
@@ -6892,17 +6892,17 @@
       <c r="A334" s="1" t="n"/>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.AllRarities</t>
+          <t>UI.Tool.RarityOrBelow</t>
         </is>
       </c>
       <c r="C334" s="6" t="inlineStr">
         <is>
-          <t>등급 전체</t>
+          <t>{0} 이하</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>All Rarities</t>
+          <t>{0} or lower</t>
         </is>
       </c>
       <c r="E334" s="1" t="n"/>
@@ -6911,17 +6911,17 @@
       <c r="A335" s="1" t="n"/>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.AllGroups</t>
+          <t>UI.Tool.AllRarities</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
         <is>
-          <t>분류 전체</t>
+          <t>등급 전체</t>
         </is>
       </c>
       <c r="D335" s="6" t="inlineStr">
         <is>
-          <t>All Categories</t>
+          <t>All Rarities</t>
         </is>
       </c>
       <c r="E335" s="1" t="n"/>
@@ -6930,17 +6930,17 @@
       <c r="A336" s="1" t="n"/>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.AllIndustries</t>
+          <t>UI.Tool.AllGroups</t>
         </is>
       </c>
       <c r="C336" s="6" t="inlineStr">
         <is>
-          <t>산업 전체</t>
+          <t>분류 전체</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
-          <t>All Industries</t>
+          <t>All Categories</t>
         </is>
       </c>
       <c r="E336" s="1" t="n"/>
@@ -6949,17 +6949,17 @@
       <c r="A337" s="1" t="n"/>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NoneToAdd</t>
+          <t>UI.Tool.AllIndustries</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
         <is>
-          <t>{0} 이하로 담을 {1}이(가) 없습니다.</t>
+          <t>산업 전체</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
         <is>
-          <t>No {1} at {0} or lower to add.</t>
+          <t>All Industries</t>
         </is>
       </c>
       <c r="E337" s="1" t="n"/>
@@ -6968,17 +6968,17 @@
       <c r="A338" s="1" t="n"/>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.Added</t>
+          <t>UI.Tool.NoneToAdd</t>
         </is>
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}을(를) 담았습니다.</t>
+          <t>{0} 이하로 담을 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
         <is>
-          <t>Added {1} {0}.</t>
+          <t>No {1} at {0} or lower to add.</t>
         </is>
       </c>
       <c r="E338" s="1" t="n"/>
@@ -6987,17 +6987,17 @@
       <c r="A339" s="1" t="n"/>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.KindResource</t>
+          <t>UI.Tool.Added</t>
         </is>
       </c>
       <c r="C339" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>{0} {1}을(를) 담았습니다.</t>
         </is>
       </c>
       <c r="D339" s="6" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>Added {1} {0}.</t>
         </is>
       </c>
       <c r="E339" s="1" t="n"/>
@@ -7006,17 +7006,17 @@
       <c r="A340" s="1" t="n"/>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.KindCharacter</t>
+          <t>UI.Tool.KindResource</t>
         </is>
       </c>
       <c r="C340" s="6" t="inlineStr">
         <is>
-          <t>캐릭터</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>characters</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="E340" s="1" t="n"/>
@@ -7025,17 +7025,17 @@
       <c r="A341" s="1" t="n"/>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.KindEquip</t>
+          <t>UI.Tool.KindCharacter</t>
         </is>
       </c>
       <c r="C341" s="6" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>캐릭터</t>
         </is>
       </c>
       <c r="D341" s="6" t="inlineStr">
         <is>
-          <t>gear</t>
+          <t>characters</t>
         </is>
       </c>
       <c r="E341" s="1" t="n"/>
@@ -7044,17 +7044,17 @@
       <c r="A342" s="1" t="n"/>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NItem</t>
+          <t>UI.Tool.KindEquip</t>
         </is>
       </c>
       <c r="C342" s="6" t="inlineStr">
         <is>
-          <t>{0}종</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="D342" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>gear</t>
         </is>
       </c>
       <c r="E342" s="1" t="n"/>
@@ -7063,12 +7063,12 @@
       <c r="A343" s="1" t="n"/>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NCharacter</t>
+          <t>UI.Tool.NItem</t>
         </is>
       </c>
       <c r="C343" s="6" t="inlineStr">
         <is>
-          <t>{0}명</t>
+          <t>{0}종</t>
         </is>
       </c>
       <c r="D343" s="6" t="inlineStr">
@@ -7082,12 +7082,12 @@
       <c r="A344" s="1" t="n"/>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.NEquip</t>
+          <t>UI.Tool.NCharacter</t>
         </is>
       </c>
       <c r="C344" s="6" t="inlineStr">
         <is>
-          <t>{0}개</t>
+          <t>{0}명</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
@@ -7101,17 +7101,17 @@
       <c r="A345" s="1" t="n"/>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.LockedN</t>
+          <t>UI.Tool.NEquip</t>
         </is>
       </c>
       <c r="C345" s="6" t="inlineStr">
         <is>
-          <t>잠금 {0}</t>
+          <t>{0}개</t>
         </is>
       </c>
       <c r="D345" s="6" t="inlineStr">
         <is>
-          <t>{0} locked</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E345" s="1" t="n"/>
@@ -7120,17 +7120,17 @@
       <c r="A346" s="1" t="n"/>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.ExcludedWrap</t>
+          <t>UI.Tool.LockedN</t>
         </is>
       </c>
       <c r="C346" s="6" t="inlineStr">
         <is>
-          <t>({0} 제외)</t>
+          <t>잠금 {0}</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
         <is>
-          <t>(excluded: {0})</t>
+          <t>{0} locked</t>
         </is>
       </c>
       <c r="E346" s="1" t="n"/>
@@ -7139,17 +7139,17 @@
       <c r="A347" s="1" t="n"/>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SkippedWrap</t>
+          <t>UI.Tool.ExcludedWrap</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
         <is>
-          <t>({0} 제외 — [제외]에서 체크를 풀면 함께 담깁니다)</t>
+          <t>({0} 제외)</t>
         </is>
       </c>
       <c r="D347" s="6" t="inlineStr">
         <is>
-          <t>(excluded: {0} — uncheck them in [Exclude] to include)</t>
+          <t>(excluded: {0})</t>
         </is>
       </c>
       <c r="E347" s="1" t="n"/>
@@ -7158,17 +7158,17 @@
       <c r="A348" s="1" t="n"/>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.UnlockHint</t>
+          <t>UI.Tool.SkippedWrap</t>
         </is>
       </c>
       <c r="C348" s="6" t="inlineStr">
         <is>
-          <t>잠금은 Ctrl+좌클릭으로 풀 수 있습니다.</t>
+          <t>({0} 제외 — [제외]에서 체크를 풀면 함께 담깁니다)</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Left-click to unlock.</t>
+          <t>(excluded: {0} — uncheck them in [Exclude] to include)</t>
         </is>
       </c>
       <c r="E348" s="1" t="n"/>
@@ -7177,17 +7177,17 @@
       <c r="A349" s="1" t="n"/>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.CharacterBlocked</t>
+          <t>UI.Tool.UnlockHint</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
         <is>
-          <t>배치 중 · 장비 착용 · 마지막 캐릭터</t>
+          <t>잠금은 Ctrl+좌클릭으로 풀 수 있습니다.</t>
         </is>
       </c>
       <c r="D349" s="6" t="inlineStr">
         <is>
-          <t>assigned · wearing gear · last character</t>
+          <t>Ctrl+Left-click to unlock.</t>
         </is>
       </c>
       <c r="E349" s="1" t="n"/>
@@ -7196,17 +7196,17 @@
       <c r="A350" s="1" t="n"/>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.EquipBlocked</t>
+          <t>UI.Tool.CharacterBlocked</t>
         </is>
       </c>
       <c r="C350" s="6" t="inlineStr">
         <is>
-          <t>캐릭터가 끼고 있는 장비</t>
+          <t>배치 중 · 장비 착용 · 마지막 캐릭터</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
         <is>
-          <t>equipped by a character</t>
+          <t>assigned · wearing gear · last character</t>
         </is>
       </c>
       <c r="E350" s="1" t="n"/>
@@ -7215,17 +7215,17 @@
       <c r="A351" s="1" t="n"/>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.ExcludeNone</t>
+          <t>UI.Tool.EquipBlocked</t>
         </is>
       </c>
       <c r="C351" s="6" t="inlineStr">
         <is>
-          <t>제외 없음</t>
+          <t>캐릭터가 끼고 있는 장비</t>
         </is>
       </c>
       <c r="D351" s="6" t="inlineStr">
         <is>
-          <t>No Exclusions</t>
+          <t>equipped by a character</t>
         </is>
       </c>
       <c r="E351" s="1" t="n"/>
@@ -7234,17 +7234,17 @@
       <c r="A352" s="1" t="n"/>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.ExcludeCount</t>
+          <t>UI.Tool.ExcludeNone</t>
         </is>
       </c>
       <c r="C352" s="6" t="inlineStr">
         <is>
-          <t>제외 {0}</t>
+          <t>제외 없음</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>Exclude {0}</t>
+          <t>No Exclusions</t>
         </is>
       </c>
       <c r="E352" s="1" t="n"/>
@@ -7253,17 +7253,17 @@
       <c r="A353" s="1" t="n"/>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.TabResource</t>
+          <t>UI.Tool.ExcludeCount</t>
         </is>
       </c>
       <c r="C353" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>제외 {0}</t>
         </is>
       </c>
       <c r="D353" s="6" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>Exclude {0}</t>
         </is>
       </c>
       <c r="E353" s="1" t="n"/>
@@ -7272,17 +7272,17 @@
       <c r="A354" s="1" t="n"/>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.TabTrait</t>
+          <t>UI.Inventory.TabResource</t>
         </is>
       </c>
       <c r="C354" s="6" t="inlineStr">
         <is>
-          <t>특성</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>Traits</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="E354" s="1" t="n"/>
@@ -7291,17 +7291,17 @@
       <c r="A355" s="1" t="n"/>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.BulkAdd</t>
+          <t>UI.Inventory.TabTrait</t>
         </is>
       </c>
       <c r="C355" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>특성</t>
         </is>
       </c>
       <c r="D355" s="6" t="inlineStr">
         <is>
-          <t>Add to Sell</t>
+          <t>Traits</t>
         </is>
       </c>
       <c r="E355" s="1" t="n"/>
@@ -7310,17 +7310,17 @@
       <c r="A356" s="1" t="n"/>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.SearchName</t>
+          <t>UI.Tool.BulkAdd</t>
         </is>
       </c>
       <c r="C356" s="6" t="inlineStr">
         <is>
-          <t>이름 검색</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
         <is>
-          <t>Search name</t>
+          <t>Add to Sell</t>
         </is>
       </c>
       <c r="E356" s="1" t="n"/>
@@ -7329,17 +7329,17 @@
       <c r="A357" s="1" t="n"/>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>UI.Tool.Reset</t>
+          <t>UI.Tool.SearchName</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
         <is>
-          <t>초기화</t>
+          <t>이름 검색</t>
         </is>
       </c>
       <c r="D357" s="6" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>Search name</t>
         </is>
       </c>
       <c r="E357" s="1" t="n"/>
@@ -7348,17 +7348,17 @@
       <c r="A358" s="1" t="n"/>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.NoMatch</t>
+          <t>UI.Tool.Reset</t>
         </is>
       </c>
       <c r="C358" s="6" t="inlineStr">
         <is>
-          <t>조건에 맞는 항목이 없습니다</t>
+          <t>초기화</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="E358" s="1" t="n"/>
@@ -7367,17 +7367,17 @@
       <c r="A359" s="1" t="n"/>
       <c r="B359" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Empty</t>
+          <t>UI.Tool.Merge</t>
         </is>
       </c>
       <c r="C359" s="6" t="inlineStr">
         <is>
-          <t>자원을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다</t>
+          <t>합치기</t>
         </is>
       </c>
       <c r="D359" s="6" t="inlineStr">
         <is>
-          <t>Right-click items to add — they sell instantly at the instant sell price</t>
+          <t>Merge</t>
         </is>
       </c>
       <c r="E359" s="1" t="n"/>
@@ -7386,17 +7386,17 @@
       <c r="A360" s="1" t="n"/>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.Clear</t>
+          <t>UI.Tool.MergeTip</t>
         </is>
       </c>
       <c r="C360" s="6" t="inlineStr">
         <is>
-          <t>비우기</t>
+          <t>같은 자원이 여러 칸에 나뉘어 있으면 앞 칸부터 가득 채워 합칩니다 — 칸 순서는 그대로이고 비게 된 칸은 빈 칸으로 남습니다</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Combines split stacks of the same resource, filling the earliest slot first — slot order stays and emptied slots are left blank</t>
         </is>
       </c>
       <c r="E360" s="1" t="n"/>
@@ -7405,17 +7405,17 @@
       <c r="A361" s="1" t="n"/>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.HighRarity</t>
+          <t>UI.Tool.NothingToMerge</t>
         </is>
       </c>
       <c r="C361" s="6" t="inlineStr">
         <is>
-          <t>주의! 상위 등급 포함</t>
+          <t>합칠 칸이 없습니다.</t>
         </is>
       </c>
       <c r="D361" s="6" t="inlineStr">
         <is>
-          <t>Caution! Includes high rarity</t>
+          <t>Nothing to merge.</t>
         </is>
       </c>
       <c r="E361" s="1" t="n"/>
@@ -7424,17 +7424,17 @@
       <c r="A362" s="1" t="n"/>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.GrownWarning</t>
+          <t>UI.Inventory.NoMatch</t>
         </is>
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
-          <t>주의! 성장한 개체 {0}개 포함</t>
+          <t>조건에 맞는 항목이 없습니다</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>Caution! Includes {0} upgraded</t>
+          <t>Nothing matches</t>
         </is>
       </c>
       <c r="E362" s="1" t="n"/>
@@ -7443,17 +7443,17 @@
       <c r="A363" s="1" t="n"/>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.InstantSell</t>
+          <t>UI.Sell.Empty</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매</t>
+          <t>자원을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
         <is>
-          <t>Instant Sell</t>
+          <t>Right-click items to add — they sell instantly at the instant sell price</t>
         </is>
       </c>
       <c r="E363" s="1" t="n"/>
@@ -7462,17 +7462,17 @@
       <c r="A364" s="1" t="n"/>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.MarkSell</t>
+          <t>UI.Sell.Clear</t>
         </is>
       </c>
       <c r="C364" s="6" t="inlineStr">
         <is>
-          <t>판</t>
+          <t>비우기</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="E364" s="1" t="n"/>
@@ -7481,17 +7481,17 @@
       <c r="A365" s="1" t="n"/>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.MarkAssign</t>
+          <t>UI.Sell.HighRarity</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>주의! 상위 등급 포함</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Caution! Includes high rarity</t>
         </is>
       </c>
       <c r="E365" s="1" t="n"/>
@@ -7500,17 +7500,17 @@
       <c r="A366" s="1" t="n"/>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>UI.Inventory.PendingSelect</t>
+          <t>UI.Sell.GrownWarning</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
         <is>
-          <t>선택 대기</t>
+          <t>주의! 성장한 개체 {0}개 포함</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Caution! Includes {0} upgraded</t>
         </is>
       </c>
       <c r="E366" s="1" t="n"/>
@@ -7519,17 +7519,17 @@
       <c r="A367" s="1" t="n"/>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>UI.Common.Waiting</t>
+          <t>UI.Sell.InstantSell</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
         <is>
-          <t>응답을 기다리는 중</t>
+          <t>즉시 판매</t>
         </is>
       </c>
       <c r="D367" s="6" t="inlineStr">
         <is>
-          <t>Waiting for response</t>
+          <t>Instant Sell</t>
         </is>
       </c>
       <c r="E367" s="1" t="n"/>
@@ -7538,17 +7538,17 @@
       <c r="A368" s="1" t="n"/>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.AlreadyMax</t>
+          <t>UI.Inventory.MarkSell</t>
         </is>
       </c>
       <c r="C368" s="6" t="inlineStr">
         <is>
-          <t>이미 최고 단계입니다 — 더 넣을 수 없습니다.</t>
+          <t>판</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>Already at the top stage — nothing more can be added.</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E368" s="1" t="n"/>
@@ -7557,17 +7557,17 @@
       <c r="A369" s="1" t="n"/>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.BusyMaterial</t>
+          <t>UI.Inventory.MarkAssign</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
-          <t>배치됐거나 장비를 낀 캐릭터는 재료로 넣을 수 없습니다.</t>
+          <t>배</t>
         </is>
       </c>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>Assigned or geared characters can't be used as material.</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E369" s="1" t="n"/>
@@ -7576,17 +7576,17 @@
       <c r="A370" s="1" t="n"/>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.LockedMaterial</t>
+          <t>UI.Inventory.PendingSelect</t>
         </is>
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>잠긴 캐릭터는 재료로 넣을 수 없습니다 — Ctrl+좌클릭으로 풀 수 있습니다.</t>
+          <t>선택 대기</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
         <is>
-          <t>Locked characters can't be used as material — Ctrl+Left-click to unlock.</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E370" s="1" t="n"/>
@@ -7595,17 +7595,17 @@
       <c r="A371" s="1" t="n"/>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Info</t>
+          <t>UI.Common.Waiting</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
         <is>
-          <t>응축 누적 {0} / {1}</t>
+          <t>응답을 기다리는 중</t>
         </is>
       </c>
       <c r="D371" s="6" t="inlineStr">
         <is>
-          <t>Condensed {0} / {1}</t>
+          <t>Waiting for response</t>
         </is>
       </c>
       <c r="E371" s="1" t="n"/>
@@ -7614,17 +7614,17 @@
       <c r="A372" s="1" t="n"/>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Now</t>
+          <t>UI.Condense.AlreadyMax</t>
         </is>
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
-          <t>지금 {0}성</t>
+          <t>이미 최고 단계입니다 — 더 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
-          <t>Now {0}★</t>
+          <t>Already at the top stage — nothing more can be added.</t>
         </is>
       </c>
       <c r="E372" s="1" t="n"/>
@@ -7633,17 +7633,17 @@
       <c r="A373" s="1" t="n"/>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.After</t>
+          <t>UI.Condense.BusyMaterial</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
         <is>
-          <t>응축 후 {0}성</t>
+          <t>배치됐거나 장비를 낀 캐릭터는 재료로 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D373" s="6" t="inlineStr">
         <is>
-          <t>After {0}★</t>
+          <t>Assigned or geared characters can't be used as material.</t>
         </is>
       </c>
       <c r="E373" s="1" t="n"/>
@@ -7652,17 +7652,17 @@
       <c r="A374" s="1" t="n"/>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.TotalPlus</t>
+          <t>UI.Condense.LockedMaterial</t>
         </is>
       </c>
       <c r="C374" s="6" t="inlineStr">
         <is>
-          <t>누적 {0} + {1} = {2}</t>
+          <t>잠긴 캐릭터는 재료로 넣을 수 없습니다 — Ctrl+좌클릭으로 풀 수 있습니다.</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>Total {0} + {1} = {2}</t>
+          <t>Locked characters can't be used as material — Ctrl+Left-click to unlock.</t>
         </is>
       </c>
       <c r="E374" s="1" t="n"/>
@@ -7671,17 +7671,17 @@
       <c r="A375" s="1" t="n"/>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Total</t>
+          <t>UI.Condense.Info</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
-          <t>누적 {0}</t>
+          <t>응축 누적 {0} / {1}</t>
         </is>
       </c>
       <c r="D375" s="6" t="inlineStr">
         <is>
-          <t>Total {0}</t>
+          <t>Condensed {0} / {1}</t>
         </is>
       </c>
       <c r="E375" s="1" t="n"/>
@@ -7690,17 +7690,17 @@
       <c r="A376" s="1" t="n"/>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.MaxStage</t>
+          <t>UI.Condense.Now</t>
         </is>
       </c>
       <c r="C376" s="6" t="inlineStr">
         <is>
-          <t>최고 단계</t>
+          <t>지금 {0}성</t>
         </is>
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Max Stage</t>
+          <t>Now {0}★</t>
         </is>
       </c>
       <c r="E376" s="1" t="n"/>
@@ -7709,17 +7709,17 @@
       <c r="A377" s="1" t="n"/>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Reached</t>
+          <t>UI.Condense.After</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
-          <t>{0}성 도달</t>
+          <t>응축 후 {0}성</t>
         </is>
       </c>
       <c r="D377" s="6" t="inlineStr">
         <is>
-          <t>Reaches {0}★</t>
+          <t>After {0}★</t>
         </is>
       </c>
       <c r="E377" s="1" t="n"/>
@@ -7728,17 +7728,17 @@
       <c r="A378" s="1" t="n"/>
       <c r="B378" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ToNext</t>
+          <t>UI.Condense.TotalPlus</t>
         </is>
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
-          <t>{0}성까지 {1}</t>
+          <t>누적 {0} + {1} = {2}</t>
         </is>
       </c>
       <c r="D378" s="6" t="inlineStr">
         <is>
-          <t>{1} to {0}★</t>
+          <t>Total {0} + {1} = {2}</t>
         </is>
       </c>
       <c r="E378" s="1" t="n"/>
@@ -7747,17 +7747,17 @@
       <c r="A379" s="1" t="n"/>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Overflow</t>
+          <t>UI.Condense.Total</t>
         </is>
       </c>
       <c r="C379" s="6" t="inlineStr">
         <is>
-          <t>넘치는 재료 {0}마리는 효과 없이 사라집니다.</t>
+          <t>누적 {0}</t>
         </is>
       </c>
       <c r="D379" s="6" t="inlineStr">
         <is>
-          <t>{0} excess material(s) will be lost with no effect.</t>
+          <t>Total {0}</t>
         </is>
       </c>
       <c r="E379" s="1" t="n"/>
@@ -7766,17 +7766,17 @@
       <c r="A380" s="1" t="n"/>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialBusy</t>
+          <t>UI.Condense.MaxStage</t>
         </is>
       </c>
       <c r="C380" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다 — {1}마리는 배치·착용 중입니다.</t>
+          <t>최고 단계</t>
         </is>
       </c>
       <c r="D380" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material — {1} are assigned or geared.</t>
+          <t>Max Stage</t>
         </is>
       </c>
       <c r="E380" s="1" t="n"/>
@@ -7785,17 +7785,17 @@
       <c r="A381" s="1" t="n"/>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialSame</t>
+          <t>UI.Condense.Reached</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다 — 같은 캐릭터끼리만 응축됩니다.</t>
+          <t>{0}성 도달</t>
         </is>
       </c>
       <c r="D381" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material — only the same character can be condensed.</t>
+          <t>Reaches {0}★</t>
         </is>
       </c>
       <c r="E381" s="1" t="n"/>
@@ -7804,17 +7804,17 @@
       <c r="A382" s="1" t="n"/>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.BusyCount</t>
+          <t>UI.Condense.ToNext</t>
         </is>
       </c>
       <c r="C382" s="6" t="inlineStr">
         <is>
-          <t>배치·착용 중인 {0} {1}마리는 재료로 넣을 수 없습니다.</t>
+          <t>{0}성까지 {1}</t>
         </is>
       </c>
       <c r="D382" s="6" t="inlineStr">
         <is>
-          <t>{1} assigned or geared {0} can't be used as material.</t>
+          <t>{1} to {0}★</t>
         </is>
       </c>
       <c r="E382" s="1" t="n"/>
@@ -7823,17 +7823,17 @@
       <c r="A383" s="1" t="n"/>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickHint</t>
+          <t>UI.Condense.Overflow</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터 칸을 눌러 재료로 담으세요.</t>
+          <t>넘치는 재료 {0}마리는 효과 없이 사라집니다.</t>
         </is>
       </c>
       <c r="D383" s="6" t="inlineStr">
         <is>
-          <t>Click slots of the same character to add them as material.</t>
+          <t>{0} excess material(s) will be lost with no effect.</t>
         </is>
       </c>
       <c r="E383" s="1" t="n"/>
@@ -7842,17 +7842,17 @@
       <c r="A384" s="1" t="n"/>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickMaterial</t>
+          <t>UI.Condense.NoMaterialBusy</t>
         </is>
       </c>
       <c r="C384" s="6" t="inlineStr">
         <is>
-          <t>재료를 고르세요</t>
+          <t>재료로 넣을 {0}이(가) 없습니다 — {1}마리는 배치·착용 중입니다.</t>
         </is>
       </c>
       <c r="D384" s="6" t="inlineStr">
         <is>
-          <t>Choose Material</t>
+          <t>No {0} to use as material — {1} are assigned or geared.</t>
         </is>
       </c>
       <c r="E384" s="1" t="n"/>
@@ -7861,17 +7861,17 @@
       <c r="A385" s="1" t="n"/>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.Confirm</t>
+          <t>UI.Condense.NoMaterialSame</t>
         </is>
       </c>
       <c r="C385" s="6" t="inlineStr">
         <is>
-          <t>응축 ({0}마리)</t>
+          <t>재료로 넣을 {0}이(가) 없습니다 — 같은 캐릭터끼리만 응축됩니다.</t>
         </is>
       </c>
       <c r="D385" s="6" t="inlineStr">
         <is>
-          <t>Condense ({0})</t>
+          <t>No {0} to use as material — only the same character can be condensed.</t>
         </is>
       </c>
       <c r="E385" s="1" t="n"/>
@@ -7880,19 +7880,17 @@
       <c r="A386" s="1" t="n"/>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.NoMaterialNotice</t>
+          <t>UI.Condense.BusyCount</t>
         </is>
       </c>
       <c r="C386" s="6" t="inlineStr">
         <is>
-          <t>재료로 넣을 {0}이(가) 없습니다.
-같은 캐릭터끼리만 응축됩니다.</t>
+          <t>배치·착용 중인 {0} {1}마리는 재료로 넣을 수 없습니다.</t>
         </is>
       </c>
       <c r="D386" s="6" t="inlineStr">
         <is>
-          <t>No {0} to use as material.
-Only the same character can be condensed.</t>
+          <t>{1} assigned or geared {0} can't be used as material.</t>
         </is>
       </c>
       <c r="E386" s="1" t="n"/>
@@ -7901,17 +7899,17 @@
       <c r="A387" s="1" t="n"/>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.PickFirst</t>
+          <t>UI.Condense.PickHint</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터 칸을 눌러 재료를 먼저 고르세요.</t>
+          <t>같은 캐릭터 칸을 눌러 재료로 담으세요.</t>
         </is>
       </c>
       <c r="D387" s="6" t="inlineStr">
         <is>
-          <t>Click slots of the same character to choose material first.</t>
+          <t>Click slots of the same character to add them as material.</t>
         </is>
       </c>
       <c r="E387" s="1" t="n"/>
@@ -7920,17 +7918,17 @@
       <c r="A388" s="1" t="n"/>
       <c r="B388" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmText</t>
+          <t>UI.Condense.PickMaterial</t>
         </is>
       </c>
       <c r="C388" s="6" t="inlineStr">
         <is>
-          <t>재료 {0}마리를 녹여 {1}의 단계를 올립니다.</t>
+          <t>재료를 고르세요</t>
         </is>
       </c>
       <c r="D388" s="6" t="inlineStr">
         <is>
-          <t>Melt {0} material(s) to raise {1}'s stage.</t>
+          <t>Choose Material</t>
         </is>
       </c>
       <c r="E388" s="1" t="n"/>
@@ -7939,17 +7937,17 @@
       <c r="A389" s="1" t="n"/>
       <c r="B389" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmGrown</t>
+          <t>UI.Condense.Confirm</t>
         </is>
       </c>
       <c r="C389" s="6" t="inlineStr">
         <is>
-          <t>Lv{0} 이상 재료 {1}마리의 레벨·경험치는 사라집니다.</t>
+          <t>응축 ({0}마리)</t>
         </is>
       </c>
       <c r="D389" s="6" t="inlineStr">
         <is>
-          <t>Level and EXP of {1} material(s) at Lv{0}+ will be lost.</t>
+          <t>Condense ({0})</t>
         </is>
       </c>
       <c r="E389" s="1" t="n"/>
@@ -7958,17 +7956,19 @@
       <c r="A390" s="1" t="n"/>
       <c r="B390" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.ConfirmCondensed</t>
+          <t>UI.Condense.NoMaterialNotice</t>
         </is>
       </c>
       <c r="C390" s="6" t="inlineStr">
         <is>
-          <t>응축을 쌓은 재료 {0}마리의 응축 단계·누적도 사라집니다.</t>
+          <t>재료로 넣을 {0}이(가) 없습니다.
+같은 캐릭터끼리만 응축됩니다.</t>
         </is>
       </c>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>Condense progress of {0} material(s) will also be lost.</t>
+          <t>No {0} to use as material.
+Only the same character can be condensed.</t>
         </is>
       </c>
       <c r="E390" s="1" t="n"/>
@@ -7977,17 +7977,17 @@
       <c r="A391" s="1" t="n"/>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.FillNext</t>
+          <t>UI.Condense.PickFirst</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
         <is>
-          <t>다음 단계까지 채우기</t>
+          <t>같은 캐릭터 칸을 눌러 재료를 먼저 고르세요.</t>
         </is>
       </c>
       <c r="D391" s="6" t="inlineStr">
         <is>
-          <t>Fill to Next Stage</t>
+          <t>Click slots of the same character to choose material first.</t>
         </is>
       </c>
       <c r="E391" s="1" t="n"/>
@@ -7996,17 +7996,17 @@
       <c r="A392" s="1" t="n"/>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpTitle</t>
+          <t>UI.Condense.ConfirmText</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
         <is>
-          <t>응축</t>
+          <t>재료 {0}마리를 녹여 {1}의 단계를 올립니다.</t>
         </is>
       </c>
       <c r="D392" s="6" t="inlineStr">
         <is>
-          <t>Condense</t>
+          <t>Melt {0} material(s) to raise {1}'s stage.</t>
         </is>
       </c>
       <c r="E392" s="1" t="n"/>
@@ -8015,17 +8015,17 @@
       <c r="A393" s="1" t="n"/>
       <c r="B393" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpSame</t>
+          <t>UI.Condense.ConfirmGrown</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
         <is>
-          <t>같은 캐릭터를 재료로 녹여 누적을 쌓습니다 — 재료 1마리 = 누적 +1</t>
+          <t>Lv{0} 이상 재료 {1}마리의 레벨·경험치는 사라집니다.</t>
         </is>
       </c>
       <c r="D393" s="6" t="inlineStr">
         <is>
-          <t>Melt duplicates of the same character to build up the total — 1 material = +1</t>
+          <t>Level and EXP of {1} material(s) at Lv{0}+ will be lost.</t>
         </is>
       </c>
       <c r="E393" s="1" t="n"/>
@@ -8034,17 +8034,17 @@
       <c r="A394" s="1" t="n"/>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpStar</t>
+          <t>UI.Condense.ConfirmCondensed</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
         <is>
-          <t>누적이 단계 기준에 닿으면 ★이 오르고 작업속도가 늘어납니다</t>
+          <t>응축을 쌓은 재료 {0}마리의 응축 단계·누적도 사라집니다.</t>
         </is>
       </c>
       <c r="D394" s="6" t="inlineStr">
         <is>
-          <t>Reaching a stage total raises the stars and work speed</t>
+          <t>Condense progress of {0} material(s) will also be lost.</t>
         </is>
       </c>
       <c r="E394" s="1" t="n"/>
@@ -8053,17 +8053,17 @@
       <c r="A395" s="1" t="n"/>
       <c r="B395" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpLost</t>
+          <t>UI.Condense.FillNext</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
         <is>
-          <t>재료의 레벨 · 경험치 · 응축은 사라지고 되돌릴 수 없습니다</t>
+          <t>다음 단계까지 채우기</t>
         </is>
       </c>
       <c r="D395" s="6" t="inlineStr">
         <is>
-          <t>Materials lose their level, EXP and condense — this can't be undone</t>
+          <t>Fill to Next Stage</t>
         </is>
       </c>
       <c r="E395" s="1" t="n"/>
@@ -8072,17 +8072,17 @@
       <c r="A396" s="1" t="n"/>
       <c r="B396" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpOverflow</t>
+          <t>UI.Condense.HelpTitle</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
         <is>
-          <t>최고 단계를 넘는 재료는 효과 없이 사라집니다</t>
+          <t>응축</t>
         </is>
       </c>
       <c r="D396" s="6" t="inlineStr">
         <is>
-          <t>Materials beyond the top stage are consumed with no effect</t>
+          <t>Condense</t>
         </is>
       </c>
       <c r="E396" s="1" t="n"/>
@@ -8091,17 +8091,17 @@
       <c r="A397" s="1" t="n"/>
       <c r="B397" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpBusy</t>
+          <t>UI.Condense.HelpSame</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
         <is>
-          <t>배치 · 장비 착용 · 잠긴 캐릭터는 재료로 넣을 수 없습니다</t>
+          <t>같은 캐릭터를 재료로 녹여 누적을 쌓습니다 — 재료 1마리 = 누적 +1</t>
         </is>
       </c>
       <c r="D397" s="6" t="inlineStr">
         <is>
-          <t>Assigned, gear-wearing or locked characters can't be materials</t>
+          <t>Melt duplicates of the same character to build up the total — 1 material = +1</t>
         </is>
       </c>
       <c r="E397" s="1" t="n"/>
@@ -8110,17 +8110,17 @@
       <c r="A398" s="1" t="n"/>
       <c r="B398" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpStage</t>
+          <t>UI.Condense.HelpStar</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
         <is>
-          <t>■ 단계</t>
+          <t>누적이 단계 기준에 닿으면 ★이 오르고 작업속도가 늘어납니다</t>
         </is>
       </c>
       <c r="D398" s="6" t="inlineStr">
         <is>
-          <t>■ Stage</t>
+          <t>Reaching a stage total raises the stars and work speed</t>
         </is>
       </c>
       <c r="E398" s="1" t="n"/>
@@ -8129,17 +8129,17 @@
       <c r="A399" s="1" t="n"/>
       <c r="B399" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.HelpTotal</t>
+          <t>UI.Condense.HelpLost</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
         <is>
-          <t>누적</t>
+          <t>재료의 레벨 · 경험치 · 응축은 사라지고 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D399" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Materials lose their level, EXP and condense — this can't be undone</t>
         </is>
       </c>
       <c r="E399" s="1" t="n"/>
@@ -8148,17 +8148,17 @@
       <c r="A400" s="1" t="n"/>
       <c r="B400" s="6" t="inlineStr">
         <is>
-          <t>UI.Condense.StarN</t>
+          <t>UI.Condense.HelpOverflow</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
         <is>
-          <t>{0}성</t>
+          <t>최고 단계를 넘는 재료는 효과 없이 사라집니다</t>
         </is>
       </c>
       <c r="D400" s="6" t="inlineStr">
         <is>
-          <t>{0}-Star</t>
+          <t>Materials beyond the top stage are consumed with no effect</t>
         </is>
       </c>
       <c r="E400" s="1" t="n"/>
@@ -8167,17 +8167,17 @@
       <c r="A401" s="1" t="n"/>
       <c r="B401" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Speed</t>
+          <t>UI.Condense.HelpBusy</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
         <is>
-          <t>속도</t>
+          <t>배치 · 장비 착용 · 잠긴 캐릭터는 재료로 넣을 수 없습니다</t>
         </is>
       </c>
       <c r="D401" s="6" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Assigned, gear-wearing or locked characters can't be materials</t>
         </is>
       </c>
       <c r="E401" s="1" t="n"/>
@@ -8186,17 +8186,17 @@
       <c r="A402" s="1" t="n"/>
       <c r="B402" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Common</t>
+          <t>UI.Condense.HelpStage</t>
         </is>
       </c>
       <c r="C402" s="6" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>■ 단계</t>
         </is>
       </c>
       <c r="D402" s="6" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>■ Stage</t>
         </is>
       </c>
       <c r="E402" s="1" t="n"/>
@@ -8205,17 +8205,17 @@
       <c r="A403" s="1" t="n"/>
       <c r="B403" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Condition</t>
+          <t>UI.Condense.HelpTotal</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>조건</t>
+          <t>누적</t>
         </is>
       </c>
       <c r="D403" s="6" t="inlineStr">
         <is>
-          <t>Requires</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E403" s="1" t="n"/>
@@ -8224,17 +8224,17 @@
       <c r="A404" s="1" t="n"/>
       <c r="B404" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentLevel</t>
+          <t>UI.Condense.StarN</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
         <is>
-          <t>(지금 {0})</t>
+          <t>{0}성</t>
         </is>
       </c>
       <c r="D404" s="6" t="inlineStr">
         <is>
-          <t>(now {0})</t>
+          <t>{0}-Star</t>
         </is>
       </c>
       <c r="E404" s="1" t="n"/>
@@ -8243,17 +8243,17 @@
       <c r="A405" s="1" t="n"/>
       <c r="B405" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.LevelUp</t>
+          <t>UI.Trait.Speed</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
         <is>
-          <t>레벨 올리기 ({0}점)</t>
+          <t>속도</t>
         </is>
       </c>
       <c r="D405" s="6" t="inlineStr">
         <is>
-          <t>Level Up ({0} pt)</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E405" s="1" t="n"/>
@@ -8262,17 +8262,17 @@
       <c r="A406" s="1" t="n"/>
       <c r="B406" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.CurrentEffect</t>
+          <t>UI.Trait.Common</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
         <is>
-          <t>현재 효과</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D406" s="6" t="inlineStr">
         <is>
-          <t>Current Effect</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E406" s="1" t="n"/>
@@ -8281,17 +8281,17 @@
       <c r="A407" s="1" t="n"/>
       <c r="B407" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NowLevel</t>
+          <t>UI.Trait.Condition</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
         <is>
-          <t>지금 (Lv{0})</t>
+          <t>조건</t>
         </is>
       </c>
       <c r="D407" s="6" t="inlineStr">
         <is>
-          <t>Now (Lv{0})</t>
+          <t>Requires</t>
         </is>
       </c>
       <c r="E407" s="1" t="n"/>
@@ -8300,17 +8300,17 @@
       <c r="A408" s="1" t="n"/>
       <c r="B408" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NextLevel</t>
+          <t>UI.Trait.CurrentLevel</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
         <is>
-          <t>다음 (Lv{0})</t>
+          <t>(지금 {0})</t>
         </is>
       </c>
       <c r="D408" s="6" t="inlineStr">
         <is>
-          <t>Next (Lv{0})</t>
+          <t>(now {0})</t>
         </is>
       </c>
       <c r="E408" s="1" t="n"/>
@@ -8319,17 +8319,17 @@
       <c r="A409" s="1" t="n"/>
       <c r="B409" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Points</t>
+          <t>UI.Trait.LevelUp</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
         <is>
-          <t>보유 포인트 {0}</t>
+          <t>레벨 올리기 ({0}점)</t>
         </is>
       </c>
       <c r="D409" s="6" t="inlineStr">
         <is>
-          <t>Points {0}</t>
+          <t>Level Up ({0} pt)</t>
         </is>
       </c>
       <c r="E409" s="1" t="n"/>
@@ -8338,17 +8338,17 @@
       <c r="A410" s="1" t="n"/>
       <c r="B410" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.UpTo</t>
+          <t>UI.Trait.CurrentEffect</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
         <is>
-          <t>{0}까지</t>
+          <t>현재 효과</t>
         </is>
       </c>
       <c r="D410" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Current Effect</t>
         </is>
       </c>
       <c r="E410" s="1" t="n"/>
@@ -8357,17 +8357,17 @@
       <c r="A411" s="1" t="n"/>
       <c r="B411" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.Opens</t>
+          <t>UI.Trait.NowLevel</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
         <is>
-          <t>{0} 열림</t>
+          <t>지금 (Lv{0})</t>
         </is>
       </c>
       <c r="D411" s="6" t="inlineStr">
         <is>
-          <t>Opens {0}</t>
+          <t>Now (Lv{0})</t>
         </is>
       </c>
       <c r="E411" s="1" t="n"/>
@@ -8376,17 +8376,17 @@
       <c r="A412" s="1" t="n"/>
       <c r="B412" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescUnlock</t>
+          <t>UI.Trait.NextLevel</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
         <is>
-          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
+          <t>다음 (Lv{0})</t>
         </is>
       </c>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
+          <t>Next (Lv{0})</t>
         </is>
       </c>
       <c r="E412" s="1" t="n"/>
@@ -8395,17 +8395,17 @@
       <c r="A413" s="1" t="n"/>
       <c r="B413" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescSpeed</t>
+          <t>UI.Trait.Points</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
         <is>
-          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
+          <t>보유 포인트 {0}</t>
         </is>
       </c>
       <c r="D413" s="6" t="inlineStr">
         <is>
-          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
+          <t>Points {0}</t>
         </is>
       </c>
       <c r="E413" s="1" t="n"/>
@@ -8414,17 +8414,17 @@
       <c r="A414" s="1" t="n"/>
       <c r="B414" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYield</t>
+          <t>UI.Trait.UpTo</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
         <is>
-          <t>판정 1회에 같은 자원이 더 나옵니다. 상자 · 경험치는 늘지 않습니다.</t>
+          <t>{0}까지</t>
         </is>
       </c>
       <c r="D414" s="6" t="inlineStr">
         <is>
-          <t>Each roll yields more of the same resource. Boxes and EXP don't increase.</t>
+          <t>Up to {0}</t>
         </is>
       </c>
       <c r="E414" s="1" t="n"/>
@@ -8433,17 +8433,17 @@
       <c r="A415" s="1" t="n"/>
       <c r="B415" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.DescYieldAll</t>
+          <t>UI.Trait.Opens</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
         <is>
-          <t>모든 산업에 붙습니다.</t>
+          <t>{0} 열림</t>
         </is>
       </c>
       <c r="D415" s="6" t="inlineStr">
         <is>
-          <t>Applies to all industries.</t>
+          <t>Opens {0}</t>
         </is>
       </c>
       <c r="E415" s="1" t="n"/>
@@ -8452,17 +8452,17 @@
       <c r="A416" s="1" t="n"/>
       <c r="B416" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.AlreadyMax</t>
+          <t>UI.Trait.DescUnlock</t>
         </is>
       </c>
       <c r="C416" s="6" t="inlineStr">
         <is>
-          <t>이미 최대 레벨입니다.</t>
+          <t>그 산업의 다음 레벨 작업지를 엽니다. 작업슬롯에서 고를 수 있게 됩니다.</t>
         </is>
       </c>
       <c r="D416" s="6" t="inlineStr">
         <is>
-          <t>Already at max level.</t>
+          <t>Opens the next-level site for that industry. You can then pick it in a work slot.</t>
         </is>
       </c>
       <c r="E416" s="1" t="n"/>
@@ -8471,17 +8471,17 @@
       <c r="A417" s="1" t="n"/>
       <c r="B417" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.NotEnoughPoints</t>
+          <t>UI.Trait.DescSpeed</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
+          <t>작업 주기가 짧아집니다. 자원 · 상자 · 경험치가 모두 더 빨리 쌓입니다.</t>
         </is>
       </c>
       <c r="D417" s="6" t="inlineStr">
         <is>
-          <t>Not enough trait points. ({0} pt required)</t>
+          <t>Shortens the work cycle. Resources, boxes and EXP all accumulate faster.</t>
         </is>
       </c>
       <c r="E417" s="1" t="n"/>
@@ -8490,19 +8490,17 @@
       <c r="A418" s="1" t="n"/>
       <c r="B418" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.ConfirmLearn</t>
+          <t>UI.Trait.DescYield</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
         <is>
-          <t>특성 포인트 {0}점을 사용합니다.
-'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
+          <t>판정 1회에 같은 자원이 더 나옵니다. 상자 · 경험치는 늘지 않습니다.</t>
         </is>
       </c>
       <c r="D418" s="6" t="inlineStr">
         <is>
-          <t>This uses {0} trait point(s).
-Raise '{1}' to Lv{2}?</t>
+          <t>Each roll yields more of the same resource. Boxes and EXP don't increase.</t>
         </is>
       </c>
       <c r="E418" s="1" t="n"/>
@@ -8511,17 +8509,17 @@
       <c r="A419" s="1" t="n"/>
       <c r="B419" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.WaitLearn</t>
+          <t>UI.Trait.DescYieldAll</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>특성 레벨 올리기</t>
+          <t>모든 산업에 붙습니다.</t>
         </is>
       </c>
       <c r="D419" s="6" t="inlineStr">
         <is>
-          <t>Level Up Trait</t>
+          <t>Applies to all industries.</t>
         </is>
       </c>
       <c r="E419" s="1" t="n"/>
@@ -8530,17 +8528,17 @@
       <c r="A420" s="1" t="n"/>
       <c r="B420" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.EmptyDetail</t>
+          <t>UI.Trait.AlreadyMax</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
         <is>
-          <t>특성을 누르면 여기에 펼쳐집니다</t>
+          <t>이미 최대 레벨입니다.</t>
         </is>
       </c>
       <c r="D420" s="6" t="inlineStr">
         <is>
-          <t>Click a trait to see details here</t>
+          <t>Already at max level.</t>
         </is>
       </c>
       <c r="E420" s="1" t="n"/>
@@ -8549,17 +8547,17 @@
       <c r="A421" s="1" t="n"/>
       <c r="B421" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpTitle</t>
+          <t>UI.Trait.NotEnoughPoints</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
         <is>
-          <t>특성</t>
+          <t>특성 포인트가 부족합니다. ({0}점 필요)</t>
         </is>
       </c>
       <c r="D421" s="6" t="inlineStr">
         <is>
-          <t>Traits</t>
+          <t>Not enough trait points. ({0} pt required)</t>
         </is>
       </c>
       <c r="E421" s="1" t="n"/>
@@ -8568,17 +8566,19 @@
       <c r="A422" s="1" t="n"/>
       <c r="B422" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpPoint</t>
+          <t>UI.Trait.ConfirmLearn</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
         <is>
-          <t>계정 레벨이 오르면 특성 포인트를 얻습니다</t>
+          <t>특성 포인트 {0}점을 사용합니다.
+'{1}'을(를) Lv{2}로 올리시겠습니까?</t>
         </is>
       </c>
       <c r="D422" s="6" t="inlineStr">
         <is>
-          <t>You earn trait points as your account level rises</t>
+          <t>This uses {0} trait point(s).
+Raise '{1}' to Lv{2}?</t>
         </is>
       </c>
       <c r="E422" s="1" t="n"/>
@@ -8587,17 +8587,17 @@
       <c r="A423" s="1" t="n"/>
       <c r="B423" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpLevel</t>
+          <t>UI.Trait.WaitLearn</t>
         </is>
       </c>
       <c r="C423" s="6" t="inlineStr">
         <is>
-          <t>레벨을 올리려면 포인트와 계정 레벨 조건이 함께 필요합니다</t>
+          <t>특성 레벨 올리기</t>
         </is>
       </c>
       <c r="D423" s="6" t="inlineStr">
         <is>
-          <t>Leveling up needs both points and the account level requirement</t>
+          <t>Level Up Trait</t>
         </is>
       </c>
       <c r="E423" s="1" t="n"/>
@@ -8606,17 +8606,17 @@
       <c r="A424" s="1" t="n"/>
       <c r="B424" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpChoose</t>
+          <t>UI.Trait.EmptyDetail</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>포인트로 전부 올릴 수는 없습니다 — 키울 산업을 고르세요</t>
+          <t>특성을 누르면 여기에 펼쳐집니다</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
         <is>
-          <t>Points can't max everything — choose which industries to grow</t>
+          <t>Click a trait to see details here</t>
         </is>
       </c>
       <c r="E424" s="1" t="n"/>
@@ -8625,17 +8625,17 @@
       <c r="A425" s="1" t="n"/>
       <c r="B425" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpKinds</t>
+          <t>UI.Trait.HelpTitle</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
         <is>
-          <t>종류</t>
+          <t>특성</t>
         </is>
       </c>
       <c r="D425" s="6" t="inlineStr">
         <is>
-          <t>Types</t>
+          <t>Traits</t>
         </is>
       </c>
       <c r="E425" s="1" t="n"/>
@@ -8644,17 +8644,17 @@
       <c r="A426" s="1" t="n"/>
       <c r="B426" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpYieldCalc</t>
+          <t>UI.Trait.HelpPoint</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
         <is>
-          <t>산출량 120%면 1개 + 20% 확률로 1개 더</t>
+          <t>계정 레벨이 오르면 특성 포인트를 얻습니다</t>
         </is>
       </c>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>Yield 120% = 1 plus a 20% chance of 1 more</t>
+          <t>You earn trait points as your account level rises</t>
         </is>
       </c>
       <c r="E426" s="1" t="n"/>
@@ -8663,17 +8663,17 @@
       <c r="A427" s="1" t="n"/>
       <c r="B427" s="6" t="inlineStr">
         <is>
-          <t>UI.Trait.HelpYieldRarity</t>
+          <t>UI.Trait.HelpLevel</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
         <is>
-          <t>산출량이 올라도 좋은 자원이 나올 확률은 그대로입니다</t>
+          <t>레벨을 올리려면 포인트와 계정 레벨 조건이 함께 필요합니다</t>
         </is>
       </c>
       <c r="D427" s="6" t="inlineStr">
         <is>
-          <t>Yield doesn't change the odds of better resources</t>
+          <t>Leveling up needs both points and the account level requirement</t>
         </is>
       </c>
       <c r="E427" s="1" t="n"/>
@@ -8682,17 +8682,17 @@
       <c r="A428" s="1" t="n"/>
       <c r="B428" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Base</t>
+          <t>UI.Trait.HelpChoose</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
         <is>
-          <t>기본 {0}</t>
+          <t>포인트로 전부 올릴 수는 없습니다 — 키울 산업을 고르세요</t>
         </is>
       </c>
       <c r="D428" s="6" t="inlineStr">
         <is>
-          <t>Base {0}</t>
+          <t>Points can't max everything — choose which industries to grow</t>
         </is>
       </c>
       <c r="E428" s="1" t="n"/>
@@ -8701,17 +8701,17 @@
       <c r="A429" s="1" t="n"/>
       <c r="B429" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.StatSlotCount</t>
+          <t>UI.Trait.HelpKinds</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
         <is>
-          <t>능력치 칸 {0}개</t>
+          <t>종류</t>
         </is>
       </c>
       <c r="D429" s="6" t="inlineStr">
         <is>
-          <t>{0} stat slots</t>
+          <t>Types</t>
         </is>
       </c>
       <c r="E429" s="1" t="n"/>
@@ -8720,17 +8720,17 @@
       <c r="A430" s="1" t="n"/>
       <c r="B430" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.GradeUp</t>
+          <t>UI.Trait.HelpYieldCalc</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
         <is>
-          <t>등급 상승!</t>
+          <t>산출량 120%면 1개 + 20% 확률로 1개 더</t>
         </is>
       </c>
       <c r="D430" s="6" t="inlineStr">
         <is>
-          <t>Grade Up!</t>
+          <t>Yield 120% = 1 plus a 20% chance of 1 more</t>
         </is>
       </c>
       <c r="E430" s="1" t="n"/>
@@ -8739,17 +8739,17 @@
       <c r="A431" s="1" t="n"/>
       <c r="B431" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CapAll</t>
+          <t>UI.Trait.HelpYieldRarity</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
         <is>
-          <t>보유 전부</t>
+          <t>산출량이 올라도 좋은 자원이 나올 확률은 그대로입니다</t>
         </is>
       </c>
       <c r="D431" s="6" t="inlineStr">
         <is>
-          <t>All Owned</t>
+          <t>Yield doesn't change the odds of better resources</t>
         </is>
       </c>
       <c r="E431" s="1" t="n"/>
@@ -8758,17 +8758,17 @@
       <c r="A432" s="1" t="n"/>
       <c r="B432" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.All</t>
+          <t>UI.Enchant.Base</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>기본 {0}</t>
         </is>
       </c>
       <c r="D432" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Base {0}</t>
         </is>
       </c>
       <c r="E432" s="1" t="n"/>
@@ -8777,17 +8777,17 @@
       <c r="A433" s="1" t="n"/>
       <c r="B433" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.EveryCombo</t>
+          <t>UI.Enchant.StatSlotCount</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
         <is>
-          <t>칸마다 전체 또는 {0}</t>
+          <t>능력치 칸 {0}개</t>
         </is>
       </c>
       <c r="D433" s="6" t="inlineStr">
         <is>
-          <t>Each slot: All or {0}</t>
+          <t>{0} stat slots</t>
         </is>
       </c>
       <c r="E433" s="1" t="n"/>
@@ -8796,17 +8796,17 @@
       <c r="A434" s="1" t="n"/>
       <c r="B434" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCombo</t>
+          <t>UI.Enchant.GradeUp</t>
         </is>
       </c>
       <c r="C434" s="6" t="inlineStr">
         <is>
-          <t>칸 조합 없음</t>
+          <t>등급 상승!</t>
         </is>
       </c>
       <c r="D434" s="6" t="inlineStr">
         <is>
-          <t>No slot combos</t>
+          <t>Grade Up!</t>
         </is>
       </c>
       <c r="E434" s="1" t="n"/>
@@ -8815,17 +8815,17 @@
       <c r="A435" s="1" t="n"/>
       <c r="B435" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combos</t>
+          <t>UI.Enchant.CapAll</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
         <is>
-          <t>칸 {0}</t>
+          <t>보유 전부</t>
         </is>
       </c>
       <c r="D435" s="6" t="inlineStr">
         <is>
-          <t>Slots {0}</t>
+          <t>All Owned</t>
         </is>
       </c>
       <c r="E435" s="1" t="n"/>
@@ -8834,19 +8834,17 @@
       <c r="A436" s="1" t="n"/>
       <c r="B436" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NotChosen</t>
+          <t>UI.Enchant.All</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
         <is>
-          <t>아직 선택하지 않았습니다.
-BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D436" s="6" t="inlineStr">
         <is>
-          <t>You haven't chosen yet.
-Pick either BEFORE or AFTER.</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E436" s="1" t="n"/>
@@ -8855,17 +8853,17 @@
       <c r="A437" s="1" t="n"/>
       <c r="B437" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WornBy</t>
+          <t>UI.Enchant.EveryCombo</t>
         </is>
       </c>
       <c r="C437" s="6" t="inlineStr">
         <is>
-          <t>{0} 착용 중</t>
+          <t>칸마다 전체 또는 {0}</t>
         </is>
       </c>
       <c r="D437" s="6" t="inlineStr">
         <is>
-          <t>Worn by {0}</t>
+          <t>Each slot: All or {0}</t>
         </is>
       </c>
       <c r="E437" s="1" t="n"/>
@@ -8874,17 +8872,17 @@
       <c r="A438" s="1" t="n"/>
       <c r="B438" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ResultHere</t>
+          <t>UI.Enchant.NoCombo</t>
         </is>
       </c>
       <c r="C438" s="6" t="inlineStr">
         <is>
-          <t>결과가 여기에 나옵니다</t>
+          <t>칸 조합 없음</t>
         </is>
       </c>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>The result appears here</t>
+          <t>No slot combos</t>
         </is>
       </c>
       <c r="E438" s="1" t="n"/>
@@ -8893,17 +8891,17 @@
       <c r="A439" s="1" t="n"/>
       <c r="B439" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoEnchant</t>
+          <t>UI.Enchant.Combos</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
         <is>
-          <t>인챈트 없음</t>
+          <t>칸 {0}</t>
         </is>
       </c>
       <c r="D439" s="6" t="inlineStr">
         <is>
-          <t>No Enchant</t>
+          <t>Slots {0}</t>
         </is>
       </c>
       <c r="E439" s="1" t="n"/>
@@ -8912,17 +8910,19 @@
       <c r="A440" s="1" t="n"/>
       <c r="B440" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PickOne</t>
+          <t>UI.Enchant.NotChosen</t>
         </is>
       </c>
       <c r="C440" s="6" t="inlineStr">
         <is>
-          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
+          <t>아직 선택하지 않았습니다.
+BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D440" s="6" t="inlineStr">
         <is>
-          <t>[Select] either BEFORE or AFTER.</t>
+          <t>You haven't chosen yet.
+Pick either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E440" s="1" t="n"/>
@@ -8931,17 +8931,17 @@
       <c r="A441" s="1" t="n"/>
       <c r="B441" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RerollKeepsBefore</t>
+          <t>UI.Enchant.WornBy</t>
         </is>
       </c>
       <c r="C441" s="6" t="inlineStr">
         <is>
-          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
+          <t>{0} 착용 중</t>
         </is>
       </c>
       <c r="D441" s="6" t="inlineStr">
         <is>
-          <t>Using it again without choosing keeps BEFORE.</t>
+          <t>Worn by {0}</t>
         </is>
       </c>
       <c r="E441" s="1" t="n"/>
@@ -8950,17 +8950,17 @@
       <c r="A442" s="1" t="n"/>
       <c r="B442" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleFirst</t>
+          <t>UI.Enchant.ResultHere</t>
         </is>
       </c>
       <c r="C442" s="6" t="inlineStr">
         <is>
-          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
+          <t>결과가 여기에 나옵니다</t>
         </is>
       </c>
       <c r="D442" s="6" t="inlineStr">
         <is>
-          <t>First use fills {1} slot(s) at {0} grade.</t>
+          <t>The result appears here</t>
         </is>
       </c>
       <c r="E442" s="1" t="n"/>
@@ -8969,17 +8969,17 @@
       <c r="A443" s="1" t="n"/>
       <c r="B443" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleMythic</t>
+          <t>UI.Enchant.NoEnchant</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
         <is>
-          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
+          <t>인챈트 없음</t>
         </is>
       </c>
       <c r="D443" s="6" t="inlineStr">
         <is>
-          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
+          <t>No Enchant</t>
         </is>
       </c>
       <c r="E443" s="1" t="n"/>
@@ -8988,17 +8988,17 @@
       <c r="A444" s="1" t="n"/>
       <c r="B444" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleNormal</t>
+          <t>UI.Enchant.PickOne</t>
         </is>
       </c>
       <c r="C444" s="6" t="inlineStr">
         <is>
-          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
+          <t>BEFORE · AFTER 중 하나를 [선택]하세요.</t>
         </is>
       </c>
       <c r="D444" s="6" t="inlineStr">
         <is>
-          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
+          <t>[Select] either BEFORE or AFTER.</t>
         </is>
       </c>
       <c r="E444" s="1" t="n"/>
@@ -9007,17 +9007,17 @@
       <c r="A445" s="1" t="n"/>
       <c r="B445" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.RuleKeep</t>
+          <t>UI.Enchant.RerollKeepsBefore</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
         <is>
-          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
+          <t>고르지 않고 다시 사용하면 BEFORE가 남습니다.</t>
         </is>
       </c>
       <c r="D445" s="6" t="inlineStr">
         <is>
-          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
+          <t>Using it again without choosing keeps BEFORE.</t>
         </is>
       </c>
       <c r="E445" s="1" t="n"/>
@@ -9026,17 +9026,17 @@
       <c r="A446" s="1" t="n"/>
       <c r="B446" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeFirst</t>
+          <t>UI.Enchant.RuleFirst</t>
         </is>
       </c>
       <c r="C446" s="6" t="inlineStr">
         <is>
-          <t>첫 사용 · 일반 확정</t>
+          <t>처음 쓰면 {0} 등급으로 칸 {1}개를 채웁니다.</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
         <is>
-          <t>First use · Common guaranteed</t>
+          <t>First use fills {1} slot(s) at {0} grade.</t>
         </is>
       </c>
       <c r="E446" s="1" t="n"/>
@@ -9045,17 +9045,17 @@
       <c r="A447" s="1" t="n"/>
       <c r="B447" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOptionsOnly</t>
+          <t>UI.Enchant.RuleMythic</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
         <is>
-          <t>옵션만 다시 뽑기</t>
+          <t>최고 등급입니다. 쓰면 칸 {0}개를 같은 등급으로 다시 뽑습니다.</t>
         </is>
       </c>
       <c r="D447" s="6" t="inlineStr">
         <is>
-          <t>Options reroll only</t>
+          <t>Top grade reached. Using it rerolls {0} slot(s) at the same grade.</t>
         </is>
       </c>
       <c r="E447" s="1" t="n"/>
@@ -9064,17 +9064,17 @@
       <c r="A448" s="1" t="n"/>
       <c r="B448" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeUp</t>
+          <t>UI.Enchant.RuleNormal</t>
         </is>
       </c>
       <c r="C448" s="6" t="inlineStr">
         <is>
-          <t>{0} 상승 {1}</t>
+          <t>쓰면 칸 {0}개를 전부 다시 뽑고, 확률로 {1}(으)로 오릅니다. 내려가지 않습니다.</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
         <is>
-          <t>{0} up {1}</t>
+          <t>Rerolls all {0} slot(s), with a chance to rise to {1}. It never drops.</t>
         </is>
       </c>
       <c r="E448" s="1" t="n"/>
@@ -9083,17 +9083,17 @@
       <c r="A449" s="1" t="n"/>
       <c r="B449" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.CubeOwned</t>
+          <t>UI.Enchant.RuleKeep</t>
         </is>
       </c>
       <c r="C449" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개</t>
+          <t>굴린 뒤 이전 값을 고를 수 있습니다. 등급이 오르면 새 값을 알아서 고릅니다.</t>
         </is>
       </c>
       <c r="D449" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>After rolling you can keep the previous result. On a grade up, the new one is picked for you.</t>
         </is>
       </c>
       <c r="E449" s="1" t="n"/>
@@ -9102,17 +9102,17 @@
       <c r="A450" s="1" t="n"/>
       <c r="B450" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeData</t>
+          <t>UI.Enchant.CubeFirst</t>
         </is>
       </c>
       <c r="C450" s="6" t="inlineStr">
         <is>
-          <t>큐브 정보가 없습니다</t>
+          <t>첫 사용 · 일반 확정</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
         <is>
-          <t>No cube data</t>
+          <t>First use · Common guaranteed</t>
         </is>
       </c>
       <c r="E450" s="1" t="n"/>
@@ -9121,17 +9121,17 @@
       <c r="A451" s="1" t="n"/>
       <c r="B451" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UseCube</t>
+          <t>UI.Enchant.CubeOptionsOnly</t>
         </is>
       </c>
       <c r="C451" s="6" t="inlineStr">
         <is>
-          <t>{0} 사용</t>
+          <t>옵션만 다시 뽑기</t>
         </is>
       </c>
       <c r="D451" s="6" t="inlineStr">
         <is>
-          <t>Use {0}</t>
+          <t>Options reroll only</t>
         </is>
       </c>
       <c r="E451" s="1" t="n"/>
@@ -9140,17 +9140,17 @@
       <c r="A452" s="1" t="n"/>
       <c r="B452" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCube</t>
+          <t>UI.Enchant.CubeUp</t>
         </is>
       </c>
       <c r="C452" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다</t>
+          <t>{0} 상승 {1}</t>
         </is>
       </c>
       <c r="D452" s="6" t="inlineStr">
         <is>
-          <t>No {0}</t>
+          <t>{0} up {1}</t>
         </is>
       </c>
       <c r="E452" s="1" t="n"/>
@@ -9159,17 +9159,17 @@
       <c r="A453" s="1" t="n"/>
       <c r="B453" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnequipAndUse</t>
+          <t>UI.Enchant.CubeOwned</t>
         </is>
       </c>
       <c r="C453" s="6" t="inlineStr">
         <is>
-          <t>해제하고 {0} 사용</t>
+          <t>보유 {0}개</t>
         </is>
       </c>
       <c r="D453" s="6" t="inlineStr">
         <is>
-          <t>Unequip and Use {0}</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E453" s="1" t="n"/>
@@ -9178,17 +9178,17 @@
       <c r="A454" s="1" t="n"/>
       <c r="B454" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoCubeNotice</t>
+          <t>UI.Enchant.NoCubeData</t>
         </is>
       </c>
       <c r="C454" s="6" t="inlineStr">
         <is>
-          <t>{0}가 없습니다.</t>
+          <t>큐브 정보가 없습니다</t>
         </is>
       </c>
       <c r="D454" s="6" t="inlineStr">
         <is>
-          <t>You have no {0}.</t>
+          <t>No cube data</t>
         </is>
       </c>
       <c r="E454" s="1" t="n"/>
@@ -9197,19 +9197,17 @@
       <c r="A455" s="1" t="n"/>
       <c r="B455" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ConfirmUnequip</t>
+          <t>UI.Enchant.UseCube</t>
         </is>
       </c>
       <c r="C455" s="6" t="inlineStr">
         <is>
-          <t>{0}이(가) 끼고 있는 장비입니다.
-해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
+          <t>{0} 사용</t>
         </is>
       </c>
       <c r="D455" s="6" t="inlineStr">
         <is>
-          <t>{0} is wearing this gear.
-It will be unequipped before using the cube. (It won't be re-equipped.)</t>
+          <t>Use {0}</t>
         </is>
       </c>
       <c r="E455" s="1" t="n"/>
@@ -9218,17 +9216,17 @@
       <c r="A456" s="1" t="n"/>
       <c r="B456" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitUse</t>
+          <t>UI.Enchant.NoCube</t>
         </is>
       </c>
       <c r="C456" s="6" t="inlineStr">
         <is>
-          <t>큐브 사용</t>
+          <t>{0}가 없습니다</t>
         </is>
       </c>
       <c r="D456" s="6" t="inlineStr">
         <is>
-          <t>Use Cube</t>
+          <t>No {0}</t>
         </is>
       </c>
       <c r="E456" s="1" t="n"/>
@@ -9237,17 +9235,17 @@
       <c r="A457" s="1" t="n"/>
       <c r="B457" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.WaitChoose</t>
+          <t>UI.Enchant.UnequipAndUse</t>
         </is>
       </c>
       <c r="C457" s="6" t="inlineStr">
         <is>
-          <t>큐브 결과 고르기</t>
+          <t>해제하고 {0} 사용</t>
         </is>
       </c>
       <c r="D457" s="6" t="inlineStr">
         <is>
-          <t>Choose Cube Result</t>
+          <t>Unequip and Use {0}</t>
         </is>
       </c>
       <c r="E457" s="1" t="n"/>
@@ -9256,17 +9254,17 @@
       <c r="A458" s="1" t="n"/>
       <c r="B458" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.ChooseFirst</t>
+          <t>UI.Enchant.NoCubeNotice</t>
         </is>
       </c>
       <c r="C458" s="6" t="inlineStr">
         <is>
-          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
+          <t>{0}가 없습니다.</t>
         </is>
       </c>
       <c r="D458" s="6" t="inlineStr">
         <is>
-          <t>Pick BEFORE or AFTER first.</t>
+          <t>You have no {0}.</t>
         </is>
       </c>
       <c r="E458" s="1" t="n"/>
@@ -9275,17 +9273,19 @@
       <c r="A459" s="1" t="n"/>
       <c r="B459" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoAutoWorn</t>
+          <t>UI.Enchant.ConfirmUnequip</t>
         </is>
       </c>
       <c r="C459" s="6" t="inlineStr">
         <is>
-          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
+          <t>{0}이(가) 끼고 있는 장비입니다.
+해제한 뒤 큐브를 사용합니다. (사용 후 다시 끼지 않습니다)</t>
         </is>
       </c>
       <c r="D459" s="6" t="inlineStr">
         <is>
-          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
+          <t>{0} is wearing this gear.
+It will be unequipped before using the cube. (It won't be re-equipped.)</t>
         </is>
       </c>
       <c r="E459" s="1" t="n"/>
@@ -9294,17 +9294,17 @@
       <c r="A460" s="1" t="n"/>
       <c r="B460" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStart</t>
+          <t>UI.Enchant.WaitUse</t>
         </is>
       </c>
       <c r="C460" s="6" t="inlineStr">
         <is>
-          <t>자동 시작 ▶</t>
+          <t>큐브 사용</t>
         </is>
       </c>
       <c r="D460" s="6" t="inlineStr">
         <is>
-          <t>Start Auto ▶</t>
+          <t>Use Cube</t>
         </is>
       </c>
       <c r="E460" s="1" t="n"/>
@@ -9313,17 +9313,17 @@
       <c r="A461" s="1" t="n"/>
       <c r="B461" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AlreadyMythic</t>
+          <t>UI.Enchant.WaitChoose</t>
         </is>
       </c>
       <c r="C461" s="6" t="inlineStr">
         <is>
-          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
+          <t>큐브 결과 고르기</t>
         </is>
       </c>
       <c r="D461" s="6" t="inlineStr">
         <is>
-          <t>Already Mythic. Pick an option to aim for.</t>
+          <t>Choose Cube Result</t>
         </is>
       </c>
       <c r="E461" s="1" t="n"/>
@@ -9332,17 +9332,17 @@
       <c r="A462" s="1" t="n"/>
       <c r="B462" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NeedCombo</t>
+          <t>UI.Enchant.ChooseFirst</t>
         </is>
       </c>
       <c r="C462" s="6" t="inlineStr">
         <is>
-          <t>조합을 하나 이상 켜 주세요.</t>
+          <t>먼저 BEFORE · AFTER 중 하나를 골라 주세요.</t>
         </is>
       </c>
       <c r="D462" s="6" t="inlineStr">
         <is>
-          <t>Turn on at least one combo.</t>
+          <t>Pick BEFORE or AFTER first.</t>
         </is>
       </c>
       <c r="E462" s="1" t="n"/>
@@ -9351,17 +9351,17 @@
       <c r="A463" s="1" t="n"/>
       <c r="B463" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.MeanCount</t>
+          <t>UI.Enchant.NoAutoWorn</t>
         </is>
       </c>
       <c r="C463" s="6" t="inlineStr">
         <is>
-          <t>{0}개 (약 {1})</t>
+          <t>착용 중인 장비는 자동으로 돌릴 수 없습니다. 먼저 벗겨 주세요.</t>
         </is>
       </c>
       <c r="D463" s="6" t="inlineStr">
         <is>
-          <t>{0} (about {1})</t>
+          <t>Worn gear can't be auto-rolled. Unequip it first.</t>
         </is>
       </c>
       <c r="E463" s="1" t="n"/>
@@ -9370,17 +9370,17 @@
       <c r="A464" s="1" t="n"/>
       <c r="B464" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Within</t>
+          <t>UI.Enchant.AutoStart</t>
         </is>
       </c>
       <c r="C464" s="6" t="inlineStr">
         <is>
-          <t>{0}개 안에 {1}</t>
+          <t>자동 시작 ▶</t>
         </is>
       </c>
       <c r="D464" s="6" t="inlineStr">
         <is>
-          <t>{1} within {0}</t>
+          <t>Start Auto ▶</t>
         </is>
       </c>
       <c r="E464" s="1" t="n"/>
@@ -9389,17 +9389,17 @@
       <c r="A465" s="1" t="n"/>
       <c r="B465" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Mean</t>
+          <t>UI.Enchant.AlreadyMythic</t>
         </is>
       </c>
       <c r="C465" s="6" t="inlineStr">
         <is>
-          <t>평균 {0}</t>
+          <t>이미 신화입니다. 노릴 옵션을 골라 주세요.</t>
         </is>
       </c>
       <c r="D465" s="6" t="inlineStr">
         <is>
-          <t>avg {0}</t>
+          <t>Already Mythic. Pick an option to aim for.</t>
         </is>
       </c>
       <c r="E465" s="1" t="n"/>
@@ -9408,17 +9408,17 @@
       <c r="A466" s="1" t="n"/>
       <c r="B466" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.UnderMin</t>
+          <t>UI.Enchant.NeedCombo</t>
         </is>
       </c>
       <c r="C466" s="6" t="inlineStr">
         <is>
-          <t>0.01% 미만</t>
+          <t>조합을 하나 이상 켜 주세요.</t>
         </is>
       </c>
       <c r="D466" s="6" t="inlineStr">
         <is>
-          <t>under 0.01%</t>
+          <t>Turn on at least one combo.</t>
         </is>
       </c>
       <c r="E466" s="1" t="n"/>
@@ -9427,17 +9427,17 @@
       <c r="A467" s="1" t="n"/>
       <c r="B467" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Minutes</t>
+          <t>UI.Enchant.MeanCount</t>
         </is>
       </c>
       <c r="C467" s="6" t="inlineStr">
         <is>
-          <t>{0}분</t>
+          <t>{0}개 (약 {1})</t>
         </is>
       </c>
       <c r="D467" s="6" t="inlineStr">
         <is>
-          <t>{0}m</t>
+          <t>{0} (about {1})</t>
         </is>
       </c>
       <c r="E467" s="1" t="n"/>
@@ -9446,17 +9446,17 @@
       <c r="A468" s="1" t="n"/>
       <c r="B468" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Hours</t>
+          <t>UI.Enchant.Within</t>
         </is>
       </c>
       <c r="C468" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>{0}개 안에 {1}</t>
         </is>
       </c>
       <c r="D468" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>{1} within {0}</t>
         </is>
       </c>
       <c r="E468" s="1" t="n"/>
@@ -9465,17 +9465,17 @@
       <c r="A469" s="1" t="n"/>
       <c r="B469" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoRunning</t>
+          <t>UI.Enchant.Mean</t>
         </is>
       </c>
       <c r="C469" s="6" t="inlineStr">
         <is>
-          <t>자동 진행 중 {0} / {1}개</t>
+          <t>평균 {0}</t>
         </is>
       </c>
       <c r="D469" s="6" t="inlineStr">
         <is>
-          <t>Auto running {0} / {1}</t>
+          <t>avg {0}</t>
         </is>
       </c>
       <c r="E469" s="1" t="n"/>
@@ -9484,17 +9484,17 @@
       <c r="A470" s="1" t="n"/>
       <c r="B470" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Goal</t>
+          <t>UI.Enchant.UnderMin</t>
         </is>
       </c>
       <c r="C470" s="6" t="inlineStr">
         <is>
-          <t>목표 {0} 이상</t>
+          <t>0.01% 미만</t>
         </is>
       </c>
       <c r="D470" s="6" t="inlineStr">
         <is>
-          <t>Goal: {0} or higher</t>
+          <t>under 0.01%</t>
         </is>
       </c>
       <c r="E470" s="1" t="n"/>
@@ -9503,17 +9503,17 @@
       <c r="A471" s="1" t="n"/>
       <c r="B471" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.NoSlotRule</t>
+          <t>UI.Enchant.Minutes</t>
         </is>
       </c>
       <c r="C471" s="6" t="inlineStr">
         <is>
-          <t>칸 조건 없음 — 등급만 봅니다</t>
+          <t>{0}분</t>
         </is>
       </c>
       <c r="D471" s="6" t="inlineStr">
         <is>
-          <t>No slot condition — grade only</t>
+          <t>{0}m</t>
         </is>
       </c>
       <c r="E471" s="1" t="n"/>
@@ -9522,17 +9522,17 @@
       <c r="A472" s="1" t="n"/>
       <c r="B472" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.PerRoll</t>
+          <t>UI.Enchant.Hours</t>
         </is>
       </c>
       <c r="C472" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D472" s="6" t="inlineStr">
         <is>
-          <t>{0} per roll</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E472" s="1" t="n"/>
@@ -9541,17 +9541,17 @@
       <c r="A473" s="1" t="n"/>
       <c r="B473" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoStop</t>
+          <t>UI.Enchant.AutoRunning</t>
         </is>
       </c>
       <c r="C473" s="6" t="inlineStr">
         <is>
-          <t>■ 멈춤</t>
+          <t>자동 진행 중 {0} / {1}개</t>
         </is>
       </c>
       <c r="D473" s="6" t="inlineStr">
         <is>
-          <t>■ Stop</t>
+          <t>Auto running {0} / {1}</t>
         </is>
       </c>
       <c r="E473" s="1" t="n"/>
@@ -9560,17 +9560,17 @@
       <c r="A474" s="1" t="n"/>
       <c r="B474" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Auto</t>
+          <t>UI.Enchant.Goal</t>
         </is>
       </c>
       <c r="C474" s="6" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>목표 {0} 이상</t>
         </is>
       </c>
       <c r="D474" s="6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Goal: {0} or higher</t>
         </is>
       </c>
       <c r="E474" s="1" t="n"/>
@@ -9579,17 +9579,17 @@
       <c r="A475" s="1" t="n"/>
       <c r="B475" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndStopped</t>
+          <t>UI.Enchant.NoSlotRule</t>
         </is>
       </c>
       <c r="C475" s="6" t="inlineStr">
         <is>
-          <t>자동을 멈췄습니다</t>
+          <t>칸 조건 없음 — 등급만 봅니다</t>
         </is>
       </c>
       <c r="D475" s="6" t="inlineStr">
         <is>
-          <t>Auto stopped</t>
+          <t>No slot condition — grade only</t>
         </is>
       </c>
       <c r="E475" s="1" t="n"/>
@@ -9598,17 +9598,17 @@
       <c r="A476" s="1" t="n"/>
       <c r="B476" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndCap</t>
+          <t>UI.Enchant.PerRoll</t>
         </is>
       </c>
       <c r="C476" s="6" t="inlineStr">
         <is>
-          <t>상한에 닿아 멈췄습니다</t>
+          <t>한 번에 {0}</t>
         </is>
       </c>
       <c r="D476" s="6" t="inlineStr">
         <is>
-          <t>Stopped at the limit</t>
+          <t>{0} per roll</t>
         </is>
       </c>
       <c r="E476" s="1" t="n"/>
@@ -9617,17 +9617,17 @@
       <c r="A477" s="1" t="n"/>
       <c r="B477" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndNoCube</t>
+          <t>UI.Enchant.AutoStop</t>
         </is>
       </c>
       <c r="C477" s="6" t="inlineStr">
         <is>
-          <t>큐브가 떨어져 멈췄습니다</t>
+          <t>■ 멈춤</t>
         </is>
       </c>
       <c r="D477" s="6" t="inlineStr">
         <is>
-          <t>Stopped — out of cubes</t>
+          <t>■ Stop</t>
         </is>
       </c>
       <c r="E477" s="1" t="n"/>
@@ -9636,17 +9636,17 @@
       <c r="A478" s="1" t="n"/>
       <c r="B478" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndRejected</t>
+          <t>UI.Enchant.Auto</t>
         </is>
       </c>
       <c r="C478" s="6" t="inlineStr">
         <is>
-          <t>서버가 거절해 멈췄습니다</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="D478" s="6" t="inlineStr">
         <is>
-          <t>Stopped — server rejected</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E478" s="1" t="n"/>
@@ -9655,17 +9655,17 @@
       <c r="A479" s="1" t="n"/>
       <c r="B479" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndGoal</t>
+          <t>UI.Enchant.AutoEndStopped</t>
         </is>
       </c>
       <c r="C479" s="6" t="inlineStr">
         <is>
-          <t>목표 달성!</t>
+          <t>자동을 멈췄습니다</t>
         </is>
       </c>
       <c r="D479" s="6" t="inlineStr">
         <is>
-          <t>Goal reached!</t>
+          <t>Auto stopped</t>
         </is>
       </c>
       <c r="E479" s="1" t="n"/>
@@ -9674,17 +9674,17 @@
       <c r="A480" s="1" t="n"/>
       <c r="B480" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.AutoEndSummary</t>
+          <t>UI.Enchant.AutoEndCap</t>
         </is>
       </c>
       <c r="C480" s="6" t="inlineStr">
         <is>
-          <t>{0} — {1} {2}개 사용.</t>
+          <t>상한에 닿아 멈췄습니다</t>
         </is>
       </c>
       <c r="D480" s="6" t="inlineStr">
         <is>
-          <t>{0} — used {2} {1}.</t>
+          <t>Stopped at the limit</t>
         </is>
       </c>
       <c r="E480" s="1" t="n"/>
@@ -9693,17 +9693,17 @@
       <c r="A481" s="1" t="n"/>
       <c r="B481" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.TargetGrade</t>
+          <t>UI.Enchant.AutoEndNoCube</t>
         </is>
       </c>
       <c r="C481" s="6" t="inlineStr">
         <is>
-          <t>목표 등급</t>
+          <t>큐브가 떨어져 멈췄습니다</t>
         </is>
       </c>
       <c r="D481" s="6" t="inlineStr">
         <is>
-          <t>Target Grade</t>
+          <t>Stopped — out of cubes</t>
         </is>
       </c>
       <c r="E481" s="1" t="n"/>
@@ -9712,17 +9712,17 @@
       <c r="A482" s="1" t="n"/>
       <c r="B482" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.FocusOption</t>
+          <t>UI.Enchant.AutoEndRejected</t>
         </is>
       </c>
       <c r="C482" s="6" t="inlineStr">
         <is>
-          <t>노릴 옵션</t>
+          <t>서버가 거절해 멈췄습니다</t>
         </is>
       </c>
       <c r="D482" s="6" t="inlineStr">
         <is>
-          <t>Aim For</t>
+          <t>Stopped — server rejected</t>
         </is>
       </c>
       <c r="E482" s="1" t="n"/>
@@ -9731,17 +9731,17 @@
       <c r="A483" s="1" t="n"/>
       <c r="B483" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Combo</t>
+          <t>UI.Enchant.AutoEndGoal</t>
         </is>
       </c>
       <c r="C483" s="6" t="inlineStr">
         <is>
-          <t>조합</t>
+          <t>목표 달성!</t>
         </is>
       </c>
       <c r="D483" s="6" t="inlineStr">
         <is>
-          <t>Combo</t>
+          <t>Goal reached!</t>
         </is>
       </c>
       <c r="E483" s="1" t="n"/>
@@ -9750,17 +9750,17 @@
       <c r="A484" s="1" t="n"/>
       <c r="B484" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Cap</t>
+          <t>UI.Enchant.AutoEndSummary</t>
         </is>
       </c>
       <c r="C484" s="6" t="inlineStr">
         <is>
-          <t>상한</t>
+          <t>{0} — {1} {2}개 사용.</t>
         </is>
       </c>
       <c r="D484" s="6" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>{0} — used {2} {1}.</t>
         </is>
       </c>
       <c r="E484" s="1" t="n"/>
@@ -9769,17 +9769,17 @@
       <c r="A485" s="1" t="n"/>
       <c r="B485" s="6" t="inlineStr">
         <is>
-          <t>UI.Enchant.Select</t>
+          <t>UI.Enchant.TargetGrade</t>
         </is>
       </c>
       <c r="C485" s="6" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>목표 등급</t>
         </is>
       </c>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Target Grade</t>
         </is>
       </c>
       <c r="E485" s="1" t="n"/>
@@ -9788,17 +9788,17 @@
       <c r="A486" s="1" t="n"/>
       <c r="B486" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Times</t>
+          <t>UI.Enchant.FocusOption</t>
         </is>
       </c>
       <c r="C486" s="6" t="inlineStr">
         <is>
-          <t>{0}회</t>
+          <t>노릴 옵션</t>
         </is>
       </c>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>x{0}</t>
+          <t>Aim For</t>
         </is>
       </c>
       <c r="E486" s="1" t="n"/>
@@ -9807,17 +9807,17 @@
       <c r="A487" s="1" t="n"/>
       <c r="B487" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Worker</t>
+          <t>UI.Enchant.Combo</t>
         </is>
       </c>
       <c r="C487" s="6" t="inlineStr">
         <is>
-          <t>일꾼</t>
+          <t>조합</t>
         </is>
       </c>
       <c r="D487" s="6" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="E487" s="1" t="n"/>
@@ -9826,17 +9826,17 @@
       <c r="A488" s="1" t="n"/>
       <c r="B488" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.WorkSpeedUp</t>
+          <t>UI.Enchant.Cap</t>
         </is>
       </c>
       <c r="C488" s="6" t="inlineStr">
         <is>
-          <t>작업속도 증가</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="D488" s="6" t="inlineStr">
         <is>
-          <t>Work Speed Up</t>
+          <t>Limit</t>
         </is>
       </c>
       <c r="E488" s="1" t="n"/>
@@ -9845,17 +9845,17 @@
       <c r="A489" s="1" t="n"/>
       <c r="B489" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Kinds</t>
+          <t>UI.Enchant.Select</t>
         </is>
       </c>
       <c r="C489" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}종</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="D489" s="6" t="inlineStr">
         <is>
-          <t>{1} {0}</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E489" s="1" t="n"/>
@@ -9864,17 +9864,17 @@
       <c r="A490" s="1" t="n"/>
       <c r="B490" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.KindsOnly</t>
+          <t>UI.Gacha.Times</t>
         </is>
       </c>
       <c r="C490" s="6" t="inlineStr">
         <is>
-          <t>{0}종</t>
+          <t>{0}회</t>
         </is>
       </c>
       <c r="D490" s="6" t="inlineStr">
         <is>
-          <t>{0} kinds</t>
+          <t>x{0}</t>
         </is>
       </c>
       <c r="E490" s="1" t="n"/>
@@ -9883,17 +9883,17 @@
       <c r="A491" s="1" t="n"/>
       <c r="B491" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Item</t>
+          <t>UI.Gacha.Worker</t>
         </is>
       </c>
       <c r="C491" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>일꾼</t>
         </is>
       </c>
       <c r="D491" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="E491" s="1" t="n"/>
@@ -9902,17 +9902,17 @@
       <c r="A492" s="1" t="n"/>
       <c r="B492" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.RateTitle</t>
+          <t>UI.Gacha.WorkSpeedUp</t>
         </is>
       </c>
       <c r="C492" s="6" t="inlineStr">
         <is>
-          <t>{0} 확률</t>
+          <t>작업속도 증가</t>
         </is>
       </c>
       <c r="D492" s="6" t="inlineStr">
         <is>
-          <t>{0} Rates</t>
+          <t>Work Speed Up</t>
         </is>
       </c>
       <c r="E492" s="1" t="n"/>
@@ -9921,17 +9921,17 @@
       <c r="A493" s="1" t="n"/>
       <c r="B493" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoEntries</t>
+          <t>UI.Gacha.Kinds</t>
         </is>
       </c>
       <c r="C493" s="6" t="inlineStr">
         <is>
-          <t>뽑을 항목이 없다</t>
+          <t>{0} {1}종</t>
         </is>
       </c>
       <c r="D493" s="6" t="inlineStr">
         <is>
-          <t>Nothing to draw</t>
+          <t>{1} {0}</t>
         </is>
       </c>
       <c r="E493" s="1" t="n"/>
@@ -9940,17 +9940,17 @@
       <c r="A494" s="1" t="n"/>
       <c r="B494" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.NoRarity</t>
+          <t>UI.Gacha.KindsOnly</t>
         </is>
       </c>
       <c r="C494" s="6" t="inlineStr">
         <is>
-          <t>등급 없음</t>
+          <t>{0}종</t>
         </is>
       </c>
       <c r="D494" s="6" t="inlineStr">
         <is>
-          <t>No Rarity</t>
+          <t>{0} kinds</t>
         </is>
       </c>
       <c r="E494" s="1" t="n"/>
@@ -9959,17 +9959,17 @@
       <c r="A495" s="1" t="n"/>
       <c r="B495" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SameRate</t>
+          <t>UI.Gacha.Item</t>
         </is>
       </c>
       <c r="C495" s="6" t="inlineStr">
         <is>
-          <t>10회도 한 번마다 같은 확률</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>x10 uses the same odds for each draw</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E495" s="1" t="n"/>
@@ -9978,17 +9978,17 @@
       <c r="A496" s="1" t="n"/>
       <c r="B496" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Wait</t>
+          <t>UI.Gacha.RateTitle</t>
         </is>
       </c>
       <c r="C496" s="6" t="inlineStr">
         <is>
-          <t>가챠 {0}회</t>
+          <t>{0} 확률</t>
         </is>
       </c>
       <c r="D496" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0}</t>
+          <t>{0} Rates</t>
         </is>
       </c>
       <c r="E496" s="1" t="n"/>
@@ -9997,17 +9997,17 @@
       <c r="A497" s="1" t="n"/>
       <c r="B497" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Source</t>
+          <t>UI.Gacha.NoEntries</t>
         </is>
       </c>
       <c r="C497" s="6" t="inlineStr">
         <is>
-          <t>가챠</t>
+          <t>뽑을 항목이 없다</t>
         </is>
       </c>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Nothing to draw</t>
         </is>
       </c>
       <c r="E497" s="1" t="n"/>
@@ -10016,17 +10016,17 @@
       <c r="A498" s="1" t="n"/>
       <c r="B498" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceBox</t>
+          <t>UI.Gacha.NoRarity</t>
         </is>
       </c>
       <c r="C498" s="6" t="inlineStr">
         <is>
-          <t>상자 개봉</t>
+          <t>등급 없음</t>
         </is>
       </c>
       <c r="D498" s="6" t="inlineStr">
         <is>
-          <t>Box Opening</t>
+          <t>No Rarity</t>
         </is>
       </c>
       <c r="E498" s="1" t="n"/>
@@ -10035,17 +10035,17 @@
       <c r="A499" s="1" t="n"/>
       <c r="B499" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceMail</t>
+          <t>UI.Gacha.SameRate</t>
         </is>
       </c>
       <c r="C499" s="6" t="inlineStr">
         <is>
-          <t>우편 수령</t>
+          <t>10회도 한 번마다 같은 확률</t>
         </is>
       </c>
       <c r="D499" s="6" t="inlineStr">
         <is>
-          <t>Mail Claim</t>
+          <t>x10 uses the same odds for each draw</t>
         </is>
       </c>
       <c r="E499" s="1" t="n"/>
@@ -10054,17 +10054,17 @@
       <c r="A500" s="1" t="n"/>
       <c r="B500" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.ResultTitle</t>
+          <t>UI.Gacha.Wait</t>
         </is>
       </c>
       <c r="C500" s="6" t="inlineStr">
         <is>
-          <t>{0} 결과</t>
+          <t>가챠 {0}회</t>
         </is>
       </c>
       <c r="D500" s="6" t="inlineStr">
         <is>
-          <t>{0} Results</t>
+          <t>Draw x{0}</t>
         </is>
       </c>
       <c r="E500" s="1" t="n"/>
@@ -10073,17 +10073,17 @@
       <c r="A501" s="1" t="n"/>
       <c r="B501" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.DrawAgain</t>
+          <t>UI.Gacha.Source</t>
         </is>
       </c>
       <c r="C501" s="6" t="inlineStr">
         <is>
-          <t>{0}회 더 뽑기</t>
+          <t>가챠</t>
         </is>
       </c>
       <c r="D501" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0} Again</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E501" s="1" t="n"/>
@@ -10092,17 +10092,17 @@
       <c r="A502" s="1" t="n"/>
       <c r="B502" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Tab</t>
+          <t>UI.Gacha.SourceBox</t>
         </is>
       </c>
       <c r="C502" s="6" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>상자 개봉</t>
         </is>
       </c>
       <c r="D502" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Box Opening</t>
         </is>
       </c>
       <c r="E502" s="1" t="n"/>
@@ -10111,17 +10111,17 @@
       <c r="A503" s="1" t="n"/>
       <c r="B503" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.CloseResult</t>
+          <t>UI.Gacha.SourceMail</t>
         </is>
       </c>
       <c r="C503" s="6" t="inlineStr">
         <is>
-          <t>[결과 닫기]</t>
+          <t>우편 수령</t>
         </is>
       </c>
       <c r="D503" s="6" t="inlineStr">
         <is>
-          <t>[Close]</t>
+          <t>Mail Claim</t>
         </is>
       </c>
       <c r="E503" s="1" t="n"/>
@@ -10130,17 +10130,17 @@
       <c r="A504" s="1" t="n"/>
       <c r="B504" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Gacha.ResultTitle</t>
         </is>
       </c>
       <c r="C504" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>{0} 결과</t>
         </is>
       </c>
       <c r="D504" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>{0} Results</t>
         </is>
       </c>
       <c r="E504" s="1" t="n"/>
@@ -10149,17 +10149,17 @@
       <c r="A505" s="1" t="n"/>
       <c r="B505" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Gacha.DrawAgain</t>
         </is>
       </c>
       <c r="C505" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>{0}회 더 뽑기</t>
         </is>
       </c>
       <c r="D505" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Draw x{0} Again</t>
         </is>
       </c>
       <c r="E505" s="1" t="n"/>
@@ -10168,17 +10168,17 @@
       <c r="A506" s="1" t="n"/>
       <c r="B506" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Gacha.Tab</t>
         </is>
       </c>
       <c r="C506" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="D506" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E506" s="1" t="n"/>
@@ -10187,17 +10187,17 @@
       <c r="A507" s="1" t="n"/>
       <c r="B507" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Gacha.CloseResult</t>
         </is>
       </c>
       <c r="C507" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>[결과 닫기]</t>
         </is>
       </c>
       <c r="D507" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>[Close]</t>
         </is>
       </c>
       <c r="E507" s="1" t="n"/>
@@ -10206,17 +10206,17 @@
       <c r="A508" s="1" t="n"/>
       <c r="B508" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C508" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D508" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E508" s="1" t="n"/>
@@ -10225,17 +10225,17 @@
       <c r="A509" s="1" t="n"/>
       <c r="B509" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Warehouse.Stack</t>
         </is>
       </c>
       <c r="C509" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>창고에 쌓기</t>
         </is>
       </c>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Stack in Warehouse</t>
         </is>
       </c>
       <c r="E509" s="1" t="n"/>
@@ -10244,17 +10244,17 @@
       <c r="A510" s="1" t="n"/>
       <c r="B510" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Warehouse.StackTip</t>
         </is>
       </c>
       <c r="C510" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
         </is>
       </c>
       <c r="D510" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
         </is>
       </c>
       <c r="E510" s="1" t="n"/>
@@ -10263,17 +10263,17 @@
       <c r="A511" s="1" t="n"/>
       <c r="B511" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Warehouse.NothingToStack</t>
         </is>
       </c>
       <c r="C511" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
         </is>
       </c>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
         </is>
       </c>
       <c r="E511" s="1" t="n"/>
@@ -10282,17 +10282,17 @@
       <c r="A512" s="1" t="n"/>
       <c r="B512" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C512" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E512" s="1" t="n"/>
@@ -10301,17 +10301,17 @@
       <c r="A513" s="1" t="n"/>
       <c r="B513" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C513" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E513" s="1" t="n"/>
@@ -10320,17 +10320,17 @@
       <c r="A514" s="1" t="n"/>
       <c r="B514" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C514" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D514" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E514" s="1" t="n"/>
@@ -10339,17 +10339,17 @@
       <c r="A515" s="1" t="n"/>
       <c r="B515" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C515" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D515" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E515" s="1" t="n"/>
@@ -10358,17 +10358,17 @@
       <c r="A516" s="1" t="n"/>
       <c r="B516" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C516" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D516" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E516" s="1" t="n"/>
@@ -10377,17 +10377,17 @@
       <c r="A517" s="1" t="n"/>
       <c r="B517" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C517" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D517" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E517" s="1" t="n"/>
@@ -10396,17 +10396,17 @@
       <c r="A518" s="1" t="n"/>
       <c r="B518" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C518" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D518" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E518" s="1" t="n"/>
@@ -10415,17 +10415,17 @@
       <c r="A519" s="1" t="n"/>
       <c r="B519" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C519" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E519" s="1" t="n"/>
@@ -10434,17 +10434,17 @@
       <c r="A520" s="1" t="n"/>
       <c r="B520" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C520" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D520" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E520" s="1" t="n"/>
@@ -10453,17 +10453,17 @@
       <c r="A521" s="1" t="n"/>
       <c r="B521" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C521" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E521" s="1" t="n"/>
@@ -10472,17 +10472,17 @@
       <c r="A522" s="1" t="n"/>
       <c r="B522" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C522" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D522" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E522" s="1" t="n"/>
@@ -10491,17 +10491,17 @@
       <c r="A523" s="1" t="n"/>
       <c r="B523" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C523" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D523" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E523" s="1" t="n"/>
@@ -10510,17 +10510,17 @@
       <c r="A524" s="1" t="n"/>
       <c r="B524" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C524" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D524" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E524" s="1" t="n"/>
@@ -10529,17 +10529,17 @@
       <c r="A525" s="1" t="n"/>
       <c r="B525" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C525" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D525" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E525" s="1" t="n"/>
@@ -10548,17 +10548,17 @@
       <c r="A526" s="1" t="n"/>
       <c r="B526" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C526" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D526" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E526" s="1" t="n"/>
@@ -10567,17 +10567,17 @@
       <c r="A527" s="1" t="n"/>
       <c r="B527" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C527" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D527" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E527" s="1" t="n"/>
@@ -10586,17 +10586,17 @@
       <c r="A528" s="1" t="n"/>
       <c r="B528" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D528" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E528" s="1" t="n"/>
@@ -10605,17 +10605,17 @@
       <c r="A529" s="1" t="n"/>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D529" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E529" s="1" t="n"/>
@@ -10624,17 +10624,17 @@
       <c r="A530" s="1" t="n"/>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D530" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E530" s="1" t="n"/>
@@ -10643,17 +10643,17 @@
       <c r="A531" s="1" t="n"/>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D531" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E531" s="1" t="n"/>
@@ -10662,17 +10662,17 @@
       <c r="A532" s="1" t="n"/>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D532" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E532" s="1" t="n"/>
@@ -10681,17 +10681,17 @@
       <c r="A533" s="1" t="n"/>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D533" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E533" s="1" t="n"/>
@@ -10700,17 +10700,17 @@
       <c r="A534" s="1" t="n"/>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D534" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E534" s="1" t="n"/>
@@ -10719,17 +10719,17 @@
       <c r="A535" s="1" t="n"/>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D535" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E535" s="1" t="n"/>
@@ -10738,17 +10738,17 @@
       <c r="A536" s="1" t="n"/>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E536" s="1" t="n"/>
@@ -10757,17 +10757,17 @@
       <c r="A537" s="1" t="n"/>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E537" s="1" t="n"/>
@@ -10776,17 +10776,17 @@
       <c r="A538" s="1" t="n"/>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D538" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E538" s="1" t="n"/>
@@ -10795,17 +10795,17 @@
       <c r="A539" s="1" t="n"/>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D539" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E539" s="1" t="n"/>
@@ -10814,17 +10814,17 @@
       <c r="A540" s="1" t="n"/>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,17 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11631,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11650,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11669,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11688,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11707,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11726,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11745,17 +11745,17 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11764,17 +11764,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11783,17 +11783,17 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11802,17 +11802,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11821,17 +11821,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11840,17 +11840,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11859,17 +11859,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11878,17 +11878,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11897,17 +11897,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11916,17 +11916,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11935,17 +11935,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11954,17 +11954,17 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11973,17 +11973,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11992,17 +11992,17 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12011,17 +12011,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12030,17 +12030,17 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12049,17 +12049,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12068,17 +12068,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12087,19 +12087,17 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12108,17 +12106,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12127,17 +12125,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12146,17 +12144,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12165,17 +12163,17 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E611" s="1" t="n"/>
@@ -12184,17 +12182,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12203,17 +12201,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12222,17 +12220,19 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12241,17 +12241,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12260,17 +12260,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12279,17 +12279,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12298,19 +12298,17 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12319,17 +12317,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12338,19 +12336,17 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12359,17 +12355,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12378,17 +12374,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12397,17 +12393,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12416,17 +12412,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12435,17 +12431,19 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12454,17 +12452,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12473,17 +12471,19 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12492,17 +12492,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12511,17 +12511,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12530,17 +12530,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12549,17 +12549,17 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12568,17 +12568,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12587,17 +12587,17 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12606,17 +12606,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>Owned {0} · up to {1} per listing</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12625,17 +12625,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12644,17 +12644,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12663,17 +12663,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12682,17 +12682,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12701,17 +12701,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12720,17 +12720,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12739,17 +12739,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12758,17 +12758,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12777,17 +12777,17 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E643" s="1" t="n"/>
@@ -12796,17 +12796,17 @@
       <c r="A644" s="1" t="n"/>
       <c r="B644" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C644" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D644" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E644" s="1" t="n"/>
@@ -12815,17 +12815,17 @@
       <c r="A645" s="1" t="n"/>
       <c r="B645" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E645" s="1" t="n"/>
@@ -12834,17 +12834,17 @@
       <c r="A646" s="1" t="n"/>
       <c r="B646" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C646" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D646" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E646" s="1" t="n"/>
@@ -12853,17 +12853,17 @@
       <c r="A647" s="1" t="n"/>
       <c r="B647" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D647" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E647" s="1" t="n"/>
@@ -12872,17 +12872,17 @@
       <c r="A648" s="1" t="n"/>
       <c r="B648" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C648" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D648" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E648" s="1" t="n"/>
@@ -12891,19 +12891,17 @@
       <c r="A649" s="1" t="n"/>
       <c r="B649" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D649" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E649" s="1" t="n"/>
@@ -12912,17 +12910,17 @@
       <c r="A650" s="1" t="n"/>
       <c r="B650" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C650" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D650" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E650" s="1" t="n"/>
@@ -12931,17 +12929,17 @@
       <c r="A651" s="1" t="n"/>
       <c r="B651" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C651" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E651" s="1" t="n"/>
@@ -12950,17 +12948,17 @@
       <c r="A652" s="1" t="n"/>
       <c r="B652" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C652" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D652" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E652" s="1" t="n"/>
@@ -12969,17 +12967,17 @@
       <c r="A653" s="1" t="n"/>
       <c r="B653" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C653" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D653" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E653" s="1" t="n"/>
@@ -12988,17 +12986,17 @@
       <c r="A654" s="1" t="n"/>
       <c r="B654" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C654" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D654" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E654" s="1" t="n"/>
@@ -13007,17 +13005,17 @@
       <c r="A655" s="1" t="n"/>
       <c r="B655" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C655" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D655" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E655" s="1" t="n"/>
@@ -13026,17 +13024,19 @@
       <c r="A656" s="1" t="n"/>
       <c r="B656" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C656" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D656" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E656" s="1" t="n"/>
@@ -13045,17 +13045,17 @@
       <c r="A657" s="1" t="n"/>
       <c r="B657" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C657" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D657" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E657" s="1" t="n"/>
@@ -13064,17 +13064,17 @@
       <c r="A658" s="1" t="n"/>
       <c r="B658" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C658" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D658" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E658" s="1" t="n"/>
@@ -13083,17 +13083,17 @@
       <c r="A659" s="1" t="n"/>
       <c r="B659" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.ChartTitle</t>
         </is>
       </c>
       <c r="C659" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
         </is>
       </c>
       <c r="D659" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
         </is>
       </c>
       <c r="E659" s="1" t="n"/>
@@ -13102,17 +13102,17 @@
       <c r="A660" s="1" t="n"/>
       <c r="B660" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.ChartEmpty</t>
         </is>
       </c>
       <c r="C660" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>최근 14일 동안 거래가 없습니다</t>
         </is>
       </c>
       <c r="D660" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>No trades in the last 14 days</t>
         </is>
       </c>
       <c r="E660" s="1" t="n"/>
@@ -13121,17 +13121,17 @@
       <c r="A661" s="1" t="n"/>
       <c r="B661" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.LevelsTitle</t>
         </is>
       </c>
       <c r="C661" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
         </is>
       </c>
       <c r="D661" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
         </is>
       </c>
       <c r="E661" s="1" t="n"/>
@@ -13140,17 +13140,17 @@
       <c r="A662" s="1" t="n"/>
       <c r="B662" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.LevelsEmpty</t>
         </is>
       </c>
       <c r="C662" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>지금 판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D662" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Nothing on sale right now</t>
         </is>
       </c>
       <c r="E662" s="1" t="n"/>
@@ -13159,17 +13159,17 @@
       <c r="A663" s="1" t="n"/>
       <c r="B663" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.RegisterOpen</t>
         </is>
       </c>
       <c r="C663" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>+ 판매 등록</t>
         </is>
       </c>
       <c r="D663" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>+ List Item</t>
         </is>
       </c>
       <c r="E663" s="1" t="n"/>
@@ -13178,17 +13178,17 @@
       <c r="A664" s="1" t="n"/>
       <c r="B664" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.ColItem</t>
         </is>
       </c>
       <c r="C664" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D664" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E664" s="1" t="n"/>
@@ -13197,17 +13197,17 @@
       <c r="A665" s="1" t="n"/>
       <c r="B665" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.ColNet</t>
         </is>
       </c>
       <c r="C665" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
+          <t>팔리면 받는 금액</t>
         </is>
       </c>
       <c r="D665" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.</t>
+          <t>You Get If Sold</t>
         </is>
       </c>
       <c r="E665" s="1" t="n"/>
@@ -13216,17 +13216,17 @@
       <c r="A666" s="1" t="n"/>
       <c r="B666" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.ColDate</t>
         </is>
       </c>
       <c r="C666" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="D666" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E666" s="1" t="n"/>
@@ -13235,17 +13235,17 @@
       <c r="A667" s="1" t="n"/>
       <c r="B667" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.ColType</t>
         </is>
       </c>
       <c r="C667" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="D667" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E667" s="1" t="n"/>
@@ -13254,17 +13254,17 @@
       <c r="A668" s="1" t="n"/>
       <c r="B668" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Register</t>
+          <t>UI.Auction.ColAmount</t>
         </is>
       </c>
       <c r="C668" s="6" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="D668" s="6" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E668" s="1" t="n"/>
@@ -13273,17 +13273,17 @@
       <c r="A669" s="1" t="n"/>
       <c r="B669" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideTitle</t>
+          <t>UI.Auction.ColDest</t>
         </is>
       </c>
       <c r="C669" s="6" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>받는 곳</t>
         </is>
       </c>
       <c r="D669" s="6" t="inlineStr">
         <is>
-          <t>Auction House</t>
+          <t>Goes To</t>
         </is>
       </c>
       <c r="E669" s="1" t="n"/>
@@ -13292,17 +13292,17 @@
       <c r="A670" s="1" t="n"/>
       <c r="B670" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyWhole</t>
+          <t>UI.Auction.RegisterTitle</t>
         </is>
       </c>
       <c r="C670" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D670" s="6" t="inlineStr">
         <is>
-          <t>Listings are bought whole — no partial purchases</t>
+          <t>List an Item</t>
         </is>
       </c>
       <c r="E670" s="1" t="n"/>
@@ -13311,17 +13311,17 @@
       <c r="A671" s="1" t="n"/>
       <c r="B671" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyOwn</t>
+          <t>UI.Auction.FindByName</t>
         </is>
       </c>
       <c r="C671" s="6" t="inlineStr">
         <is>
-          <t>내 매물은 살 수 없습니다</t>
+          <t>이름으로 찾기</t>
         </is>
       </c>
       <c r="D671" s="6" t="inlineStr">
         <is>
-          <t>You can't buy your own listings</t>
+          <t>Find by name</t>
         </is>
       </c>
       <c r="E671" s="1" t="n"/>
@@ -13330,17 +13330,17 @@
       <c r="A672" s="1" t="n"/>
       <c r="B672" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMailHeader</t>
+          <t>UI.Auction.RegisterEmptyCard</t>
         </is>
       </c>
       <c r="C672" s="6" t="inlineStr">
         <is>
-          <t>우편</t>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
         </is>
       </c>
       <c r="D672" s="6" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>[Select] something to list on the left.</t>
         </is>
       </c>
       <c r="E672" s="1" t="n"/>
@@ -13349,17 +13349,17 @@
       <c r="A673" s="1" t="n"/>
       <c r="B673" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMail</t>
+          <t>UI.Auction.ShowPrice</t>
         </is>
       </c>
       <c r="C673" s="6" t="inlineStr">
         <is>
-          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
+          <t>시세 보기</t>
         </is>
       </c>
       <c r="D673" s="6" t="inlineStr">
         <is>
-          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
+          <t>View Prices</t>
         </is>
       </c>
       <c r="E673" s="1" t="n"/>
@@ -13368,17 +13368,17 @@
       <c r="A674" s="1" t="n"/>
       <c r="B674" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideSellHint</t>
+          <t>UI.Auction.MatchLowest</t>
         </is>
       </c>
       <c r="C674" s="6" t="inlineStr">
         <is>
-          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
+          <t>최저가에 맞춤</t>
         </is>
       </c>
       <c r="D674" s="6" t="inlineStr">
         <is>
-          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
+          <t>Match Lowest</t>
         </is>
       </c>
       <c r="E674" s="1" t="n"/>
@@ -13387,17 +13387,17 @@
       <c r="A675" s="1" t="n"/>
       <c r="B675" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleAuction</t>
+          <t>UI.Auction.Register</t>
         </is>
       </c>
       <c r="C675" s="6" t="inlineStr">
         <is>
-          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="D675" s="6" t="inlineStr">
         <is>
-          <t>Auction — sell to other players at your price · wait until it sells</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E675" s="1" t="n"/>
@@ -13406,17 +13406,17 @@
       <c r="A676" s="1" t="n"/>
       <c r="B676" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleInstant</t>
+          <t>UI.Auction.GuideTitle</t>
         </is>
       </c>
       <c r="C676" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D676" s="6" t="inlineStr">
         <is>
-          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
+          <t>Auction House</t>
         </is>
       </c>
       <c r="E676" s="1" t="n"/>
@@ -13425,17 +13425,17 @@
       <c r="A677" s="1" t="n"/>
       <c r="B677" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleHeader</t>
+          <t>UI.Auction.GuideBuyWhole</t>
         </is>
       </c>
       <c r="C677" s="6" t="inlineStr">
         <is>
-          <t>등록 규칙</t>
+          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
         </is>
       </c>
       <c r="D677" s="6" t="inlineStr">
         <is>
-          <t>Listing Rules</t>
+          <t>Listings are bought whole — no partial purchases</t>
         </is>
       </c>
       <c r="E677" s="1" t="n"/>
@@ -13444,17 +13444,17 @@
       <c r="A678" s="1" t="n"/>
       <c r="B678" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RulePrice</t>
+          <t>UI.Auction.GuideBuyOwn</t>
         </is>
       </c>
       <c r="C678" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 이상 ~ {0} G</t>
+          <t>내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D678" s="6" t="inlineStr">
         <is>
-          <t>From the instant price ~ {0} G</t>
+          <t>You can't buy your own listings</t>
         </is>
       </c>
       <c r="E678" s="1" t="n"/>
@@ -13463,17 +13463,17 @@
       <c r="A679" s="1" t="n"/>
       <c r="B679" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCountLabel</t>
+          <t>UI.Auction.GuideMailHeader</t>
         </is>
       </c>
       <c r="C679" s="6" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>우편</t>
         </is>
       </c>
       <c r="D679" s="6" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Mail</t>
         </is>
       </c>
       <c r="E679" s="1" t="n"/>
@@ -13482,17 +13482,17 @@
       <c r="A680" s="1" t="n"/>
       <c r="B680" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCount</t>
+          <t>UI.Auction.GuideMail</t>
         </is>
       </c>
       <c r="C680" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
+          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D680" s="6" t="inlineStr">
         <is>
-          <t>Up to {0} per listing · sold only whole</t>
+          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
         </is>
       </c>
       <c r="E680" s="1" t="n"/>
@@ -13501,17 +13501,17 @@
       <c r="A681" s="1" t="n"/>
       <c r="B681" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSlots</t>
+          <t>UI.Auction.GuideSellHint</t>
         </is>
       </c>
       <c r="C681" s="6" t="inlineStr">
         <is>
-          <t>최대 {0}건</t>
+          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
         </is>
       </c>
       <c r="D681" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
         </is>
       </c>
       <c r="E681" s="1" t="n"/>
@@ -13520,17 +13520,17 @@
       <c r="A682" s="1" t="n"/>
       <c r="B682" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleListingFee</t>
+          <t>UI.Auction.RuleAuction</t>
         </is>
       </c>
       <c r="C682" s="6" t="inlineStr">
         <is>
-          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
         </is>
       </c>
       <c r="D682" s="6" t="inlineStr">
         <is>
-          <t>Paid on listing · refunded on expiry, not on cancel</t>
+          <t>Auction — sell to other players at your price · wait until it sells</t>
         </is>
       </c>
       <c r="E682" s="1" t="n"/>
@@ -13539,17 +13539,17 @@
       <c r="A683" s="1" t="n"/>
       <c r="B683" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSaleFee</t>
+          <t>UI.Auction.RuleInstant</t>
         </is>
       </c>
       <c r="C683" s="6" t="inlineStr">
         <is>
-          <t>팔린 금액에서 뗌</t>
+          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
         </is>
       </c>
       <c r="D683" s="6" t="inlineStr">
         <is>
-          <t>Deducted from the sale</t>
+          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
         </is>
       </c>
       <c r="E683" s="1" t="n"/>
@@ -13558,20 +13558,153 @@
       <c r="A684" s="1" t="n"/>
       <c r="B684" s="6" t="inlineStr">
         <is>
+          <t>UI.Auction.RuleHeader</t>
+        </is>
+      </c>
+      <c r="C684" s="6" t="inlineStr">
+        <is>
+          <t>등록 규칙</t>
+        </is>
+      </c>
+      <c r="D684" s="6" t="inlineStr">
+        <is>
+          <t>Listing Rules</t>
+        </is>
+      </c>
+      <c r="E684" s="1" t="n"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n"/>
+      <c r="B685" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RulePrice</t>
+        </is>
+      </c>
+      <c r="C685" s="6" t="inlineStr">
+        <is>
+          <t>즉시 판매가 이상 ~ {0} G</t>
+        </is>
+      </c>
+      <c r="D685" s="6" t="inlineStr">
+        <is>
+          <t>From the instant price ~ {0} G</t>
+        </is>
+      </c>
+      <c r="E685" s="1" t="n"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n"/>
+      <c r="B686" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleCountLabel</t>
+        </is>
+      </c>
+      <c r="C686" s="6" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D686" s="6" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="E686" s="1" t="n"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n"/>
+      <c r="B687" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleCount</t>
+        </is>
+      </c>
+      <c r="C687" s="6" t="inlineStr">
+        <is>
+          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
+        </is>
+      </c>
+      <c r="D687" s="6" t="inlineStr">
+        <is>
+          <t>Up to {0} per listing · sold only whole</t>
+        </is>
+      </c>
+      <c r="E687" s="1" t="n"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n"/>
+      <c r="B688" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleSlots</t>
+        </is>
+      </c>
+      <c r="C688" s="6" t="inlineStr">
+        <is>
+          <t>최대 {0}건</t>
+        </is>
+      </c>
+      <c r="D688" s="6" t="inlineStr">
+        <is>
+          <t>Up to {0}</t>
+        </is>
+      </c>
+      <c r="E688" s="1" t="n"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n"/>
+      <c r="B689" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleListingFee</t>
+        </is>
+      </c>
+      <c r="C689" s="6" t="inlineStr">
+        <is>
+          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+        </is>
+      </c>
+      <c r="D689" s="6" t="inlineStr">
+        <is>
+          <t>Paid on listing · refunded on expiry, not on cancel</t>
+        </is>
+      </c>
+      <c r="E689" s="1" t="n"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n"/>
+      <c r="B690" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleSaleFee</t>
+        </is>
+      </c>
+      <c r="C690" s="6" t="inlineStr">
+        <is>
+          <t>팔린 금액에서 뗌</t>
+        </is>
+      </c>
+      <c r="D690" s="6" t="inlineStr">
+        <is>
+          <t>Deducted from the sale</t>
+        </is>
+      </c>
+      <c r="E690" s="1" t="n"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n"/>
+      <c r="B691" s="6" t="inlineStr">
+        <is>
           <t>UI.Auction.RuleCantList</t>
         </is>
       </c>
-      <c r="C684" s="6" t="inlineStr">
+      <c r="C691" s="6" t="inlineStr">
         <is>
           <t>끼고 있는 장비 · 일하는 캐릭터 · 잠긴 것은 올릴 수 없습니다 (흐린 줄 — 올리면 사유)</t>
         </is>
       </c>
-      <c r="D684" s="6" t="inlineStr">
+      <c r="D691" s="6" t="inlineStr">
         <is>
           <t>Worn gear, working characters and locked items can't be listed (dimmed — hover for why)</t>
         </is>
       </c>
-      <c r="E684" s="1" t="n"/>
+      <c r="E691" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E763"/>
+  <dimension ref="A1:E765"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10605,17 +10605,17 @@
       <c r="A529" s="1" t="n"/>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.DrawAgain</t>
+          <t>UI.Gacha.ArtifactFound</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
         <is>
-          <t>{0}회 더 뽑기</t>
+          <t>아티팩트 발견!</t>
         </is>
       </c>
       <c r="D529" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0} Again</t>
+          <t>Artifact Found!</t>
         </is>
       </c>
       <c r="E529" s="1" t="n"/>
@@ -10624,17 +10624,17 @@
       <c r="A530" s="1" t="n"/>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Tab</t>
+          <t>UI.Gacha.SpecialRelicFound</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>Special 유물 발견!</t>
         </is>
       </c>
       <c r="D530" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Special Relic Found!</t>
         </is>
       </c>
       <c r="E530" s="1" t="n"/>
@@ -10643,17 +10643,17 @@
       <c r="A531" s="1" t="n"/>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.CloseResult</t>
+          <t>UI.Gacha.DrawAgain</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
         <is>
-          <t>[결과 닫기]</t>
+          <t>{0}회 더 뽑기</t>
         </is>
       </c>
       <c r="D531" s="6" t="inlineStr">
         <is>
-          <t>[Close]</t>
+          <t>Draw x{0} Again</t>
         </is>
       </c>
       <c r="E531" s="1" t="n"/>
@@ -10662,17 +10662,17 @@
       <c r="A532" s="1" t="n"/>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Gacha.Tab</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="D532" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E532" s="1" t="n"/>
@@ -10681,17 +10681,17 @@
       <c r="A533" s="1" t="n"/>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Stack</t>
+          <t>UI.Gacha.CloseResult</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
         <is>
-          <t>창고에 쌓기</t>
+          <t>[결과 닫기]</t>
         </is>
       </c>
       <c r="D533" s="6" t="inlineStr">
         <is>
-          <t>Stack in Warehouse</t>
+          <t>[Close]</t>
         </is>
       </c>
       <c r="E533" s="1" t="n"/>
@@ -10700,17 +10700,17 @@
       <c r="A534" s="1" t="n"/>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.StackTip</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
         <is>
-          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D534" s="6" t="inlineStr">
         <is>
-          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E534" s="1" t="n"/>
@@ -10719,17 +10719,17 @@
       <c r="A535" s="1" t="n"/>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.NothingToStack</t>
+          <t>UI.Warehouse.Stack</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
         <is>
-          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
+          <t>창고에 쌓기</t>
         </is>
       </c>
       <c r="D535" s="6" t="inlineStr">
         <is>
-          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
+          <t>Stack in Warehouse</t>
         </is>
       </c>
       <c r="E535" s="1" t="n"/>
@@ -10738,17 +10738,17 @@
       <c r="A536" s="1" t="n"/>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Warehouse.StackTip</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
         </is>
       </c>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
         </is>
       </c>
       <c r="E536" s="1" t="n"/>
@@ -10757,17 +10757,17 @@
       <c r="A537" s="1" t="n"/>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Warehouse.NothingToStack</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
         </is>
       </c>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
         </is>
       </c>
       <c r="E537" s="1" t="n"/>
@@ -10776,17 +10776,17 @@
       <c r="A538" s="1" t="n"/>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D538" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E538" s="1" t="n"/>
@@ -10795,17 +10795,17 @@
       <c r="A539" s="1" t="n"/>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D539" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E539" s="1" t="n"/>
@@ -10814,17 +10814,17 @@
       <c r="A540" s="1" t="n"/>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Title</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>Artifacts</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpTitle</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>Artifacts</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpGet</t>
+          <t>UI.Artifact.Title</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>유물을 감정하면 나옵니다 — 인벤토리 자원 탭에서 유물을 좌클릭</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>Appraise relics to get them — left-click a relic in the Inventory Resources tab</t>
+          <t>Artifacts</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpEquip</t>
+          <t>UI.Artifact.HelpTitle</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착해야 효과가 붙습니다 — 번호마다 1개, 장착은 되돌릴 수 없습니다</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>Effects apply only once placed in the codex — one per kind, and it can't be undone</t>
+          <t>Artifacts</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpToggle</t>
+          <t>UI.Artifact.HelpGet</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>장착한 아티팩트는 효과를 켜고 끌 수 있습니다 — 꺼 두면 효과가 없습니다</t>
+          <t>유물을 감정하면 나옵니다 — 인벤토리 자원 탭에서 유물을 좌클릭</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>Codex artifacts can be turned on or off — off means no effect</t>
+          <t>Appraise relics to get them — left-click a relic in the Inventory Resources tab</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpSell</t>
+          <t>UI.Artifact.HelpEquip</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>남는 것은 우클릭으로 즉시 판매하거나, Ctrl+우클릭으로 경매에 올려 더 비싸게 팝니다</t>
+          <t>도감에 장착해야 효과가 붙습니다 — 번호마다 1개, 장착은 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>Right-click extras to sell instantly, or Ctrl+right-click to list them on the auction for more</t>
+          <t>Effects apply only once placed in the codex — one per kind, and it can't be undone</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,17 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Codex</t>
+          <t>UI.Artifact.HelpToggle</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>장착한 아티팩트는 효과를 켜고 끌 수 있습니다 — 꺼 두면 효과가 없습니다</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Codex artifacts can be turned on or off — off means no effect</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11631,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EquippedCount</t>
+          <t>UI.Artifact.HelpSell</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>장착 {0} / {1}</t>
+          <t>남는 것은 우클릭으로 즉시 판매하거나, Ctrl+우클릭으로 경매에 올려 더 비싸게 팝니다</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>Placed {0} / {1}</t>
+          <t>Right-click extras to sell instantly, or Ctrl+right-click to list them on the auction for more</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11650,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.FilterAll</t>
+          <t>UI.Artifact.Codex</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11669,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.FilterEquipped</t>
+          <t>UI.Artifact.EquippedCount</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>장착 {0} / {1}</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Placed {0} / {1}</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11688,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.GroupHead</t>
+          <t>UI.Artifact.FilterAll</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>{0}   획득 {1} / {2}</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>{0}   Collected {1} / {2}</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11707,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Unknown</t>
+          <t>UI.Artifact.FilterEquipped</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11726,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.UnknownHint</t>
+          <t>UI.Artifact.GroupHead</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>아직 얻지 못한 아티팩트입니다</t>
+          <t>{0}   획득 {1} / {2}</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>You haven't found this artifact yet</t>
+          <t>{0}   Collected {1} / {2}</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11745,17 +11745,17 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Off</t>
+          <t>UI.Artifact.Unknown</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>꺼짐</t>
+          <t>???</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>???</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11764,17 +11764,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.OwnedShort</t>
+          <t>UI.Artifact.UnknownHint</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}</t>
+          <t>아직 얻지 못한 아티팩트입니다</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>You haven't found this artifact yet</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11783,17 +11783,17 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Holding</t>
+          <t>UI.Artifact.Off</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>보유 아티팩트  {0}종 · {1}개</t>
+          <t>꺼짐</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>Owned Artifacts  {0} kinds · {1}</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11802,17 +11802,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HoldingEmpty</t>
+          <t>UI.Artifact.OwnedShort</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>보유한 아티팩트가 없습니다 — 유물을 감정하면 생깁니다</t>
+          <t>보유 {0}</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>No artifacts yet — appraise relics to get some</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11821,17 +11821,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.New</t>
+          <t>UI.Artifact.Holding</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>보유 아티팩트  {0}종 · {1}개</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>Owned Artifacts  {0} kinds · {1}</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11840,17 +11840,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.DetailEmpty</t>
+          <t>UI.Artifact.HoldingEmpty</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>아티팩트를 고르면 설명이 여기에 뜹니다</t>
+          <t>보유한 아티팩트가 없습니다 — 유물을 감정하면 생깁니다</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>Select an artifact to see its details here</t>
+          <t>No artifacts yet — appraise relics to get some</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11859,17 +11859,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Effect</t>
+          <t>UI.Artifact.New</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11878,17 +11878,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateOn</t>
+          <t>UI.Artifact.DetailEmpty</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>장착 · 켜짐</t>
+          <t>아티팩트를 고르면 설명이 여기에 뜹니다</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>Placed · On</t>
+          <t>Select an artifact to see its details here</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11897,17 +11897,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateOff</t>
+          <t>UI.Artifact.Effect</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>장착 · 꺼짐</t>
+          <t>효과</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>Placed · Off</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11916,17 +11916,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateNone</t>
+          <t>UI.Artifact.StateOn</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>도감에 없음</t>
+          <t>장착 · 켜짐</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>Not in codex</t>
+          <t>Placed · On</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11935,17 +11935,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.ShowDetail</t>
+          <t>UI.Artifact.StateOff</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>장착 · 꺼짐</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Placed · Off</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11954,17 +11954,17 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Equip</t>
+          <t>UI.Artifact.StateNone</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착</t>
+          <t>도감에 없음</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>Place in Codex</t>
+          <t>Not in codex</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11973,17 +11973,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.TurnOff</t>
+          <t>UI.Artifact.ShowDetail</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>효과 끄기</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>Turn Off</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11992,17 +11992,17 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.TurnOn</t>
+          <t>UI.Artifact.Equip</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>효과 켜기</t>
+          <t>도감에 장착</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>Turn On</t>
+          <t>Place in Codex</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12011,17 +12011,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.WaitEquip</t>
+          <t>UI.Artifact.TurnOff</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>도감 장착</t>
+          <t>효과 끄기</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>Place in Codex</t>
+          <t>Turn Off</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12030,17 +12030,17 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.WaitToggle</t>
+          <t>UI.Artifact.TurnOn</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>켜고 끄기</t>
+          <t>효과 켜기</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>Turn On/Off</t>
+          <t>Turn On</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12049,17 +12049,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Equipped</t>
+          <t>UI.Artifact.WaitEquip</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착했습니다 — {0}</t>
+          <t>도감 장착</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>Placed in codex — {0}</t>
+          <t>Place in Codex</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12068,17 +12068,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellHead</t>
+          <t>UI.Artifact.WaitToggle</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 판매 {0}종</t>
+          <t>켜고 끄기</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>Sell Artifacts ({0})</t>
+          <t>Turn On/Off</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12087,17 +12087,17 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellEmpty</t>
+          <t>UI.Artifact.Equipped</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>보유 칸을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다. 비싸게 팔려면 Ctrl+우클릭(경매)</t>
+          <t>도감에 장착했습니다 — {0}</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>Right-click owned artifacts to add — they sell instantly. Ctrl+right-click to list on the auction for more</t>
+          <t>Placed in codex — {0}</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12106,17 +12106,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellUncollected</t>
+          <t>UI.Artifact.SellHead</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>주의! 도감에 없는 아티팩트 포함 — 팔면 도감에 남지 않습니다</t>
+          <t>아티팩트 판매 {0}종</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>Caution! Includes artifacts not in your codex — selling won't record them</t>
+          <t>Sell Artifacts ({0})</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12125,17 +12125,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.AllIndustry</t>
+          <t>UI.Artifact.SellEmpty</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>전 산업</t>
+          <t>보유 칸을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다. 비싸게 팔려면 Ctrl+우클릭(경매)</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>All industries</t>
+          <t>Right-click owned artifacts to add — they sell instantly. Ctrl+right-click to list on the auction for more</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12144,17 +12144,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectSpeed</t>
+          <t>UI.Artifact.SellUncollected</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>{0} 작업속도 +{1}</t>
+          <t>주의! 도감에 없는 아티팩트 포함 — 팔면 도감에 남지 않습니다</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>{0} work speed +{1}</t>
+          <t>Caution! Includes artifacts not in your codex — selling won't record them</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12163,17 +12163,17 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectYield</t>
+          <t>UI.Artifact.AllIndustry</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>{0} 산출량 +{1}</t>
+          <t>전 산업</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
         <is>
-          <t>{0} yield +{1}</t>
+          <t>All industries</t>
         </is>
       </c>
       <c r="E611" s="1" t="n"/>
@@ -12182,17 +12182,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectAppraise</t>
+          <t>UI.Artifact.EffectSpeed</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>감정 비용 −{0}</t>
+          <t>{0} 작업속도 +{1}</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>Appraisal cost −{0}</t>
+          <t>{0} work speed +{1}</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12201,17 +12201,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectRelic</t>
+          <t>UI.Artifact.EffectYield</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>유물 발견 확률 +{0}</t>
+          <t>{0} 산출량 +{1}</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Relic find chance +{0}</t>
+          <t>{0} yield +{1}</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12220,17 +12220,17 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Window</t>
+          <t>UI.Artifact.EffectAppraise</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 — 도감에 장착</t>
+          <t>감정 비용 −{0}</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>Artifact — Place in Codex</t>
+          <t>Appraisal cost −{0}</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12239,17 +12239,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.AlreadyEquipped</t>
+          <t>UI.Artifact.EffectRelic</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>이미 도감에 장착함</t>
+          <t>유물 발견 확률 +{0}</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>Already in Codex</t>
+          <t>Relic find chance +{0}</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12258,17 +12258,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.OpenCodex</t>
+          <t>UI.Artifact.Window</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>도감 보기</t>
+          <t>아티팩트 — 도감에 장착</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>View Codex</t>
+          <t>Artifact — Place in Codex</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12277,17 +12277,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EquipHint</t>
+          <t>UI.Artifact.AlreadyEquipped</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>장착하면 효과가 켜집니다 — 번호마다 1개, 되돌릴 수 없습니다</t>
+          <t>이미 도감에 장착함</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>Placing turns its effect on — one per kind, and it can't be undone</t>
+          <t>Already in Codex</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12296,17 +12296,17 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellHint</t>
+          <t>UI.Artifact.OpenCodex</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>남는 것은 우클릭 즉시 판매 · Ctrl+우클릭 경매</t>
+          <t>도감 보기</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>Right-click extras to sell · Ctrl+right-click to auction</t>
+          <t>View Codex</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12315,17 +12315,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.NoLock</t>
+          <t>UI.Artifact.EquipHint</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>아티팩트는 아직 잠글 수 없습니다</t>
+          <t>장착하면 효과가 켜집니다 — 번호마다 1개, 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>Artifacts can't be locked yet</t>
+          <t>Placing turns its effect on — one per kind, and it can't be undone</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12334,17 +12334,17 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.NoMove</t>
+          <t>UI.Artifact.SellHint</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 칸은 아직 옮길 수 없습니다</t>
+          <t>남는 것은 우클릭 즉시 판매 · Ctrl+우클릭 경매</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>Artifact slots can't be moved yet</t>
+          <t>Right-click extras to sell · Ctrl+right-click to auction</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12353,17 +12353,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.KindArtifact</t>
+          <t>UI.Artifact.NoLock</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 판매 {0}종</t>
+          <t>아티팩트는 아직 잠글 수 없습니다</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>Sell Artifacts ({0})</t>
+          <t>Artifacts can't be locked yet</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12372,17 +12372,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.ArtifactNoShard</t>
+          <t>UI.Artifact.NoMove</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>아티팩트는 아직 마석으로 분해할 수 없습니다 — 분해는 장비만</t>
+          <t>아티팩트 칸은 아직 옮길 수 없습니다</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>Artifacts can't be disassembled into shards yet — gear only</t>
+          <t>Artifact slots can't be moved yet</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12391,17 +12391,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Sell.KindArtifact</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>아티팩트 판매 {0}종</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>Sell Artifacts ({0})</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12410,17 +12410,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Sell.ArtifactNoShard</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>아티팩트는 아직 마석으로 분해할 수 없습니다 — 분해는 장비만</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>Artifacts can't be disassembled into shards yet — gear only</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12429,17 +12429,17 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12448,17 +12448,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12467,17 +12467,17 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12486,17 +12486,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12505,17 +12505,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12524,17 +12524,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12543,17 +12543,17 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12562,17 +12562,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12581,17 +12581,17 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12600,17 +12600,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12619,17 +12619,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12638,17 +12638,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12657,17 +12657,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12676,17 +12676,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12695,17 +12695,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12714,17 +12714,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12733,17 +12733,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12752,17 +12752,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12771,17 +12771,17 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E643" s="1" t="n"/>
@@ -12790,17 +12790,17 @@
       <c r="A644" s="1" t="n"/>
       <c r="B644" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C644" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D644" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E644" s="1" t="n"/>
@@ -12809,17 +12809,17 @@
       <c r="A645" s="1" t="n"/>
       <c r="B645" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E645" s="1" t="n"/>
@@ -12828,17 +12828,17 @@
       <c r="A646" s="1" t="n"/>
       <c r="B646" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C646" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D646" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E646" s="1" t="n"/>
@@ -12847,17 +12847,17 @@
       <c r="A647" s="1" t="n"/>
       <c r="B647" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D647" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E647" s="1" t="n"/>
@@ -12866,17 +12866,17 @@
       <c r="A648" s="1" t="n"/>
       <c r="B648" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C648" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D648" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E648" s="1" t="n"/>
@@ -12885,17 +12885,17 @@
       <c r="A649" s="1" t="n"/>
       <c r="B649" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D649" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E649" s="1" t="n"/>
@@ -12904,17 +12904,17 @@
       <c r="A650" s="1" t="n"/>
       <c r="B650" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C650" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D650" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E650" s="1" t="n"/>
@@ -12923,17 +12923,17 @@
       <c r="A651" s="1" t="n"/>
       <c r="B651" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C651" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E651" s="1" t="n"/>
@@ -12942,17 +12942,17 @@
       <c r="A652" s="1" t="n"/>
       <c r="B652" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C652" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D652" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E652" s="1" t="n"/>
@@ -12961,17 +12961,17 @@
       <c r="A653" s="1" t="n"/>
       <c r="B653" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C653" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D653" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E653" s="1" t="n"/>
@@ -12980,17 +12980,17 @@
       <c r="A654" s="1" t="n"/>
       <c r="B654" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C654" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D654" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E654" s="1" t="n"/>
@@ -12999,17 +12999,17 @@
       <c r="A655" s="1" t="n"/>
       <c r="B655" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C655" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D655" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E655" s="1" t="n"/>
@@ -13018,17 +13018,17 @@
       <c r="A656" s="1" t="n"/>
       <c r="B656" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C656" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D656" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E656" s="1" t="n"/>
@@ -13037,17 +13037,17 @@
       <c r="A657" s="1" t="n"/>
       <c r="B657" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C657" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D657" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E657" s="1" t="n"/>
@@ -13056,17 +13056,17 @@
       <c r="A658" s="1" t="n"/>
       <c r="B658" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C658" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D658" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E658" s="1" t="n"/>
@@ -13075,17 +13075,17 @@
       <c r="A659" s="1" t="n"/>
       <c r="B659" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C659" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D659" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E659" s="1" t="n"/>
@@ -13094,17 +13094,17 @@
       <c r="A660" s="1" t="n"/>
       <c r="B660" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C660" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D660" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E660" s="1" t="n"/>
@@ -13113,17 +13113,17 @@
       <c r="A661" s="1" t="n"/>
       <c r="B661" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C661" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D661" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E661" s="1" t="n"/>
@@ -13132,17 +13132,17 @@
       <c r="A662" s="1" t="n"/>
       <c r="B662" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C662" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D662" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E662" s="1" t="n"/>
@@ -13151,17 +13151,17 @@
       <c r="A663" s="1" t="n"/>
       <c r="B663" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C663" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D663" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E663" s="1" t="n"/>
@@ -13170,17 +13170,17 @@
       <c r="A664" s="1" t="n"/>
       <c r="B664" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C664" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D664" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E664" s="1" t="n"/>
@@ -13189,17 +13189,17 @@
       <c r="A665" s="1" t="n"/>
       <c r="B665" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C665" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D665" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E665" s="1" t="n"/>
@@ -13208,17 +13208,17 @@
       <c r="A666" s="1" t="n"/>
       <c r="B666" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C666" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D666" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E666" s="1" t="n"/>
@@ -13227,17 +13227,17 @@
       <c r="A667" s="1" t="n"/>
       <c r="B667" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C667" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D667" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E667" s="1" t="n"/>
@@ -13246,17 +13246,17 @@
       <c r="A668" s="1" t="n"/>
       <c r="B668" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C668" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D668" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E668" s="1" t="n"/>
@@ -13265,17 +13265,17 @@
       <c r="A669" s="1" t="n"/>
       <c r="B669" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C669" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D669" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E669" s="1" t="n"/>
@@ -13284,17 +13284,17 @@
       <c r="A670" s="1" t="n"/>
       <c r="B670" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C670" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D670" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E670" s="1" t="n"/>
@@ -13303,17 +13303,17 @@
       <c r="A671" s="1" t="n"/>
       <c r="B671" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C671" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D671" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E671" s="1" t="n"/>
@@ -13322,17 +13322,17 @@
       <c r="A672" s="1" t="n"/>
       <c r="B672" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C672" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D672" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E672" s="1" t="n"/>
@@ -13341,17 +13341,17 @@
       <c r="A673" s="1" t="n"/>
       <c r="B673" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C673" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D673" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E673" s="1" t="n"/>
@@ -13360,17 +13360,17 @@
       <c r="A674" s="1" t="n"/>
       <c r="B674" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C674" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D674" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E674" s="1" t="n"/>
@@ -13379,17 +13379,17 @@
       <c r="A675" s="1" t="n"/>
       <c r="B675" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C675" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D675" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E675" s="1" t="n"/>
@@ -13398,17 +13398,17 @@
       <c r="A676" s="1" t="n"/>
       <c r="B676" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C676" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D676" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E676" s="1" t="n"/>
@@ -13417,17 +13417,17 @@
       <c r="A677" s="1" t="n"/>
       <c r="B677" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C677" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D677" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E677" s="1" t="n"/>
@@ -13436,17 +13436,17 @@
       <c r="A678" s="1" t="n"/>
       <c r="B678" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C678" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D678" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E678" s="1" t="n"/>
@@ -13455,17 +13455,17 @@
       <c r="A679" s="1" t="n"/>
       <c r="B679" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C679" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D679" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E679" s="1" t="n"/>
@@ -13474,17 +13474,17 @@
       <c r="A680" s="1" t="n"/>
       <c r="B680" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C680" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D680" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E680" s="1" t="n"/>
@@ -13493,17 +13493,17 @@
       <c r="A681" s="1" t="n"/>
       <c r="B681" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C681" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D681" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E681" s="1" t="n"/>
@@ -13512,17 +13512,17 @@
       <c r="A682" s="1" t="n"/>
       <c r="B682" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C682" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D682" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E682" s="1" t="n"/>
@@ -13531,17 +13531,17 @@
       <c r="A683" s="1" t="n"/>
       <c r="B683" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C683" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D683" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E683" s="1" t="n"/>
@@ -13550,17 +13550,17 @@
       <c r="A684" s="1" t="n"/>
       <c r="B684" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C684" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D684" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E684" s="1" t="n"/>
@@ -13569,19 +13569,17 @@
       <c r="A685" s="1" t="n"/>
       <c r="B685" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C685" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D685" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E685" s="1" t="n"/>
@@ -13590,17 +13588,17 @@
       <c r="A686" s="1" t="n"/>
       <c r="B686" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C686" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D686" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E686" s="1" t="n"/>
@@ -13609,17 +13607,19 @@
       <c r="A687" s="1" t="n"/>
       <c r="B687" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C687" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D687" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E687" s="1" t="n"/>
@@ -13628,17 +13628,17 @@
       <c r="A688" s="1" t="n"/>
       <c r="B688" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C688" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D688" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E688" s="1" t="n"/>
@@ -13647,17 +13647,17 @@
       <c r="A689" s="1" t="n"/>
       <c r="B689" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C689" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D689" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E689" s="1" t="n"/>
@@ -13666,17 +13666,17 @@
       <c r="A690" s="1" t="n"/>
       <c r="B690" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C690" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D690" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E690" s="1" t="n"/>
@@ -13685,17 +13685,17 @@
       <c r="A691" s="1" t="n"/>
       <c r="B691" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C691" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D691" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E691" s="1" t="n"/>
@@ -13704,17 +13704,17 @@
       <c r="A692" s="1" t="n"/>
       <c r="B692" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C692" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D692" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E692" s="1" t="n"/>
@@ -13723,17 +13723,17 @@
       <c r="A693" s="1" t="n"/>
       <c r="B693" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C693" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D693" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E693" s="1" t="n"/>
@@ -13742,17 +13742,17 @@
       <c r="A694" s="1" t="n"/>
       <c r="B694" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C694" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D694" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E694" s="1" t="n"/>
@@ -13761,17 +13761,17 @@
       <c r="A695" s="1" t="n"/>
       <c r="B695" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C695" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D695" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E695" s="1" t="n"/>
@@ -13780,19 +13780,17 @@
       <c r="A696" s="1" t="n"/>
       <c r="B696" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C696" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D696" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E696" s="1" t="n"/>
@@ -13801,17 +13799,17 @@
       <c r="A697" s="1" t="n"/>
       <c r="B697" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C697" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D697" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E697" s="1" t="n"/>
@@ -13820,19 +13818,19 @@
       <c r="A698" s="1" t="n"/>
       <c r="B698" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C698" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D698" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E698" s="1" t="n"/>
@@ -13841,17 +13839,17 @@
       <c r="A699" s="1" t="n"/>
       <c r="B699" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C699" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D699" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E699" s="1" t="n"/>
@@ -13860,17 +13858,19 @@
       <c r="A700" s="1" t="n"/>
       <c r="B700" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C700" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D700" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E700" s="1" t="n"/>
@@ -13879,17 +13879,17 @@
       <c r="A701" s="1" t="n"/>
       <c r="B701" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C701" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D701" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E701" s="1" t="n"/>
@@ -13898,17 +13898,17 @@
       <c r="A702" s="1" t="n"/>
       <c r="B702" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C702" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D702" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E702" s="1" t="n"/>
@@ -13917,17 +13917,17 @@
       <c r="A703" s="1" t="n"/>
       <c r="B703" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C703" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D703" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E703" s="1" t="n"/>
@@ -13936,17 +13936,17 @@
       <c r="A704" s="1" t="n"/>
       <c r="B704" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C704" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D704" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E704" s="1" t="n"/>
@@ -13955,17 +13955,17 @@
       <c r="A705" s="1" t="n"/>
       <c r="B705" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C705" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D705" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E705" s="1" t="n"/>
@@ -13974,17 +13974,17 @@
       <c r="A706" s="1" t="n"/>
       <c r="B706" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C706" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D706" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E706" s="1" t="n"/>
@@ -13993,17 +13993,17 @@
       <c r="A707" s="1" t="n"/>
       <c r="B707" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C707" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지</t>
         </is>
       </c>
       <c r="D707" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Owned {0} · up to {1} per listing</t>
         </is>
       </c>
       <c r="E707" s="1" t="n"/>
@@ -14012,17 +14012,17 @@
       <c r="A708" s="1" t="n"/>
       <c r="B708" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C708" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D708" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E708" s="1" t="n"/>
@@ -14031,17 +14031,17 @@
       <c r="A709" s="1" t="n"/>
       <c r="B709" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C709" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D709" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E709" s="1" t="n"/>
@@ -14050,17 +14050,17 @@
       <c r="A710" s="1" t="n"/>
       <c r="B710" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C710" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D710" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E710" s="1" t="n"/>
@@ -14069,17 +14069,17 @@
       <c r="A711" s="1" t="n"/>
       <c r="B711" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C711" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D711" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E711" s="1" t="n"/>
@@ -14088,17 +14088,17 @@
       <c r="A712" s="1" t="n"/>
       <c r="B712" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C712" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D712" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E712" s="1" t="n"/>
@@ -14107,17 +14107,17 @@
       <c r="A713" s="1" t="n"/>
       <c r="B713" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantViaArtifact</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C713" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 아티팩트 [판매]</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D713" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Artifacts [Sell]</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E713" s="1" t="n"/>
@@ -14126,17 +14126,17 @@
       <c r="A714" s="1" t="n"/>
       <c r="B714" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C714" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D714" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E714" s="1" t="n"/>
@@ -14145,17 +14145,17 @@
       <c r="A715" s="1" t="n"/>
       <c r="B715" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.InstantViaArtifact</t>
         </is>
       </c>
       <c r="C715" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>{0} G — 아티팩트 [판매]</t>
         </is>
       </c>
       <c r="D715" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>{0} G — Artifacts [Sell]</t>
         </is>
       </c>
       <c r="E715" s="1" t="n"/>
@@ -14164,17 +14164,17 @@
       <c r="A716" s="1" t="n"/>
       <c r="B716" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C716" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D716" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E716" s="1" t="n"/>
@@ -14183,17 +14183,17 @@
       <c r="A717" s="1" t="n"/>
       <c r="B717" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C717" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D717" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E717" s="1" t="n"/>
@@ -14202,17 +14202,17 @@
       <c r="A718" s="1" t="n"/>
       <c r="B718" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C718" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D718" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E718" s="1" t="n"/>
@@ -14221,17 +14221,17 @@
       <c r="A719" s="1" t="n"/>
       <c r="B719" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C719" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D719" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E719" s="1" t="n"/>
@@ -14240,17 +14240,17 @@
       <c r="A720" s="1" t="n"/>
       <c r="B720" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C720" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D720" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E720" s="1" t="n"/>
@@ -14259,17 +14259,17 @@
       <c r="A721" s="1" t="n"/>
       <c r="B721" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C721" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D721" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E721" s="1" t="n"/>
@@ -14278,17 +14278,17 @@
       <c r="A722" s="1" t="n"/>
       <c r="B722" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C722" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D722" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E722" s="1" t="n"/>
@@ -14297,17 +14297,17 @@
       <c r="A723" s="1" t="n"/>
       <c r="B723" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C723" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D723" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E723" s="1" t="n"/>
@@ -14316,17 +14316,17 @@
       <c r="A724" s="1" t="n"/>
       <c r="B724" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C724" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D724" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E724" s="1" t="n"/>
@@ -14335,17 +14335,17 @@
       <c r="A725" s="1" t="n"/>
       <c r="B725" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C725" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D725" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E725" s="1" t="n"/>
@@ -14354,17 +14354,17 @@
       <c r="A726" s="1" t="n"/>
       <c r="B726" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C726" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D726" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E726" s="1" t="n"/>
@@ -14373,17 +14373,17 @@
       <c r="A727" s="1" t="n"/>
       <c r="B727" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C727" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D727" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E727" s="1" t="n"/>
@@ -14392,19 +14392,17 @@
       <c r="A728" s="1" t="n"/>
       <c r="B728" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C728" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D728" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E728" s="1" t="n"/>
@@ -14413,17 +14411,17 @@
       <c r="A729" s="1" t="n"/>
       <c r="B729" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C729" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D729" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E729" s="1" t="n"/>
@@ -14432,17 +14430,19 @@
       <c r="A730" s="1" t="n"/>
       <c r="B730" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C730" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D730" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E730" s="1" t="n"/>
@@ -14451,17 +14451,17 @@
       <c r="A731" s="1" t="n"/>
       <c r="B731" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C731" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D731" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E731" s="1" t="n"/>
@@ -14470,17 +14470,17 @@
       <c r="A732" s="1" t="n"/>
       <c r="B732" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C732" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D732" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E732" s="1" t="n"/>
@@ -14489,17 +14489,17 @@
       <c r="A733" s="1" t="n"/>
       <c r="B733" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.ChartTitle</t>
         </is>
       </c>
       <c r="C733" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
         </is>
       </c>
       <c r="D733" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
         </is>
       </c>
       <c r="E733" s="1" t="n"/>
@@ -14508,17 +14508,17 @@
       <c r="A734" s="1" t="n"/>
       <c r="B734" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.ChartEmpty</t>
         </is>
       </c>
       <c r="C734" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>최근 14일 동안 거래가 없습니다</t>
         </is>
       </c>
       <c r="D734" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>No trades in the last 14 days</t>
         </is>
       </c>
       <c r="E734" s="1" t="n"/>
@@ -14527,17 +14527,17 @@
       <c r="A735" s="1" t="n"/>
       <c r="B735" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.LevelsTitle</t>
         </is>
       </c>
       <c r="C735" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
         </is>
       </c>
       <c r="D735" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
         </is>
       </c>
       <c r="E735" s="1" t="n"/>
@@ -14546,17 +14546,17 @@
       <c r="A736" s="1" t="n"/>
       <c r="B736" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.LevelsEmpty</t>
         </is>
       </c>
       <c r="C736" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>지금 판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D736" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Nothing on sale right now</t>
         </is>
       </c>
       <c r="E736" s="1" t="n"/>
@@ -14565,17 +14565,17 @@
       <c r="A737" s="1" t="n"/>
       <c r="B737" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.RegisterOpen</t>
         </is>
       </c>
       <c r="C737" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>+ 판매 등록</t>
         </is>
       </c>
       <c r="D737" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>+ List Item</t>
         </is>
       </c>
       <c r="E737" s="1" t="n"/>
@@ -14584,17 +14584,17 @@
       <c r="A738" s="1" t="n"/>
       <c r="B738" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.ColItem</t>
         </is>
       </c>
       <c r="C738" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D738" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E738" s="1" t="n"/>
@@ -14603,17 +14603,17 @@
       <c r="A739" s="1" t="n"/>
       <c r="B739" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.ColNet</t>
         </is>
       </c>
       <c r="C739" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>팔리면 받는 금액</t>
         </is>
       </c>
       <c r="D739" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>You Get If Sold</t>
         </is>
       </c>
       <c r="E739" s="1" t="n"/>
@@ -14622,17 +14622,17 @@
       <c r="A740" s="1" t="n"/>
       <c r="B740" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.ColDate</t>
         </is>
       </c>
       <c r="C740" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="D740" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E740" s="1" t="n"/>
@@ -14641,17 +14641,17 @@
       <c r="A741" s="1" t="n"/>
       <c r="B741" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.ColType</t>
         </is>
       </c>
       <c r="C741" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="D741" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E741" s="1" t="n"/>
@@ -14660,17 +14660,17 @@
       <c r="A742" s="1" t="n"/>
       <c r="B742" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.ColAmount</t>
         </is>
       </c>
       <c r="C742" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="D742" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E742" s="1" t="n"/>
@@ -14679,17 +14679,17 @@
       <c r="A743" s="1" t="n"/>
       <c r="B743" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.ColDest</t>
         </is>
       </c>
       <c r="C743" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>받는 곳</t>
         </is>
       </c>
       <c r="D743" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>Goes To</t>
         </is>
       </c>
       <c r="E743" s="1" t="n"/>
@@ -14698,17 +14698,17 @@
       <c r="A744" s="1" t="n"/>
       <c r="B744" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.RegisterTitle</t>
         </is>
       </c>
       <c r="C744" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D744" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.</t>
+          <t>List an Item</t>
         </is>
       </c>
       <c r="E744" s="1" t="n"/>
@@ -14717,17 +14717,17 @@
       <c r="A745" s="1" t="n"/>
       <c r="B745" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.FindByName</t>
         </is>
       </c>
       <c r="C745" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>이름으로 찾기</t>
         </is>
       </c>
       <c r="D745" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>Find by name</t>
         </is>
       </c>
       <c r="E745" s="1" t="n"/>
@@ -14736,17 +14736,17 @@
       <c r="A746" s="1" t="n"/>
       <c r="B746" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.RegisterEmptyCard</t>
         </is>
       </c>
       <c r="C746" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
         </is>
       </c>
       <c r="D746" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>[Select] something to list on the left.</t>
         </is>
       </c>
       <c r="E746" s="1" t="n"/>
@@ -14755,17 +14755,17 @@
       <c r="A747" s="1" t="n"/>
       <c r="B747" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Register</t>
+          <t>UI.Auction.ShowPrice</t>
         </is>
       </c>
       <c r="C747" s="6" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>시세 보기</t>
         </is>
       </c>
       <c r="D747" s="6" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>View Prices</t>
         </is>
       </c>
       <c r="E747" s="1" t="n"/>
@@ -14774,17 +14774,17 @@
       <c r="A748" s="1" t="n"/>
       <c r="B748" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideTitle</t>
+          <t>UI.Auction.MatchLowest</t>
         </is>
       </c>
       <c r="C748" s="6" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>최저가에 맞춤</t>
         </is>
       </c>
       <c r="D748" s="6" t="inlineStr">
         <is>
-          <t>Auction House</t>
+          <t>Match Lowest</t>
         </is>
       </c>
       <c r="E748" s="1" t="n"/>
@@ -14793,17 +14793,17 @@
       <c r="A749" s="1" t="n"/>
       <c r="B749" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyWhole</t>
+          <t>UI.Auction.Register</t>
         </is>
       </c>
       <c r="C749" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="D749" s="6" t="inlineStr">
         <is>
-          <t>Listings are bought whole — no partial purchases</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E749" s="1" t="n"/>
@@ -14812,17 +14812,17 @@
       <c r="A750" s="1" t="n"/>
       <c r="B750" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyOwn</t>
+          <t>UI.Auction.GuideTitle</t>
         </is>
       </c>
       <c r="C750" s="6" t="inlineStr">
         <is>
-          <t>내 매물은 살 수 없습니다</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D750" s="6" t="inlineStr">
         <is>
-          <t>You can't buy your own listings</t>
+          <t>Auction House</t>
         </is>
       </c>
       <c r="E750" s="1" t="n"/>
@@ -14831,17 +14831,17 @@
       <c r="A751" s="1" t="n"/>
       <c r="B751" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMailHeader</t>
+          <t>UI.Auction.GuideBuyWhole</t>
         </is>
       </c>
       <c r="C751" s="6" t="inlineStr">
         <is>
-          <t>우편</t>
+          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
         </is>
       </c>
       <c r="D751" s="6" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Listings are bought whole — no partial purchases</t>
         </is>
       </c>
       <c r="E751" s="1" t="n"/>
@@ -14850,17 +14850,17 @@
       <c r="A752" s="1" t="n"/>
       <c r="B752" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMail</t>
+          <t>UI.Auction.GuideBuyOwn</t>
         </is>
       </c>
       <c r="C752" s="6" t="inlineStr">
         <is>
-          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
+          <t>내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D752" s="6" t="inlineStr">
         <is>
-          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
+          <t>You can't buy your own listings</t>
         </is>
       </c>
       <c r="E752" s="1" t="n"/>
@@ -14869,17 +14869,17 @@
       <c r="A753" s="1" t="n"/>
       <c r="B753" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideSellHint</t>
+          <t>UI.Auction.GuideMailHeader</t>
         </is>
       </c>
       <c r="C753" s="6" t="inlineStr">
         <is>
-          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
+          <t>우편</t>
         </is>
       </c>
       <c r="D753" s="6" t="inlineStr">
         <is>
-          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
+          <t>Mail</t>
         </is>
       </c>
       <c r="E753" s="1" t="n"/>
@@ -14888,17 +14888,17 @@
       <c r="A754" s="1" t="n"/>
       <c r="B754" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleAuction</t>
+          <t>UI.Auction.GuideMail</t>
         </is>
       </c>
       <c r="C754" s="6" t="inlineStr">
         <is>
-          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
+          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D754" s="6" t="inlineStr">
         <is>
-          <t>Auction — sell to other players at your price · wait until it sells</t>
+          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
         </is>
       </c>
       <c r="E754" s="1" t="n"/>
@@ -14907,17 +14907,17 @@
       <c r="A755" s="1" t="n"/>
       <c r="B755" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleInstant</t>
+          <t>UI.Auction.GuideSellHint</t>
         </is>
       </c>
       <c r="C755" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
+          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
         </is>
       </c>
       <c r="D755" s="6" t="inlineStr">
         <is>
-          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
+          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
         </is>
       </c>
       <c r="E755" s="1" t="n"/>
@@ -14926,17 +14926,17 @@
       <c r="A756" s="1" t="n"/>
       <c r="B756" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleHeader</t>
+          <t>UI.Auction.RuleAuction</t>
         </is>
       </c>
       <c r="C756" s="6" t="inlineStr">
         <is>
-          <t>등록 규칙</t>
+          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
         </is>
       </c>
       <c r="D756" s="6" t="inlineStr">
         <is>
-          <t>Listing Rules</t>
+          <t>Auction — sell to other players at your price · wait until it sells</t>
         </is>
       </c>
       <c r="E756" s="1" t="n"/>
@@ -14945,17 +14945,17 @@
       <c r="A757" s="1" t="n"/>
       <c r="B757" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RulePrice</t>
+          <t>UI.Auction.RuleInstant</t>
         </is>
       </c>
       <c r="C757" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 이상 ~ {0} G</t>
+          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
         </is>
       </c>
       <c r="D757" s="6" t="inlineStr">
         <is>
-          <t>From the instant price ~ {0} G</t>
+          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
         </is>
       </c>
       <c r="E757" s="1" t="n"/>
@@ -14964,17 +14964,17 @@
       <c r="A758" s="1" t="n"/>
       <c r="B758" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCountLabel</t>
+          <t>UI.Auction.RuleHeader</t>
         </is>
       </c>
       <c r="C758" s="6" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>등록 규칙</t>
         </is>
       </c>
       <c r="D758" s="6" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Listing Rules</t>
         </is>
       </c>
       <c r="E758" s="1" t="n"/>
@@ -14983,17 +14983,17 @@
       <c r="A759" s="1" t="n"/>
       <c r="B759" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCount</t>
+          <t>UI.Auction.RulePrice</t>
         </is>
       </c>
       <c r="C759" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
+          <t>즉시 판매가 이상 ~ {0} G</t>
         </is>
       </c>
       <c r="D759" s="6" t="inlineStr">
         <is>
-          <t>Up to {0} per listing · sold only whole</t>
+          <t>From the instant price ~ {0} G</t>
         </is>
       </c>
       <c r="E759" s="1" t="n"/>
@@ -15002,17 +15002,17 @@
       <c r="A760" s="1" t="n"/>
       <c r="B760" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSlots</t>
+          <t>UI.Auction.RuleCountLabel</t>
         </is>
       </c>
       <c r="C760" s="6" t="inlineStr">
         <is>
-          <t>최대 {0}건</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="D760" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="E760" s="1" t="n"/>
@@ -15021,17 +15021,17 @@
       <c r="A761" s="1" t="n"/>
       <c r="B761" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleListingFee</t>
+          <t>UI.Auction.RuleCount</t>
         </is>
       </c>
       <c r="C761" s="6" t="inlineStr">
         <is>
-          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
         </is>
       </c>
       <c r="D761" s="6" t="inlineStr">
         <is>
-          <t>Paid on listing · refunded on expiry, not on cancel</t>
+          <t>Up to {0} per listing · sold only whole</t>
         </is>
       </c>
       <c r="E761" s="1" t="n"/>
@@ -15040,17 +15040,17 @@
       <c r="A762" s="1" t="n"/>
       <c r="B762" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSaleFee</t>
+          <t>UI.Auction.RuleSlots</t>
         </is>
       </c>
       <c r="C762" s="6" t="inlineStr">
         <is>
-          <t>팔린 금액에서 뗌</t>
+          <t>최대 {0}건</t>
         </is>
       </c>
       <c r="D762" s="6" t="inlineStr">
         <is>
-          <t>Deducted from the sale</t>
+          <t>Up to {0}</t>
         </is>
       </c>
       <c r="E762" s="1" t="n"/>
@@ -15059,20 +15059,58 @@
       <c r="A763" s="1" t="n"/>
       <c r="B763" s="6" t="inlineStr">
         <is>
+          <t>UI.Auction.RuleListingFee</t>
+        </is>
+      </c>
+      <c r="C763" s="6" t="inlineStr">
+        <is>
+          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+        </is>
+      </c>
+      <c r="D763" s="6" t="inlineStr">
+        <is>
+          <t>Paid on listing · refunded on expiry, not on cancel</t>
+        </is>
+      </c>
+      <c r="E763" s="1" t="n"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="n"/>
+      <c r="B764" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleSaleFee</t>
+        </is>
+      </c>
+      <c r="C764" s="6" t="inlineStr">
+        <is>
+          <t>팔린 금액에서 뗌</t>
+        </is>
+      </c>
+      <c r="D764" s="6" t="inlineStr">
+        <is>
+          <t>Deducted from the sale</t>
+        </is>
+      </c>
+      <c r="E764" s="1" t="n"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n"/>
+      <c r="B765" s="6" t="inlineStr">
+        <is>
           <t>UI.Auction.RuleCantList</t>
         </is>
       </c>
-      <c r="C763" s="6" t="inlineStr">
+      <c r="C765" s="6" t="inlineStr">
         <is>
           <t>끼고 있는 장비 · 일하는 캐릭터 · 잠긴 것은 올릴 수 없습니다 (흐린 줄 — 올리면 사유)</t>
         </is>
       </c>
-      <c r="D763" s="6" t="inlineStr">
+      <c r="D765" s="6" t="inlineStr">
         <is>
           <t>Worn gear, working characters and locked items can't be listed (dimmed — hover for why)</t>
         </is>
       </c>
-      <c r="E763" s="1" t="n"/>
+      <c r="E765" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E771"/>
+  <dimension ref="A1:E774"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10586,17 +10586,17 @@
       <c r="A528" s="1" t="n"/>
       <c r="B528" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SourceMail</t>
+          <t>UI.Gacha.SourceItem</t>
         </is>
       </c>
       <c r="C528" s="6" t="inlineStr">
         <is>
-          <t>우편 수령</t>
+          <t>{0} 개봉</t>
         </is>
       </c>
       <c r="D528" s="6" t="inlineStr">
         <is>
-          <t>Mail Claim</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E528" s="1" t="n"/>
@@ -10605,17 +10605,17 @@
       <c r="A529" s="1" t="n"/>
       <c r="B529" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.ResultTitle</t>
+          <t>UI.Gacha.SourceMail</t>
         </is>
       </c>
       <c r="C529" s="6" t="inlineStr">
         <is>
-          <t>{0} 결과</t>
+          <t>우편 수령</t>
         </is>
       </c>
       <c r="D529" s="6" t="inlineStr">
         <is>
-          <t>{0} Results</t>
+          <t>Mail Claim</t>
         </is>
       </c>
       <c r="E529" s="1" t="n"/>
@@ -10624,17 +10624,17 @@
       <c r="A530" s="1" t="n"/>
       <c r="B530" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.ArtifactFound</t>
+          <t>UI.Gacha.ResultTitle</t>
         </is>
       </c>
       <c r="C530" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 발견!</t>
+          <t>{0} 결과</t>
         </is>
       </c>
       <c r="D530" s="6" t="inlineStr">
         <is>
-          <t>Artifact Found!</t>
+          <t>{0} Results</t>
         </is>
       </c>
       <c r="E530" s="1" t="n"/>
@@ -10643,17 +10643,17 @@
       <c r="A531" s="1" t="n"/>
       <c r="B531" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.SpecialRelicFound</t>
+          <t>UI.Gacha.ArtifactFound</t>
         </is>
       </c>
       <c r="C531" s="6" t="inlineStr">
         <is>
-          <t>Special 유물 발견!</t>
+          <t>아티팩트 발견!</t>
         </is>
       </c>
       <c r="D531" s="6" t="inlineStr">
         <is>
-          <t>Special Relic Found!</t>
+          <t>Artifact Found!</t>
         </is>
       </c>
       <c r="E531" s="1" t="n"/>
@@ -10662,17 +10662,17 @@
       <c r="A532" s="1" t="n"/>
       <c r="B532" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.DrawAgain</t>
+          <t>UI.Gacha.SpecialRelicFound</t>
         </is>
       </c>
       <c r="C532" s="6" t="inlineStr">
         <is>
-          <t>{0}회 더 뽑기</t>
+          <t>Special 유물 발견!</t>
         </is>
       </c>
       <c r="D532" s="6" t="inlineStr">
         <is>
-          <t>Draw x{0} Again</t>
+          <t>Special Relic Found!</t>
         </is>
       </c>
       <c r="E532" s="1" t="n"/>
@@ -10681,17 +10681,17 @@
       <c r="A533" s="1" t="n"/>
       <c r="B533" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.Tab</t>
+          <t>UI.Gacha.DrawAgain</t>
         </is>
       </c>
       <c r="C533" s="6" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>{0}회 더 뽑기</t>
         </is>
       </c>
       <c r="D533" s="6" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Draw x{0} Again</t>
         </is>
       </c>
       <c r="E533" s="1" t="n"/>
@@ -10700,17 +10700,17 @@
       <c r="A534" s="1" t="n"/>
       <c r="B534" s="6" t="inlineStr">
         <is>
-          <t>UI.Gacha.CloseResult</t>
+          <t>UI.Gacha.Tab</t>
         </is>
       </c>
       <c r="C534" s="6" t="inlineStr">
         <is>
-          <t>[결과 닫기]</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="D534" s="6" t="inlineStr">
         <is>
-          <t>[Close]</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="E534" s="1" t="n"/>
@@ -10719,17 +10719,17 @@
       <c r="A535" s="1" t="n"/>
       <c r="B535" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.Tab</t>
+          <t>UI.Gacha.CloseResult</t>
         </is>
       </c>
       <c r="C535" s="6" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>[결과 닫기]</t>
         </is>
       </c>
       <c r="D535" s="6" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>[Close]</t>
         </is>
       </c>
       <c r="E535" s="1" t="n"/>
@@ -10738,17 +10738,17 @@
       <c r="A536" s="1" t="n"/>
       <c r="B536" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.Count</t>
+          <t>UI.Shop.Tab</t>
         </is>
       </c>
       <c r="C536" s="6" t="inlineStr">
         <is>
-          <t>{0}장</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>x{0}</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="E536" s="1" t="n"/>
@@ -10757,17 +10757,17 @@
       <c r="A537" s="1" t="n"/>
       <c r="B537" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.Owned</t>
+          <t>UI.Shop.Count</t>
         </is>
       </c>
       <c r="C537" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}장</t>
+          <t>{0}장</t>
         </is>
       </c>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>x{0}</t>
         </is>
       </c>
       <c r="E537" s="1" t="n"/>
@@ -10776,17 +10776,17 @@
       <c r="A538" s="1" t="n"/>
       <c r="B538" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.Wait</t>
+          <t>UI.Shop.Owned</t>
         </is>
       </c>
       <c r="C538" s="6" t="inlineStr">
         <is>
-          <t>상점 구매 {0}장</t>
+          <t>보유 {0}장</t>
         </is>
       </c>
       <c r="D538" s="6" t="inlineStr">
         <is>
-          <t>Buy x{0}</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E538" s="1" t="n"/>
@@ -10795,17 +10795,17 @@
       <c r="A539" s="1" t="n"/>
       <c r="B539" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.Bought</t>
+          <t>UI.Shop.Wait</t>
         </is>
       </c>
       <c r="C539" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}장을 샀습니다. 인벤토리에서 열어 보세요.</t>
+          <t>상점 구매 {0}장</t>
         </is>
       </c>
       <c r="D539" s="6" t="inlineStr">
         <is>
-          <t>Bought {0} x{1}. Open it from your inventory.</t>
+          <t>Buy x{0}</t>
         </is>
       </c>
       <c r="E539" s="1" t="n"/>
@@ -10814,17 +10814,17 @@
       <c r="A540" s="1" t="n"/>
       <c r="B540" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Shop.Bought</t>
         </is>
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>{0} {1}장을 샀습니다.</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>Bought {0} x{1}.</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Stack</t>
+          <t>UI.Shop.Open</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>창고에 쌓기</t>
+          <t>열기</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>Stack in Warehouse</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.StackTip</t>
+          <t>UI.Shop.WaitOpen</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
+          <t>{0} {1}장 열기</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
+          <t>Open {0} x{1}</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.NothingToStack</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Warehouse.Stack</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>창고에 쌓기</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Stack in Warehouse</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Warehouse.StackTip</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Warehouse.NothingToStack</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,17 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11631,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11650,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Title</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>Artifacts</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11669,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpTitle</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>Artifacts</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11688,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpGet</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>유물을 감정하면 나옵니다 — 인벤토리 자원 탭에서 유물을 좌클릭</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>Appraise relics to get them — left-click a relic in the Inventory Resources tab</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11707,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpEquip</t>
+          <t>UI.Artifact.Title</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착해야 효과가 붙습니다 — 번호마다 1개, 장착은 되돌릴 수 없습니다</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>Effects apply only once placed in the codex — one per kind, and it can't be undone</t>
+          <t>Artifacts</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11726,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpToggle</t>
+          <t>UI.Artifact.HelpTitle</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>장착한 아티팩트는 효과를 켜고 끌 수 있습니다 — 꺼 두면 효과가 없습니다</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>Codex artifacts can be turned on or off — off means no effect</t>
+          <t>Artifacts</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11745,17 +11745,17 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpSell</t>
+          <t>UI.Artifact.HelpGet</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>남는 것은 우클릭으로 즉시 판매하거나, Ctrl+우클릭으로 경매에 올려 더 비싸게 팝니다</t>
+          <t>유물을 감정하면 나옵니다 — 인벤토리 자원 탭에서 유물을 좌클릭</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>Right-click extras to sell instantly, or Ctrl+right-click to list them on the auction for more</t>
+          <t>Appraise relics to get them — left-click a relic in the Inventory Resources tab</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11764,17 +11764,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Codex</t>
+          <t>UI.Artifact.HelpEquip</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>도감에 장착해야 효과가 붙습니다 — 번호마다 1개, 장착은 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Effects apply only once placed in the codex — one per kind, and it can't be undone</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11783,17 +11783,17 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EquippedCount</t>
+          <t>UI.Artifact.HelpToggle</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>장착 {0} / {1}</t>
+          <t>장착한 아티팩트는 효과를 켜고 끌 수 있습니다 — 꺼 두면 효과가 없습니다</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>Placed {0} / {1}</t>
+          <t>Codex artifacts can be turned on or off — off means no effect</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11802,17 +11802,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.FilterAll</t>
+          <t>UI.Artifact.HelpSell</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>남는 것은 우클릭으로 즉시 판매하거나, Ctrl+우클릭으로 경매에 올려 더 비싸게 팝니다</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Right-click extras to sell instantly, or Ctrl+right-click to list them on the auction for more</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11821,17 +11821,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.FilterEquipped</t>
+          <t>UI.Artifact.Codex</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11840,17 +11840,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.GroupHead</t>
+          <t>UI.Artifact.EquippedCount</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>{0}   획득 {1} / {2}</t>
+          <t>장착 {0} / {1}</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>{0}   Collected {1} / {2}</t>
+          <t>Placed {0} / {1}</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11859,17 +11859,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Unknown</t>
+          <t>UI.Artifact.FilterAll</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11878,17 +11878,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.UnknownHint</t>
+          <t>UI.Artifact.FilterEquipped</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>아직 얻지 못한 아티팩트입니다</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>You haven't found this artifact yet</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11897,17 +11897,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Off</t>
+          <t>UI.Artifact.GroupHead</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>꺼짐</t>
+          <t>{0}   획득 {1} / {2}</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>{0}   Collected {1} / {2}</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11916,17 +11916,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.OwnedShort</t>
+          <t>UI.Artifact.Unknown</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}</t>
+          <t>???</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>???</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11935,17 +11935,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Holding</t>
+          <t>UI.Artifact.UnknownHint</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>보유 아티팩트  {0}종 · {1}개</t>
+          <t>아직 얻지 못한 아티팩트입니다</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>Owned Artifacts  {0} kinds · {1}</t>
+          <t>You haven't found this artifact yet</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11954,17 +11954,17 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HoldingEmpty</t>
+          <t>UI.Artifact.Off</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>보유한 아티팩트가 없습니다 — 유물을 감정하면 생깁니다</t>
+          <t>꺼짐</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>No artifacts yet — appraise relics to get some</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11973,17 +11973,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.New</t>
+          <t>UI.Artifact.OwnedShort</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>보유 {0}</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11992,17 +11992,17 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.DetailEmpty</t>
+          <t>UI.Artifact.Holding</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>아티팩트를 고르면 설명이 여기에 뜹니다</t>
+          <t>보유 아티팩트  {0}종 · {1}개</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>Select an artifact to see its details here</t>
+          <t>Owned Artifacts  {0} kinds · {1}</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12011,17 +12011,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Effect</t>
+          <t>UI.Artifact.HoldingEmpty</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>보유한 아티팩트가 없습니다 — 유물을 감정하면 생깁니다</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>No artifacts yet — appraise relics to get some</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12030,17 +12030,17 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateOn</t>
+          <t>UI.Artifact.New</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>장착 · 켜짐</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>Placed · On</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12049,17 +12049,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateOff</t>
+          <t>UI.Artifact.DetailEmpty</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>장착 · 꺼짐</t>
+          <t>아티팩트를 고르면 설명이 여기에 뜹니다</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>Placed · Off</t>
+          <t>Select an artifact to see its details here</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12068,17 +12068,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateNone</t>
+          <t>UI.Artifact.Effect</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>도감에 없음</t>
+          <t>효과</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>Not in codex</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12087,17 +12087,17 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.ShowDetail</t>
+          <t>UI.Artifact.StateOn</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>장착 · 켜짐</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Placed · On</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12106,17 +12106,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Equip</t>
+          <t>UI.Artifact.StateOff</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착</t>
+          <t>장착 · 꺼짐</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>Place in Codex</t>
+          <t>Placed · Off</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12125,17 +12125,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.TurnOff</t>
+          <t>UI.Artifact.StateNone</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>효과 끄기</t>
+          <t>도감에 없음</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>Turn Off</t>
+          <t>Not in codex</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12144,17 +12144,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.TurnOn</t>
+          <t>UI.Artifact.ShowDetail</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>효과 켜기</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>Turn On</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12163,12 +12163,12 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.WaitEquip</t>
+          <t>UI.Artifact.Equip</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>도감 장착</t>
+          <t>도감에 장착</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
@@ -12182,17 +12182,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.WaitToggle</t>
+          <t>UI.Artifact.TurnOff</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>켜고 끄기</t>
+          <t>효과 끄기</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>Turn On/Off</t>
+          <t>Turn Off</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12201,17 +12201,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Equipped</t>
+          <t>UI.Artifact.TurnOn</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착했습니다 — {0}</t>
+          <t>효과 켜기</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Placed in codex — {0}</t>
+          <t>Turn On</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12220,17 +12220,17 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellHead</t>
+          <t>UI.Artifact.WaitEquip</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 판매 {0}종</t>
+          <t>도감 장착</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>Sell Artifacts ({0})</t>
+          <t>Place in Codex</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12239,17 +12239,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellEmpty</t>
+          <t>UI.Artifact.WaitToggle</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>보유 칸을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다. 비싸게 팔려면 Ctrl+우클릭(경매)</t>
+          <t>켜고 끄기</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>Right-click owned artifacts to add — they sell instantly. Ctrl+right-click to list on the auction for more</t>
+          <t>Turn On/Off</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12258,17 +12258,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellUncollected</t>
+          <t>UI.Artifact.Equipped</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>주의! 도감에 없는 아티팩트 포함 — 팔면 도감에 남지 않습니다</t>
+          <t>도감에 장착했습니다 — {0}</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>Caution! Includes artifacts not in your codex — selling won't record them</t>
+          <t>Placed in codex — {0}</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12277,17 +12277,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.AllIndustry</t>
+          <t>UI.Artifact.SellHead</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>전 산업</t>
+          <t>아티팩트 판매 {0}종</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>All industries</t>
+          <t>Sell Artifacts ({0})</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12296,17 +12296,17 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectSpeed</t>
+          <t>UI.Artifact.SellEmpty</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>{0} 작업속도 +{1}</t>
+          <t>보유 칸을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다. 비싸게 팔려면 Ctrl+우클릭(경매)</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>{0} work speed +{1}</t>
+          <t>Right-click owned artifacts to add — they sell instantly. Ctrl+right-click to list on the auction for more</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12315,17 +12315,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectYield</t>
+          <t>UI.Artifact.SellUncollected</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>{0} 산출량 +{1}</t>
+          <t>주의! 도감에 없는 아티팩트 포함 — 팔면 도감에 남지 않습니다</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>{0} yield +{1}</t>
+          <t>Caution! Includes artifacts not in your codex — selling won't record them</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12334,17 +12334,17 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectAppraise</t>
+          <t>UI.Artifact.AllIndustry</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>감정 비용 −{0}</t>
+          <t>전 산업</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>Appraisal cost −{0}</t>
+          <t>All industries</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12353,17 +12353,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectRelic</t>
+          <t>UI.Artifact.EffectSpeed</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>유물 발견 확률 +{0}</t>
+          <t>{0} 작업속도 +{1}</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>Relic find chance +{0}</t>
+          <t>{0} work speed +{1}</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12372,17 +12372,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Window</t>
+          <t>UI.Artifact.EffectYield</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 — 도감에 장착</t>
+          <t>{0} 산출량 +{1}</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>Artifact — Place in Codex</t>
+          <t>{0} yield +{1}</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12391,17 +12391,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.AlreadyEquipped</t>
+          <t>UI.Artifact.EffectAppraise</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>이미 도감에 장착함</t>
+          <t>감정 비용 −{0}</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>Already in Codex</t>
+          <t>Appraisal cost −{0}</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12410,17 +12410,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.OpenCodex</t>
+          <t>UI.Artifact.EffectRelic</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>도감 보기</t>
+          <t>유물 발견 확률 +{0}</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>View Codex</t>
+          <t>Relic find chance +{0}</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12429,17 +12429,17 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EquipHint</t>
+          <t>UI.Artifact.Window</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>장착하면 효과가 켜집니다 — 번호마다 1개, 되돌릴 수 없습니다</t>
+          <t>아티팩트 — 도감에 장착</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>Placing turns its effect on — one per kind, and it can't be undone</t>
+          <t>Artifact — Place in Codex</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12448,17 +12448,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellHint</t>
+          <t>UI.Artifact.AlreadyEquipped</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>남는 것은 우클릭 즉시 판매 · Ctrl+우클릭 경매</t>
+          <t>이미 도감에 장착함</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Right-click extras to sell · Ctrl+right-click to auction</t>
+          <t>Already in Codex</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12467,17 +12467,17 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.NoLock</t>
+          <t>UI.Artifact.OpenCodex</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>아티팩트는 아직 잠글 수 없습니다</t>
+          <t>도감 보기</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>Artifacts can't be locked yet</t>
+          <t>View Codex</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12486,17 +12486,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.NoMove</t>
+          <t>UI.Artifact.EquipHint</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 칸은 아직 옮길 수 없습니다</t>
+          <t>장착하면 효과가 켜집니다 — 번호마다 1개, 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>Artifact slots can't be moved yet</t>
+          <t>Placing turns its effect on — one per kind, and it can't be undone</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12505,17 +12505,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.KindArtifact</t>
+          <t>UI.Artifact.SellHint</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 판매 {0}종</t>
+          <t>남는 것은 우클릭 즉시 판매 · Ctrl+우클릭 경매</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>Sell Artifacts ({0})</t>
+          <t>Right-click extras to sell · Ctrl+right-click to auction</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12524,17 +12524,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.ArtifactNoShard</t>
+          <t>UI.Artifact.NoLock</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>아티팩트는 아직 마석으로 분해할 수 없습니다 — 분해는 장비만</t>
+          <t>아티팩트는 아직 잠글 수 없습니다</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>Artifacts can't be disassembled into shards yet — gear only</t>
+          <t>Artifacts can't be locked yet</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12543,17 +12543,17 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Artifact.NoMove</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>아티팩트 칸은 아직 옮길 수 없습니다</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>Artifact slots can't be moved yet</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12562,17 +12562,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Sell.KindArtifact</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>아티팩트 판매 {0}종</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>Sell Artifacts ({0})</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12581,17 +12581,17 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Sell.ArtifactNoShard</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>아티팩트는 아직 마석으로 분해할 수 없습니다 — 분해는 장비만</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>Artifacts can't be disassembled into shards yet — gear only</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12600,17 +12600,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12619,17 +12619,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12638,17 +12638,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12657,17 +12657,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12676,17 +12676,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12695,17 +12695,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12714,17 +12714,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12733,17 +12733,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12752,17 +12752,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12771,17 +12771,17 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E643" s="1" t="n"/>
@@ -12790,17 +12790,17 @@
       <c r="A644" s="1" t="n"/>
       <c r="B644" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C644" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D644" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E644" s="1" t="n"/>
@@ -12809,17 +12809,17 @@
       <c r="A645" s="1" t="n"/>
       <c r="B645" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E645" s="1" t="n"/>
@@ -12828,17 +12828,17 @@
       <c r="A646" s="1" t="n"/>
       <c r="B646" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C646" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D646" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E646" s="1" t="n"/>
@@ -12847,17 +12847,17 @@
       <c r="A647" s="1" t="n"/>
       <c r="B647" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D647" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E647" s="1" t="n"/>
@@ -12866,17 +12866,17 @@
       <c r="A648" s="1" t="n"/>
       <c r="B648" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C648" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D648" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E648" s="1" t="n"/>
@@ -12885,17 +12885,17 @@
       <c r="A649" s="1" t="n"/>
       <c r="B649" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D649" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E649" s="1" t="n"/>
@@ -12904,17 +12904,17 @@
       <c r="A650" s="1" t="n"/>
       <c r="B650" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C650" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D650" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E650" s="1" t="n"/>
@@ -12923,17 +12923,17 @@
       <c r="A651" s="1" t="n"/>
       <c r="B651" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C651" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E651" s="1" t="n"/>
@@ -12942,17 +12942,17 @@
       <c r="A652" s="1" t="n"/>
       <c r="B652" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C652" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D652" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E652" s="1" t="n"/>
@@ -12961,17 +12961,17 @@
       <c r="A653" s="1" t="n"/>
       <c r="B653" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C653" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D653" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E653" s="1" t="n"/>
@@ -12980,17 +12980,17 @@
       <c r="A654" s="1" t="n"/>
       <c r="B654" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C654" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D654" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E654" s="1" t="n"/>
@@ -12999,17 +12999,17 @@
       <c r="A655" s="1" t="n"/>
       <c r="B655" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C655" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D655" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E655" s="1" t="n"/>
@@ -13018,17 +13018,17 @@
       <c r="A656" s="1" t="n"/>
       <c r="B656" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C656" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D656" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E656" s="1" t="n"/>
@@ -13037,17 +13037,17 @@
       <c r="A657" s="1" t="n"/>
       <c r="B657" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C657" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D657" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E657" s="1" t="n"/>
@@ -13056,17 +13056,17 @@
       <c r="A658" s="1" t="n"/>
       <c r="B658" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C658" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D658" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E658" s="1" t="n"/>
@@ -13075,17 +13075,17 @@
       <c r="A659" s="1" t="n"/>
       <c r="B659" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C659" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D659" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E659" s="1" t="n"/>
@@ -13094,17 +13094,17 @@
       <c r="A660" s="1" t="n"/>
       <c r="B660" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C660" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D660" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E660" s="1" t="n"/>
@@ -13113,17 +13113,17 @@
       <c r="A661" s="1" t="n"/>
       <c r="B661" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C661" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D661" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E661" s="1" t="n"/>
@@ -13132,17 +13132,17 @@
       <c r="A662" s="1" t="n"/>
       <c r="B662" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C662" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D662" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E662" s="1" t="n"/>
@@ -13151,17 +13151,17 @@
       <c r="A663" s="1" t="n"/>
       <c r="B663" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C663" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D663" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E663" s="1" t="n"/>
@@ -13170,17 +13170,17 @@
       <c r="A664" s="1" t="n"/>
       <c r="B664" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C664" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D664" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E664" s="1" t="n"/>
@@ -13189,17 +13189,17 @@
       <c r="A665" s="1" t="n"/>
       <c r="B665" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C665" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D665" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E665" s="1" t="n"/>
@@ -13208,17 +13208,17 @@
       <c r="A666" s="1" t="n"/>
       <c r="B666" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C666" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D666" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E666" s="1" t="n"/>
@@ -13227,17 +13227,17 @@
       <c r="A667" s="1" t="n"/>
       <c r="B667" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C667" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D667" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E667" s="1" t="n"/>
@@ -13246,17 +13246,17 @@
       <c r="A668" s="1" t="n"/>
       <c r="B668" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C668" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D668" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E668" s="1" t="n"/>
@@ -13265,17 +13265,17 @@
       <c r="A669" s="1" t="n"/>
       <c r="B669" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C669" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D669" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E669" s="1" t="n"/>
@@ -13284,17 +13284,17 @@
       <c r="A670" s="1" t="n"/>
       <c r="B670" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C670" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D670" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E670" s="1" t="n"/>
@@ -13303,17 +13303,17 @@
       <c r="A671" s="1" t="n"/>
       <c r="B671" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C671" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D671" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E671" s="1" t="n"/>
@@ -13322,17 +13322,17 @@
       <c r="A672" s="1" t="n"/>
       <c r="B672" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C672" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D672" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E672" s="1" t="n"/>
@@ -13341,17 +13341,17 @@
       <c r="A673" s="1" t="n"/>
       <c r="B673" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C673" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D673" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E673" s="1" t="n"/>
@@ -13360,17 +13360,17 @@
       <c r="A674" s="1" t="n"/>
       <c r="B674" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C674" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D674" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E674" s="1" t="n"/>
@@ -13379,17 +13379,17 @@
       <c r="A675" s="1" t="n"/>
       <c r="B675" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C675" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D675" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E675" s="1" t="n"/>
@@ -13398,17 +13398,17 @@
       <c r="A676" s="1" t="n"/>
       <c r="B676" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C676" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D676" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E676" s="1" t="n"/>
@@ -13417,17 +13417,17 @@
       <c r="A677" s="1" t="n"/>
       <c r="B677" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C677" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D677" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E677" s="1" t="n"/>
@@ -13436,17 +13436,17 @@
       <c r="A678" s="1" t="n"/>
       <c r="B678" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C678" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D678" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E678" s="1" t="n"/>
@@ -13455,17 +13455,17 @@
       <c r="A679" s="1" t="n"/>
       <c r="B679" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C679" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D679" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E679" s="1" t="n"/>
@@ -13474,17 +13474,17 @@
       <c r="A680" s="1" t="n"/>
       <c r="B680" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C680" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D680" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E680" s="1" t="n"/>
@@ -13493,17 +13493,17 @@
       <c r="A681" s="1" t="n"/>
       <c r="B681" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C681" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D681" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E681" s="1" t="n"/>
@@ -13512,17 +13512,17 @@
       <c r="A682" s="1" t="n"/>
       <c r="B682" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C682" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D682" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E682" s="1" t="n"/>
@@ -13531,17 +13531,17 @@
       <c r="A683" s="1" t="n"/>
       <c r="B683" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C683" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D683" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E683" s="1" t="n"/>
@@ -13550,17 +13550,17 @@
       <c r="A684" s="1" t="n"/>
       <c r="B684" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C684" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D684" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E684" s="1" t="n"/>
@@ -13569,17 +13569,17 @@
       <c r="A685" s="1" t="n"/>
       <c r="B685" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C685" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D685" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E685" s="1" t="n"/>
@@ -13588,17 +13588,17 @@
       <c r="A686" s="1" t="n"/>
       <c r="B686" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C686" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D686" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E686" s="1" t="n"/>
@@ -13607,17 +13607,17 @@
       <c r="A687" s="1" t="n"/>
       <c r="B687" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C687" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D687" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E687" s="1" t="n"/>
@@ -13626,17 +13626,17 @@
       <c r="A688" s="1" t="n"/>
       <c r="B688" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C688" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D688" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E688" s="1" t="n"/>
@@ -13645,17 +13645,17 @@
       <c r="A689" s="1" t="n"/>
       <c r="B689" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C689" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D689" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E689" s="1" t="n"/>
@@ -13664,17 +13664,17 @@
       <c r="A690" s="1" t="n"/>
       <c r="B690" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C690" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D690" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E690" s="1" t="n"/>
@@ -13683,17 +13683,17 @@
       <c r="A691" s="1" t="n"/>
       <c r="B691" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C691" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D691" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E691" s="1" t="n"/>
@@ -13702,17 +13702,17 @@
       <c r="A692" s="1" t="n"/>
       <c r="B692" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C692" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D692" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E692" s="1" t="n"/>
@@ -13721,19 +13721,17 @@
       <c r="A693" s="1" t="n"/>
       <c r="B693" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C693" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D693" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E693" s="1" t="n"/>
@@ -13742,17 +13740,17 @@
       <c r="A694" s="1" t="n"/>
       <c r="B694" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C694" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D694" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E694" s="1" t="n"/>
@@ -13761,17 +13759,17 @@
       <c r="A695" s="1" t="n"/>
       <c r="B695" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C695" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D695" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E695" s="1" t="n"/>
@@ -13780,17 +13778,19 @@
       <c r="A696" s="1" t="n"/>
       <c r="B696" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C696" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D696" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E696" s="1" t="n"/>
@@ -13799,17 +13799,17 @@
       <c r="A697" s="1" t="n"/>
       <c r="B697" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C697" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D697" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E697" s="1" t="n"/>
@@ -13818,17 +13818,17 @@
       <c r="A698" s="1" t="n"/>
       <c r="B698" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C698" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D698" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E698" s="1" t="n"/>
@@ -13837,17 +13837,17 @@
       <c r="A699" s="1" t="n"/>
       <c r="B699" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C699" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D699" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E699" s="1" t="n"/>
@@ -13856,17 +13856,17 @@
       <c r="A700" s="1" t="n"/>
       <c r="B700" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C700" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D700" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E700" s="1" t="n"/>
@@ -13875,17 +13875,17 @@
       <c r="A701" s="1" t="n"/>
       <c r="B701" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C701" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D701" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E701" s="1" t="n"/>
@@ -13894,17 +13894,17 @@
       <c r="A702" s="1" t="n"/>
       <c r="B702" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C702" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D702" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E702" s="1" t="n"/>
@@ -13913,17 +13913,17 @@
       <c r="A703" s="1" t="n"/>
       <c r="B703" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C703" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D703" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E703" s="1" t="n"/>
@@ -13932,19 +13932,17 @@
       <c r="A704" s="1" t="n"/>
       <c r="B704" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C704" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D704" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E704" s="1" t="n"/>
@@ -13953,17 +13951,17 @@
       <c r="A705" s="1" t="n"/>
       <c r="B705" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C705" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D705" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E705" s="1" t="n"/>
@@ -13972,19 +13970,17 @@
       <c r="A706" s="1" t="n"/>
       <c r="B706" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C706" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D706" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E706" s="1" t="n"/>
@@ -13993,17 +13989,19 @@
       <c r="A707" s="1" t="n"/>
       <c r="B707" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C707" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D707" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E707" s="1" t="n"/>
@@ -14012,17 +14010,17 @@
       <c r="A708" s="1" t="n"/>
       <c r="B708" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C708" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D708" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E708" s="1" t="n"/>
@@ -14031,17 +14029,19 @@
       <c r="A709" s="1" t="n"/>
       <c r="B709" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C709" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D709" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E709" s="1" t="n"/>
@@ -14050,17 +14050,17 @@
       <c r="A710" s="1" t="n"/>
       <c r="B710" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C710" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D710" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E710" s="1" t="n"/>
@@ -14069,17 +14069,17 @@
       <c r="A711" s="1" t="n"/>
       <c r="B711" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C711" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D711" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E711" s="1" t="n"/>
@@ -14088,17 +14088,17 @@
       <c r="A712" s="1" t="n"/>
       <c r="B712" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C712" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D712" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E712" s="1" t="n"/>
@@ -14107,17 +14107,17 @@
       <c r="A713" s="1" t="n"/>
       <c r="B713" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C713" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D713" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E713" s="1" t="n"/>
@@ -14126,17 +14126,17 @@
       <c r="A714" s="1" t="n"/>
       <c r="B714" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C714" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D714" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E714" s="1" t="n"/>
@@ -14145,17 +14145,17 @@
       <c r="A715" s="1" t="n"/>
       <c r="B715" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C715" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D715" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E715" s="1" t="n"/>
@@ -14164,17 +14164,17 @@
       <c r="A716" s="1" t="n"/>
       <c r="B716" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C716" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지</t>
         </is>
       </c>
       <c r="D716" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>Owned {0} · up to {1} per listing</t>
         </is>
       </c>
       <c r="E716" s="1" t="n"/>
@@ -14183,17 +14183,17 @@
       <c r="A717" s="1" t="n"/>
       <c r="B717" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C717" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D717" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E717" s="1" t="n"/>
@@ -14202,17 +14202,17 @@
       <c r="A718" s="1" t="n"/>
       <c r="B718" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C718" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D718" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E718" s="1" t="n"/>
@@ -14221,17 +14221,17 @@
       <c r="A719" s="1" t="n"/>
       <c r="B719" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C719" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D719" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E719" s="1" t="n"/>
@@ -14240,17 +14240,17 @@
       <c r="A720" s="1" t="n"/>
       <c r="B720" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C720" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D720" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E720" s="1" t="n"/>
@@ -14259,17 +14259,17 @@
       <c r="A721" s="1" t="n"/>
       <c r="B721" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantViaArtifact</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C721" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 아티팩트 [판매]</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D721" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Artifacts [Sell]</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E721" s="1" t="n"/>
@@ -14278,17 +14278,17 @@
       <c r="A722" s="1" t="n"/>
       <c r="B722" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C722" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D722" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E722" s="1" t="n"/>
@@ -14297,17 +14297,17 @@
       <c r="A723" s="1" t="n"/>
       <c r="B723" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C723" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D723" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E723" s="1" t="n"/>
@@ -14316,17 +14316,17 @@
       <c r="A724" s="1" t="n"/>
       <c r="B724" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.InstantViaArtifact</t>
         </is>
       </c>
       <c r="C724" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>{0} G — 아티팩트 [판매]</t>
         </is>
       </c>
       <c r="D724" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>{0} G — Artifacts [Sell]</t>
         </is>
       </c>
       <c r="E724" s="1" t="n"/>
@@ -14335,17 +14335,17 @@
       <c r="A725" s="1" t="n"/>
       <c r="B725" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C725" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D725" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E725" s="1" t="n"/>
@@ -14354,17 +14354,17 @@
       <c r="A726" s="1" t="n"/>
       <c r="B726" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C726" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D726" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E726" s="1" t="n"/>
@@ -14373,17 +14373,17 @@
       <c r="A727" s="1" t="n"/>
       <c r="B727" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C727" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D727" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E727" s="1" t="n"/>
@@ -14392,17 +14392,17 @@
       <c r="A728" s="1" t="n"/>
       <c r="B728" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C728" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D728" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E728" s="1" t="n"/>
@@ -14411,17 +14411,17 @@
       <c r="A729" s="1" t="n"/>
       <c r="B729" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C729" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D729" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E729" s="1" t="n"/>
@@ -14430,17 +14430,17 @@
       <c r="A730" s="1" t="n"/>
       <c r="B730" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C730" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D730" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E730" s="1" t="n"/>
@@ -14449,17 +14449,17 @@
       <c r="A731" s="1" t="n"/>
       <c r="B731" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C731" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D731" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E731" s="1" t="n"/>
@@ -14468,17 +14468,17 @@
       <c r="A732" s="1" t="n"/>
       <c r="B732" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C732" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D732" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E732" s="1" t="n"/>
@@ -14487,17 +14487,17 @@
       <c r="A733" s="1" t="n"/>
       <c r="B733" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C733" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D733" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E733" s="1" t="n"/>
@@ -14506,17 +14506,17 @@
       <c r="A734" s="1" t="n"/>
       <c r="B734" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C734" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D734" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E734" s="1" t="n"/>
@@ -14525,17 +14525,17 @@
       <c r="A735" s="1" t="n"/>
       <c r="B735" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C735" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D735" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E735" s="1" t="n"/>
@@ -14544,19 +14544,17 @@
       <c r="A736" s="1" t="n"/>
       <c r="B736" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C736" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D736" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E736" s="1" t="n"/>
@@ -14565,17 +14563,17 @@
       <c r="A737" s="1" t="n"/>
       <c r="B737" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C737" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D737" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E737" s="1" t="n"/>
@@ -14584,17 +14582,17 @@
       <c r="A738" s="1" t="n"/>
       <c r="B738" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C738" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D738" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E738" s="1" t="n"/>
@@ -14603,17 +14601,19 @@
       <c r="A739" s="1" t="n"/>
       <c r="B739" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C739" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D739" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E739" s="1" t="n"/>
@@ -14622,17 +14622,17 @@
       <c r="A740" s="1" t="n"/>
       <c r="B740" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C740" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D740" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E740" s="1" t="n"/>
@@ -14641,17 +14641,17 @@
       <c r="A741" s="1" t="n"/>
       <c r="B741" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C741" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D741" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E741" s="1" t="n"/>
@@ -14660,17 +14660,17 @@
       <c r="A742" s="1" t="n"/>
       <c r="B742" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.ChartTitle</t>
         </is>
       </c>
       <c r="C742" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
         </is>
       </c>
       <c r="D742" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
         </is>
       </c>
       <c r="E742" s="1" t="n"/>
@@ -14679,17 +14679,17 @@
       <c r="A743" s="1" t="n"/>
       <c r="B743" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.ChartEmpty</t>
         </is>
       </c>
       <c r="C743" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>최근 14일 동안 거래가 없습니다</t>
         </is>
       </c>
       <c r="D743" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>No trades in the last 14 days</t>
         </is>
       </c>
       <c r="E743" s="1" t="n"/>
@@ -14698,17 +14698,17 @@
       <c r="A744" s="1" t="n"/>
       <c r="B744" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.LevelsTitle</t>
         </is>
       </c>
       <c r="C744" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
         </is>
       </c>
       <c r="D744" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
         </is>
       </c>
       <c r="E744" s="1" t="n"/>
@@ -14717,17 +14717,17 @@
       <c r="A745" s="1" t="n"/>
       <c r="B745" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.LevelsEmpty</t>
         </is>
       </c>
       <c r="C745" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>지금 판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D745" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>Nothing on sale right now</t>
         </is>
       </c>
       <c r="E745" s="1" t="n"/>
@@ -14736,17 +14736,17 @@
       <c r="A746" s="1" t="n"/>
       <c r="B746" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.RegisterOpen</t>
         </is>
       </c>
       <c r="C746" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>+ 판매 등록</t>
         </is>
       </c>
       <c r="D746" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>+ List Item</t>
         </is>
       </c>
       <c r="E746" s="1" t="n"/>
@@ -14755,17 +14755,17 @@
       <c r="A747" s="1" t="n"/>
       <c r="B747" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.ColItem</t>
         </is>
       </c>
       <c r="C747" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D747" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E747" s="1" t="n"/>
@@ -14774,17 +14774,17 @@
       <c r="A748" s="1" t="n"/>
       <c r="B748" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.ColNet</t>
         </is>
       </c>
       <c r="C748" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>팔리면 받는 금액</t>
         </is>
       </c>
       <c r="D748" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>You Get If Sold</t>
         </is>
       </c>
       <c r="E748" s="1" t="n"/>
@@ -14793,17 +14793,17 @@
       <c r="A749" s="1" t="n"/>
       <c r="B749" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.ColDate</t>
         </is>
       </c>
       <c r="C749" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="D749" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E749" s="1" t="n"/>
@@ -14812,17 +14812,17 @@
       <c r="A750" s="1" t="n"/>
       <c r="B750" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.ColType</t>
         </is>
       </c>
       <c r="C750" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="D750" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E750" s="1" t="n"/>
@@ -14831,17 +14831,17 @@
       <c r="A751" s="1" t="n"/>
       <c r="B751" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.ColAmount</t>
         </is>
       </c>
       <c r="C751" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="D751" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E751" s="1" t="n"/>
@@ -14850,17 +14850,17 @@
       <c r="A752" s="1" t="n"/>
       <c r="B752" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.ColDest</t>
         </is>
       </c>
       <c r="C752" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
+          <t>받는 곳</t>
         </is>
       </c>
       <c r="D752" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.</t>
+          <t>Goes To</t>
         </is>
       </c>
       <c r="E752" s="1" t="n"/>
@@ -14869,17 +14869,17 @@
       <c r="A753" s="1" t="n"/>
       <c r="B753" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.RegisterTitle</t>
         </is>
       </c>
       <c r="C753" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D753" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>List an Item</t>
         </is>
       </c>
       <c r="E753" s="1" t="n"/>
@@ -14888,17 +14888,17 @@
       <c r="A754" s="1" t="n"/>
       <c r="B754" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.FindByName</t>
         </is>
       </c>
       <c r="C754" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>이름으로 찾기</t>
         </is>
       </c>
       <c r="D754" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>Find by name</t>
         </is>
       </c>
       <c r="E754" s="1" t="n"/>
@@ -14907,17 +14907,17 @@
       <c r="A755" s="1" t="n"/>
       <c r="B755" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Register</t>
+          <t>UI.Auction.RegisterEmptyCard</t>
         </is>
       </c>
       <c r="C755" s="6" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
         </is>
       </c>
       <c r="D755" s="6" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>[Select] something to list on the left.</t>
         </is>
       </c>
       <c r="E755" s="1" t="n"/>
@@ -14926,17 +14926,17 @@
       <c r="A756" s="1" t="n"/>
       <c r="B756" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideTitle</t>
+          <t>UI.Auction.ShowPrice</t>
         </is>
       </c>
       <c r="C756" s="6" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>시세 보기</t>
         </is>
       </c>
       <c r="D756" s="6" t="inlineStr">
         <is>
-          <t>Auction House</t>
+          <t>View Prices</t>
         </is>
       </c>
       <c r="E756" s="1" t="n"/>
@@ -14945,17 +14945,17 @@
       <c r="A757" s="1" t="n"/>
       <c r="B757" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyWhole</t>
+          <t>UI.Auction.MatchLowest</t>
         </is>
       </c>
       <c r="C757" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
+          <t>최저가에 맞춤</t>
         </is>
       </c>
       <c r="D757" s="6" t="inlineStr">
         <is>
-          <t>Listings are bought whole — no partial purchases</t>
+          <t>Match Lowest</t>
         </is>
       </c>
       <c r="E757" s="1" t="n"/>
@@ -14964,17 +14964,17 @@
       <c r="A758" s="1" t="n"/>
       <c r="B758" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyOwn</t>
+          <t>UI.Auction.Register</t>
         </is>
       </c>
       <c r="C758" s="6" t="inlineStr">
         <is>
-          <t>내 매물은 살 수 없습니다</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="D758" s="6" t="inlineStr">
         <is>
-          <t>You can't buy your own listings</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E758" s="1" t="n"/>
@@ -14983,17 +14983,17 @@
       <c r="A759" s="1" t="n"/>
       <c r="B759" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMailHeader</t>
+          <t>UI.Auction.GuideTitle</t>
         </is>
       </c>
       <c r="C759" s="6" t="inlineStr">
         <is>
-          <t>우편</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D759" s="6" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Auction House</t>
         </is>
       </c>
       <c r="E759" s="1" t="n"/>
@@ -15002,17 +15002,17 @@
       <c r="A760" s="1" t="n"/>
       <c r="B760" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMail</t>
+          <t>UI.Auction.GuideBuyWhole</t>
         </is>
       </c>
       <c r="C760" s="6" t="inlineStr">
         <is>
-          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
+          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
         </is>
       </c>
       <c r="D760" s="6" t="inlineStr">
         <is>
-          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
+          <t>Listings are bought whole — no partial purchases</t>
         </is>
       </c>
       <c r="E760" s="1" t="n"/>
@@ -15021,17 +15021,17 @@
       <c r="A761" s="1" t="n"/>
       <c r="B761" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideSellHint</t>
+          <t>UI.Auction.GuideBuyOwn</t>
         </is>
       </c>
       <c r="C761" s="6" t="inlineStr">
         <is>
-          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
+          <t>내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D761" s="6" t="inlineStr">
         <is>
-          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
+          <t>You can't buy your own listings</t>
         </is>
       </c>
       <c r="E761" s="1" t="n"/>
@@ -15040,17 +15040,17 @@
       <c r="A762" s="1" t="n"/>
       <c r="B762" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleAuction</t>
+          <t>UI.Auction.GuideMailHeader</t>
         </is>
       </c>
       <c r="C762" s="6" t="inlineStr">
         <is>
-          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
+          <t>우편</t>
         </is>
       </c>
       <c r="D762" s="6" t="inlineStr">
         <is>
-          <t>Auction — sell to other players at your price · wait until it sells</t>
+          <t>Mail</t>
         </is>
       </c>
       <c r="E762" s="1" t="n"/>
@@ -15059,17 +15059,17 @@
       <c r="A763" s="1" t="n"/>
       <c r="B763" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleInstant</t>
+          <t>UI.Auction.GuideMail</t>
         </is>
       </c>
       <c r="C763" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
+          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D763" s="6" t="inlineStr">
         <is>
-          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
+          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
         </is>
       </c>
       <c r="E763" s="1" t="n"/>
@@ -15078,17 +15078,17 @@
       <c r="A764" s="1" t="n"/>
       <c r="B764" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleHeader</t>
+          <t>UI.Auction.GuideSellHint</t>
         </is>
       </c>
       <c r="C764" s="6" t="inlineStr">
         <is>
-          <t>등록 규칙</t>
+          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
         </is>
       </c>
       <c r="D764" s="6" t="inlineStr">
         <is>
-          <t>Listing Rules</t>
+          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
         </is>
       </c>
       <c r="E764" s="1" t="n"/>
@@ -15097,17 +15097,17 @@
       <c r="A765" s="1" t="n"/>
       <c r="B765" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RulePrice</t>
+          <t>UI.Auction.RuleAuction</t>
         </is>
       </c>
       <c r="C765" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 이상 ~ {0} G</t>
+          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
         </is>
       </c>
       <c r="D765" s="6" t="inlineStr">
         <is>
-          <t>From the instant price ~ {0} G</t>
+          <t>Auction — sell to other players at your price · wait until it sells</t>
         </is>
       </c>
       <c r="E765" s="1" t="n"/>
@@ -15116,17 +15116,17 @@
       <c r="A766" s="1" t="n"/>
       <c r="B766" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCountLabel</t>
+          <t>UI.Auction.RuleInstant</t>
         </is>
       </c>
       <c r="C766" s="6" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
         </is>
       </c>
       <c r="D766" s="6" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
         </is>
       </c>
       <c r="E766" s="1" t="n"/>
@@ -15135,17 +15135,17 @@
       <c r="A767" s="1" t="n"/>
       <c r="B767" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCount</t>
+          <t>UI.Auction.RuleHeader</t>
         </is>
       </c>
       <c r="C767" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
+          <t>등록 규칙</t>
         </is>
       </c>
       <c r="D767" s="6" t="inlineStr">
         <is>
-          <t>Up to {0} per listing · sold only whole</t>
+          <t>Listing Rules</t>
         </is>
       </c>
       <c r="E767" s="1" t="n"/>
@@ -15154,17 +15154,17 @@
       <c r="A768" s="1" t="n"/>
       <c r="B768" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSlots</t>
+          <t>UI.Auction.RulePrice</t>
         </is>
       </c>
       <c r="C768" s="6" t="inlineStr">
         <is>
-          <t>최대 {0}건</t>
+          <t>즉시 판매가 이상 ~ {0} G</t>
         </is>
       </c>
       <c r="D768" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>From the instant price ~ {0} G</t>
         </is>
       </c>
       <c r="E768" s="1" t="n"/>
@@ -15173,17 +15173,17 @@
       <c r="A769" s="1" t="n"/>
       <c r="B769" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleListingFee</t>
+          <t>UI.Auction.RuleCountLabel</t>
         </is>
       </c>
       <c r="C769" s="6" t="inlineStr">
         <is>
-          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="D769" s="6" t="inlineStr">
         <is>
-          <t>Paid on listing · refunded on expiry, not on cancel</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="E769" s="1" t="n"/>
@@ -15192,17 +15192,17 @@
       <c r="A770" s="1" t="n"/>
       <c r="B770" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSaleFee</t>
+          <t>UI.Auction.RuleCount</t>
         </is>
       </c>
       <c r="C770" s="6" t="inlineStr">
         <is>
-          <t>팔린 금액에서 뗌</t>
+          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
         </is>
       </c>
       <c r="D770" s="6" t="inlineStr">
         <is>
-          <t>Deducted from the sale</t>
+          <t>Up to {0} per listing · sold only whole</t>
         </is>
       </c>
       <c r="E770" s="1" t="n"/>
@@ -15211,20 +15211,77 @@
       <c r="A771" s="1" t="n"/>
       <c r="B771" s="6" t="inlineStr">
         <is>
+          <t>UI.Auction.RuleSlots</t>
+        </is>
+      </c>
+      <c r="C771" s="6" t="inlineStr">
+        <is>
+          <t>최대 {0}건</t>
+        </is>
+      </c>
+      <c r="D771" s="6" t="inlineStr">
+        <is>
+          <t>Up to {0}</t>
+        </is>
+      </c>
+      <c r="E771" s="1" t="n"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="n"/>
+      <c r="B772" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleListingFee</t>
+        </is>
+      </c>
+      <c r="C772" s="6" t="inlineStr">
+        <is>
+          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+        </is>
+      </c>
+      <c r="D772" s="6" t="inlineStr">
+        <is>
+          <t>Paid on listing · refunded on expiry, not on cancel</t>
+        </is>
+      </c>
+      <c r="E772" s="1" t="n"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n"/>
+      <c r="B773" s="6" t="inlineStr">
+        <is>
+          <t>UI.Auction.RuleSaleFee</t>
+        </is>
+      </c>
+      <c r="C773" s="6" t="inlineStr">
+        <is>
+          <t>팔린 금액에서 뗌</t>
+        </is>
+      </c>
+      <c r="D773" s="6" t="inlineStr">
+        <is>
+          <t>Deducted from the sale</t>
+        </is>
+      </c>
+      <c r="E773" s="1" t="n"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="n"/>
+      <c r="B774" s="6" t="inlineStr">
+        <is>
           <t>UI.Auction.RuleCantList</t>
         </is>
       </c>
-      <c r="C771" s="6" t="inlineStr">
+      <c r="C774" s="6" t="inlineStr">
         <is>
           <t>끼고 있는 장비 · 일하는 캐릭터 · 잠긴 것은 올릴 수 없습니다 (흐린 줄 — 올리면 사유)</t>
         </is>
       </c>
-      <c r="D771" s="6" t="inlineStr">
+      <c r="D774" s="6" t="inlineStr">
         <is>
           <t>Worn gear, working characters and locked items can't be listed (dimmed — hover for why)</t>
         </is>
       </c>
-      <c r="E771" s="1" t="n"/>
+      <c r="E774" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E774"/>
+  <dimension ref="A1:E772"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="C540" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}장을 샀습니다.</t>
+          <t>{0} {1}장을 샀습니다. 인벤토리에서 열어 보세요.</t>
         </is>
       </c>
       <c r="D540" s="6" t="inlineStr">
         <is>
-          <t>Bought {0} x{1}.</t>
+          <t>Bought {0} x{1}. Open it from your inventory.</t>
         </is>
       </c>
       <c r="E540" s="1" t="n"/>
@@ -10833,17 +10833,17 @@
       <c r="A541" s="1" t="n"/>
       <c r="B541" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.Open</t>
+          <t>UI.Warehouse.Hint</t>
         </is>
       </c>
       <c r="C541" s="6" t="inlineStr">
         <is>
-          <t>열기</t>
+          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
         </is>
       </c>
       <c r="D541" s="6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Drag slots to move between inventory ↔ warehouse</t>
         </is>
       </c>
       <c r="E541" s="1" t="n"/>
@@ -10852,17 +10852,17 @@
       <c r="A542" s="1" t="n"/>
       <c r="B542" s="6" t="inlineStr">
         <is>
-          <t>UI.Shop.WaitOpen</t>
+          <t>UI.Warehouse.Stack</t>
         </is>
       </c>
       <c r="C542" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}장 열기</t>
+          <t>창고에 쌓기</t>
         </is>
       </c>
       <c r="D542" s="6" t="inlineStr">
         <is>
-          <t>Open {0} x{1}</t>
+          <t>Stack in Warehouse</t>
         </is>
       </c>
       <c r="E542" s="1" t="n"/>
@@ -10871,17 +10871,17 @@
       <c r="A543" s="1" t="n"/>
       <c r="B543" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Hint</t>
+          <t>UI.Warehouse.StackTip</t>
         </is>
       </c>
       <c r="C543" s="6" t="inlineStr">
         <is>
-          <t>칸을 끌어 인벤토리 ↔ 창고로 옮깁니다</t>
+          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
         </is>
       </c>
       <c r="D543" s="6" t="inlineStr">
         <is>
-          <t>Drag slots to move between inventory ↔ warehouse</t>
+          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
         </is>
       </c>
       <c r="E543" s="1" t="n"/>
@@ -10890,17 +10890,17 @@
       <c r="A544" s="1" t="n"/>
       <c r="B544" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.Stack</t>
+          <t>UI.Warehouse.NothingToStack</t>
         </is>
       </c>
       <c r="C544" s="6" t="inlineStr">
         <is>
-          <t>창고에 쌓기</t>
+          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
         </is>
       </c>
       <c r="D544" s="6" t="inlineStr">
         <is>
-          <t>Stack in Warehouse</t>
+          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
         </is>
       </c>
       <c r="E544" s="1" t="n"/>
@@ -10909,17 +10909,17 @@
       <c r="A545" s="1" t="n"/>
       <c r="B545" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.StackTip</t>
+          <t>UI.Auction.KindItem</t>
         </is>
       </c>
       <c r="C545" s="6" t="inlineStr">
         <is>
-          <t>인벤토리 자원을 창고에 이미 있는 같은 자원 칸으로 채웁니다 — 창고에 없는 자원은 옮기지 않고, 창고 칸이 차면 남은 몫은 인벤토리에 둡니다</t>
+          <t>자원</t>
         </is>
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>Fills warehouse slots that already hold the same resource from your inventory — resources not in the warehouse stay put, and any overflow stays in the inventory</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="E545" s="1" t="n"/>
@@ -10928,17 +10928,17 @@
       <c r="A546" s="1" t="n"/>
       <c r="B546" s="6" t="inlineStr">
         <is>
-          <t>UI.Warehouse.NothingToStack</t>
+          <t>UI.Auction.KindArtifact</t>
         </is>
       </c>
       <c r="C546" s="6" t="inlineStr">
         <is>
-          <t>창고에 쌓을 자원이 없습니다 — 창고에 덜 찬 같은 자원 칸이 있어야 합니다.</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D546" s="6" t="inlineStr">
         <is>
-          <t>Nothing to stack — the warehouse needs a partly filled slot of the same resource.</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="E546" s="1" t="n"/>
@@ -10947,17 +10947,17 @@
       <c r="A547" s="1" t="n"/>
       <c r="B547" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindItem</t>
+          <t>UI.Auction.NoAptitude</t>
         </is>
       </c>
       <c r="C547" s="6" t="inlineStr">
         <is>
-          <t>자원</t>
+          <t>적성 없음</t>
         </is>
       </c>
       <c r="D547" s="6" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>No aptitude</t>
         </is>
       </c>
       <c r="E547" s="1" t="n"/>
@@ -10966,17 +10966,17 @@
       <c r="A548" s="1" t="n"/>
       <c r="B548" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.KindArtifact</t>
+          <t>UI.Auction.NoStats</t>
         </is>
       </c>
       <c r="C548" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>능력치 없음</t>
         </is>
       </c>
       <c r="D548" s="6" t="inlineStr">
         <is>
-          <t>Artifact</t>
+          <t>No stats</t>
         </is>
       </c>
       <c r="E548" s="1" t="n"/>
@@ -10985,17 +10985,17 @@
       <c r="A549" s="1" t="n"/>
       <c r="B549" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoAptitude</t>
+          <t>UI.Auction.Stats</t>
         </is>
       </c>
       <c r="C549" s="6" t="inlineStr">
         <is>
-          <t>적성 없음</t>
+          <t>능력치</t>
         </is>
       </c>
       <c r="D549" s="6" t="inlineStr">
         <is>
-          <t>No aptitude</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="E549" s="1" t="n"/>
@@ -11004,17 +11004,17 @@
       <c r="A550" s="1" t="n"/>
       <c r="B550" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoStats</t>
+          <t>UI.Auction.HoursMinutes</t>
         </is>
       </c>
       <c r="C550" s="6" t="inlineStr">
         <is>
-          <t>능력치 없음</t>
+          <t>{0}시간 {1}분</t>
         </is>
       </c>
       <c r="D550" s="6" t="inlineStr">
         <is>
-          <t>No stats</t>
+          <t>{0}h {1}m</t>
         </is>
       </c>
       <c r="E550" s="1" t="n"/>
@@ -11023,17 +11023,17 @@
       <c r="A551" s="1" t="n"/>
       <c r="B551" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Stats</t>
+          <t>UI.Auction.ExpiringSoon</t>
         </is>
       </c>
       <c r="C551" s="6" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>곧 만료</t>
         </is>
       </c>
       <c r="D551" s="6" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Expiring soon</t>
         </is>
       </c>
       <c r="E551" s="1" t="n"/>
@@ -11042,17 +11042,17 @@
       <c r="A552" s="1" t="n"/>
       <c r="B552" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursMinutes</t>
+          <t>UI.Auction.Buying</t>
         </is>
       </c>
       <c r="C552" s="6" t="inlineStr">
         <is>
-          <t>{0}시간 {1}분</t>
+          <t>구매 진행 중</t>
         </is>
       </c>
       <c r="D552" s="6" t="inlineStr">
         <is>
-          <t>{0}h {1}m</t>
+          <t>Being bought</t>
         </is>
       </c>
       <c r="E552" s="1" t="n"/>
@@ -11061,17 +11061,17 @@
       <c r="A553" s="1" t="n"/>
       <c r="B553" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ExpiringSoon</t>
+          <t>UI.Auction.Me</t>
         </is>
       </c>
       <c r="C553" s="6" t="inlineStr">
         <is>
-          <t>곧 만료</t>
+          <t>나</t>
         </is>
       </c>
       <c r="D553" s="6" t="inlineStr">
         <is>
-          <t>Expiring soon</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="E553" s="1" t="n"/>
@@ -11080,17 +11080,17 @@
       <c r="A554" s="1" t="n"/>
       <c r="B554" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buying</t>
+          <t>UI.Auction.Price</t>
         </is>
       </c>
       <c r="C554" s="6" t="inlineStr">
         <is>
-          <t>구매 진행 중</t>
+          <t>시세</t>
         </is>
       </c>
       <c r="D554" s="6" t="inlineStr">
         <is>
-          <t>Being bought</t>
+          <t>Prices</t>
         </is>
       </c>
       <c r="E554" s="1" t="n"/>
@@ -11099,17 +11099,17 @@
       <c r="A555" s="1" t="n"/>
       <c r="B555" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Me</t>
+          <t>UI.Auction.MyListing</t>
         </is>
       </c>
       <c r="C555" s="6" t="inlineStr">
         <is>
-          <t>나</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D555" s="6" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="E555" s="1" t="n"/>
@@ -11118,17 +11118,17 @@
       <c r="A556" s="1" t="n"/>
       <c r="B556" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Price</t>
+          <t>UI.Auction.Buy</t>
         </is>
       </c>
       <c r="C556" s="6" t="inlineStr">
         <is>
-          <t>시세</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D556" s="6" t="inlineStr">
         <is>
-          <t>Prices</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="E556" s="1" t="n"/>
@@ -11137,17 +11137,17 @@
       <c r="A557" s="1" t="n"/>
       <c r="B557" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyListing</t>
+          <t>UI.Auction.OnSale</t>
         </is>
       </c>
       <c r="C557" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>판매 중</t>
         </is>
       </c>
       <c r="D557" s="6" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>On Sale</t>
         </is>
       </c>
       <c r="E557" s="1" t="n"/>
@@ -11156,17 +11156,17 @@
       <c r="A558" s="1" t="n"/>
       <c r="B558" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Buy</t>
+          <t>UI.Auction.UnitPrice</t>
         </is>
       </c>
       <c r="C558" s="6" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="D558" s="6" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Unit Price</t>
         </is>
       </c>
       <c r="E558" s="1" t="n"/>
@@ -11175,17 +11175,17 @@
       <c r="A559" s="1" t="n"/>
       <c r="B559" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OnSale</t>
+          <t>UI.Auction.TotalPrice</t>
         </is>
       </c>
       <c r="C559" s="6" t="inlineStr">
         <is>
-          <t>판매 중</t>
+          <t>총액</t>
         </is>
       </c>
       <c r="D559" s="6" t="inlineStr">
         <is>
-          <t>On Sale</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E559" s="1" t="n"/>
@@ -11194,17 +11194,17 @@
       <c r="A560" s="1" t="n"/>
       <c r="B560" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPrice</t>
+          <t>UI.Auction.TimeLeft</t>
         </is>
       </c>
       <c r="C560" s="6" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>남은 시간</t>
         </is>
       </c>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>Unit Price</t>
+          <t>Time Left</t>
         </is>
       </c>
       <c r="E560" s="1" t="n"/>
@@ -11213,17 +11213,17 @@
       <c r="A561" s="1" t="n"/>
       <c r="B561" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TotalPrice</t>
+          <t>UI.Auction.Seller</t>
         </is>
       </c>
       <c r="C561" s="6" t="inlineStr">
         <is>
-          <t>총액</t>
+          <t>판매자</t>
         </is>
       </c>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="E561" s="1" t="n"/>
@@ -11232,17 +11232,17 @@
       <c r="A562" s="1" t="n"/>
       <c r="B562" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TimeLeft</t>
+          <t>UI.Auction.SellerIsMe</t>
         </is>
       </c>
       <c r="C562" s="6" t="inlineStr">
         <is>
-          <t>남은 시간</t>
+          <t>나 — 내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D562" s="6" t="inlineStr">
         <is>
-          <t>Time Left</t>
+          <t>Me — you can't buy your own listing</t>
         </is>
       </c>
       <c r="E562" s="1" t="n"/>
@@ -11251,17 +11251,17 @@
       <c r="A563" s="1" t="n"/>
       <c r="B563" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Seller</t>
+          <t>UI.Auction.CantList</t>
         </is>
       </c>
       <c r="C563" s="6" t="inlineStr">
         <is>
-          <t>판매자</t>
+          <t>등록 불가</t>
         </is>
       </c>
       <c r="D563" s="6" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Can't List</t>
         </is>
       </c>
       <c r="E563" s="1" t="n"/>
@@ -11270,17 +11270,17 @@
       <c r="A564" s="1" t="n"/>
       <c r="B564" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SellerIsMe</t>
+          <t>UI.Auction.PriceRules</t>
         </is>
       </c>
       <c r="C564" s="6" t="inlineStr">
         <is>
-          <t>나 — 내 매물은 살 수 없습니다</t>
+          <t>가격 기준</t>
         </is>
       </c>
       <c r="D564" s="6" t="inlineStr">
         <is>
-          <t>Me — you can't buy your own listing</t>
+          <t>Price Basis</t>
         </is>
       </c>
       <c r="E564" s="1" t="n"/>
@@ -11289,17 +11289,17 @@
       <c r="A565" s="1" t="n"/>
       <c r="B565" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantList</t>
+          <t>UI.Auction.PageOf</t>
         </is>
       </c>
       <c r="C565" s="6" t="inlineStr">
         <is>
-          <t>등록 불가</t>
+          <t>{0} / {1} 쪽</t>
         </is>
       </c>
       <c r="D565" s="6" t="inlineStr">
         <is>
-          <t>Can't List</t>
+          <t>Page {0} / {1}</t>
         </is>
       </c>
       <c r="E565" s="1" t="n"/>
@@ -11308,17 +11308,17 @@
       <c r="A566" s="1" t="n"/>
       <c r="B566" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRules</t>
+          <t>UI.Auction.Page</t>
         </is>
       </c>
       <c r="C566" s="6" t="inlineStr">
         <is>
-          <t>가격 기준</t>
+          <t>{0} 쪽</t>
         </is>
       </c>
       <c r="D566" s="6" t="inlineStr">
         <is>
-          <t>Price Basis</t>
+          <t>Page {0}</t>
         </is>
       </c>
       <c r="E566" s="1" t="n"/>
@@ -11327,17 +11327,17 @@
       <c r="A567" s="1" t="n"/>
       <c r="B567" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PageOf</t>
+          <t>UI.Auction.PriceQueryPlaceholder</t>
         </is>
       </c>
       <c r="C567" s="6" t="inlineStr">
         <is>
-          <t>{0} / {1} 쪽</t>
+          <t>시세 볼 아이템 이름</t>
         </is>
       </c>
       <c r="D567" s="6" t="inlineStr">
         <is>
-          <t>Page {0} / {1}</t>
+          <t>Item name to check prices</t>
         </is>
       </c>
       <c r="E567" s="1" t="n"/>
@@ -11346,17 +11346,17 @@
       <c r="A568" s="1" t="n"/>
       <c r="B568" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Page</t>
+          <t>UI.Auction.PriceQueryHint</t>
         </is>
       </c>
       <c r="C568" s="6" t="inlineStr">
         <is>
-          <t>{0} 쪽</t>
+          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
         </is>
       </c>
       <c r="D568" s="6" t="inlineStr">
         <is>
-          <t>Page {0}</t>
+          <t>[Search] — opens prices for the matching item</t>
         </is>
       </c>
       <c r="E568" s="1" t="n"/>
@@ -11365,17 +11365,17 @@
       <c r="A569" s="1" t="n"/>
       <c r="B569" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryPlaceholder</t>
+          <t>UI.Auction.NoSuchItem</t>
         </is>
       </c>
       <c r="C569" s="6" t="inlineStr">
         <is>
-          <t>시세 볼 아이템 이름</t>
+          <t>'{0}'(이)라는 아이템이 없습니다.</t>
         </is>
       </c>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>Item name to check prices</t>
+          <t>There's no item named '{0}'.</t>
         </is>
       </c>
       <c r="E569" s="1" t="n"/>
@@ -11384,17 +11384,17 @@
       <c r="A570" s="1" t="n"/>
       <c r="B570" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceQueryHint</t>
+          <t>UI.Auction.NoListings</t>
         </is>
       </c>
       <c r="C570" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 이름이 맞는 아이템의 시세를 엽니다</t>
+          <t>매물 없음</t>
         </is>
       </c>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>[Search] — opens prices for the matching item</t>
+          <t>No listings</t>
         </is>
       </c>
       <c r="E570" s="1" t="n"/>
@@ -11403,17 +11403,17 @@
       <c r="A571" s="1" t="n"/>
       <c r="B571" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchItem</t>
+          <t>UI.Auction.NoTrades</t>
         </is>
       </c>
       <c r="C571" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 아이템이 없습니다.</t>
+          <t>거래 없음</t>
         </is>
       </c>
       <c r="D571" s="6" t="inlineStr">
         <is>
-          <t>There's no item named '{0}'.</t>
+          <t>No trades</t>
         </is>
       </c>
       <c r="E571" s="1" t="n"/>
@@ -11422,17 +11422,17 @@
       <c r="A572" s="1" t="n"/>
       <c r="B572" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListings</t>
+          <t>UI.Auction.CountWord</t>
         </is>
       </c>
       <c r="C572" s="6" t="inlineStr">
         <is>
-          <t>매물 없음</t>
+          <t>개</t>
         </is>
       </c>
       <c r="D572" s="6" t="inlineStr">
         <is>
-          <t>No listings</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E572" s="1" t="n"/>
@@ -11441,17 +11441,17 @@
       <c r="A573" s="1" t="n"/>
       <c r="B573" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoTrades</t>
+          <t>UI.Auction.NoSummary</t>
         </is>
       </c>
       <c r="C573" s="6" t="inlineStr">
         <is>
-          <t>거래 없음</t>
+          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="D573" s="6" t="inlineStr">
         <is>
-          <t>No trades</t>
+          <t>Couldn't get prices — you can check again in the Prices tab</t>
         </is>
       </c>
       <c r="E573" s="1" t="n"/>
@@ -11460,17 +11460,17 @@
       <c r="A574" s="1" t="n"/>
       <c r="B574" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountWord</t>
+          <t>UI.Auction.LowestPrice</t>
         </is>
       </c>
       <c r="C574" s="6" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>최저가</t>
         </is>
       </c>
       <c r="D574" s="6" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>Lowest</t>
         </is>
       </c>
       <c r="E574" s="1" t="n"/>
@@ -11479,17 +11479,17 @@
       <c r="A575" s="1" t="n"/>
       <c r="B575" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSummary</t>
+          <t>UI.Auction.RecentPrice</t>
         </is>
       </c>
       <c r="C575" s="6" t="inlineStr">
         <is>
-          <t>시세를 받지 못했습니다 — 시세 탭에서 다시 볼 수 있습니다</t>
+          <t>최근 거래가</t>
         </is>
       </c>
       <c r="D575" s="6" t="inlineStr">
         <is>
-          <t>Couldn't get prices — you can check again in the Prices tab</t>
+          <t>Last Sale</t>
         </is>
       </c>
       <c r="E575" s="1" t="n"/>
@@ -11498,17 +11498,17 @@
       <c r="A576" s="1" t="n"/>
       <c r="B576" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LowestPrice</t>
+          <t>UI.Auction.YesterdayAvg</t>
         </is>
       </c>
       <c r="C576" s="6" t="inlineStr">
         <is>
-          <t>최저가</t>
+          <t>전일 평균</t>
         </is>
       </c>
       <c r="D576" s="6" t="inlineStr">
         <is>
-          <t>Lowest</t>
+          <t>Yesterday Avg</t>
         </is>
       </c>
       <c r="E576" s="1" t="n"/>
@@ -11517,17 +11517,17 @@
       <c r="A577" s="1" t="n"/>
       <c r="B577" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RecentPrice</t>
+          <t>UI.Auction.NoCompare</t>
         </is>
       </c>
       <c r="C577" s="6" t="inlineStr">
         <is>
-          <t>최근 거래가</t>
+          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
         </is>
       </c>
       <c r="D577" s="6" t="inlineStr">
         <is>
-          <t>Last Sale</t>
+          <t>No trades yesterday, so there's no average to compare</t>
         </is>
       </c>
       <c r="E577" s="1" t="n"/>
@@ -11536,17 +11536,17 @@
       <c r="A578" s="1" t="n"/>
       <c r="B578" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.YesterdayAvg</t>
+          <t>UI.Auction.ThisUnitPrice</t>
         </is>
       </c>
       <c r="C578" s="6" t="inlineStr">
         <is>
-          <t>전일 평균</t>
+          <t>이 매물 단가는</t>
         </is>
       </c>
       <c r="D578" s="6" t="inlineStr">
         <is>
-          <t>Yesterday Avg</t>
+          <t>This unit price is</t>
         </is>
       </c>
       <c r="E578" s="1" t="n"/>
@@ -11555,17 +11555,17 @@
       <c r="A579" s="1" t="n"/>
       <c r="B579" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoCompare</t>
+          <t>UI.Auction.SameAsAvg</t>
         </is>
       </c>
       <c r="C579" s="6" t="inlineStr">
         <is>
-          <t>전일 거래가 없어 평균과 비교할 수 없습니다</t>
+          <t>전일 평균과 같습니다</t>
         </is>
       </c>
       <c r="D579" s="6" t="inlineStr">
         <is>
-          <t>No trades yesterday, so there's no average to compare</t>
+          <t>the same as yesterday's average</t>
         </is>
       </c>
       <c r="E579" s="1" t="n"/>
@@ -11574,17 +11574,17 @@
       <c r="A580" s="1" t="n"/>
       <c r="B580" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThisUnitPrice</t>
+          <t>UI.Auction.PricierBy</t>
         </is>
       </c>
       <c r="C580" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는</t>
+          <t>{0}% 비쌉니다</t>
         </is>
       </c>
       <c r="D580" s="6" t="inlineStr">
         <is>
-          <t>This unit price is</t>
+          <t>{0}% higher</t>
         </is>
       </c>
       <c r="E580" s="1" t="n"/>
@@ -11593,17 +11593,17 @@
       <c r="A581" s="1" t="n"/>
       <c r="B581" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SameAsAvg</t>
+          <t>UI.Auction.CheaperBy</t>
         </is>
       </c>
       <c r="C581" s="6" t="inlineStr">
         <is>
-          <t>전일 평균과 같습니다</t>
+          <t>{0}% 쌉니다</t>
         </is>
       </c>
       <c r="D581" s="6" t="inlineStr">
         <is>
-          <t>the same as yesterday's average</t>
+          <t>{0}% lower</t>
         </is>
       </c>
       <c r="E581" s="1" t="n"/>
@@ -11612,17 +11612,17 @@
       <c r="A582" s="1" t="n"/>
       <c r="B582" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PricierBy</t>
+          <t>UI.Auction.ThanAvg</t>
         </is>
       </c>
       <c r="C582" s="6" t="inlineStr">
         <is>
-          <t>{0}% 비쌉니다</t>
+          <t>이 매물 단가는 전일 평균보다</t>
         </is>
       </c>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>{0}% higher</t>
+          <t>Vs. yesterday's average, this unit price is</t>
         </is>
       </c>
       <c r="E582" s="1" t="n"/>
@@ -11631,17 +11631,17 @@
       <c r="A583" s="1" t="n"/>
       <c r="B583" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CheaperBy</t>
+          <t>UI.Auction.TradeCount</t>
         </is>
       </c>
       <c r="C583" s="6" t="inlineStr">
         <is>
-          <t>{0}% 쌉니다</t>
+          <t>{0}개 거래</t>
         </is>
       </c>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>{0}% lower</t>
+          <t>{0} traded</t>
         </is>
       </c>
       <c r="E583" s="1" t="n"/>
@@ -11650,17 +11650,17 @@
       <c r="A584" s="1" t="n"/>
       <c r="B584" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ThanAvg</t>
+          <t>UI.Auction.GoldOwned</t>
         </is>
       </c>
       <c r="C584" s="6" t="inlineStr">
         <is>
-          <t>이 매물 단가는 전일 평균보다</t>
+          <t>보유 골드</t>
         </is>
       </c>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>Vs. yesterday's average, this unit price is</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E584" s="1" t="n"/>
@@ -11669,17 +11669,17 @@
       <c r="A585" s="1" t="n"/>
       <c r="B585" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TradeCount</t>
+          <t>UI.Artifact.Title</t>
         </is>
       </c>
       <c r="C585" s="6" t="inlineStr">
         <is>
-          <t>{0}개 거래</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>{0} traded</t>
+          <t>Artifacts</t>
         </is>
       </c>
       <c r="E585" s="1" t="n"/>
@@ -11688,17 +11688,17 @@
       <c r="A586" s="1" t="n"/>
       <c r="B586" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldOwned</t>
+          <t>UI.Artifact.HelpTitle</t>
         </is>
       </c>
       <c r="C586" s="6" t="inlineStr">
         <is>
-          <t>보유 골드</t>
+          <t>아티팩트</t>
         </is>
       </c>
       <c r="D586" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Artifacts</t>
         </is>
       </c>
       <c r="E586" s="1" t="n"/>
@@ -11707,17 +11707,17 @@
       <c r="A587" s="1" t="n"/>
       <c r="B587" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Title</t>
+          <t>UI.Artifact.HelpGet</t>
         </is>
       </c>
       <c r="C587" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>유물을 감정하면 나옵니다 — 인벤토리 자원 탭에서 유물을 좌클릭</t>
         </is>
       </c>
       <c r="D587" s="6" t="inlineStr">
         <is>
-          <t>Artifacts</t>
+          <t>Appraise relics to get them — left-click a relic in the Inventory Resources tab</t>
         </is>
       </c>
       <c r="E587" s="1" t="n"/>
@@ -11726,17 +11726,17 @@
       <c r="A588" s="1" t="n"/>
       <c r="B588" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpTitle</t>
+          <t>UI.Artifact.HelpEquip</t>
         </is>
       </c>
       <c r="C588" s="6" t="inlineStr">
         <is>
-          <t>아티팩트</t>
+          <t>도감에 장착해야 효과가 붙습니다 — 번호마다 1개, 장착은 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D588" s="6" t="inlineStr">
         <is>
-          <t>Artifacts</t>
+          <t>Effects apply only once placed in the codex — one per kind, and it can't be undone</t>
         </is>
       </c>
       <c r="E588" s="1" t="n"/>
@@ -11745,17 +11745,17 @@
       <c r="A589" s="1" t="n"/>
       <c r="B589" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpGet</t>
+          <t>UI.Artifact.HelpToggle</t>
         </is>
       </c>
       <c r="C589" s="6" t="inlineStr">
         <is>
-          <t>유물을 감정하면 나옵니다 — 인벤토리 자원 탭에서 유물을 좌클릭</t>
+          <t>장착한 아티팩트는 효과를 켜고 끌 수 있습니다 — 꺼 두면 효과가 없습니다</t>
         </is>
       </c>
       <c r="D589" s="6" t="inlineStr">
         <is>
-          <t>Appraise relics to get them — left-click a relic in the Inventory Resources tab</t>
+          <t>Codex artifacts can be turned on or off — off means no effect</t>
         </is>
       </c>
       <c r="E589" s="1" t="n"/>
@@ -11764,17 +11764,17 @@
       <c r="A590" s="1" t="n"/>
       <c r="B590" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpEquip</t>
+          <t>UI.Artifact.HelpSell</t>
         </is>
       </c>
       <c r="C590" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착해야 효과가 붙습니다 — 번호마다 1개, 장착은 되돌릴 수 없습니다</t>
+          <t>남는 것은 우클릭으로 즉시 판매하거나, Ctrl+우클릭으로 경매에 올려 더 비싸게 팝니다</t>
         </is>
       </c>
       <c r="D590" s="6" t="inlineStr">
         <is>
-          <t>Effects apply only once placed in the codex — one per kind, and it can't be undone</t>
+          <t>Right-click extras to sell instantly, or Ctrl+right-click to list them on the auction for more</t>
         </is>
       </c>
       <c r="E590" s="1" t="n"/>
@@ -11783,17 +11783,17 @@
       <c r="A591" s="1" t="n"/>
       <c r="B591" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpToggle</t>
+          <t>UI.Artifact.Codex</t>
         </is>
       </c>
       <c r="C591" s="6" t="inlineStr">
         <is>
-          <t>장착한 아티팩트는 효과를 켜고 끌 수 있습니다 — 꺼 두면 효과가 없습니다</t>
+          <t>도감</t>
         </is>
       </c>
       <c r="D591" s="6" t="inlineStr">
         <is>
-          <t>Codex artifacts can be turned on or off — off means no effect</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="E591" s="1" t="n"/>
@@ -11802,17 +11802,17 @@
       <c r="A592" s="1" t="n"/>
       <c r="B592" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HelpSell</t>
+          <t>UI.Artifact.EquippedCount</t>
         </is>
       </c>
       <c r="C592" s="6" t="inlineStr">
         <is>
-          <t>남는 것은 우클릭으로 즉시 판매하거나, Ctrl+우클릭으로 경매에 올려 더 비싸게 팝니다</t>
+          <t>장착 {0} / {1}</t>
         </is>
       </c>
       <c r="D592" s="6" t="inlineStr">
         <is>
-          <t>Right-click extras to sell instantly, or Ctrl+right-click to list them on the auction for more</t>
+          <t>Placed {0} / {1}</t>
         </is>
       </c>
       <c r="E592" s="1" t="n"/>
@@ -11821,17 +11821,17 @@
       <c r="A593" s="1" t="n"/>
       <c r="B593" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Codex</t>
+          <t>UI.Artifact.FilterAll</t>
         </is>
       </c>
       <c r="C593" s="6" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E593" s="1" t="n"/>
@@ -11840,17 +11840,17 @@
       <c r="A594" s="1" t="n"/>
       <c r="B594" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EquippedCount</t>
+          <t>UI.Artifact.FilterEquipped</t>
         </is>
       </c>
       <c r="C594" s="6" t="inlineStr">
         <is>
-          <t>장착 {0} / {1}</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>Placed {0} / {1}</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="E594" s="1" t="n"/>
@@ -11859,17 +11859,17 @@
       <c r="A595" s="1" t="n"/>
       <c r="B595" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.FilterAll</t>
+          <t>UI.Artifact.GroupHead</t>
         </is>
       </c>
       <c r="C595" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>{0}   획득 {1} / {2}</t>
         </is>
       </c>
       <c r="D595" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>{0}   Collected {1} / {2}</t>
         </is>
       </c>
       <c r="E595" s="1" t="n"/>
@@ -11878,17 +11878,17 @@
       <c r="A596" s="1" t="n"/>
       <c r="B596" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.FilterEquipped</t>
+          <t>UI.Artifact.Unknown</t>
         </is>
       </c>
       <c r="C596" s="6" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>???</t>
         </is>
       </c>
       <c r="D596" s="6" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>???</t>
         </is>
       </c>
       <c r="E596" s="1" t="n"/>
@@ -11897,17 +11897,17 @@
       <c r="A597" s="1" t="n"/>
       <c r="B597" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.GroupHead</t>
+          <t>UI.Artifact.UnknownHint</t>
         </is>
       </c>
       <c r="C597" s="6" t="inlineStr">
         <is>
-          <t>{0}   획득 {1} / {2}</t>
+          <t>아직 얻지 못한 아티팩트입니다</t>
         </is>
       </c>
       <c r="D597" s="6" t="inlineStr">
         <is>
-          <t>{0}   Collected {1} / {2}</t>
+          <t>You haven't found this artifact yet</t>
         </is>
       </c>
       <c r="E597" s="1" t="n"/>
@@ -11916,17 +11916,17 @@
       <c r="A598" s="1" t="n"/>
       <c r="B598" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Unknown</t>
+          <t>UI.Artifact.Off</t>
         </is>
       </c>
       <c r="C598" s="6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>꺼짐</t>
         </is>
       </c>
       <c r="D598" s="6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E598" s="1" t="n"/>
@@ -11935,17 +11935,17 @@
       <c r="A599" s="1" t="n"/>
       <c r="B599" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.UnknownHint</t>
+          <t>UI.Artifact.OwnedShort</t>
         </is>
       </c>
       <c r="C599" s="6" t="inlineStr">
         <is>
-          <t>아직 얻지 못한 아티팩트입니다</t>
+          <t>보유 {0}</t>
         </is>
       </c>
       <c r="D599" s="6" t="inlineStr">
         <is>
-          <t>You haven't found this artifact yet</t>
+          <t>Owned {0}</t>
         </is>
       </c>
       <c r="E599" s="1" t="n"/>
@@ -11954,17 +11954,17 @@
       <c r="A600" s="1" t="n"/>
       <c r="B600" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Off</t>
+          <t>UI.Artifact.Holding</t>
         </is>
       </c>
       <c r="C600" s="6" t="inlineStr">
         <is>
-          <t>꺼짐</t>
+          <t>보유 아티팩트  {0}종 · {1}개</t>
         </is>
       </c>
       <c r="D600" s="6" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Owned Artifacts  {0} kinds · {1}</t>
         </is>
       </c>
       <c r="E600" s="1" t="n"/>
@@ -11973,17 +11973,17 @@
       <c r="A601" s="1" t="n"/>
       <c r="B601" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.OwnedShort</t>
+          <t>UI.Artifact.HoldingEmpty</t>
         </is>
       </c>
       <c r="C601" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}</t>
+          <t>보유한 아티팩트가 없습니다 — 유물을 감정하면 생깁니다</t>
         </is>
       </c>
       <c r="D601" s="6" t="inlineStr">
         <is>
-          <t>Owned {0}</t>
+          <t>No artifacts yet — appraise relics to get some</t>
         </is>
       </c>
       <c r="E601" s="1" t="n"/>
@@ -11992,17 +11992,17 @@
       <c r="A602" s="1" t="n"/>
       <c r="B602" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Holding</t>
+          <t>UI.Artifact.New</t>
         </is>
       </c>
       <c r="C602" s="6" t="inlineStr">
         <is>
-          <t>보유 아티팩트  {0}종 · {1}개</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="D602" s="6" t="inlineStr">
         <is>
-          <t>Owned Artifacts  {0} kinds · {1}</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E602" s="1" t="n"/>
@@ -12011,17 +12011,17 @@
       <c r="A603" s="1" t="n"/>
       <c r="B603" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.HoldingEmpty</t>
+          <t>UI.Artifact.DetailEmpty</t>
         </is>
       </c>
       <c r="C603" s="6" t="inlineStr">
         <is>
-          <t>보유한 아티팩트가 없습니다 — 유물을 감정하면 생깁니다</t>
+          <t>아티팩트를 고르면 설명이 여기에 뜹니다</t>
         </is>
       </c>
       <c r="D603" s="6" t="inlineStr">
         <is>
-          <t>No artifacts yet — appraise relics to get some</t>
+          <t>Select an artifact to see its details here</t>
         </is>
       </c>
       <c r="E603" s="1" t="n"/>
@@ -12030,17 +12030,17 @@
       <c r="A604" s="1" t="n"/>
       <c r="B604" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.New</t>
+          <t>UI.Artifact.Effect</t>
         </is>
       </c>
       <c r="C604" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>효과</t>
         </is>
       </c>
       <c r="D604" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E604" s="1" t="n"/>
@@ -12049,17 +12049,17 @@
       <c r="A605" s="1" t="n"/>
       <c r="B605" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.DetailEmpty</t>
+          <t>UI.Artifact.StateOn</t>
         </is>
       </c>
       <c r="C605" s="6" t="inlineStr">
         <is>
-          <t>아티팩트를 고르면 설명이 여기에 뜹니다</t>
+          <t>장착 · 켜짐</t>
         </is>
       </c>
       <c r="D605" s="6" t="inlineStr">
         <is>
-          <t>Select an artifact to see its details here</t>
+          <t>Placed · On</t>
         </is>
       </c>
       <c r="E605" s="1" t="n"/>
@@ -12068,17 +12068,17 @@
       <c r="A606" s="1" t="n"/>
       <c r="B606" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Effect</t>
+          <t>UI.Artifact.StateOff</t>
         </is>
       </c>
       <c r="C606" s="6" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>장착 · 꺼짐</t>
         </is>
       </c>
       <c r="D606" s="6" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>Placed · Off</t>
         </is>
       </c>
       <c r="E606" s="1" t="n"/>
@@ -12087,17 +12087,17 @@
       <c r="A607" s="1" t="n"/>
       <c r="B607" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateOn</t>
+          <t>UI.Artifact.StateNone</t>
         </is>
       </c>
       <c r="C607" s="6" t="inlineStr">
         <is>
-          <t>장착 · 켜짐</t>
+          <t>도감에 없음</t>
         </is>
       </c>
       <c r="D607" s="6" t="inlineStr">
         <is>
-          <t>Placed · On</t>
+          <t>Not in codex</t>
         </is>
       </c>
       <c r="E607" s="1" t="n"/>
@@ -12106,17 +12106,17 @@
       <c r="A608" s="1" t="n"/>
       <c r="B608" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateOff</t>
+          <t>UI.Artifact.ShowDetail</t>
         </is>
       </c>
       <c r="C608" s="6" t="inlineStr">
         <is>
-          <t>장착 · 꺼짐</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="D608" s="6" t="inlineStr">
         <is>
-          <t>Placed · Off</t>
+          <t>Details</t>
         </is>
       </c>
       <c r="E608" s="1" t="n"/>
@@ -12125,17 +12125,17 @@
       <c r="A609" s="1" t="n"/>
       <c r="B609" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.StateNone</t>
+          <t>UI.Artifact.Equip</t>
         </is>
       </c>
       <c r="C609" s="6" t="inlineStr">
         <is>
-          <t>도감에 없음</t>
+          <t>도감에 장착</t>
         </is>
       </c>
       <c r="D609" s="6" t="inlineStr">
         <is>
-          <t>Not in codex</t>
+          <t>Place in Codex</t>
         </is>
       </c>
       <c r="E609" s="1" t="n"/>
@@ -12144,17 +12144,17 @@
       <c r="A610" s="1" t="n"/>
       <c r="B610" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.ShowDetail</t>
+          <t>UI.Artifact.TurnOff</t>
         </is>
       </c>
       <c r="C610" s="6" t="inlineStr">
         <is>
-          <t>상세 보기</t>
+          <t>효과 끄기</t>
         </is>
       </c>
       <c r="D610" s="6" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Turn Off</t>
         </is>
       </c>
       <c r="E610" s="1" t="n"/>
@@ -12163,17 +12163,17 @@
       <c r="A611" s="1" t="n"/>
       <c r="B611" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Equip</t>
+          <t>UI.Artifact.TurnOn</t>
         </is>
       </c>
       <c r="C611" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착</t>
+          <t>효과 켜기</t>
         </is>
       </c>
       <c r="D611" s="6" t="inlineStr">
         <is>
-          <t>Place in Codex</t>
+          <t>Turn On</t>
         </is>
       </c>
       <c r="E611" s="1" t="n"/>
@@ -12182,17 +12182,17 @@
       <c r="A612" s="1" t="n"/>
       <c r="B612" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.TurnOff</t>
+          <t>UI.Artifact.WaitEquip</t>
         </is>
       </c>
       <c r="C612" s="6" t="inlineStr">
         <is>
-          <t>효과 끄기</t>
+          <t>도감 장착</t>
         </is>
       </c>
       <c r="D612" s="6" t="inlineStr">
         <is>
-          <t>Turn Off</t>
+          <t>Place in Codex</t>
         </is>
       </c>
       <c r="E612" s="1" t="n"/>
@@ -12201,17 +12201,17 @@
       <c r="A613" s="1" t="n"/>
       <c r="B613" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.TurnOn</t>
+          <t>UI.Artifact.WaitToggle</t>
         </is>
       </c>
       <c r="C613" s="6" t="inlineStr">
         <is>
-          <t>효과 켜기</t>
+          <t>켜고 끄기</t>
         </is>
       </c>
       <c r="D613" s="6" t="inlineStr">
         <is>
-          <t>Turn On</t>
+          <t>Turn On/Off</t>
         </is>
       </c>
       <c r="E613" s="1" t="n"/>
@@ -12220,17 +12220,17 @@
       <c r="A614" s="1" t="n"/>
       <c r="B614" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.WaitEquip</t>
+          <t>UI.Artifact.Equipped</t>
         </is>
       </c>
       <c r="C614" s="6" t="inlineStr">
         <is>
-          <t>도감 장착</t>
+          <t>도감에 장착했습니다 — {0}</t>
         </is>
       </c>
       <c r="D614" s="6" t="inlineStr">
         <is>
-          <t>Place in Codex</t>
+          <t>Placed in codex — {0}</t>
         </is>
       </c>
       <c r="E614" s="1" t="n"/>
@@ -12239,17 +12239,17 @@
       <c r="A615" s="1" t="n"/>
       <c r="B615" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.WaitToggle</t>
+          <t>UI.Artifact.SellHead</t>
         </is>
       </c>
       <c r="C615" s="6" t="inlineStr">
         <is>
-          <t>켜고 끄기</t>
+          <t>아티팩트 판매 {0}종</t>
         </is>
       </c>
       <c r="D615" s="6" t="inlineStr">
         <is>
-          <t>Turn On/Off</t>
+          <t>Sell Artifacts ({0})</t>
         </is>
       </c>
       <c r="E615" s="1" t="n"/>
@@ -12258,17 +12258,17 @@
       <c r="A616" s="1" t="n"/>
       <c r="B616" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Equipped</t>
+          <t>UI.Artifact.SellEmpty</t>
         </is>
       </c>
       <c r="C616" s="6" t="inlineStr">
         <is>
-          <t>도감에 장착했습니다 — {0}</t>
+          <t>보유 칸을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다. 비싸게 팔려면 Ctrl+우클릭(경매)</t>
         </is>
       </c>
       <c r="D616" s="6" t="inlineStr">
         <is>
-          <t>Placed in codex — {0}</t>
+          <t>Right-click owned artifacts to add — they sell instantly. Ctrl+right-click to list on the auction for more</t>
         </is>
       </c>
       <c r="E616" s="1" t="n"/>
@@ -12277,17 +12277,17 @@
       <c r="A617" s="1" t="n"/>
       <c r="B617" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellHead</t>
+          <t>UI.Artifact.SellUncollected</t>
         </is>
       </c>
       <c r="C617" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 판매 {0}종</t>
+          <t>주의! 도감에 없는 아티팩트 포함 — 팔면 도감에 남지 않습니다</t>
         </is>
       </c>
       <c r="D617" s="6" t="inlineStr">
         <is>
-          <t>Sell Artifacts ({0})</t>
+          <t>Caution! Includes artifacts not in your codex — selling won't record them</t>
         </is>
       </c>
       <c r="E617" s="1" t="n"/>
@@ -12296,17 +12296,17 @@
       <c r="A618" s="1" t="n"/>
       <c r="B618" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellEmpty</t>
+          <t>UI.Artifact.AllIndustry</t>
         </is>
       </c>
       <c r="C618" s="6" t="inlineStr">
         <is>
-          <t>보유 칸을 우클릭해 담으세요 — 즉시 판매가로 바로 팝니다. 비싸게 팔려면 Ctrl+우클릭(경매)</t>
+          <t>전 산업</t>
         </is>
       </c>
       <c r="D618" s="6" t="inlineStr">
         <is>
-          <t>Right-click owned artifacts to add — they sell instantly. Ctrl+right-click to list on the auction for more</t>
+          <t>All industries</t>
         </is>
       </c>
       <c r="E618" s="1" t="n"/>
@@ -12315,17 +12315,17 @@
       <c r="A619" s="1" t="n"/>
       <c r="B619" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellUncollected</t>
+          <t>UI.Artifact.EffectSpeed</t>
         </is>
       </c>
       <c r="C619" s="6" t="inlineStr">
         <is>
-          <t>주의! 도감에 없는 아티팩트 포함 — 팔면 도감에 남지 않습니다</t>
+          <t>{0} 작업속도 +{1}</t>
         </is>
       </c>
       <c r="D619" s="6" t="inlineStr">
         <is>
-          <t>Caution! Includes artifacts not in your codex — selling won't record them</t>
+          <t>{0} work speed +{1}</t>
         </is>
       </c>
       <c r="E619" s="1" t="n"/>
@@ -12334,17 +12334,17 @@
       <c r="A620" s="1" t="n"/>
       <c r="B620" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.AllIndustry</t>
+          <t>UI.Artifact.EffectYield</t>
         </is>
       </c>
       <c r="C620" s="6" t="inlineStr">
         <is>
-          <t>전 산업</t>
+          <t>{0} 산출량 +{1}</t>
         </is>
       </c>
       <c r="D620" s="6" t="inlineStr">
         <is>
-          <t>All industries</t>
+          <t>{0} yield +{1}</t>
         </is>
       </c>
       <c r="E620" s="1" t="n"/>
@@ -12353,17 +12353,17 @@
       <c r="A621" s="1" t="n"/>
       <c r="B621" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectSpeed</t>
+          <t>UI.Artifact.EffectAppraise</t>
         </is>
       </c>
       <c r="C621" s="6" t="inlineStr">
         <is>
-          <t>{0} 작업속도 +{1}</t>
+          <t>감정 비용 −{0}</t>
         </is>
       </c>
       <c r="D621" s="6" t="inlineStr">
         <is>
-          <t>{0} work speed +{1}</t>
+          <t>Appraisal cost −{0}</t>
         </is>
       </c>
       <c r="E621" s="1" t="n"/>
@@ -12372,17 +12372,17 @@
       <c r="A622" s="1" t="n"/>
       <c r="B622" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectYield</t>
+          <t>UI.Artifact.EffectRelic</t>
         </is>
       </c>
       <c r="C622" s="6" t="inlineStr">
         <is>
-          <t>{0} 산출량 +{1}</t>
+          <t>유물 발견 확률 +{0}</t>
         </is>
       </c>
       <c r="D622" s="6" t="inlineStr">
         <is>
-          <t>{0} yield +{1}</t>
+          <t>Relic find chance +{0}</t>
         </is>
       </c>
       <c r="E622" s="1" t="n"/>
@@ -12391,17 +12391,17 @@
       <c r="A623" s="1" t="n"/>
       <c r="B623" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectAppraise</t>
+          <t>UI.Artifact.Window</t>
         </is>
       </c>
       <c r="C623" s="6" t="inlineStr">
         <is>
-          <t>감정 비용 −{0}</t>
+          <t>아티팩트 — 도감에 장착</t>
         </is>
       </c>
       <c r="D623" s="6" t="inlineStr">
         <is>
-          <t>Appraisal cost −{0}</t>
+          <t>Artifact — Place in Codex</t>
         </is>
       </c>
       <c r="E623" s="1" t="n"/>
@@ -12410,17 +12410,17 @@
       <c r="A624" s="1" t="n"/>
       <c r="B624" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EffectRelic</t>
+          <t>UI.Artifact.AlreadyEquipped</t>
         </is>
       </c>
       <c r="C624" s="6" t="inlineStr">
         <is>
-          <t>유물 발견 확률 +{0}</t>
+          <t>이미 도감에 장착함</t>
         </is>
       </c>
       <c r="D624" s="6" t="inlineStr">
         <is>
-          <t>Relic find chance +{0}</t>
+          <t>Already in Codex</t>
         </is>
       </c>
       <c r="E624" s="1" t="n"/>
@@ -12429,17 +12429,17 @@
       <c r="A625" s="1" t="n"/>
       <c r="B625" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.Window</t>
+          <t>UI.Artifact.OpenCodex</t>
         </is>
       </c>
       <c r="C625" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 — 도감에 장착</t>
+          <t>도감 보기</t>
         </is>
       </c>
       <c r="D625" s="6" t="inlineStr">
         <is>
-          <t>Artifact — Place in Codex</t>
+          <t>View Codex</t>
         </is>
       </c>
       <c r="E625" s="1" t="n"/>
@@ -12448,17 +12448,17 @@
       <c r="A626" s="1" t="n"/>
       <c r="B626" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.AlreadyEquipped</t>
+          <t>UI.Artifact.EquipHint</t>
         </is>
       </c>
       <c r="C626" s="6" t="inlineStr">
         <is>
-          <t>이미 도감에 장착함</t>
+          <t>장착하면 효과가 켜집니다 — 번호마다 1개, 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D626" s="6" t="inlineStr">
         <is>
-          <t>Already in Codex</t>
+          <t>Placing turns its effect on — one per kind, and it can't be undone</t>
         </is>
       </c>
       <c r="E626" s="1" t="n"/>
@@ -12467,17 +12467,17 @@
       <c r="A627" s="1" t="n"/>
       <c r="B627" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.OpenCodex</t>
+          <t>UI.Artifact.SellHint</t>
         </is>
       </c>
       <c r="C627" s="6" t="inlineStr">
         <is>
-          <t>도감 보기</t>
+          <t>남는 것은 우클릭 즉시 판매 · Ctrl+우클릭 경매</t>
         </is>
       </c>
       <c r="D627" s="6" t="inlineStr">
         <is>
-          <t>View Codex</t>
+          <t>Right-click extras to sell · Ctrl+right-click to auction</t>
         </is>
       </c>
       <c r="E627" s="1" t="n"/>
@@ -12486,17 +12486,17 @@
       <c r="A628" s="1" t="n"/>
       <c r="B628" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.EquipHint</t>
+          <t>UI.Artifact.NoLock</t>
         </is>
       </c>
       <c r="C628" s="6" t="inlineStr">
         <is>
-          <t>장착하면 효과가 켜집니다 — 번호마다 1개, 되돌릴 수 없습니다</t>
+          <t>아티팩트는 아직 잠글 수 없습니다</t>
         </is>
       </c>
       <c r="D628" s="6" t="inlineStr">
         <is>
-          <t>Placing turns its effect on — one per kind, and it can't be undone</t>
+          <t>Artifacts can't be locked yet</t>
         </is>
       </c>
       <c r="E628" s="1" t="n"/>
@@ -12505,17 +12505,17 @@
       <c r="A629" s="1" t="n"/>
       <c r="B629" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.SellHint</t>
+          <t>UI.Artifact.NoMove</t>
         </is>
       </c>
       <c r="C629" s="6" t="inlineStr">
         <is>
-          <t>남는 것은 우클릭 즉시 판매 · Ctrl+우클릭 경매</t>
+          <t>아티팩트 칸은 아직 옮길 수 없습니다</t>
         </is>
       </c>
       <c r="D629" s="6" t="inlineStr">
         <is>
-          <t>Right-click extras to sell · Ctrl+right-click to auction</t>
+          <t>Artifact slots can't be moved yet</t>
         </is>
       </c>
       <c r="E629" s="1" t="n"/>
@@ -12524,17 +12524,17 @@
       <c r="A630" s="1" t="n"/>
       <c r="B630" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.NoLock</t>
+          <t>UI.Sell.KindArtifact</t>
         </is>
       </c>
       <c r="C630" s="6" t="inlineStr">
         <is>
-          <t>아티팩트는 아직 잠글 수 없습니다</t>
+          <t>아티팩트 판매 {0}종</t>
         </is>
       </c>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>Artifacts can't be locked yet</t>
+          <t>Sell Artifacts ({0})</t>
         </is>
       </c>
       <c r="E630" s="1" t="n"/>
@@ -12543,17 +12543,17 @@
       <c r="A631" s="1" t="n"/>
       <c r="B631" s="6" t="inlineStr">
         <is>
-          <t>UI.Artifact.NoMove</t>
+          <t>UI.Sell.ArtifactNoShard</t>
         </is>
       </c>
       <c r="C631" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 칸은 아직 옮길 수 없습니다</t>
+          <t>아티팩트는 아직 마석으로 분해할 수 없습니다 — 분해는 장비만</t>
         </is>
       </c>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>Artifact slots can't be moved yet</t>
+          <t>Artifacts can't be disassembled into shards yet — gear only</t>
         </is>
       </c>
       <c r="E631" s="1" t="n"/>
@@ -12562,17 +12562,17 @@
       <c r="A632" s="1" t="n"/>
       <c r="B632" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.KindArtifact</t>
+          <t>UI.Auction.SortPriceAsc</t>
         </is>
       </c>
       <c r="C632" s="6" t="inlineStr">
         <is>
-          <t>아티팩트 판매 {0}종</t>
+          <t>단가 낮은순</t>
         </is>
       </c>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>Sell Artifacts ({0})</t>
+          <t>Price: Low to High</t>
         </is>
       </c>
       <c r="E632" s="1" t="n"/>
@@ -12581,17 +12581,17 @@
       <c r="A633" s="1" t="n"/>
       <c r="B633" s="6" t="inlineStr">
         <is>
-          <t>UI.Sell.ArtifactNoShard</t>
+          <t>UI.Auction.SortPriceDesc</t>
         </is>
       </c>
       <c r="C633" s="6" t="inlineStr">
         <is>
-          <t>아티팩트는 아직 마석으로 분해할 수 없습니다 — 분해는 장비만</t>
+          <t>단가 높은순</t>
         </is>
       </c>
       <c r="D633" s="6" t="inlineStr">
         <is>
-          <t>Artifacts can't be disassembled into shards yet — gear only</t>
+          <t>Price: High to Low</t>
         </is>
       </c>
       <c r="E633" s="1" t="n"/>
@@ -12600,17 +12600,17 @@
       <c r="A634" s="1" t="n"/>
       <c r="B634" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceAsc</t>
+          <t>UI.Auction.SortExpires</t>
         </is>
       </c>
       <c r="C634" s="6" t="inlineStr">
         <is>
-          <t>단가 낮은순</t>
+          <t>마감 임박순</t>
         </is>
       </c>
       <c r="D634" s="6" t="inlineStr">
         <is>
-          <t>Price: Low to High</t>
+          <t>Ending Soonest</t>
         </is>
       </c>
       <c r="E634" s="1" t="n"/>
@@ -12619,17 +12619,17 @@
       <c r="A635" s="1" t="n"/>
       <c r="B635" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortPriceDesc</t>
+          <t>UI.Auction.SortRarity</t>
         </is>
       </c>
       <c r="C635" s="6" t="inlineStr">
         <is>
-          <t>단가 높은순</t>
+          <t>등급 높은순</t>
         </is>
       </c>
       <c r="D635" s="6" t="inlineStr">
         <is>
-          <t>Price: High to Low</t>
+          <t>Rarity: High to Low</t>
         </is>
       </c>
       <c r="E635" s="1" t="n"/>
@@ -12638,17 +12638,17 @@
       <c r="A636" s="1" t="n"/>
       <c r="B636" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortExpires</t>
+          <t>UI.Auction.SortSpeed</t>
         </is>
       </c>
       <c r="C636" s="6" t="inlineStr">
         <is>
-          <t>마감 임박순</t>
+          <t>작업속도 높은순 (장비)</t>
         </is>
       </c>
       <c r="D636" s="6" t="inlineStr">
         <is>
-          <t>Ending Soonest</t>
+          <t>Work Speed (Gear)</t>
         </is>
       </c>
       <c r="E636" s="1" t="n"/>
@@ -12657,17 +12657,17 @@
       <c r="A637" s="1" t="n"/>
       <c r="B637" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortRarity</t>
+          <t>UI.Auction.SortLevel</t>
         </is>
       </c>
       <c r="C637" s="6" t="inlineStr">
         <is>
-          <t>등급 높은순</t>
+          <t>레벨 높은순 (캐릭터)</t>
         </is>
       </c>
       <c r="D637" s="6" t="inlineStr">
         <is>
-          <t>Rarity: High to Low</t>
+          <t>Level (Character)</t>
         </is>
       </c>
       <c r="E637" s="1" t="n"/>
@@ -12676,17 +12676,17 @@
       <c r="A638" s="1" t="n"/>
       <c r="B638" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortSpeed</t>
+          <t>UI.Auction.NeedsCondition</t>
         </is>
       </c>
       <c r="C638" s="6" t="inlineStr">
         <is>
-          <t>작업속도 높은순 (장비)</t>
+          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
         </is>
       </c>
       <c r="D638" s="6" t="inlineStr">
         <is>
-          <t>Work Speed (Gear)</t>
+          <t>Pick a category or enter a name to search</t>
         </is>
       </c>
       <c r="E638" s="1" t="n"/>
@@ -12695,17 +12695,17 @@
       <c r="A639" s="1" t="n"/>
       <c r="B639" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SortLevel</t>
+          <t>UI.Auction.SearchEmpty</t>
         </is>
       </c>
       <c r="C639" s="6" t="inlineStr">
         <is>
-          <t>레벨 높은순 (캐릭터)</t>
+          <t>검색 결과가 없습니다</t>
         </is>
       </c>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>Level (Character)</t>
+          <t>No results</t>
         </is>
       </c>
       <c r="E639" s="1" t="n"/>
@@ -12714,17 +12714,17 @@
       <c r="A640" s="1" t="n"/>
       <c r="B640" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NeedsCondition</t>
+          <t>UI.Auction.SearchPlaceholder</t>
         </is>
       </c>
       <c r="C640" s="6" t="inlineStr">
         <is>
-          <t>분류를 고르거나 이름을 넣어 검색하세요</t>
+          <t>아이템 이름</t>
         </is>
       </c>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>Pick a category or enter a name to search</t>
+          <t>Item name</t>
         </is>
       </c>
       <c r="E640" s="1" t="n"/>
@@ -12733,17 +12733,17 @@
       <c r="A641" s="1" t="n"/>
       <c r="B641" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchEmpty</t>
+          <t>UI.Auction.SearchHint</t>
         </is>
       </c>
       <c r="C641" s="6" t="inlineStr">
         <is>
-          <t>검색 결과가 없습니다</t>
+          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
         </is>
       </c>
       <c r="D641" s="6" t="inlineStr">
         <is>
-          <t>No results</t>
+          <t>[Search] — searches with the category and options</t>
         </is>
       </c>
       <c r="E641" s="1" t="n"/>
@@ -12752,17 +12752,17 @@
       <c r="A642" s="1" t="n"/>
       <c r="B642" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchPlaceholder</t>
+          <t>UI.Auction.All</t>
         </is>
       </c>
       <c r="C642" s="6" t="inlineStr">
         <is>
-          <t>아이템 이름</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="D642" s="6" t="inlineStr">
         <is>
-          <t>Item name</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E642" s="1" t="n"/>
@@ -12771,17 +12771,17 @@
       <c r="A643" s="1" t="n"/>
       <c r="B643" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchHint</t>
+          <t>UI.Auction.OrHigher</t>
         </is>
       </c>
       <c r="C643" s="6" t="inlineStr">
         <is>
-          <t>[검색] — 분류·옵션과 함께 조회합니다</t>
+          <t>{0} 이상</t>
         </is>
       </c>
       <c r="D643" s="6" t="inlineStr">
         <is>
-          <t>[Search] — searches with the category and options</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E643" s="1" t="n"/>
@@ -12790,17 +12790,17 @@
       <c r="A644" s="1" t="n"/>
       <c r="B644" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.All</t>
+          <t>UI.Auction.NodeItem</t>
         </is>
       </c>
       <c r="C644" s="6" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D644" s="6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="E644" s="1" t="n"/>
@@ -12809,17 +12809,17 @@
       <c r="A645" s="1" t="n"/>
       <c r="B645" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrHigher</t>
+          <t>UI.Auction.ItemWord</t>
         </is>
       </c>
       <c r="C645" s="6" t="inlineStr">
         <is>
-          <t>{0} 이상</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>item</t>
         </is>
       </c>
       <c r="E645" s="1" t="n"/>
@@ -12828,17 +12828,17 @@
       <c r="A646" s="1" t="n"/>
       <c r="B646" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NodeItem</t>
+          <t>UI.Auction.NoSuchKind</t>
         </is>
       </c>
       <c r="C646" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
         </is>
       </c>
       <c r="D646" s="6" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>There's no {1} named '{0}'.</t>
         </is>
       </c>
       <c r="E646" s="1" t="n"/>
@@ -12847,17 +12847,17 @@
       <c r="A647" s="1" t="n"/>
       <c r="B647" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ItemWord</t>
+          <t>UI.Auction.PriceRange</t>
         </is>
       </c>
       <c r="C647" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>단가 {0} ~ {1}</t>
         </is>
       </c>
       <c r="D647" s="6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>Price {0} ~ {1}</t>
         </is>
       </c>
       <c r="E647" s="1" t="n"/>
@@ -12866,17 +12866,17 @@
       <c r="A648" s="1" t="n"/>
       <c r="B648" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoSuchKind</t>
+          <t>UI.Auction.AttrSpeed</t>
         </is>
       </c>
       <c r="C648" s="6" t="inlineStr">
         <is>
-          <t>'{0}'(이)라는 {1}이(가) 없습니다.</t>
+          <t>작업속도</t>
         </is>
       </c>
       <c r="D648" s="6" t="inlineStr">
         <is>
-          <t>There's no {1} named '{0}'.</t>
+          <t>Work Speed</t>
         </is>
       </c>
       <c r="E648" s="1" t="n"/>
@@ -12885,17 +12885,17 @@
       <c r="A649" s="1" t="n"/>
       <c r="B649" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceRange</t>
+          <t>UI.Auction.AttrEnchantSpeed</t>
         </is>
       </c>
       <c r="C649" s="6" t="inlineStr">
         <is>
-          <t>단가 {0} ~ {1}</t>
+          <t>인챈트 속도 합</t>
         </is>
       </c>
       <c r="D649" s="6" t="inlineStr">
         <is>
-          <t>Price {0} ~ {1}</t>
+          <t>Enchant Speed Total</t>
         </is>
       </c>
       <c r="E649" s="1" t="n"/>
@@ -12904,17 +12904,17 @@
       <c r="A650" s="1" t="n"/>
       <c r="B650" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrSpeed</t>
+          <t>UI.Auction.AttrEnchantExp</t>
         </is>
       </c>
       <c r="C650" s="6" t="inlineStr">
         <is>
-          <t>작업속도</t>
+          <t>인챈트 경험치 합</t>
         </is>
       </c>
       <c r="D650" s="6" t="inlineStr">
         <is>
-          <t>Work Speed</t>
+          <t>Enchant EXP Total</t>
         </is>
       </c>
       <c r="E650" s="1" t="n"/>
@@ -12923,17 +12923,17 @@
       <c r="A651" s="1" t="n"/>
       <c r="B651" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantSpeed</t>
+          <t>UI.Auction.EnchantAtLeast</t>
         </is>
       </c>
       <c r="C651" s="6" t="inlineStr">
         <is>
-          <t>인챈트 속도 합</t>
+          <t>인챈트 {0}↑</t>
         </is>
       </c>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total</t>
+          <t>Enchant {0}↑</t>
         </is>
       </c>
       <c r="E651" s="1" t="n"/>
@@ -12942,17 +12942,17 @@
       <c r="A652" s="1" t="n"/>
       <c r="B652" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AttrEnchantExp</t>
+          <t>UI.Auction.AptitudeAtLeast</t>
         </is>
       </c>
       <c r="C652" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합</t>
+          <t>{0} 적성 {1}↑</t>
         </is>
       </c>
       <c r="D652" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total</t>
+          <t>{0} Aptitude {1}↑</t>
         </is>
       </c>
       <c r="E652" s="1" t="n"/>
@@ -12961,17 +12961,17 @@
       <c r="A653" s="1" t="n"/>
       <c r="B653" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantAtLeast</t>
+          <t>UI.Auction.WaitSearch</t>
         </is>
       </c>
       <c r="C653" s="6" t="inlineStr">
         <is>
-          <t>인챈트 {0}↑</t>
+          <t>경매장 검색</t>
         </is>
       </c>
       <c r="D653" s="6" t="inlineStr">
         <is>
-          <t>Enchant {0}↑</t>
+          <t>Auction Search</t>
         </is>
       </c>
       <c r="E653" s="1" t="n"/>
@@ -12980,17 +12980,17 @@
       <c r="A654" s="1" t="n"/>
       <c r="B654" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AptitudeAtLeast</t>
+          <t>UI.Auction.WaitPrice</t>
         </is>
       </c>
       <c r="C654" s="6" t="inlineStr">
         <is>
-          <t>{0} 적성 {1}↑</t>
+          <t>시세 확인</t>
         </is>
       </c>
       <c r="D654" s="6" t="inlineStr">
         <is>
-          <t>{0} Aptitude {1}↑</t>
+          <t>Price Check</t>
         </is>
       </c>
       <c r="E654" s="1" t="n"/>
@@ -12999,17 +12999,17 @@
       <c r="A655" s="1" t="n"/>
       <c r="B655" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitSearch</t>
+          <t>UI.Auction.BuyWhatMulti</t>
         </is>
       </c>
       <c r="C655" s="6" t="inlineStr">
         <is>
-          <t>경매장 검색</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
         </is>
       </c>
       <c r="D655" s="6" t="inlineStr">
         <is>
-          <t>Auction Search</t>
+          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
         </is>
       </c>
       <c r="E655" s="1" t="n"/>
@@ -13018,17 +13018,17 @@
       <c r="A656" s="1" t="n"/>
       <c r="B656" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitPrice</t>
+          <t>UI.Auction.AfterBuy</t>
         </is>
       </c>
       <c r="C656" s="6" t="inlineStr">
         <is>
-          <t>시세 확인</t>
+          <t>구매 후</t>
         </is>
       </c>
       <c r="D656" s="6" t="inlineStr">
         <is>
-          <t>Price Check</t>
+          <t>After Purchase</t>
         </is>
       </c>
       <c r="E656" s="1" t="n"/>
@@ -13037,17 +13037,17 @@
       <c r="A657" s="1" t="n"/>
       <c r="B657" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyWhatMulti</t>
+          <t>UI.Auction.BuyNote</t>
         </is>
       </c>
       <c r="C657" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; {1}개 — 개당 {2} G · 총 {3} G</t>
+          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
         </is>
       </c>
       <c r="D657" s="6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;{0}&lt;/b&gt; x{1} — {2} G each · {3} G total</t>
+          <t>You buy the whole listing · purchases arrive by mail</t>
         </is>
       </c>
       <c r="E657" s="1" t="n"/>
@@ -13056,17 +13056,17 @@
       <c r="A658" s="1" t="n"/>
       <c r="B658" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AfterBuy</t>
+          <t>UI.Auction.WaitBuy</t>
         </is>
       </c>
       <c r="C658" s="6" t="inlineStr">
         <is>
-          <t>구매 후</t>
+          <t>경매장 구매</t>
         </is>
       </c>
       <c r="D658" s="6" t="inlineStr">
         <is>
-          <t>After Purchase</t>
+          <t>Auction Purchase</t>
         </is>
       </c>
       <c r="E658" s="1" t="n"/>
@@ -13075,17 +13075,17 @@
       <c r="A659" s="1" t="n"/>
       <c r="B659" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.BuyNote</t>
+          <t>UI.Auction.Bought</t>
         </is>
       </c>
       <c r="C659" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 · 산 물건은 우편으로 받습니다</t>
+          <t>구매했습니다. 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D659" s="6" t="inlineStr">
         <is>
-          <t>You buy the whole listing · purchases arrive by mail</t>
+          <t>Purchased. Claim it from your mailbox.</t>
         </is>
       </c>
       <c r="E659" s="1" t="n"/>
@@ -13094,17 +13094,17 @@
       <c r="A660" s="1" t="n"/>
       <c r="B660" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitBuy</t>
+          <t>UI.Auction.SearchCount</t>
         </is>
       </c>
       <c r="C660" s="6" t="inlineStr">
         <is>
-          <t>경매장 구매</t>
+          <t>검색 결과 {0}</t>
         </is>
       </c>
       <c r="D660" s="6" t="inlineStr">
         <is>
-          <t>Auction Purchase</t>
+          <t>Results {0}</t>
         </is>
       </c>
       <c r="E660" s="1" t="n"/>
@@ -13113,17 +13113,17 @@
       <c r="A661" s="1" t="n"/>
       <c r="B661" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Bought</t>
+          <t>UI.Auction.HeadItemRarity</t>
         </is>
       </c>
       <c r="C661" s="6" t="inlineStr">
         <is>
-          <t>구매했습니다. 우편함에서 받아 주세요.</t>
+          <t>아이템 (등급)</t>
         </is>
       </c>
       <c r="D661" s="6" t="inlineStr">
         <is>
-          <t>Purchased. Claim it from your mailbox.</t>
+          <t>Item (Rarity)</t>
         </is>
       </c>
       <c r="E661" s="1" t="n"/>
@@ -13132,17 +13132,17 @@
       <c r="A662" s="1" t="n"/>
       <c r="B662" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SearchCount</t>
+          <t>UI.Auction.Cases</t>
         </is>
       </c>
       <c r="C662" s="6" t="inlineStr">
         <is>
-          <t>검색 결과 {0}</t>
+          <t>{0}건</t>
         </is>
       </c>
       <c r="D662" s="6" t="inlineStr">
         <is>
-          <t>Results {0}</t>
+          <t>{0}</t>
         </is>
       </c>
       <c r="E662" s="1" t="n"/>
@@ -13151,17 +13151,17 @@
       <c r="A663" s="1" t="n"/>
       <c r="B663" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HeadItemRarity</t>
+          <t>UI.Auction.CasesOrMore</t>
         </is>
       </c>
       <c r="C663" s="6" t="inlineStr">
         <is>
-          <t>아이템 (등급)</t>
+          <t>{0}건 이상</t>
         </is>
       </c>
       <c r="D663" s="6" t="inlineStr">
         <is>
-          <t>Item (Rarity)</t>
+          <t>{0}+</t>
         </is>
       </c>
       <c r="E663" s="1" t="n"/>
@@ -13170,17 +13170,17 @@
       <c r="A664" s="1" t="n"/>
       <c r="B664" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Cases</t>
+          <t>UI.Auction.TypeSold</t>
         </is>
       </c>
       <c r="C664" s="6" t="inlineStr">
         <is>
-          <t>{0}건</t>
+          <t>판매 완료</t>
         </is>
       </c>
       <c r="D664" s="6" t="inlineStr">
         <is>
-          <t>{0}</t>
+          <t>Sold</t>
         </is>
       </c>
       <c r="E664" s="1" t="n"/>
@@ -13189,17 +13189,17 @@
       <c r="A665" s="1" t="n"/>
       <c r="B665" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CasesOrMore</t>
+          <t>UI.Auction.TypeBought</t>
         </is>
       </c>
       <c r="C665" s="6" t="inlineStr">
         <is>
-          <t>{0}건 이상</t>
+          <t>구매 완료</t>
         </is>
       </c>
       <c r="D665" s="6" t="inlineStr">
         <is>
-          <t>{0}+</t>
+          <t>Bought</t>
         </is>
       </c>
       <c r="E665" s="1" t="n"/>
@@ -13208,17 +13208,17 @@
       <c r="A666" s="1" t="n"/>
       <c r="B666" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeSold</t>
+          <t>UI.Auction.TypeExpired</t>
         </is>
       </c>
       <c r="C666" s="6" t="inlineStr">
         <is>
-          <t>판매 완료</t>
+          <t>기간 만료</t>
         </is>
       </c>
       <c r="D666" s="6" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="E666" s="1" t="n"/>
@@ -13227,17 +13227,17 @@
       <c r="A667" s="1" t="n"/>
       <c r="B667" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeBought</t>
+          <t>UI.Auction.TypeCancelled</t>
         </is>
       </c>
       <c r="C667" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="D667" s="6" t="inlineStr">
         <is>
-          <t>Bought</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E667" s="1" t="n"/>
@@ -13246,17 +13246,17 @@
       <c r="A668" s="1" t="n"/>
       <c r="B668" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeExpired</t>
+          <t>UI.Auction.TypeReturned</t>
         </is>
       </c>
       <c r="C668" s="6" t="inlineStr">
         <is>
-          <t>기간 만료</t>
+          <t>반환</t>
         </is>
       </c>
       <c r="D668" s="6" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="E668" s="1" t="n"/>
@@ -13265,17 +13265,17 @@
       <c r="A669" s="1" t="n"/>
       <c r="B669" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeCancelled</t>
+          <t>UI.Auction.PeriodToday</t>
         </is>
       </c>
       <c r="C669" s="6" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="D669" s="6" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="E669" s="1" t="n"/>
@@ -13284,17 +13284,17 @@
       <c r="A670" s="1" t="n"/>
       <c r="B670" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TypeReturned</t>
+          <t>UI.Auction.Period7</t>
         </is>
       </c>
       <c r="C670" s="6" t="inlineStr">
         <is>
-          <t>반환</t>
+          <t>최근 7일</t>
         </is>
       </c>
       <c r="D670" s="6" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Last 7 Days</t>
         </is>
       </c>
       <c r="E670" s="1" t="n"/>
@@ -13303,17 +13303,17 @@
       <c r="A671" s="1" t="n"/>
       <c r="B671" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PeriodToday</t>
+          <t>UI.Auction.Period30</t>
         </is>
       </c>
       <c r="C671" s="6" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>최근 30일</t>
         </is>
       </c>
       <c r="D671" s="6" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Last 30 Days</t>
         </is>
       </c>
       <c r="E671" s="1" t="n"/>
@@ -13322,17 +13322,17 @@
       <c r="A672" s="1" t="n"/>
       <c r="B672" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period7</t>
+          <t>UI.Auction.HistoryPlaceholder</t>
         </is>
       </c>
       <c r="C672" s="6" t="inlineStr">
         <is>
-          <t>최근 7일</t>
+          <t>기록에서 찾을 아이템 이름</t>
         </is>
       </c>
       <c r="D672" s="6" t="inlineStr">
         <is>
-          <t>Last 7 Days</t>
+          <t>Item name to find in history</t>
         </is>
       </c>
       <c r="E672" s="1" t="n"/>
@@ -13341,17 +13341,17 @@
       <c r="A673" s="1" t="n"/>
       <c r="B673" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Period30</t>
+          <t>UI.Auction.HistoryHint</t>
         </is>
       </c>
       <c r="C673" s="6" t="inlineStr">
         <is>
-          <t>최근 30일</t>
+          <t>치는 대로 아래 기록을 거릅니다</t>
         </is>
       </c>
       <c r="D673" s="6" t="inlineStr">
         <is>
-          <t>Last 30 Days</t>
+          <t>Filters the history below as you type</t>
         </is>
       </c>
       <c r="E673" s="1" t="n"/>
@@ -13360,17 +13360,17 @@
       <c r="A674" s="1" t="n"/>
       <c r="B674" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryPlaceholder</t>
+          <t>UI.Auction.WaitHistory</t>
         </is>
       </c>
       <c r="C674" s="6" t="inlineStr">
         <is>
-          <t>기록에서 찾을 아이템 이름</t>
+          <t>거래 기록</t>
         </is>
       </c>
       <c r="D674" s="6" t="inlineStr">
         <is>
-          <t>Item name to find in history</t>
+          <t>Trade History</t>
         </is>
       </c>
       <c r="E674" s="1" t="n"/>
@@ -13379,17 +13379,17 @@
       <c r="A675" s="1" t="n"/>
       <c r="B675" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryHint</t>
+          <t>UI.Auction.HistoryEmpty</t>
         </is>
       </c>
       <c r="C675" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 기록을 거릅니다</t>
+          <t>이 기간에 거래 기록이 없습니다</t>
         </is>
       </c>
       <c r="D675" s="6" t="inlineStr">
         <is>
-          <t>Filters the history below as you type</t>
+          <t>No trades in this period</t>
         </is>
       </c>
       <c r="E675" s="1" t="n"/>
@@ -13398,17 +13398,17 @@
       <c r="A676" s="1" t="n"/>
       <c r="B676" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitHistory</t>
+          <t>UI.Auction.HistoryNoMatch</t>
         </is>
       </c>
       <c r="C676" s="6" t="inlineStr">
         <is>
-          <t>거래 기록</t>
+          <t>이름이 맞는 기록이 없습니다</t>
         </is>
       </c>
       <c r="D676" s="6" t="inlineStr">
         <is>
-          <t>Trade History</t>
+          <t>No records match that name</t>
         </is>
       </c>
       <c r="E676" s="1" t="n"/>
@@ -13417,17 +13417,17 @@
       <c r="A677" s="1" t="n"/>
       <c r="B677" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryEmpty</t>
+          <t>UI.Auction.HistoryCount</t>
         </is>
       </c>
       <c r="C677" s="6" t="inlineStr">
         <is>
-          <t>이 기간에 거래 기록이 없습니다</t>
+          <t>기록 {0}건</t>
         </is>
       </c>
       <c r="D677" s="6" t="inlineStr">
         <is>
-          <t>No trades in this period</t>
+          <t>{0} records</t>
         </is>
       </c>
       <c r="E677" s="1" t="n"/>
@@ -13436,17 +13436,17 @@
       <c r="A678" s="1" t="n"/>
       <c r="B678" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNoMatch</t>
+          <t>UI.Auction.OrMore</t>
         </is>
       </c>
       <c r="C678" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 기록이 없습니다</t>
+          <t>이상</t>
         </is>
       </c>
       <c r="D678" s="6" t="inlineStr">
         <is>
-          <t>No records match that name</t>
+          <t>or more</t>
         </is>
       </c>
       <c r="E678" s="1" t="n"/>
@@ -13455,17 +13455,17 @@
       <c r="A679" s="1" t="n"/>
       <c r="B679" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryCount</t>
+          <t>UI.Auction.GoldReceived</t>
         </is>
       </c>
       <c r="C679" s="6" t="inlineStr">
         <is>
-          <t>기록 {0}건</t>
+          <t>받은 골드</t>
         </is>
       </c>
       <c r="D679" s="6" t="inlineStr">
         <is>
-          <t>{0} records</t>
+          <t>Gold Received</t>
         </is>
       </c>
       <c r="E679" s="1" t="n"/>
@@ -13474,17 +13474,17 @@
       <c r="A680" s="1" t="n"/>
       <c r="B680" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.OrMore</t>
+          <t>UI.Auction.GoldSpent</t>
         </is>
       </c>
       <c r="C680" s="6" t="inlineStr">
         <is>
-          <t>이상</t>
+          <t>쓴 골드</t>
         </is>
       </c>
       <c r="D680" s="6" t="inlineStr">
         <is>
-          <t>or more</t>
+          <t>Gold Spent</t>
         </is>
       </c>
       <c r="E680" s="1" t="n"/>
@@ -13493,17 +13493,17 @@
       <c r="A681" s="1" t="n"/>
       <c r="B681" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldReceived</t>
+          <t>UI.Auction.HistoryNote</t>
         </is>
       </c>
       <c r="C681" s="6" t="inlineStr">
         <is>
-          <t>받은 골드</t>
+          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
         </is>
       </c>
       <c r="D681" s="6" t="inlineStr">
         <is>
-          <t>Gold Received</t>
+          <t>Items, proceeds and refunds all go to the mailbox</t>
         </is>
       </c>
       <c r="E681" s="1" t="n"/>
@@ -13512,17 +13512,17 @@
       <c r="A682" s="1" t="n"/>
       <c r="B682" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoldSpent</t>
+          <t>UI.Auction.Fee</t>
         </is>
       </c>
       <c r="C682" s="6" t="inlineStr">
         <is>
-          <t>쓴 골드</t>
+          <t>수수료 {0}</t>
         </is>
       </c>
       <c r="D682" s="6" t="inlineStr">
         <is>
-          <t>Gold Spent</t>
+          <t>Fee {0}</t>
         </is>
       </c>
       <c r="E682" s="1" t="n"/>
@@ -13531,17 +13531,17 @@
       <c r="A683" s="1" t="n"/>
       <c r="B683" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HistoryNote</t>
+          <t>UI.Auction.DestProceeds</t>
         </is>
       </c>
       <c r="C683" s="6" t="inlineStr">
         <is>
-          <t>물건 · 대금 · 환급은 모두 우편으로 갑니다</t>
+          <t>대금 → 우편</t>
         </is>
       </c>
       <c r="D683" s="6" t="inlineStr">
         <is>
-          <t>Items, proceeds and refunds all go to the mailbox</t>
+          <t>Proceeds → Mail</t>
         </is>
       </c>
       <c r="E683" s="1" t="n"/>
@@ -13550,17 +13550,17 @@
       <c r="A684" s="1" t="n"/>
       <c r="B684" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Fee</t>
+          <t>UI.Auction.DestItem</t>
         </is>
       </c>
       <c r="C684" s="6" t="inlineStr">
         <is>
-          <t>수수료 {0}</t>
+          <t>물건 → 우편</t>
         </is>
       </c>
       <c r="D684" s="6" t="inlineStr">
         <is>
-          <t>Fee {0}</t>
+          <t>Item → Mail</t>
         </is>
       </c>
       <c r="E684" s="1" t="n"/>
@@ -13569,17 +13569,17 @@
       <c r="A685" s="1" t="n"/>
       <c r="B685" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestProceeds</t>
+          <t>UI.Auction.DestItemFee</t>
         </is>
       </c>
       <c r="C685" s="6" t="inlineStr">
         <is>
-          <t>대금 → 우편</t>
+          <t>물건 · 등록비 → 우편</t>
         </is>
       </c>
       <c r="D685" s="6" t="inlineStr">
         <is>
-          <t>Proceeds → Mail</t>
+          <t>Item · Fee → Mail</t>
         </is>
       </c>
       <c r="E685" s="1" t="n"/>
@@ -13588,17 +13588,17 @@
       <c r="A686" s="1" t="n"/>
       <c r="B686" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItem</t>
+          <t>UI.Auction.MyPlaceholder</t>
         </is>
       </c>
       <c r="C686" s="6" t="inlineStr">
         <is>
-          <t>물건 → 우편</t>
+          <t>판매 중인 아이템 이름</t>
         </is>
       </c>
       <c r="D686" s="6" t="inlineStr">
         <is>
-          <t>Item → Mail</t>
+          <t>Name of an item you're selling</t>
         </is>
       </c>
       <c r="E686" s="1" t="n"/>
@@ -13607,17 +13607,17 @@
       <c r="A687" s="1" t="n"/>
       <c r="B687" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.DestItemFee</t>
+          <t>UI.Auction.MyHint</t>
         </is>
       </c>
       <c r="C687" s="6" t="inlineStr">
         <is>
-          <t>물건 · 등록비 → 우편</t>
+          <t>치는 대로 아래 목록을 거릅니다</t>
         </is>
       </c>
       <c r="D687" s="6" t="inlineStr">
         <is>
-          <t>Item · Fee → Mail</t>
+          <t>Filters the list below as you type</t>
         </is>
       </c>
       <c r="E687" s="1" t="n"/>
@@ -13626,17 +13626,17 @@
       <c r="A688" s="1" t="n"/>
       <c r="B688" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyPlaceholder</t>
+          <t>UI.Auction.ListingPeriod</t>
         </is>
       </c>
       <c r="C688" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 아이템 이름</t>
+          <t>등록 기간</t>
         </is>
       </c>
       <c r="D688" s="6" t="inlineStr">
         <is>
-          <t>Name of an item you're selling</t>
+          <t>Listing Period</t>
         </is>
       </c>
       <c r="E688" s="1" t="n"/>
@@ -13645,17 +13645,17 @@
       <c r="A689" s="1" t="n"/>
       <c r="B689" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyHint</t>
+          <t>UI.Auction.HoursOnly</t>
         </is>
       </c>
       <c r="C689" s="6" t="inlineStr">
         <is>
-          <t>치는 대로 아래 목록을 거릅니다</t>
+          <t>{0}시간</t>
         </is>
       </c>
       <c r="D689" s="6" t="inlineStr">
         <is>
-          <t>Filters the list below as you type</t>
+          <t>{0}h</t>
         </is>
       </c>
       <c r="E689" s="1" t="n"/>
@@ -13664,17 +13664,17 @@
       <c r="A690" s="1" t="n"/>
       <c r="B690" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingPeriod</t>
+          <t>UI.Auction.ListingFee</t>
         </is>
       </c>
       <c r="C690" s="6" t="inlineStr">
         <is>
-          <t>등록 기간</t>
+          <t>등록비</t>
         </is>
       </c>
       <c r="D690" s="6" t="inlineStr">
         <is>
-          <t>Listing Period</t>
+          <t>Listing Fee</t>
         </is>
       </c>
       <c r="E690" s="1" t="n"/>
@@ -13683,17 +13683,17 @@
       <c r="A691" s="1" t="n"/>
       <c r="B691" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.HoursOnly</t>
+          <t>UI.Auction.RefundOnExpiry</t>
         </is>
       </c>
       <c r="C691" s="6" t="inlineStr">
         <is>
-          <t>{0}시간</t>
+          <t>(만료되면 돌려받음)</t>
         </is>
       </c>
       <c r="D691" s="6" t="inlineStr">
         <is>
-          <t>{0}h</t>
+          <t>(refunded on expiry)</t>
         </is>
       </c>
       <c r="E691" s="1" t="n"/>
@@ -13702,17 +13702,17 @@
       <c r="A692" s="1" t="n"/>
       <c r="B692" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ListingFee</t>
+          <t>UI.Auction.SaleFee</t>
         </is>
       </c>
       <c r="C692" s="6" t="inlineStr">
         <is>
-          <t>등록비</t>
+          <t>판매 수수료</t>
         </is>
       </c>
       <c r="D692" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee</t>
+          <t>Sale Fee</t>
         </is>
       </c>
       <c r="E692" s="1" t="n"/>
@@ -13721,17 +13721,17 @@
       <c r="A693" s="1" t="n"/>
       <c r="B693" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RefundOnExpiry</t>
+          <t>UI.Auction.WaitMyListings</t>
         </is>
       </c>
       <c r="C693" s="6" t="inlineStr">
         <is>
-          <t>(만료되면 돌려받음)</t>
+          <t>내 매물</t>
         </is>
       </c>
       <c r="D693" s="6" t="inlineStr">
         <is>
-          <t>(refunded on expiry)</t>
+          <t>My Listings</t>
         </is>
       </c>
       <c r="E693" s="1" t="n"/>
@@ -13740,17 +13740,19 @@
       <c r="A694" s="1" t="n"/>
       <c r="B694" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SaleFee</t>
+          <t>UI.Auction.ConfirmCancel</t>
         </is>
       </c>
       <c r="C694" s="6" t="inlineStr">
         <is>
-          <t>판매 수수료</t>
+          <t>{0} 판매를 취소합니다.
+남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
         </is>
       </c>
       <c r="D694" s="6" t="inlineStr">
         <is>
-          <t>Sale Fee</t>
+          <t>Cancel the sale of {0}.
+The item returns by mail, and the listing fee is not refunded.</t>
         </is>
       </c>
       <c r="E694" s="1" t="n"/>
@@ -13759,17 +13761,17 @@
       <c r="A695" s="1" t="n"/>
       <c r="B695" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitMyListings</t>
+          <t>UI.Auction.WaitCancel</t>
         </is>
       </c>
       <c r="C695" s="6" t="inlineStr">
         <is>
-          <t>내 매물</t>
+          <t>판매 취소</t>
         </is>
       </c>
       <c r="D695" s="6" t="inlineStr">
         <is>
-          <t>My Listings</t>
+          <t>Cancel Sale</t>
         </is>
       </c>
       <c r="E695" s="1" t="n"/>
@@ -13778,19 +13780,17 @@
       <c r="A696" s="1" t="n"/>
       <c r="B696" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmCancel</t>
+          <t>UI.Auction.CancelDone</t>
         </is>
       </c>
       <c r="C696" s="6" t="inlineStr">
         <is>
-          <t>{0} 판매를 취소합니다.
-남은 물건은 우편으로 돌아오고, 등록비는 돌려받지 못합니다.</t>
+          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
         </is>
       </c>
       <c r="D696" s="6" t="inlineStr">
         <is>
-          <t>Cancel the sale of {0}.
-The item returns by mail, and the listing fee is not refunded.</t>
+          <t>Sale cancelled. Claim the item from your mailbox.</t>
         </is>
       </c>
       <c r="E696" s="1" t="n"/>
@@ -13799,17 +13799,17 @@
       <c r="A697" s="1" t="n"/>
       <c r="B697" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitCancel</t>
+          <t>UI.Auction.RangeOf</t>
         </is>
       </c>
       <c r="C697" s="6" t="inlineStr">
         <is>
-          <t>판매 취소</t>
+          <t>{0}–{1} / {2}건</t>
         </is>
       </c>
       <c r="D697" s="6" t="inlineStr">
         <is>
-          <t>Cancel Sale</t>
+          <t>{0}–{1} / {2}</t>
         </is>
       </c>
       <c r="E697" s="1" t="n"/>
@@ -13818,17 +13818,17 @@
       <c r="A698" s="1" t="n"/>
       <c r="B698" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CancelDone</t>
+          <t>UI.Auction.MyEmpty</t>
         </is>
       </c>
       <c r="C698" s="6" t="inlineStr">
         <is>
-          <t>판매를 취소했습니다. 물건은 우편함에서 받아 주세요.</t>
+          <t>판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D698" s="6" t="inlineStr">
         <is>
-          <t>Sale cancelled. Claim the item from your mailbox.</t>
+          <t>You have no listings on sale</t>
         </is>
       </c>
       <c r="E698" s="1" t="n"/>
@@ -13837,17 +13837,17 @@
       <c r="A699" s="1" t="n"/>
       <c r="B699" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RangeOf</t>
+          <t>UI.Auction.MyNoMatch</t>
         </is>
       </c>
       <c r="C699" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}건</t>
+          <t>이름이 맞는 매물이 없습니다</t>
         </is>
       </c>
       <c r="D699" s="6" t="inlineStr">
         <is>
-          <t>{0}–{1} / {2}</t>
+          <t>No listings match that name</t>
         </is>
       </c>
       <c r="E699" s="1" t="n"/>
@@ -13856,17 +13856,17 @@
       <c r="A700" s="1" t="n"/>
       <c r="B700" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyEmpty</t>
+          <t>UI.Auction.MyNote</t>
         </is>
       </c>
       <c r="C700" s="6" t="inlineStr">
         <is>
-          <t>판매 중인 매물이 없습니다</t>
+          <t>팔리면 대금은 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D700" s="6" t="inlineStr">
         <is>
-          <t>You have no listings on sale</t>
+          <t>Proceeds arrive by mail when sold</t>
         </is>
       </c>
       <c r="E700" s="1" t="n"/>
@@ -13875,17 +13875,17 @@
       <c r="A701" s="1" t="n"/>
       <c r="B701" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNoMatch</t>
+          <t>UI.Auction.NothingToList</t>
         </is>
       </c>
       <c r="C701" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 매물이 없습니다</t>
+          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
         </is>
       </c>
       <c r="D701" s="6" t="inlineStr">
         <is>
-          <t>No listings match that name</t>
+          <t>You don't have anything that can be listed.</t>
         </is>
       </c>
       <c r="E701" s="1" t="n"/>
@@ -13894,17 +13894,17 @@
       <c r="A702" s="1" t="n"/>
       <c r="B702" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MyNote</t>
+          <t>UI.Auction.NotFound</t>
         </is>
       </c>
       <c r="C702" s="6" t="inlineStr">
         <is>
-          <t>팔리면 대금은 우편으로 옵니다</t>
+          <t>그 물건을 찾지 못했습니다.</t>
         </is>
       </c>
       <c r="D702" s="6" t="inlineStr">
         <is>
-          <t>Proceeds arrive by mail when sold</t>
+          <t>Couldn't find that item.</t>
         </is>
       </c>
       <c r="E702" s="1" t="n"/>
@@ -13913,17 +13913,17 @@
       <c r="A703" s="1" t="n"/>
       <c r="B703" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NothingToList</t>
+          <t>UI.Auction.RegisterWhatItem</t>
         </is>
       </c>
       <c r="C703" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것을 갖고 있지 않습니다.</t>
+          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
         </is>
       </c>
       <c r="D703" s="6" t="inlineStr">
         <is>
-          <t>You don't have anything that can be listed.</t>
+          <t>{0} x{1} at {2} G each ({3} G total)</t>
         </is>
       </c>
       <c r="E703" s="1" t="n"/>
@@ -13932,17 +13932,17 @@
       <c r="A704" s="1" t="n"/>
       <c r="B704" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NotFound</t>
+          <t>UI.Auction.RegisterWhatOne</t>
         </is>
       </c>
       <c r="C704" s="6" t="inlineStr">
         <is>
-          <t>그 물건을 찾지 못했습니다.</t>
+          <t>{0}을(를) {1} G에</t>
         </is>
       </c>
       <c r="D704" s="6" t="inlineStr">
         <is>
-          <t>Couldn't find that item.</t>
+          <t>{0} at {1} G</t>
         </is>
       </c>
       <c r="E704" s="1" t="n"/>
@@ -13951,17 +13951,19 @@
       <c r="A705" s="1" t="n"/>
       <c r="B705" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatItem</t>
+          <t>UI.Auction.ConfirmRegister</t>
         </is>
       </c>
       <c r="C705" s="6" t="inlineStr">
         <is>
-          <t>{0} {1}개를 개당 {2} G(총 {3} G)에</t>
+          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
+등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
         </is>
       </c>
       <c r="D705" s="6" t="inlineStr">
         <is>
-          <t>{0} x{1} at {2} G each ({3} G total)</t>
+          <t>List {0} on the auction? (Instant sell: {1} G)
+The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
         </is>
       </c>
       <c r="E705" s="1" t="n"/>
@@ -13970,17 +13972,17 @@
       <c r="A706" s="1" t="n"/>
       <c r="B706" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterWhatOne</t>
+          <t>UI.Auction.WaitRegister</t>
         </is>
       </c>
       <c r="C706" s="6" t="inlineStr">
         <is>
-          <t>{0}을(를) {1} G에</t>
+          <t>경매 등록</t>
         </is>
       </c>
       <c r="D706" s="6" t="inlineStr">
         <is>
-          <t>{0} at {1} G</t>
+          <t>Auction Listing</t>
         </is>
       </c>
       <c r="E706" s="1" t="n"/>
@@ -13989,19 +13991,19 @@
       <c r="A707" s="1" t="n"/>
       <c r="B707" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ConfirmRegister</t>
+          <t>UI.Auction.Registered</t>
         </is>
       </c>
       <c r="C707" s="6" t="inlineStr">
         <is>
-          <t>{0} 경매에 올립니다. (즉시 판매하면 {1} G)
-등록비 {2} G가 바로 빠집니다 — 취소하면 돌려받지 못하고, 기간이 끝나면 돌려받습니다.</t>
+          <t>등록했습니다. (등록비 {0} G)
+팔리면 대금이 우편으로 옵니다.</t>
         </is>
       </c>
       <c r="D707" s="6" t="inlineStr">
         <is>
-          <t>List {0} on the auction? (Instant sell: {1} G)
-The {2} G listing fee is charged now — it's lost if you cancel, and refunded when the listing expires.</t>
+          <t>Listed. (Fee {0} G)
+Proceeds arrive by mail when sold.</t>
         </is>
       </c>
       <c r="E707" s="1" t="n"/>
@@ -14010,17 +14012,17 @@
       <c r="A708" s="1" t="n"/>
       <c r="B708" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.WaitRegister</t>
+          <t>UI.Auction.ActUnavailable</t>
         </is>
       </c>
       <c r="C708" s="6" t="inlineStr">
         <is>
-          <t>경매 등록</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="D708" s="6" t="inlineStr">
         <is>
-          <t>Auction Listing</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E708" s="1" t="n"/>
@@ -14029,19 +14031,17 @@
       <c r="A709" s="1" t="n"/>
       <c r="B709" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Registered</t>
+          <t>UI.Auction.ActSelected</t>
         </is>
       </c>
       <c r="C709" s="6" t="inlineStr">
         <is>
-          <t>등록했습니다. (등록비 {0} G)
-팔리면 대금이 우편으로 옵니다.</t>
+          <t>선택됨</t>
         </is>
       </c>
       <c r="D709" s="6" t="inlineStr">
         <is>
-          <t>Listed. (Fee {0} G)
-Proceeds arrive by mail when sold.</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="E709" s="1" t="n"/>
@@ -14050,17 +14050,17 @@
       <c r="A710" s="1" t="n"/>
       <c r="B710" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActUnavailable</t>
+          <t>UI.Auction.RegisterEmpty</t>
         </is>
       </c>
       <c r="C710" s="6" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>올릴 수 있는 것이 없습니다</t>
         </is>
       </c>
       <c r="D710" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Nothing to list</t>
         </is>
       </c>
       <c r="E710" s="1" t="n"/>
@@ -14069,17 +14069,17 @@
       <c r="A711" s="1" t="n"/>
       <c r="B711" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ActSelected</t>
+          <t>UI.Auction.RegisterNoMatch</t>
         </is>
       </c>
       <c r="C711" s="6" t="inlineStr">
         <is>
-          <t>선택됨</t>
+          <t>이름이 맞는 것이 없습니다</t>
         </is>
       </c>
       <c r="D711" s="6" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Nothing matches that name</t>
         </is>
       </c>
       <c r="E711" s="1" t="n"/>
@@ -14088,17 +14088,17 @@
       <c r="A712" s="1" t="n"/>
       <c r="B712" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmpty</t>
+          <t>UI.Auction.CantListShort</t>
         </is>
       </c>
       <c r="C712" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 있는 것이 없습니다</t>
+          <t>올릴 수 없음</t>
         </is>
       </c>
       <c r="D712" s="6" t="inlineStr">
         <is>
-          <t>Nothing to list</t>
+          <t>Can't list</t>
         </is>
       </c>
       <c r="E712" s="1" t="n"/>
@@ -14107,17 +14107,17 @@
       <c r="A713" s="1" t="n"/>
       <c r="B713" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterNoMatch</t>
+          <t>UI.Auction.AuctionUnitPrice</t>
         </is>
       </c>
       <c r="C713" s="6" t="inlineStr">
         <is>
-          <t>이름이 맞는 것이 없습니다</t>
+          <t>경매 단가</t>
         </is>
       </c>
       <c r="D713" s="6" t="inlineStr">
         <is>
-          <t>Nothing matches that name</t>
+          <t>Auction Price</t>
         </is>
       </c>
       <c r="E713" s="1" t="n"/>
@@ -14126,17 +14126,17 @@
       <c r="A714" s="1" t="n"/>
       <c r="B714" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CantListShort</t>
+          <t>UI.Auction.CountHelp</t>
         </is>
       </c>
       <c r="C714" s="6" t="inlineStr">
         <is>
-          <t>올릴 수 없음</t>
+          <t>보유 {0}개 · 한 번에 {1}개까지</t>
         </is>
       </c>
       <c r="D714" s="6" t="inlineStr">
         <is>
-          <t>Can't list</t>
+          <t>Owned {0} · up to {1} per listing</t>
         </is>
       </c>
       <c r="E714" s="1" t="n"/>
@@ -14145,17 +14145,17 @@
       <c r="A715" s="1" t="n"/>
       <c r="B715" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionUnitPrice</t>
+          <t>UI.Auction.PriceHelp</t>
         </is>
       </c>
       <c r="C715" s="6" t="inlineStr">
         <is>
-          <t>경매 단가</t>
+          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
         </is>
       </c>
       <c r="D715" s="6" t="inlineStr">
         <is>
-          <t>Auction Price</t>
+          <t>From {0} G (instant sell price) ~ {1} G</t>
         </is>
       </c>
       <c r="E715" s="1" t="n"/>
@@ -14164,17 +14164,17 @@
       <c r="A716" s="1" t="n"/>
       <c r="B716" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CountHelp</t>
+          <t>UI.Auction.FormHint</t>
         </is>
       </c>
       <c r="C716" s="6" t="inlineStr">
         <is>
-          <t>보유 {0}개 · 한 번에 {1}개까지</t>
+          <t>수량과 단가를 범위 안에서 넣으세요.</t>
         </is>
       </c>
       <c r="D716" s="6" t="inlineStr">
         <is>
-          <t>Owned {0} · up to {1} per listing</t>
+          <t>Enter an amount and unit price within range.</t>
         </is>
       </c>
       <c r="E716" s="1" t="n"/>
@@ -14183,17 +14183,17 @@
       <c r="A717" s="1" t="n"/>
       <c r="B717" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceHelp</t>
+          <t>UI.Auction.AuctionTotal</t>
         </is>
       </c>
       <c r="C717" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 {0} G 이상 ~ {1} G</t>
+          <t>경매 총액</t>
         </is>
       </c>
       <c r="D717" s="6" t="inlineStr">
         <is>
-          <t>From {0} G (instant sell price) ~ {1} G</t>
+          <t>Auction Total</t>
         </is>
       </c>
       <c r="E717" s="1" t="n"/>
@@ -14202,17 +14202,17 @@
       <c r="A718" s="1" t="n"/>
       <c r="B718" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FormHint</t>
+          <t>UI.Auction.FeeNow</t>
         </is>
       </c>
       <c r="C718" s="6" t="inlineStr">
         <is>
-          <t>수량과 단가를 범위 안에서 넣으세요.</t>
+          <t>등록비 ({0}, 지금 빠짐)</t>
         </is>
       </c>
       <c r="D718" s="6" t="inlineStr">
         <is>
-          <t>Enter an amount and unit price within range.</t>
+          <t>Listing Fee ({0}, charged now)</t>
         </is>
       </c>
       <c r="E718" s="1" t="n"/>
@@ -14221,17 +14221,17 @@
       <c r="A719" s="1" t="n"/>
       <c r="B719" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.AuctionTotal</t>
+          <t>UI.Auction.NetIfSold</t>
         </is>
       </c>
       <c r="C719" s="6" t="inlineStr">
         <is>
-          <t>경매 총액</t>
+          <t>팔리면 받는 금액 (수수료 {0})</t>
         </is>
       </c>
       <c r="D719" s="6" t="inlineStr">
         <is>
-          <t>Auction Total</t>
+          <t>You Get If Sold (fee {0})</t>
         </is>
       </c>
       <c r="E719" s="1" t="n"/>
@@ -14240,17 +14240,17 @@
       <c r="A720" s="1" t="n"/>
       <c r="B720" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FeeNow</t>
+          <t>UI.Auction.IfInstant</t>
         </is>
       </c>
       <c r="C720" s="6" t="inlineStr">
         <is>
-          <t>등록비 ({0}, 지금 빠짐)</t>
+          <t>즉시 판매하면</t>
         </is>
       </c>
       <c r="D720" s="6" t="inlineStr">
         <is>
-          <t>Listing Fee ({0}, charged now)</t>
+          <t>If Sold Instantly</t>
         </is>
       </c>
       <c r="E720" s="1" t="n"/>
@@ -14259,17 +14259,17 @@
       <c r="A721" s="1" t="n"/>
       <c r="B721" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NetIfSold</t>
+          <t>UI.Auction.InstantVia</t>
         </is>
       </c>
       <c r="C721" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액 (수수료 {0})</t>
+          <t>{0} G — 인벤토리 [판매]</t>
         </is>
       </c>
       <c r="D721" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold (fee {0})</t>
+          <t>{0} G — Inventory [Sell]</t>
         </is>
       </c>
       <c r="E721" s="1" t="n"/>
@@ -14278,17 +14278,17 @@
       <c r="A722" s="1" t="n"/>
       <c r="B722" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.IfInstant</t>
+          <t>UI.Auction.InstantViaArtifact</t>
         </is>
       </c>
       <c r="C722" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매하면</t>
+          <t>{0} G — 아티팩트 [판매]</t>
         </is>
       </c>
       <c r="D722" s="6" t="inlineStr">
         <is>
-          <t>If Sold Instantly</t>
+          <t>{0} G — Artifacts [Sell]</t>
         </is>
       </c>
       <c r="E722" s="1" t="n"/>
@@ -14297,17 +14297,17 @@
       <c r="A723" s="1" t="n"/>
       <c r="B723" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantVia</t>
+          <t>UI.Auction.Search</t>
         </is>
       </c>
       <c r="C723" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 인벤토리 [판매]</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="D723" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Inventory [Sell]</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="E723" s="1" t="n"/>
@@ -14316,17 +14316,17 @@
       <c r="A724" s="1" t="n"/>
       <c r="B724" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.InstantViaArtifact</t>
+          <t>UI.Auction.TabDone</t>
         </is>
       </c>
       <c r="C724" s="6" t="inlineStr">
         <is>
-          <t>{0} G — 아티팩트 [판매]</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="D724" s="6" t="inlineStr">
         <is>
-          <t>{0} G — Artifacts [Sell]</t>
+          <t>History</t>
         </is>
       </c>
       <c r="E724" s="1" t="n"/>
@@ -14335,17 +14335,17 @@
       <c r="A725" s="1" t="n"/>
       <c r="B725" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Search</t>
+          <t>UI.Auction.EquipOptions</t>
         </is>
       </c>
       <c r="C725" s="6" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>장비 옵션</t>
         </is>
       </c>
       <c r="D725" s="6" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Gear Options</t>
         </is>
       </c>
       <c r="E725" s="1" t="n"/>
@@ -14354,17 +14354,17 @@
       <c r="A726" s="1" t="n"/>
       <c r="B726" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.TabDone</t>
+          <t>UI.Auction.Industry</t>
         </is>
       </c>
       <c r="C726" s="6" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>산업</t>
         </is>
       </c>
       <c r="D726" s="6" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E726" s="1" t="n"/>
@@ -14373,17 +14373,17 @@
       <c r="A727" s="1" t="n"/>
       <c r="B727" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EquipOptions</t>
+          <t>UI.Auction.SpeedAtLeast</t>
         </is>
       </c>
       <c r="C727" s="6" t="inlineStr">
         <is>
-          <t>장비 옵션</t>
+          <t>작업속도 % ≥</t>
         </is>
       </c>
       <c r="D727" s="6" t="inlineStr">
         <is>
-          <t>Gear Options</t>
+          <t>Work Speed % ≥</t>
         </is>
       </c>
       <c r="E727" s="1" t="n"/>
@@ -14392,17 +14392,17 @@
       <c r="A728" s="1" t="n"/>
       <c r="B728" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Industry</t>
+          <t>UI.Auction.EnchantSpeedAtLeast</t>
         </is>
       </c>
       <c r="C728" s="6" t="inlineStr">
         <is>
-          <t>산업</t>
+          <t>인챈트 작업속도 합 ≥</t>
         </is>
       </c>
       <c r="D728" s="6" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Enchant Speed Total ≥</t>
         </is>
       </c>
       <c r="E728" s="1" t="n"/>
@@ -14411,17 +14411,17 @@
       <c r="A729" s="1" t="n"/>
       <c r="B729" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.SpeedAtLeast</t>
+          <t>UI.Auction.EnchantExpAtLeast</t>
         </is>
       </c>
       <c r="C729" s="6" t="inlineStr">
         <is>
-          <t>작업속도 % ≥</t>
+          <t>인챈트 경험치 합 ≥</t>
         </is>
       </c>
       <c r="D729" s="6" t="inlineStr">
         <is>
-          <t>Work Speed % ≥</t>
+          <t>Enchant EXP Total ≥</t>
         </is>
       </c>
       <c r="E729" s="1" t="n"/>
@@ -14430,17 +14430,17 @@
       <c r="A730" s="1" t="n"/>
       <c r="B730" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantSpeedAtLeast</t>
+          <t>UI.Auction.CharacterOptions</t>
         </is>
       </c>
       <c r="C730" s="6" t="inlineStr">
         <is>
-          <t>인챈트 작업속도 합 ≥</t>
+          <t>캐릭터 옵션</t>
         </is>
       </c>
       <c r="D730" s="6" t="inlineStr">
         <is>
-          <t>Enchant Speed Total ≥</t>
+          <t>Character Options</t>
         </is>
       </c>
       <c r="E730" s="1" t="n"/>
@@ -14449,17 +14449,17 @@
       <c r="A731" s="1" t="n"/>
       <c r="B731" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.EnchantExpAtLeast</t>
+          <t>UI.Auction.Min</t>
         </is>
       </c>
       <c r="C731" s="6" t="inlineStr">
         <is>
-          <t>인챈트 경험치 합 ≥</t>
+          <t>최소</t>
         </is>
       </c>
       <c r="D731" s="6" t="inlineStr">
         <is>
-          <t>Enchant EXP Total ≥</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E731" s="1" t="n"/>
@@ -14468,17 +14468,17 @@
       <c r="A732" s="1" t="n"/>
       <c r="B732" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.CharacterOptions</t>
+          <t>UI.Auction.StarAtLeast</t>
         </is>
       </c>
       <c r="C732" s="6" t="inlineStr">
         <is>
-          <t>캐릭터 옵션</t>
+          <t>응축 ★ ≥</t>
         </is>
       </c>
       <c r="D732" s="6" t="inlineStr">
         <is>
-          <t>Character Options</t>
+          <t>Condense ★ ≥</t>
         </is>
       </c>
       <c r="E732" s="1" t="n"/>
@@ -14487,17 +14487,17 @@
       <c r="A733" s="1" t="n"/>
       <c r="B733" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Min</t>
+          <t>UI.Auction.UnitPriceGold</t>
         </is>
       </c>
       <c r="C733" s="6" t="inlineStr">
         <is>
-          <t>최소</t>
+          <t>단가 (골드)</t>
         </is>
       </c>
       <c r="D733" s="6" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Unit Price (Gold)</t>
         </is>
       </c>
       <c r="E733" s="1" t="n"/>
@@ -14506,17 +14506,17 @@
       <c r="A734" s="1" t="n"/>
       <c r="B734" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.StarAtLeast</t>
+          <t>UI.Auction.Range</t>
         </is>
       </c>
       <c r="C734" s="6" t="inlineStr">
         <is>
-          <t>응축 ★ ≥</t>
+          <t>범위</t>
         </is>
       </c>
       <c r="D734" s="6" t="inlineStr">
         <is>
-          <t>Condense ★ ≥</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="E734" s="1" t="n"/>
@@ -14525,17 +14525,17 @@
       <c r="A735" s="1" t="n"/>
       <c r="B735" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.UnitPriceGold</t>
+          <t>UI.Auction.NoListedYet</t>
         </is>
       </c>
       <c r="C735" s="6" t="inlineStr">
         <is>
-          <t>단가 (골드)</t>
+          <t>올린 매물이 없습니다</t>
         </is>
       </c>
       <c r="D735" s="6" t="inlineStr">
         <is>
-          <t>Unit Price (Gold)</t>
+          <t>No listings yet</t>
         </is>
       </c>
       <c r="E735" s="1" t="n"/>
@@ -14544,17 +14544,17 @@
       <c r="A736" s="1" t="n"/>
       <c r="B736" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Range</t>
+          <t>UI.Auction.Refresh</t>
         </is>
       </c>
       <c r="C736" s="6" t="inlineStr">
         <is>
-          <t>범위</t>
+          <t>↻ 새로고침</t>
         </is>
       </c>
       <c r="D736" s="6" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>↻ Refresh</t>
         </is>
       </c>
       <c r="E736" s="1" t="n"/>
@@ -14563,17 +14563,19 @@
       <c r="A737" s="1" t="n"/>
       <c r="B737" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.NoListedYet</t>
+          <t>UI.Auction.PriceEmpty</t>
         </is>
       </c>
       <c r="C737" s="6" t="inlineStr">
         <is>
-          <t>올린 매물이 없습니다</t>
+          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
+검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
         </is>
       </c>
       <c r="D737" s="6" t="inlineStr">
         <is>
-          <t>No listings yet</t>
+          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
+You can also open it with [Prices] on a search result row.</t>
         </is>
       </c>
       <c r="E737" s="1" t="n"/>
@@ -14582,17 +14584,17 @@
       <c r="A738" s="1" t="n"/>
       <c r="B738" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Refresh</t>
+          <t>UI.Auction.ShowListings</t>
         </is>
       </c>
       <c r="C738" s="6" t="inlineStr">
         <is>
-          <t>↻ 새로고침</t>
+          <t>이 아이템 매물 보기</t>
         </is>
       </c>
       <c r="D738" s="6" t="inlineStr">
         <is>
-          <t>↻ Refresh</t>
+          <t>View Listings</t>
         </is>
       </c>
       <c r="E738" s="1" t="n"/>
@@ -14601,19 +14603,17 @@
       <c r="A739" s="1" t="n"/>
       <c r="B739" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.PriceEmpty</t>
+          <t>UI.Auction.GoSell</t>
         </is>
       </c>
       <c r="C739" s="6" t="inlineStr">
         <is>
-          <t>위 검색창에 아이템 이름을 치면 아래에 후보가 뜹니다 — 고르면 시세를 엽니다.
-검색 결과 줄의 [시세]로도 열 수 있습니다.</t>
+          <t>팔러 가기</t>
         </is>
       </c>
       <c r="D739" s="6" t="inlineStr">
         <is>
-          <t>Type an item name in the search box above to see suggestions — pick one to open its prices.
-You can also open it with [Prices] on a search result row.</t>
+          <t>Go Sell</t>
         </is>
       </c>
       <c r="E739" s="1" t="n"/>
@@ -14622,17 +14622,17 @@
       <c r="A740" s="1" t="n"/>
       <c r="B740" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowListings</t>
+          <t>UI.Auction.ChartTitle</t>
         </is>
       </c>
       <c r="C740" s="6" t="inlineStr">
         <is>
-          <t>이 아이템 매물 보기</t>
+          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
         </is>
       </c>
       <c r="D740" s="6" t="inlineStr">
         <is>
-          <t>View Listings</t>
+          <t>Last 14 Days — bars/line: daily avg unit price</t>
         </is>
       </c>
       <c r="E740" s="1" t="n"/>
@@ -14641,17 +14641,17 @@
       <c r="A741" s="1" t="n"/>
       <c r="B741" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GoSell</t>
+          <t>UI.Auction.ChartEmpty</t>
         </is>
       </c>
       <c r="C741" s="6" t="inlineStr">
         <is>
-          <t>팔러 가기</t>
+          <t>최근 14일 동안 거래가 없습니다</t>
         </is>
       </c>
       <c r="D741" s="6" t="inlineStr">
         <is>
-          <t>Go Sell</t>
+          <t>No trades in the last 14 days</t>
         </is>
       </c>
       <c r="E741" s="1" t="n"/>
@@ -14660,17 +14660,17 @@
       <c r="A742" s="1" t="n"/>
       <c r="B742" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartTitle</t>
+          <t>UI.Auction.LevelsTitle</t>
         </is>
       </c>
       <c r="C742" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 — 막대·선: 그날 평균 단가</t>
+          <t>지금 단가별 판매 수량 (싼 것부터)</t>
         </is>
       </c>
       <c r="D742" s="6" t="inlineStr">
         <is>
-          <t>Last 14 Days — bars/line: daily avg unit price</t>
+          <t>Amount on Sale by Unit Price (cheapest first)</t>
         </is>
       </c>
       <c r="E742" s="1" t="n"/>
@@ -14679,17 +14679,17 @@
       <c r="A743" s="1" t="n"/>
       <c r="B743" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ChartEmpty</t>
+          <t>UI.Auction.LevelsEmpty</t>
         </is>
       </c>
       <c r="C743" s="6" t="inlineStr">
         <is>
-          <t>최근 14일 동안 거래가 없습니다</t>
+          <t>지금 판매 중인 매물이 없습니다</t>
         </is>
       </c>
       <c r="D743" s="6" t="inlineStr">
         <is>
-          <t>No trades in the last 14 days</t>
+          <t>Nothing on sale right now</t>
         </is>
       </c>
       <c r="E743" s="1" t="n"/>
@@ -14698,17 +14698,17 @@
       <c r="A744" s="1" t="n"/>
       <c r="B744" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsTitle</t>
+          <t>UI.Auction.RegisterOpen</t>
         </is>
       </c>
       <c r="C744" s="6" t="inlineStr">
         <is>
-          <t>지금 단가별 판매 수량 (싼 것부터)</t>
+          <t>+ 판매 등록</t>
         </is>
       </c>
       <c r="D744" s="6" t="inlineStr">
         <is>
-          <t>Amount on Sale by Unit Price (cheapest first)</t>
+          <t>+ List Item</t>
         </is>
       </c>
       <c r="E744" s="1" t="n"/>
@@ -14717,17 +14717,17 @@
       <c r="A745" s="1" t="n"/>
       <c r="B745" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.LevelsEmpty</t>
+          <t>UI.Auction.ColItem</t>
         </is>
       </c>
       <c r="C745" s="6" t="inlineStr">
         <is>
-          <t>지금 판매 중인 매물이 없습니다</t>
+          <t>아이템</t>
         </is>
       </c>
       <c r="D745" s="6" t="inlineStr">
         <is>
-          <t>Nothing on sale right now</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="E745" s="1" t="n"/>
@@ -14736,17 +14736,17 @@
       <c r="A746" s="1" t="n"/>
       <c r="B746" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterOpen</t>
+          <t>UI.Auction.ColNet</t>
         </is>
       </c>
       <c r="C746" s="6" t="inlineStr">
         <is>
-          <t>+ 판매 등록</t>
+          <t>팔리면 받는 금액</t>
         </is>
       </c>
       <c r="D746" s="6" t="inlineStr">
         <is>
-          <t>+ List Item</t>
+          <t>You Get If Sold</t>
         </is>
       </c>
       <c r="E746" s="1" t="n"/>
@@ -14755,17 +14755,17 @@
       <c r="A747" s="1" t="n"/>
       <c r="B747" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColItem</t>
+          <t>UI.Auction.ColDate</t>
         </is>
       </c>
       <c r="C747" s="6" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="D747" s="6" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E747" s="1" t="n"/>
@@ -14774,17 +14774,17 @@
       <c r="A748" s="1" t="n"/>
       <c r="B748" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColNet</t>
+          <t>UI.Auction.ColType</t>
         </is>
       </c>
       <c r="C748" s="6" t="inlineStr">
         <is>
-          <t>팔리면 받는 금액</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="D748" s="6" t="inlineStr">
         <is>
-          <t>You Get If Sold</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E748" s="1" t="n"/>
@@ -14793,17 +14793,17 @@
       <c r="A749" s="1" t="n"/>
       <c r="B749" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDate</t>
+          <t>UI.Auction.ColAmount</t>
         </is>
       </c>
       <c r="C749" s="6" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="D749" s="6" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="E749" s="1" t="n"/>
@@ -14812,17 +14812,17 @@
       <c r="A750" s="1" t="n"/>
       <c r="B750" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColType</t>
+          <t>UI.Auction.ColDest</t>
         </is>
       </c>
       <c r="C750" s="6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>받는 곳</t>
         </is>
       </c>
       <c r="D750" s="6" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Goes To</t>
         </is>
       </c>
       <c r="E750" s="1" t="n"/>
@@ -14831,17 +14831,17 @@
       <c r="A751" s="1" t="n"/>
       <c r="B751" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColAmount</t>
+          <t>UI.Auction.RegisterTitle</t>
         </is>
       </c>
       <c r="C751" s="6" t="inlineStr">
         <is>
-          <t>금액</t>
+          <t>판매 등록</t>
         </is>
       </c>
       <c r="D751" s="6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>List an Item</t>
         </is>
       </c>
       <c r="E751" s="1" t="n"/>
@@ -14850,17 +14850,17 @@
       <c r="A752" s="1" t="n"/>
       <c r="B752" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ColDest</t>
+          <t>UI.Auction.FindByName</t>
         </is>
       </c>
       <c r="C752" s="6" t="inlineStr">
         <is>
-          <t>받는 곳</t>
+          <t>이름으로 찾기</t>
         </is>
       </c>
       <c r="D752" s="6" t="inlineStr">
         <is>
-          <t>Goes To</t>
+          <t>Find by name</t>
         </is>
       </c>
       <c r="E752" s="1" t="n"/>
@@ -14869,17 +14869,17 @@
       <c r="A753" s="1" t="n"/>
       <c r="B753" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterTitle</t>
+          <t>UI.Auction.RegisterEmptyCard</t>
         </is>
       </c>
       <c r="C753" s="6" t="inlineStr">
         <is>
-          <t>판매 등록</t>
+          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
         </is>
       </c>
       <c r="D753" s="6" t="inlineStr">
         <is>
-          <t>List an Item</t>
+          <t>[Select] something to list on the left.</t>
         </is>
       </c>
       <c r="E753" s="1" t="n"/>
@@ -14888,17 +14888,17 @@
       <c r="A754" s="1" t="n"/>
       <c r="B754" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.FindByName</t>
+          <t>UI.Auction.ShowPrice</t>
         </is>
       </c>
       <c r="C754" s="6" t="inlineStr">
         <is>
-          <t>이름으로 찾기</t>
+          <t>시세 보기</t>
         </is>
       </c>
       <c r="D754" s="6" t="inlineStr">
         <is>
-          <t>Find by name</t>
+          <t>View Prices</t>
         </is>
       </c>
       <c r="E754" s="1" t="n"/>
@@ -14907,17 +14907,17 @@
       <c r="A755" s="1" t="n"/>
       <c r="B755" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RegisterEmptyCard</t>
+          <t>UI.Auction.MatchLowest</t>
         </is>
       </c>
       <c r="C755" s="6" t="inlineStr">
         <is>
-          <t>왼쪽에서 올릴 것을 [선택]하세요.</t>
+          <t>최저가에 맞춤</t>
         </is>
       </c>
       <c r="D755" s="6" t="inlineStr">
         <is>
-          <t>[Select] something to list on the left.</t>
+          <t>Match Lowest</t>
         </is>
       </c>
       <c r="E755" s="1" t="n"/>
@@ -14926,17 +14926,17 @@
       <c r="A756" s="1" t="n"/>
       <c r="B756" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.ShowPrice</t>
+          <t>UI.Auction.Register</t>
         </is>
       </c>
       <c r="C756" s="6" t="inlineStr">
         <is>
-          <t>시세 보기</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="D756" s="6" t="inlineStr">
         <is>
-          <t>View Prices</t>
+          <t>List</t>
         </is>
       </c>
       <c r="E756" s="1" t="n"/>
@@ -14945,17 +14945,17 @@
       <c r="A757" s="1" t="n"/>
       <c r="B757" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.MatchLowest</t>
+          <t>UI.Auction.GuideTitle</t>
         </is>
       </c>
       <c r="C757" s="6" t="inlineStr">
         <is>
-          <t>최저가에 맞춤</t>
+          <t>경매장</t>
         </is>
       </c>
       <c r="D757" s="6" t="inlineStr">
         <is>
-          <t>Match Lowest</t>
+          <t>Auction House</t>
         </is>
       </c>
       <c r="E757" s="1" t="n"/>
@@ -14964,17 +14964,17 @@
       <c r="A758" s="1" t="n"/>
       <c r="B758" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.Register</t>
+          <t>UI.Auction.GuideBuyWhole</t>
         </is>
       </c>
       <c r="C758" s="6" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
         </is>
       </c>
       <c r="D758" s="6" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Listings are bought whole — no partial purchases</t>
         </is>
       </c>
       <c r="E758" s="1" t="n"/>
@@ -14983,17 +14983,17 @@
       <c r="A759" s="1" t="n"/>
       <c r="B759" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideTitle</t>
+          <t>UI.Auction.GuideBuyOwn</t>
         </is>
       </c>
       <c r="C759" s="6" t="inlineStr">
         <is>
-          <t>경매장</t>
+          <t>내 매물은 살 수 없습니다</t>
         </is>
       </c>
       <c r="D759" s="6" t="inlineStr">
         <is>
-          <t>Auction House</t>
+          <t>You can't buy your own listings</t>
         </is>
       </c>
       <c r="E759" s="1" t="n"/>
@@ -15002,17 +15002,17 @@
       <c r="A760" s="1" t="n"/>
       <c r="B760" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyWhole</t>
+          <t>UI.Auction.GuideMailHeader</t>
         </is>
       </c>
       <c r="C760" s="6" t="inlineStr">
         <is>
-          <t>매물은 통째로 삽니다 — 일부만 살 수 없습니다</t>
+          <t>우편</t>
         </is>
       </c>
       <c r="D760" s="6" t="inlineStr">
         <is>
-          <t>Listings are bought whole — no partial purchases</t>
+          <t>Mail</t>
         </is>
       </c>
       <c r="E760" s="1" t="n"/>
@@ -15021,17 +15021,17 @@
       <c r="A761" s="1" t="n"/>
       <c r="B761" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideBuyOwn</t>
+          <t>UI.Auction.GuideMail</t>
         </is>
       </c>
       <c r="C761" s="6" t="inlineStr">
         <is>
-          <t>내 매물은 살 수 없습니다</t>
+          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
         </is>
       </c>
       <c r="D761" s="6" t="inlineStr">
         <is>
-          <t>You can't buy your own listings</t>
+          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
         </is>
       </c>
       <c r="E761" s="1" t="n"/>
@@ -15040,17 +15040,17 @@
       <c r="A762" s="1" t="n"/>
       <c r="B762" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMailHeader</t>
+          <t>UI.Auction.GuideSellHint</t>
         </is>
       </c>
       <c r="C762" s="6" t="inlineStr">
         <is>
-          <t>우편</t>
+          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
         </is>
       </c>
       <c r="D762" s="6" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
         </is>
       </c>
       <c r="E762" s="1" t="n"/>
@@ -15059,17 +15059,17 @@
       <c r="A763" s="1" t="n"/>
       <c r="B763" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideMail</t>
+          <t>UI.Auction.RuleAuction</t>
         </is>
       </c>
       <c r="C763" s="6" t="inlineStr">
         <is>
-          <t>산 물건 · 판매 대금 · 돌아온 물건 · 환급은 모두 우편으로 옵니다</t>
+          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
         </is>
       </c>
       <c r="D763" s="6" t="inlineStr">
         <is>
-          <t>Purchases, proceeds, returned items and refunds all arrive by mail</t>
+          <t>Auction — sell to other players at your price · wait until it sells</t>
         </is>
       </c>
       <c r="E763" s="1" t="n"/>
@@ -15078,17 +15078,17 @@
       <c r="A764" s="1" t="n"/>
       <c r="B764" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.GuideSellHint</t>
+          <t>UI.Auction.RuleInstant</t>
         </is>
       </c>
       <c r="C764" s="6" t="inlineStr">
         <is>
-          <t>파는 규칙은 [판매] → [+ 판매 등록] 창의 ?에 있습니다</t>
+          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
         </is>
       </c>
       <c r="D764" s="6" t="inlineStr">
         <is>
-          <t>Selling rules: [Sell] → [+ List Item] window's ?</t>
+          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
         </is>
       </c>
       <c r="E764" s="1" t="n"/>
@@ -15097,17 +15097,17 @@
       <c r="A765" s="1" t="n"/>
       <c r="B765" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleAuction</t>
+          <t>UI.Auction.RuleHeader</t>
         </is>
       </c>
       <c r="C765" s="6" t="inlineStr">
         <is>
-          <t>경매 — 정한 단가로 다른 플레이어에게 팝니다 · 팔릴 때까지 기다립니다</t>
+          <t>등록 규칙</t>
         </is>
       </c>
       <c r="D765" s="6" t="inlineStr">
         <is>
-          <t>Auction — sell to other players at your price · wait until it sells</t>
+          <t>Listing Rules</t>
         </is>
       </c>
       <c r="E765" s="1" t="n"/>
@@ -15116,17 +15116,17 @@
       <c r="A766" s="1" t="n"/>
       <c r="B766" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleInstant</t>
+          <t>UI.Auction.RulePrice</t>
         </is>
       </c>
       <c r="C766" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매 — 인벤토리 [판매] · 즉시 판매가로 바로 받습니다</t>
+          <t>즉시 판매가 이상 ~ {0} G</t>
         </is>
       </c>
       <c r="D766" s="6" t="inlineStr">
         <is>
-          <t>Instant sell — Inventory [Sell] · get the instant price right away</t>
+          <t>From the instant price ~ {0} G</t>
         </is>
       </c>
       <c r="E766" s="1" t="n"/>
@@ -15135,17 +15135,17 @@
       <c r="A767" s="1" t="n"/>
       <c r="B767" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleHeader</t>
+          <t>UI.Auction.RuleCountLabel</t>
         </is>
       </c>
       <c r="C767" s="6" t="inlineStr">
         <is>
-          <t>등록 규칙</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="D767" s="6" t="inlineStr">
         <is>
-          <t>Listing Rules</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="E767" s="1" t="n"/>
@@ -15154,17 +15154,17 @@
       <c r="A768" s="1" t="n"/>
       <c r="B768" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RulePrice</t>
+          <t>UI.Auction.RuleCount</t>
         </is>
       </c>
       <c r="C768" s="6" t="inlineStr">
         <is>
-          <t>즉시 판매가 이상 ~ {0} G</t>
+          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
         </is>
       </c>
       <c r="D768" s="6" t="inlineStr">
         <is>
-          <t>From the instant price ~ {0} G</t>
+          <t>Up to {0} per listing · sold only whole</t>
         </is>
       </c>
       <c r="E768" s="1" t="n"/>
@@ -15173,17 +15173,17 @@
       <c r="A769" s="1" t="n"/>
       <c r="B769" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCountLabel</t>
+          <t>UI.Auction.RuleSlots</t>
         </is>
       </c>
       <c r="C769" s="6" t="inlineStr">
         <is>
-          <t>수량</t>
+          <t>최대 {0}건</t>
         </is>
       </c>
       <c r="D769" s="6" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Up to {0}</t>
         </is>
       </c>
       <c r="E769" s="1" t="n"/>
@@ -15192,17 +15192,17 @@
       <c r="A770" s="1" t="n"/>
       <c r="B770" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleCount</t>
+          <t>UI.Auction.RuleListingFee</t>
         </is>
       </c>
       <c r="C770" s="6" t="inlineStr">
         <is>
-          <t>한 번에 {0}개까지 · 통째로만 팔림</t>
+          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
         </is>
       </c>
       <c r="D770" s="6" t="inlineStr">
         <is>
-          <t>Up to {0} per listing · sold only whole</t>
+          <t>Paid on listing · refunded on expiry, not on cancel</t>
         </is>
       </c>
       <c r="E770" s="1" t="n"/>
@@ -15211,17 +15211,17 @@
       <c r="A771" s="1" t="n"/>
       <c r="B771" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleSlots</t>
+          <t>UI.Auction.RuleSaleFee</t>
         </is>
       </c>
       <c r="C771" s="6" t="inlineStr">
         <is>
-          <t>최대 {0}건</t>
+          <t>팔린 금액에서 뗌</t>
         </is>
       </c>
       <c r="D771" s="6" t="inlineStr">
         <is>
-          <t>Up to {0}</t>
+          <t>Deducted from the sale</t>
         </is>
       </c>
       <c r="E771" s="1" t="n"/>
@@ -15230,58 +15230,20 @@
       <c r="A772" s="1" t="n"/>
       <c r="B772" s="6" t="inlineStr">
         <is>
-          <t>UI.Auction.RuleListingFee</t>
+          <t>UI.Auction.RuleCantList</t>
         </is>
       </c>
       <c r="C772" s="6" t="inlineStr">
         <is>
-          <t>등록할 때 빠짐 · 만료되면 돌려받고 취소하면 못 받음</t>
+          <t>끼고 있는 장비 · 일하는 캐릭터 · 잠긴 것은 올릴 수 없습니다 (흐린 줄 — 올리면 사유)</t>
         </is>
       </c>
       <c r="D772" s="6" t="inlineStr">
         <is>
-          <t>Paid on listing · refunded on expiry, not on cancel</t>
+          <t>Worn gear, working characters and locked items can't be listed (dimmed — hover for why)</t>
         </is>
       </c>
       <c r="E772" s="1" t="n"/>
-    </row>
-    <row r="773">
-      <c r="A773" s="1" t="n"/>
-      <c r="B773" s="6" t="inlineStr">
-        <is>
-          <t>UI.Auction.RuleSaleFee</t>
-        </is>
-      </c>
-      <c r="C773" s="6" t="inlineStr">
-        <is>
-          <t>팔린 금액에서 뗌</t>
-        </is>
-      </c>
-      <c r="D773" s="6" t="inlineStr">
-        <is>
-          <t>Deducted from the sale</t>
-        </is>
-      </c>
-      <c r="E773" s="1" t="n"/>
-    </row>
-    <row r="774">
-      <c r="A774" s="1" t="n"/>
-      <c r="B774" s="6" t="inlineStr">
-        <is>
-          <t>UI.Auction.RuleCantList</t>
-        </is>
-      </c>
-      <c r="C774" s="6" t="inlineStr">
-        <is>
-          <t>끼고 있는 장비 · 일하는 캐릭터 · 잠긴 것은 올릴 수 없습니다 (흐린 줄 — 올리면 사유)</t>
-        </is>
-      </c>
-      <c r="D774" s="6" t="inlineStr">
-        <is>
-          <t>Worn gear, working characters and locked items can't be listed (dimmed — hover for why)</t>
-        </is>
-      </c>
-      <c r="E774" s="1" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -8514,12 +8514,12 @@
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>응축을 쌓은 재료 {0}마리의 응축 단계·누적도 사라집니다.</t>
+          <t>응축을 쌓은 재료 {0}마리의 누적 응축은 {1}%(올림)만 넘어갑니다.</t>
         </is>
       </c>
       <c r="D419" s="6" t="inlineStr">
         <is>
-          <t>Condense progress of {0} material(s) will also be lost.</t>
+          <t>Only {1}% (rounded up) of the condense progress of {0} material(s) carries over.</t>
         </is>
       </c>
       <c r="E419" s="1" t="n"/>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>재료의 레벨 · 경험치 · 응축은 사라지고 되돌릴 수 없습니다</t>
+          <t>재료의 레벨 · 경험치는 사라지고 누적 응축은 {0}%(올림)만 넘어갑니다 — 되돌릴 수 없습니다</t>
         </is>
       </c>
       <c r="D424" s="6" t="inlineStr">
         <is>
-          <t>Materials lose their level, EXP and condense — this can't be undone</t>
+          <t>Materials lose their level and EXP, and only {0}% (rounded up) of their condense carries over — this can't be undone</t>
         </is>
       </c>
       <c r="E424" s="1" t="n"/>

--- a/GameDesign/Excel/Localization/Loc_UI.xlsx
+++ b/GameDesign/Excel/Localization/Loc_UI.xlsx
@@ -5425,17 +5425,17 @@
       <c r="A257" s="1" t="n"/>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>UI.Main.Hub</t>
+          <t>UI.Main.Guild</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>거점</t>
+          <t>길드</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Guild</t>
         </is>
       </c>
       <c r="E257" s="1" t="n"/>
